--- a/Tests/excel/academic_portal_all_test_cases.xlsx
+++ b/Tests/excel/academic_portal_all_test_cases.xlsx
@@ -1446,40 +1446,40 @@
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>Tải lên ảnh đại diện hợp lệ định dạng JPG</t>
+          <t>Upload valid profile photo in JPG format</t>
         </is>
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tải lên ảnh đại diện định dạng JPG thành công và cập nhật vào thông tin học sinh.</t>
+          <t>Verify functionality for tai len profile photo format JPG successfully va cap nhat vao thong tin student.</t>
         </is>
       </c>
       <c r="G2" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở trang Chi tiết Học sinh (Student Detail) của một học sinh chưa có ảnh đại diện (đang hiển thị ảnh mặc định).</t>
+          <t>User is logged in as Staff.
+Currently on Student Detail page of a student without profile photo (displaying default photo).</t>
         </is>
       </c>
       <c r="H2" s="23" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=student_avatar.jpg (kích thước &lt; 2MB)</t>
+          <t>StudentCode=PNV26001; ImageFile=student_avatar.jpg (kich thuoc &lt; 2MB)</t>
         </is>
       </c>
       <c r="I2" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001 và mở trang Chi tiết Học sinh.
-2. Nhấp chọn biểu tượng tải ảnh đại diện.
-3. Chọn file student_avatar.jpg từ thiết bị.
-4. Quan sát ảnh xem trước hiển thị trên màn hình.
-5. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Select student PNV26001 va mo trang Chi tiet Hoc sinh.
+2. Nhap select bieu tuong tai profile photo.
+3. Select file student_avatar.jpg tu thiet bi.
+4. Observe preview photo display tren man hinh.
+5. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J2" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tải lên thành công.
-Ảnh xem trước hiển thị tức thì trên giao diện trước khi lưu.
-Sau khi lưu, thông tin học sinh được cập nhật: ảnh đại diện hiển thị kiểu hình tròn tại Sidebar chi tiết (200x200 px) và danh sách học sinh (52x52 px).
-File ảnh được lưu trên Google Drive dưới tên "Nguyen_Van_A_{Timestamp}.jpg" với quyền xem "Anyone with the link".</t>
+          <t>System display notification tai len successfully.
+Anh xem truoc display tuc thi tren interface truoc khi save.
+Sau khi save, thong tin student duoc cap nhat: profile photo display kieu hinh tron tai Sidebar chi tiet (200x200 px) va danh sach student (52x52 px).
+File photo duoc save tren Google Drive duoi ten "Nguyen_Van_A_{Timestamp}.jpg" voi quyen xem "Anyone with the link".</t>
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="N2" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F01, Rule 5.2, Google Drive Integration (Mục 7)</t>
+          <t>Related to M08-F01, Rule 5.2, Google Drive Integration (Section 7)</t>
         </is>
       </c>
     </row>
@@ -1522,18 +1522,18 @@
       </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
-          <t>Tải lên ảnh đại diện hợp lệ định dạng PNG</t>
+          <t>Upload valid profile photo in PNG format</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tải lên ảnh đại diện định dạng PNG thành công và cập nhật vào thông tin học sinh.</t>
+          <t>Verify functionality for tai len profile photo format PNG successfully va cap nhat vao thong tin student.</t>
         </is>
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở trang Chi tiết Học sinh (Student Detail) của một học sinh chưa có ảnh đại diện.</t>
+          <t>User is logged in as Staff.
+Currently on Student Detail page of a student without profile photo.</t>
         </is>
       </c>
       <c r="H3" s="28" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="I3" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26002 và mở trang Chi tiết Học sinh.
-2. Nhấp chọn biểu tượng tải ảnh đại diện.
-3. Chọn file student_avatar2.png.
-4. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Select student PNV26002 va mo trang Chi tiet Hoc sinh.
+2. Nhap select bieu tuong tai profile photo.
+3. Select file student_avatar2.png.
+4. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J3" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tải lên thành công.
-Ảnh đại diện PNG hiển thị chính xác kiểu hình tròn ở tất cả các vị trí.
-File ảnh được tải lên Google Drive và được đặt tên theo định dạng {StudentName}_{Timestamp}.jpg.</t>
+          <t>System display notification tai len successfully.
+Anh dai dien PNG display chinh xac kieu hinh tron o tat ca cac vi tri.
+File photo duoc tai len Google Drive va duoc dat ten theo format {StudentName}_{Timestamp}.jpg.</t>
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="N3" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F01, Rule 5.2</t>
+          <t>Related to M08-F01, Rule 5.2</t>
         </is>
       </c>
     </row>
@@ -1596,18 +1596,18 @@
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>Thay thế ảnh đại diện hiện tại</t>
+          <t>Replace current profile photo</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>Xác minh khi tải lên ảnh đại diện mới, hệ thống tự động cập nhật thông tin học sinh và xóa file ảnh cũ trên Google Drive.</t>
+          <t>Verify khi tai len new profile photo, system tu dong cap nhat thong tin student va delete file old photo tren Google Drive.</t>
         </is>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh PNV26001 đã có sẵn ảnh đại diện cũ trên hệ thống và Google Drive.</t>
+          <t>User is logged in as Staff.
+Hoc sinh PNV26001 da co san old profile photo tren system va Google Drive.</t>
         </is>
       </c>
       <c r="H4" s="23" t="inlineStr">
@@ -1617,19 +1617,19 @@
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001 và mở trang Chi tiết Học sinh.
-2. Nhấp chọn tải ảnh đại diện mới.
-3. Chọn file new_avatar.jpg.
-4. Nhấn nút "Lưu" (Save).
-5. Kiểm tra thư mục lưu trữ trên Google Drive.</t>
+          <t>1. Select student PNV26001 va mo trang Chi tiet Hoc sinh.
+2. Nhap select tai new profile photo.
+3. Select file new_avatar.jpg.
+4. Nhan nut "Save" (Save).
+5. Verify thu muc archive tren Google Drive.</t>
         </is>
       </c>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo thay thế thành công.
-Ảnh đại diện mới hiển thị trên hệ thống.
-File ảnh cũ của học sinh PNV26001 trên Google Drive bị xóa hoàn toàn khỏi thư mục lưu trữ (không giữ lại file cũ).
-Chỉ còn lại file ảnh mới trên Google Drive.</t>
+          <t>System display notification replace successfully.
+Anh dai dien moi display tren system.
+File old photo cua student PNV26001 tren Google Drive bi delete hoan toan khoi thu muc archive (khong giu lai file cu).
+Chi con lai file new photo tren Google Drive.</t>
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="N4" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F02, Rule 5.3</t>
+          <t>Related to M08-F02, Rule 5.3</t>
         </is>
       </c>
     </row>
@@ -1672,18 +1672,18 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Xóa ảnh đại diện hiện tại (Soft Delete)</t>
+          <t>Delete current profile photo (Soft Delete)</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng xóa ảnh đại diện của học sinh, chuyển file cũ vào Google Drive Trash và hiển thị avatar mặc định.</t>
+          <t>Verify functionality for delete profile photo cua student, chuyen file cu vao Google Drive Trash va display avatar mac dinh.</t>
         </is>
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh PNV26001 đã có sẵn ảnh đại diện trên hệ thống.</t>
+          <t>User is logged in as Staff.
+Hoc sinh PNV26001 da co san profile photo tren system.</t>
         </is>
       </c>
       <c r="H5" s="28" t="inlineStr">
@@ -1693,18 +1693,18 @@
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001 và mở trang Chi tiết Học sinh.
-2. Nhấp chọn nút "Xóa ảnh" (Remove Photo).
-3. Xác nhận xóa khi hệ thống hiển thị hộp thoại xác nhận.
-4. Nhấn nút "Lưu" (Save).
-5. Kiểm tra Google Drive Trash.</t>
+          <t>1. Select student PNV26001 va mo trang Chi tiet Hoc sinh.
+2. Nhap select nut "Delete photo" (Remove Photo).
+3. Xac nhan delete khi system display hop thoai xac nhan.
+4. Nhan nut "Save" (Save).
+5. Verify Google Drive Trash.</t>
         </is>
       </c>
       <c r="J5" s="28" t="inlineStr">
         <is>
-          <t>Ảnh đại diện cũ của học sinh bị xóa khỏi giao diện.
-Hệ thống hiển thị ảnh đại diện mặc định (chữ cái viết tắt tên học sinh).
-Trên Google Drive, file ảnh cũ của học sinh được di chuyển vào thùng rác (Drive Trash) chứ không bị xóa vĩnh viễn ngay lập tức.</t>
+          <t>Anh dai dien cu cua student bi delete khoi interface.
+System display profile photo mac dinh (initials ten student).
+Tren Google Drive, file old photo cua student duoc di chuyen vao trash (Drive Trash) chu khong bi permanently deleted ngay lap tuc.</t>
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="N5" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F03, Rule 5.4</t>
+          <t>Related to M08-F03, Rule 5.4</t>
         </is>
       </c>
     </row>
@@ -1747,18 +1747,18 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Hiển thị avatar mặc định khi học sinh chưa có ảnh đại diện</t>
+          <t>Hien thi avatar mac dinh khi student chua co profile photo</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống hiển thị ảnh đại diện mặc định là 2 chữ cái đầu của tên học sinh khi không có ảnh.</t>
+          <t>Verify system display profile photo mac dinh la 2 initials cua ten student khi khong co photo.</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh "Nguyen Van A" chưa tải ảnh đại diện lên hệ thống.</t>
+          <t>User is logged in as Staff.
+Hoc sinh "Nguyen Van A" chua tai profile photo len system.</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -1768,16 +1768,16 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>1. Vào danh sách học sinh.
-2. Tìm học sinh "Nguyen Van A".
-3. Quan sát ảnh đại diện hiển thị bên cạnh tên học sinh.
-4. Kiểm tra tại trang Chi tiết học sinh và màn hình Home Dashboard.</t>
+          <t>1. Vao danh sach student.
+2. Tim student "Nguyen Van A".
+3. Observe profile photo display ben canh ten student.
+4. Verify tai trang Chi tiet student va man hinh Home Dashboard.</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống tự động hiển thị ảnh đại diện dạng hình tròn chứa 2 chữ cái viết tắt là "NA" (chữ cái đầu của Tên và Họ).
-Ảnh mặc định này hiển thị đồng bộ ở cả danh sách học sinh và chi tiết học sinh.</t>
+          <t>System tu dong display profile photo dang hinh tron chua 2 initials la "NA" (initials cua Ten va Ho).
+Anh mac dinh nay display dong bo o ca danh sach student va chi tiet student.</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
@@ -1793,11 +1793,11 @@
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F04, Rule 5.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
+          <t>Related to M08-F04, Rule 5.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
           <t>TC-M08-006</t>
@@ -1820,18 +1820,18 @@
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra kích thước hiển thị ảnh đại diện ở các vị trí khác nhau</t>
+          <t>Verify kich thuoc display profile photo o cac vi tri khac nhau</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Xác minh ảnh đại diện hiển thị đúng kích thước cấu hình và đúng định dạng hình tròn ở mọi màn hình.</t>
+          <t>Verify profile photo display dung kich thuoc cau hinh va dung format hinh tron o moi man hinh.</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh PNV26001 đã có ảnh đại diện hợp lệ.</t>
+          <t>User is logged in as Staff.
+Hoc sinh PNV26001 da co profile photo hop le.</t>
         </is>
       </c>
       <c r="H7" s="28" t="inlineStr">
@@ -1841,18 +1841,18 @@
       </c>
       <c r="I7" s="28" t="inlineStr">
         <is>
-          <t>1. Xem ảnh học sinh tại danh sách học sinh.
-2. Nhấp xem chi tiết học sinh PNV26001 và quan sát Sidebar.
-3. Mở Dialog chỉnh sửa thông tin học sinh.
-4. Về màn hình Home Dashboard và tìm ảnh đại diện học sinh đó.</t>
+          <t>1. Xem photo student tai danh sach student.
+2. Nhap xem chi tiet student PNV26001 va observe Sidebar.
+3. Mo Dialog edit thong tin student.
+4. Ve man hinh Home Dashboard va tim profile photo student do.</t>
         </is>
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>Ảnh đại diện hiển thị dưới dạng hình tròn với kích thước chuẩn:
-- Danh sách học sinh: 52 x 52 px
-- Dialog chỉnh sửa học sinh: 120 x 120 px
-- Sidebar chi tiết học sinh: 200 x 200 px
+          <t>Anh dai dien display as hinh tron voi kich thuoc chuan:
+- Danh sach student: 52 x 52 px
+- Dialog edit student: 120 x 120 px
+- Sidebar chi tiet student: 200 x 200 px
 - Home Dashboard: 52 x 52 px</t>
         </is>
       </c>
@@ -1869,11 +1869,11 @@
       </c>
       <c r="N7" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Display Locations (Mục 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="105" customHeight="1">
+          <t>Related to Display Locations (Section 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
         <is>
           <t>TC-M08-007</t>
@@ -1896,18 +1896,18 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Nhấn Lưu ảnh đại diện khi chưa chọn file ảnh</t>
+          <t>Nhan Save profile photo khi chua select file photo</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi người dùng cố tình lưu ảnh mà chưa chọn tệp tin nào.</t>
+          <t>Verify system bao error khi user co tinh save photo ma chua select tep tin nao.</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Đang mở trang Chi tiết Học sinh của một học sinh chưa có ảnh.</t>
+          <t>Nguoi dung log in quyen Staff.
+Dang mo trang Chi tiet Hoc sinh cua mot student chua co photo.</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -1917,16 +1917,16 @@
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001.
-2. Kích hoạt chế độ tải ảnh đại diện.
-3. Không chọn bất kỳ file nào từ thiết bị.
-4. Nhấn nút "Lưu" (Save) hoặc nút xác nhận tải lên.</t>
+          <t>1. Select student PNV26001.
+2. Kich hoat che do tai profile photo.
+3. Khong select bat ky file nao tu thiet bi.
+4. Nhan nut "Save" (Save) hoac nut xac nhan tai len.</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị cảnh báo lỗi yêu cầu chọn tệp tin hình ảnh (ví dụ: "Image file is required" hoặc tương đương).
-Không có bất kỳ thay đổi nào được thực hiện.</t>
+          <t>System display cphoto bao error requires select tep tin hinh photo (e.g.: "Image file is required" hoac tuong duong).
+Khong co bat ky thay doi nao duoc thuc hien.</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8)</t>
+          <t>Related to Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -1969,18 +1969,18 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>Tải lên file không phải định dạng hình ảnh</t>
+          <t>Upload file not format hinh photo</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống chặn tải lên các tệp tin có định dạng không phải là ảnh (như .pdf, .docx, .txt).</t>
+          <t>Verify system chan tai len cac tep tin co format is not a photo (nhu .pdf, .docx, .txt).</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang mở trang Chi tiết Học sinh.</t>
+          <t>User is logged in as Staff.
+Dang mo trang Chi tiet Hoc sinh.</t>
         </is>
       </c>
       <c r="H9" s="28" t="inlineStr">
@@ -1990,16 +1990,16 @@
       </c>
       <c r="I9" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001.
-2. Nhấp tải ảnh đại diện và chọn file document.pdf.
-3. Nhấn nút "Lưu" (Save) hoặc nút xác nhận tải lên.</t>
+          <t>1. Select student PNV26001.
+2. Nhap tai profile photo va select file document.pdf.
+3. Nhan nut "Save" (Save) hoac nut xac nhan tai len.</t>
         </is>
       </c>
       <c r="J9" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống không chấp nhận file PDF.
-Hiển thị thông báo lỗi yêu cầu tệp tin hình ảnh hợp lệ (ví dụ: "Invalid file format. Please upload JPG or PNG image").
-Không cho phép lưu tệp tin này làm ảnh đại diện.</t>
+          <t>System khong chap nhan file PDF.
+Hien thi notification error requires tep tin hinh photo hop le (e.g.: "Invalid file format. Please upload JPG or PNG image").
+Khong allows save tep tin nay lam profile photo.</t>
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="N9" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8)</t>
+          <t>Related to Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -2042,18 +2042,18 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Xác minh cấu trúc tên file lưu trên Google Drive</t>
+          <t>Verify cau truc ten file save tren Google Drive</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo file ảnh tải lên được đổi tên theo đúng định dạng {StudentName}_{Timestamp}.jpg.</t>
+          <t>Dam bao file photo tai len duoc doi ten theo dung format {StudentName}_{Timestamp}.jpg.</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Học sinh tên "John Smith" chưa có ảnh.</t>
+          <t>Nguoi dung log in quyen Staff.
+Hoc sinh ten "John Smith" chua co photo.</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -2063,16 +2063,16 @@
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh "John Smith" và tải lên ảnh avatar.jpg.
-2. Nhấn "Lưu" (Save).
-3. Đăng nhập vào tài khoản Google Drive quản trị, mở thư mục lưu trữ cấu hình.
-4. Tìm kiếm file ảnh mới tải lên và kiểm tra tên file.</t>
+          <t>1. Select student "John Smith" va tai len photo avatar.jpg.
+2. Nhan "Save" (Save).
+3. Log in vao account Google Drive quan tri, mo thu muc archive cau hinh.
+4. Tim kiem file new photo tai len va kiem tra ten file.</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>File ảnh được lưu trữ trên Google Drive có tên chính xác là "John_Smith_YYYYMMDDHHMMSS.jpg" (trong đó YYYYMMDDHHMMSS là thời gian lúc tải lên).
-Định dạng file được chuẩn hóa thành đuôi mở rộng .jpg.</t>
+          <t>File photo duoc archive tren Google Drive co ten chinh xac la "John_Smith_YYYYMMDDHHMMSS.jpg" (trong do YYYYMMDDHHMMSS la period luc tai len).
+Dinh dang file duoc chuan hoa thanh duoi mo rong .jpg.</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="N10" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Storage Information (Mục 3), Google Drive Integration (Mục 7)</t>
+          <t>Related to Storage Information (Section 3), Google Drive Integration (Section 7)</t>
         </is>
       </c>
     </row>
@@ -2115,36 +2115,36 @@
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>Tải lên ảnh cho học sinh có tên chứa ký tự tiếng Việt có dấu</t>
+          <t>Upload photo cho student co ten chua ky tu tieng Viet co dau</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra xem tên file trên Google Drive có được xử lý chuẩn hóa ký tự tiếng Việt có dấu và khoảng trắng hay không.</t>
+          <t>Verify whether ten file tren Google Drive co duoc xu ly chuan hoa ky tu tieng Viet co dau va khoang trang hay khong.</t>
         </is>
       </c>
       <c r="G11" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Có học sinh tên "Nguyễn Hoàng Nam".</t>
+          <t>Nguoi dung log in quyen Staff.
+Co student ten "Nguyen Hoang Nam".</t>
         </is>
       </c>
       <c r="H11" s="28" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Hoàng Nam"; ImageFile=avatar.jpg</t>
+          <t>StudentName="Nguyen Hoang Nam"; ImageFile=avatar.jpg</t>
         </is>
       </c>
       <c r="I11" s="28" t="inlineStr">
         <is>
-          <t>1. Mở trang chi tiết học sinh "Nguyễn Hoàng Nam" và tải lên ảnh đại diện.
-2. Nhấn "Lưu".
-3. Mở Google Drive kiểm tra tên file ảnh vừa tạo.</t>
+          <t>1. Mo trang chi tiet student "Nguyen Hoang Nam" va tai len profile photo.
+2. Nhan "Save".
+3. Mo Google Drive kiem tra ten file photo vua create.</t>
         </is>
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>File ảnh được tải lên thành công.
-Tên file trên Google Drive được chuẩn hóa (ví dụ chuyển thành "Nguyen_Hoang_Nam_{Timestamp}.jpg" hoặc giữ nguyên ký tự tiếng Việt có dấu nhưng khoảng trắng thay bằng gạch dưới và không bị lỗi hiển thị/mã hóa ký tự).</t>
+          <t>File photo duoc tai len successfully.
+Ten file tren Google Drive duoc chuan hoa (e.g. chuyen thanh "Nguyen_Hoang_Nam_{Timestamp}.jpg" hoac giu nguyen ky tu tieng Viet co dau nhung khoang trang thay bang gach duoi va khong bi error display/ma hoa ky tu).</t>
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
@@ -2160,11 +2160,11 @@
       </c>
       <c r="N11" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Storage Information (Mục 3), Google Drive Integration (Mục 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="120" customHeight="1">
+          <t>Related to Storage Information (Section 3), Google Drive Integration (Section 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="105" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
         <is>
           <t>TC-M08-011</t>
@@ -2187,18 +2187,18 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Xác minh quyền truy cập tệp tin (File Permission) trên Google Drive</t>
+          <t>Verify quyen access tep tin (File Permission) tren Google Drive</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo tệp tin ảnh tải lên được cấu hình quyền chia sẻ công khai ở chế độ chỉ xem để hệ thống hiển thị được.</t>
+          <t>Dam bao tep tin photo tai len duoc cau hinh quyen chia se cong khai o che do chi xem de system display duoc.</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Tải ảnh lên cho học sinh PNV26001 thành công.</t>
+          <t>Nguoi dung log in quyen Staff.
+Tai photo len cho student PNV26001 successfully.</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -2208,14 +2208,14 @@
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>1. Mở tài khoản Google Drive quản trị, tìm file ảnh của học sinh PNV26001 vừa tải lên.
-2. Nhấp chuột phải chọn "Chia sẻ" (Share) -&gt; "Nhận liên kết" (Get link).
-3. Kiểm tra cài đặt quyền truy cập chung.</t>
+          <t>1. Mo account Google Drive quan tri, tim file photo cua student PNV26001 vua tai len.
+2. Nhap chuot phai select "Chia se" (Share) -&gt; "Nhan lien ket" (Get link).
+3. Verify cai dat quyen access chung.</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>Quyền truy cập chung của file được thiết lập là "Bất kỳ ai có liên kết này" (Anyone with the link) và vai trò được gán là "Người xem" (Viewer / View only).</t>
+          <t>Quyen access chung cua file duoc thiet lap la "Bat ky ai co lien ket nay" (Anyone with the link) va vai tro duoc gan la "Nguoi xem" (Viewer / View only).</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="N12" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Storage Information (Mục 3), Google Drive Integration (Mục 7)</t>
+          <t>Related to Storage Information (Section 3), Google Drive Integration (Section 7)</t>
         </is>
       </c>
     </row>
@@ -2258,34 +2258,34 @@
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>Tải lên ảnh có dung lượng lớn</t>
+          <t>Upload photo co size lon</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra phản hồi của hệ thống khi cố gắng tải lên một hình ảnh có kích thước tệp tin lớn.</t>
+          <t>Verify phan hoi cua system khi co gang tai len mot hinh photo co kich thuoc tep tin lon.</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Đang mở giao diện tải ảnh đại diện.</t>
+          <t>Nguoi dung log in quyen Staff.
+Dang mo interface tai profile photo.</t>
         </is>
       </c>
       <c r="H13" s="28" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=large_photo.jpg (dung lượng 15MB)</t>
+          <t>StudentCode=PNV26001; ImageFile=large_photo.jpg (size 15MB)</t>
         </is>
       </c>
       <c r="I13" s="28" t="inlineStr">
         <is>
-          <t>1. Tải lên tệp tin large_photo.jpg dung lượng 15MB.
-2. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Upload tep tin large_photo.jpg size 15MB.
+2. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J13" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống tải lên thành công nếu không cấu hình giới hạn kích thước, HOẶC nếu hệ thống có giới hạn dung lượng: hiển thị thông báo lỗi yêu cầu ảnh nhỏ hơn mức quy định (ví dụ: "File size exceeds limit") và ngăn không cho tải lên.</t>
+          <t>System tai len successfully neu khong cau hinh gioi han kich thuoc, HOAC neu system co gioi han size: display notification error requires photo nho hon muc quy dinh (e.g.: "File size exceeds limit") va ngan khong cho tai len.</t>
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="N13" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Test Data Preparation (Mục 11 - Large image)</t>
+          <t>Related to Test Data Preparation (Section 11 - Large image)</t>
         </is>
       </c>
     </row>
@@ -2328,18 +2328,18 @@
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>Tải lên hình ảnh có phần mở rộng viết hoa (.JPG / .PNG)</t>
+          <t>Upload hinh photo co phan mo rong viet hoa (.JPG / .PNG)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống nhận diện và chấp nhận các đuôi mở rộng viết hoa như .JPG, .PNG mà không báo lỗi định dạng.</t>
+          <t>Verify system nhan dien va chap nhan cac duoi mo rong viet hoa nhu .JPG, .PNG ma khong bao error format.</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Đang mở giao diện tải ảnh đại diện.</t>
+          <t>Nguoi dung log in quyen Staff.
+Dang mo interface tai profile photo.</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -2349,14 +2349,14 @@
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>1. Tải lên tệp tin avatar.JPG (đuôi JPG viết hoa).
-2. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Upload tep tin avatar.JPG (duoi JPG viet hoa).
+2. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống nhận diện .JPG là định dạng hình ảnh hợp lệ.
-Tải ảnh thành công, cập nhật thông tin học sinh bình thường.</t>
+          <t>System nhan dien .JPG la format hinh photo hop le.
+Tai photo successfully, cap nhat thong tin student binh thuong.</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8 - Image File)</t>
+          <t>Related to Validation Rules (Section 8 - Image File)</t>
         </is>
       </c>
     </row>
@@ -2399,19 +2399,19 @@
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Tải lên thất bại do lỗi kết nối Google Drive</t>
+          <t>Upload failed do error ket noi Google Drive</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không lưu link ảnh lỗi và giữ nguyên thông tin học sinh nếu quá trình tải lên Google Drive thất bại.</t>
+          <t>Verify system khong save link photo error va giu nguyen thong tin student neu qua trinh tai len Google Drive failed.</t>
         </is>
       </c>
       <c r="G15" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh PNV26003 chưa có ảnh đại diện.
-Đường truyền Google Drive bị ngắt kết nối hoặc lỗi dịch vụ trong lúc tải.</t>
+          <t>User is logged in as Staff.
+Hoc sinh PNV26003 chua co profile photo.
+Duong truyen Google Drive bi ngat ket noi hoac error dich vu trong luc tai.</t>
         </is>
       </c>
       <c r="H15" s="28" t="inlineStr">
@@ -2421,17 +2421,17 @@
       </c>
       <c r="I15" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26003 và mở trang Chi tiết Học sinh.
-2. Chọn tải lên file student_avatar3.jpg.
-3. Nhấn "Lưu" (Save).
-4. Quan sát thông báo lỗi và kiểm tra thông tin học sinh.</t>
+          <t>1. Select student PNV26003 va mo trang Chi tiet Hoc sinh.
+2. Select tai len file student_avatar3.jpg.
+3. Nhan "Save" (Save).
+4. Observe notification error va kiem tra thong tin student.</t>
         </is>
       </c>
       <c r="J15" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi tải lên (ví dụ: "Upload failed" hoặc "Google Drive unavailable").
-Thông tin học sinh không bị thay đổi, không lưu đường dẫn hỏng (broken link) vào hồ sơ.
-Học sinh vẫn tiếp tục hiển thị avatar mặc định.</t>
+          <t>System display notification error tai len (e.g.: "Upload failed" hoac "Google Drive unavailable").
+Thong tin student khong bi thay doi, khong save duong dan hong (broken link) vao ho so.
+Hoc sinh van tiep tuc display avatar mac dinh.</t>
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="N15" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.5, Error Handling (Mục 9)</t>
+          <t>Related to Rule 5.5, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2474,18 +2474,18 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>Tải lên thất bại do thư mục Google Drive chưa cấu hình</t>
+          <t>Upload failed do thu muc Google Drive chua cau hinh</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hành vi của hệ thống khi cố gắng tải ảnh lên trong khi thư mục Google Drive chưa được thiết lập.</t>
+          <t>Verify hanh vi cua system khi co gang tai photo len trong khi thu muc Google Drive chua duoc thiet lap.</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Thư mục lưu trữ Google Drive chưa được cấu hình trong hệ thống.</t>
+          <t>Nguoi dung log in quyen Staff.
+Thu muc archive Google Drive chua duoc cau hinh trong system.</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -2495,15 +2495,15 @@
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>1. Mở trang Chi tiết Học sinh PNV26001.
-2. Chọn tải lên file student_avatar.jpg.
-3. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Mo trang Chi tiet Hoc sinh PNV26001.
+2. Select tai len file student_avatar.jpg.
+3. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi cấu hình (ví dụ: "Google Drive folder not configured or unavailable" hoặc "Upload error").
-Quá trình tải lên bị hủy bỏ, thông tin học sinh không bị thay đổi.</t>
+          <t>System display notification error cau hinh (e.g.: "Google Drive folder not configured or unavailable" hoac "Upload error").
+Qua trinh tai len bi huy bo, thong tin student khong bi thay doi.</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="N16" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Error Handling (Mục 9)</t>
+          <t>Related to Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2546,17 +2546,17 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Hiển thị avatar mặc định khi URL ảnh bị lỗi (HTTP 404)</t>
+          <t>Hien thi avatar mac dinh khi URL photo bi error (HTTP 404)</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống tự động phát hiện URL ảnh bị hỏng và chuyển sang hiển thị avatar mặc định.</t>
+          <t>Verify system tu dong phat hien URL photo bi hong va chuyen sang display avatar mac dinh.</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
-          <t>Học sinh "Le Thi B" có URL ảnh trong hồ sơ học sinh, nhưng file gốc trên Google Drive đã bị xóa hoặc không truy cập được (lỗi 404).</t>
+          <t>Hoc sinh "Le Thi B" co URL photo trong ho so student, nhung file goc tren Google Drive da bi delete hoac khong access duoc (error 404).</t>
         </is>
       </c>
       <c r="H17" s="28" t="inlineStr">
@@ -2566,14 +2566,14 @@
       </c>
       <c r="I17" s="28" t="inlineStr">
         <is>
-          <t>1. Đăng nhập hệ thống bằng quyền Staff.
-2. Truy cập danh sách học sinh hoặc chi tiết học sinh "Le Thi B".
-3. Quan sát ảnh đại diện hiển thị.</t>
+          <t>1. Log in system bang quyen Staff.
+2. Truy cap danh sach student hoac chi tiet student "Le Thi B".
+3. Observe profile photo display.</t>
         </is>
       </c>
       <c r="J17" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống phát hiện không tải được ảnh từ URL cũ, tự động hiển thị avatar mặc định dạng hình tròn chứa hai chữ cái viết tắt là "LB" mà không cần bất kỳ can thiệp thủ công nào từ người dùng.</t>
+          <t>System phat hien khong tai duoc photo tu URL cu, tu dong display avatar mac format hinh tron chua hai initials la "LB" ma khong can bat ky can thiep thu cong nao tu user.</t>
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="N17" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F04, Rule 5.6, Error Handling (Mục 9)</t>
+          <t>Related to M08-F04, Rule 5.6, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2616,17 +2616,17 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra quyền hạn của Student đối với ảnh đại diện</t>
+          <t>Verify quyen han cua Student for profile photo</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản Student chỉ có quyền xem ảnh đại diện của mình và không có quyền tải lên, chỉnh sửa hoặc xóa ảnh.</t>
+          <t>Verify account Student chi co quyen xem profile photo cua minh va khong co quyen tai len, edit hoac delete photo.</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập với quyền Student (email domain @student.passerellesnumeriques.org).</t>
+          <t>Nguoi dung log in voi quyen Student (email domain @student.passerellesnumeriques.org).</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -2636,17 +2636,17 @@
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>1. Đăng nhập vào Student Portal.
-2. Truy cập trang thông tin cá nhân.
-3. Kiểm tra sự tồn tại của các nút "Tải ảnh lên" (Upload), "Thay thế" (Replace) hoặc "Xóa ảnh" (Remove).
-4. Thử tìm cách tương tác chỉnh sửa ảnh đại diện.</t>
+          <t>1. Log in vao Student Portal.
+2. Truy cap trang thong tin personal.
+3. Verify su ton tai cua cac nut "Tai photo len" (Upload), "Thay the" (Replace) hoac "Delete photo" (Remove).
+4. Thu tim cach tuong tac edit profile photo.</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Học sinh có thể nhìn thấy ảnh đại diện của mình hiển thị ở góc màn hình hoặc trang thông tin.
-Không có nút hoặc tùy chọn nào để tải lên, thay thế hoặc xóa ảnh trên giao diện.
-Trạng thái truy cập hoàn toàn là Chỉ xem (Read-only).</t>
+          <t>Hoc sinh can nhin thay profile photo cua minh display o goc man hinh hoac trang thong tin.
+Khong co nut hoac tuy select nao de tai len, replace hoac delete photo tren interface.
+Status access hoan toan la Chi xem (Read-only).</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F05, Rule 5.1</t>
+          <t>Related to M08-F05, Rule 5.1</t>
         </is>
       </c>
     </row>
@@ -2689,18 +2689,18 @@
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chặn gọi trực tiếp API upload từ tài khoản Student</t>
+          <t>Verify chan goi truc tiep API upload tu account Student</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Xác minh cơ chế bảo mật phía backend từ chối yêu cầu upload/thay thế/xóa ảnh đại diện gửi từ tài khoản Student.</t>
+          <t>Verify co che bao mat phia backend denies requires upload/replace/delete profile photo gui tu account Student.</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Student.
-Sử dụng DevTools hoặc công cụ bên thứ ba gửi request trực tiếp đến hàm upload/replace/remove photo của backend.</t>
+          <t>Nguoi dung log in quyen Student.
+Su dung DevTools hoac cong cu ben Tuesday gui request truc tiep den ham upload/replace/remove photo cua backend.</t>
         </is>
       </c>
       <c r="H19" s="28" t="inlineStr">
@@ -2710,14 +2710,14 @@
       </c>
       <c r="I19" s="28" t="inlineStr">
         <is>
-          <t>1. Thực hiện gửi request trực tiếp đến API upload/replace/remove photo sử dụng token/session của Student.
-2. Quan sát phản hồi trả về từ backend.</t>
+          <t>1. Thuc hien gui request truc tiep den API upload/replace/remove photo su dung token/session cua Student.
+2. Observe phan hoi tra ve tu backend.</t>
         </is>
       </c>
       <c r="J19" s="28" t="inlineStr">
         <is>
-          <t>Backend từ chối yêu cầu, trả về mã lỗi từ chối quyền truy cập (Access Denied / Unauthorized).
-Thông tin ảnh đại diện học sinh không bị ảnh hưởng.</t>
+          <t>Backend denies requires, tra ve ma error denies quyen access (Access Denied / Unauthorized).
+Thong tin profile photo student khong bi photo huong.</t>
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
@@ -2733,11 +2733,11 @@
       </c>
       <c r="N19" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.1, Error Handling (Mục 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+          <t>Related to Rule 5.1, Error Handling (Section 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
       <c r="A20" s="21" t="inlineStr">
         <is>
           <t>TC-M08-019</t>
@@ -2760,17 +2760,17 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Từ chối truy cập đối với tài khoản ngoài tổ chức</t>
+          <t>Tu choi access for account external organization</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo người dùng với email không thuộc tổ chức (ví dụ: @gmail.com) không thể truy cập hệ thống và xem ảnh đại diện.</t>
+          <t>Dam bao user voi email khong thuoc organization (e.g.: @gmail.com) cannot access system va xem profile photo.</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Người dùng sử dụng tài khoản email cá nhân không phải domain @passerellesnumeriques.org hay @student.passerellesnumeriques.org.</t>
+          <t>Nguoi dung su dung account email personal not domain @passerellesnumeriques.org hay @student.passerellesnumeriques.org.</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -2780,15 +2780,15 @@
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>1. Mở trình duyệt ẩn danh.
-2. Truy cập URL của hệ thống.
-3. Đăng nhập bằng tài khoản guest_user@gmail.com.</t>
+          <t>1. Mo trinh duyet an danh.
+2. Truy cap URL cua system.
+3. Log in bang account guest_user@gmail.com.</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối đăng nhập và chuyển hướng người dùng đến trang "Access Denied" (Từ chối truy cập).
-Không xem được bất cứ thông tin học sinh nào bao gồm cả ảnh đại diện.</t>
+          <t>System denies log in va redirect user den trang "Access Denied" (Tu choi access).
+Khong xem duoc bat cu thong tin student nao bao gom ca profile photo.</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="N20" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Docs - Mục 4 (User Roles) &amp; Mục 6 (Authentication Flow)</t>
+          <t>Related to Docs - Section 4 (User Roles) &amp; Section 6 (Authentication Flow)</t>
         </is>
       </c>
     </row>
@@ -2831,18 +2831,18 @@
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra không tích hợp tính năng chỉnh sửa/cắt ảnh</t>
+          <t>Verify khong tich hop tinh nang edit/cat photo</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không tích hợp các chức năng chỉnh sửa ảnh, cắt ảnh hoặc xem lịch sử các ảnh đại diện cũ.</t>
+          <t>Verify system khong tich hop cac chuc nang edit photo, cat photo hoac xem lich su cac old profile photo.</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Đang trong tiến trình chọn và chuẩn bị tải ảnh lên.</t>
+          <t>Nguoi dung log in quyen Staff.
+Dang trong tien trinh select va chuan bi tai photo len.</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
@@ -2852,15 +2852,15 @@
       </c>
       <c r="I21" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn tải lên file avatar.jpg.
-2. Quan sát các nút và tùy chọn thao tác hiển thị trên giao diện xem trước ảnh.
-3. Kiểm tra xem có chức năng xoay, cắt (crop) hoặc xem danh sách ảnh cũ đã tải lên không.</t>
+          <t>1. Select tai len file avatar.jpg.
+2. Observe cac nut va tuy select thao tac display tren interface xem truoc photo.
+3. Verify whether co chuc nang xoay, cat (crop) hoac xem danh sach old photo da tai len khong.</t>
         </is>
       </c>
       <c r="J21" s="28" t="inlineStr">
         <is>
-          <t>Giao diện chỉ hiển thị ảnh xem trước đơn giản để người dùng kiểm tra trực quan.
-Không có công cụ chỉnh sửa, cắt ghép hoặc xem lại phiên bản ảnh cũ nào trên hệ thống.</t>
+          <t>Interface chi display preview photo don gian de user kiem tra truc quan.
+Khong co cong cu edit, cat ghep hoac xem lai phien ban old photo nao tren system.</t>
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="N21" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Out of Scope (Mục 13)</t>
+          <t>Related to Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>
@@ -3014,17 +3014,17 @@
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>Đăng nhập bằng tài khoản Student hợp lệ</t>
+          <t>Log in with a valid Student account</t>
         </is>
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Xác minh học sinh có email thuộc domain @student.passerellesnumeriques.org đăng nhập thành công vào Student Portal qua Google OAuth.</t>
+          <t>Verify student co email thuoc domain @student.passerellesnumeriques.org log in successfully vao Student Portal qua Google OAuth.</t>
         </is>
       </c>
       <c r="G2" s="23" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập hệ thống. Trình duyệt đã kết nối internet và hỗ trợ Google OAuth.</t>
+          <t>Nguoi dung chua log in system. Trinh duyet da ket noi internet va ho tro Google OAuth.</t>
         </is>
       </c>
       <c r="H2" s="23" t="inlineStr">
@@ -3034,17 +3034,17 @@
       </c>
       <c r="I2" s="23" t="inlineStr">
         <is>
-          <t>1. Truy cập URL của hệ thống.
-2. Tại màn hình đăng nhập Google OAuth, nhập tài khoản student01@student.passerellesnumeriques.org.
-3. Nhập mật khẩu hợp lệ và đồng ý cấp quyền nếu có.
-4. Quan sát trang web sau khi chuyển hướng.</t>
+          <t>1. Truy cap URL cua system.
+2. Tai man hinh log in Google OAuth, enter account student01@student.passerellesnumeriques.org.
+3. Enter mat khau hop le va dong y cap quyen neu co.
+4. Observe trang web sau khi redirect.</t>
         </is>
       </c>
       <c r="J2" s="23" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công. Giao diện tự động chuyển hướng đến Student Portal (mặc định mở tab Academic).
-Thông tin của học sinh hiển thị chính xác bao gồm Họ tên, Mã học sinh ở góc màn hình.
-Dữ liệu điểm học tập của chính học sinh này được tải lên thành công.</t>
+          <t>Log in successfully. Interface tu dong redirect den Student Portal (mac dinh mo tab Academic).
+Thong tin cua student display chinh xac bao gom Ho ten, Ma student o goc man hinh.
+Du lieu grade hoc tap cua chinh student nay duoc tai len successfully.</t>
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
@@ -3060,11 +3060,11 @@
       </c>
       <c r="N2" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F01, M09-F07, Rule 7.1, Rule 7.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+          <t>Related to M09-F01, M09-F07, Rule 7.1, Rule 7.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="105" customHeight="1">
       <c r="A3" s="26" t="inlineStr">
         <is>
           <t>TC-M09-002</t>
@@ -3087,17 +3087,17 @@
       </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
-          <t>Đăng nhập bằng tài khoản Staff của tổ chức</t>
+          <t>Log in with an organization Staff account</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản Staff khi đăng nhập qua Google OAuth sẽ được tự động nhận diện domain và chuyển hướng đến Staff Portal thay vì Student Portal.</t>
+          <t>Verify account Staff khi log in qua Google OAuth se duoc tu dong nhan dien domain va redirect den Staff Portal thay vi Student Portal.</t>
         </is>
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập hệ thống.</t>
+          <t>Nguoi dung chua log in system.</t>
         </is>
       </c>
       <c r="H3" s="28" t="inlineStr">
@@ -3107,16 +3107,16 @@
       </c>
       <c r="I3" s="28" t="inlineStr">
         <is>
-          <t>1. Truy cập URL của hệ thống.
-2. Thực hiện đăng nhập qua Google OAuth bằng tài khoản staff_user@passerellesnumeriques.org.
-3. Quan sát giao diện sau khi đăng nhập thành công.</t>
+          <t>1. Truy cap URL cua system.
+2. Thuc hien log in qua Google OAuth bang account staff_user@passerellesnumeriques.org.
+3. Observe interface sau khi log in successfully.</t>
         </is>
       </c>
       <c r="J3" s="28" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công.
-Hệ thống tự động nhận diện email thuộc domain @passerellesnumeriques.org.
-Chuyển hướng người dùng sang Staff Portal với đầy đủ tính năng quản trị. Không hiển thị giao diện Student Portal.</t>
+          <t>Log in successfully.
+System tu dong nhan dien email thuoc domain @passerellesnumeriques.org.
+Chuyen huong user sang Staff Portal voi day du tinh nang quan tri. Khong display interface Student Portal.</t>
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
@@ -3132,11 +3132,11 @@
       </c>
       <c r="N3" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F01, Rule 7.1, Docs - Mục 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+          <t>Related to M09-F01, Rule 7.1, Docs - Section 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="105" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
           <t>TC-M09-003</t>
@@ -3159,17 +3159,17 @@
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>Đăng nhập bằng tài khoản cá nhân ngoài tổ chức</t>
+          <t>Log in with an external personal account</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản email không thuộc các domain của tổ chức (ví dụ @gmail.com) bị hệ thống chặn truy cập.</t>
+          <t>Verify account email khong thuoc cac domain cua organization (e.g. @gmail.com) bi system chan access.</t>
         </is>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập hệ thống.</t>
+          <t>Nguoi dung chua log in system.</t>
         </is>
       </c>
       <c r="H4" s="23" t="inlineStr">
@@ -3179,16 +3179,16 @@
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>1. Truy cập URL của hệ thống.
-2. Thực hiện đăng nhập qua Google OAuth bằng tài khoản guest_user@gmail.com.
-3. Quan sát phản hồi của hệ thống.</t>
+          <t>1. Truy cap URL cua system.
+2. Thuc hien log in qua Google OAuth bang account guest_user@gmail.com.
+3. Observe phan hoi cua system.</t>
         </is>
       </c>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t>Đăng nhập thất bại.
-Hệ thống từ chối quyền truy cập của email domain @gmail.com.
-Chuyển hướng người dùng sang trang báo lỗi "Access Denied" (Từ chối truy cập). Không tải bất kỳ dữ liệu nào của hệ thống.</t>
+          <t>Log in failed.
+System denies quyen access cua email domain @gmail.com.
+Chuyen huong user sang trang bao error "Access Denied" (Tu choi access). Khong tai bat ky du lieu nao cua system.</t>
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="N4" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F01, Rule 7.1, Error Handling (Mục 9)</t>
+          <t>Related to M09-F01, Rule 7.1, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -3231,17 +3231,17 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Đăng nhập bằng email student hợp lệ nhưng không có dữ liệu trong hệ thống</t>
+          <t>Log in with valid student email but without academic records in system</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không bị lỗi crash và hiển thị thông điệp phù hợp khi email student thuộc domain hợp lệ nhưng không nằm trong danh sách dữ liệu học sinh.</t>
+          <t>Verify system khong bi error crash va display thong diep phu hop khi email student thuoc domain hop le nhung khong nam trong danh sach du lieu student.</t>
         </is>
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập hệ thống. Tài khoản Google student tồn tại nhưng email này chưa được cấu hình trong Sheet danh sách học sinh.</t>
+          <t>Nguoi dung chua log in system. Tai khoan Google student ton tai nhung email nay chua duoc cau hinh trong Sheet danh sach student.</t>
         </is>
       </c>
       <c r="H5" s="28" t="inlineStr">
@@ -3251,16 +3251,16 @@
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>1. Truy cập URL của hệ thống.
-2. Thực hiện đăng nhập qua Google OAuth bằng tài khoản new_student@student.passerellesnumeriques.org.
-3. Quan sát giao diện sau khi chuyển hướng thành công.</t>
+          <t>1. Truy cap URL cua system.
+2. Thuc hien log in qua Google OAuth bang account new_student@student.passerellesnumeriques.org.
+3. Observe interface sau khi redirect successfully.</t>
         </is>
       </c>
       <c r="J5" s="28" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công vào Student Portal.
-Hệ thống không bị lỗi crash/trắng màn hình.
-Hiển thị thông báo rõ ràng cho người dùng: "No academic records found." (Không tìm thấy dữ liệu học tập).</t>
+          <t>Log in successfully vao Student Portal.
+System khong bi error crash/trang man hinh.
+Hien thi notification ro rang cho user: "No academic records found." (Khong tim thay du lieu hoc tap).</t>
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="N5" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F01, M09-F07, Error Handling (Mục 9)</t>
+          <t>Related to M09-F01, M09-F07, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -3303,18 +3303,18 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Chuyển đổi giữa các học kỳ (Semester Selector)</t>
+          <t>Switching between semesters (Semester Selector)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>Xác minh tính năng chuyển đổi học kỳ hiển thị đúng dữ liệu điểm của học kỳ được chọn.</t>
+          <t>Verify tinh nang switching semester display dung du lieu grade cua semester duoc select.</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công vào Student Portal.
-Học sinh này đã có dữ liệu điểm ở nhiều học kỳ (ví dụ: Học kỳ 1 và Học kỳ 2).</t>
+          <t>Hoc sinh da log in successfully vao Student Portal.
+Hoc sinh nay da co du lieu grade o nhieu semester (e.g.: Semester 1 va Semester 2).</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -3324,18 +3324,18 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>1. Tại giao diện Student Portal, định vị bộ chọn học kỳ (Semester Selector).
-2. Nhấp vào danh sách thả xuống và chọn "Semester 2" (Học kỳ 2).
-3. Quan sát danh sách môn học và điểm số hiển thị.
-4. Nhấp chọn lại "Semester 1" (Học kỳ 1).
-5. Quan sát danh sách môn học và điểm số hiển thị.</t>
+          <t>1. Tai interface Student Portal, dinh vi bo select semester (Semester Selector).
+2. Nhap vao danh sach tha xuong va select "Semester 2" (Semester 2).
+3. Observe danh sach course va grades display.
+4. Nhap select lai "Semester 1" (Semester 1).
+5. Observe danh sach course va grades display.</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>Bảng điểm cập nhật nhanh chóng và chính xác theo học kỳ được chọn.
-Khi chọn "Semester 2", hệ thống chỉ tải các môn học và điểm số thuộc Học kỳ 2.
-Khi chọn "Semester 1", hệ thống chỉ tải các môn học và điểm số thuộc Học kỳ 1.</t>
+          <t>Bang grade cap nhat nhanh chong va chinh xac theo semester duoc select.
+Khi select "Semester 2", system chi tai cac course va grades thuoc Semester 2.
+Khi select "Semester 1", system chi tai cac course va grades thuoc Semester 1.</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F02, Rule 7.2</t>
+          <t>Related to M09-F02, Rule 7.2</t>
         </is>
       </c>
     </row>
@@ -3378,18 +3378,18 @@
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra phân nhóm môn học theo danh mục (Subject Categories)</t>
+          <t>Verify categorization course theo category (Subject Categories)</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Xác minh các môn học trong học kỳ hiển thị đúng phân nhóm theo 4 danh mục đào tạo.</t>
+          <t>Verify cac course trong semester display dung categorization theo 4 category dao create.</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công vào Student Portal.
-Học kỳ hiện tại có chứa các môn học thuộc cả 4 danh mục.</t>
+          <t>Hoc sinh da log in successfully vao Student Portal.
+Semester hien tai co chua cac course thuoc ca 4 category.</t>
         </is>
       </c>
       <c r="H7" s="28" t="inlineStr">
@@ -3399,16 +3399,16 @@
       </c>
       <c r="I7" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn Học kỳ 1.
-2. Quan sát bố cục hiển thị của danh sách môn học.
-3. Kiểm tra xem các môn học có được xếp dưới các tiêu đề nhóm tương ứng hay không: Fundamental, IT, English, Soft Skills.
-4. Đối chiếu môn học cụ thể (ví dụ môn Math phải thuộc Fundamental, Java thuộc IT).</t>
+          <t>1. Select Semester 1.
+2. Observe bo cuc display cua danh sach course.
+3. Verify whether cac course co duoc xep duoi cac tieu de group tuong ung hay khong: Fundamental, IT, English, Soft Skills.
+4. Doi chieu course cu the (e.g. mon Math phai thuoc Fundamental, Java thuoc IT).</t>
         </is>
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>Các môn học được phân nhóm chính xác và hiển thị dưới các tiêu đề danh mục: Fundamental, IT, English, Soft Skills.
-Bố cục phân nhóm rõ ràng, dễ đọc, không có môn học nào bị xếp sai nhóm hoặc không có nhóm.</t>
+          <t>Cac course duoc categorization chinh xac va display duoi cac tieu de category: Fundamental, IT, English, Soft Skills.
+Bo cuc categorization ro rang, de doc, khong co course nao bi xep sai group hoac khong co group.</t>
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="N7" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F02, Rule 7.3</t>
+          <t>Related to M09-F02, Rule 7.3</t>
         </is>
       </c>
     </row>
@@ -3451,17 +3451,17 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra tính năng Chỉ đọc (Read-only) của Student Portal</t>
+          <t>Verify tinh nang Read-only (Read-only) cua Student Portal</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Xác minh học sinh hoàn toàn không có quyền chỉnh sửa điểm số hay thực hiện các tác vụ thay đổi dữ liệu trên giao diện.</t>
+          <t>Verify student hoan toan khong co quyen edit grades hay thuc hien cac tac vu thay doi du lieu tren interface.</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công vào Student Portal và đang ở màn hình hiển thị điểm.</t>
+          <t>Hoc sinh da log in successfully vao Student Portal va dang o man hinh display grade.</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -3471,16 +3471,16 @@
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>1. Quan sát toàn bộ giao diện màn hình Academic.
-2. Kiểm tra sự xuất hiện của các nút: Chỉnh sửa (Edit), Lưu (Save), Xóa (Delete), Nhập điểm (Import), Tải lên (Upload).
-3. Thử nhấp chuột vào các ô điểm số (KT TX, ĐK1-ĐK6, TCK, TLCK, Final Score, GPA).
-4. Thử gõ bàn phím để thay đổi giá trị điểm.</t>
+          <t>1. Observe toan bo interface man hinh Academic.
+2. Verify su xuat hien cua cac nut: Edit (Edit), Save (Save), Delete (Delete), Enter grade (Import), Upload (Upload).
+3. Thu click chuot vao cac o grades (KT TX, DK1-DK6, TCK, TLCK, Final Score, GPA).
+4. Thu go ban phim de thay doi gia tri grade.</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>Giao diện không hiển thị bất kỳ nút hoặc công cụ nào cho phép chỉnh sửa, lưu, xóa hoặc nhập dữ liệu.
-Tất cả điểm số hiển thị dưới dạng văn bản tĩnh (read-only), không thể nhấp vào để chỉnh sửa hay nhập liệu từ bàn phím.</t>
+          <t>Interface not displayed bat ky nut hoac cong cu nao allows edit, save, delete hoac enter du lieu.
+Tat ca grades display as van ban tinh (read-only), cannot click vao de edit hay enter lieu tu ban phim.</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F02, Rule 7.4</t>
+          <t>Related to M09-F02, Rule 7.4</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>Hiển thị điểm số chưa được nhập (Empty Grades)</t>
+          <t>Hien thi grades chua duoc enter (Empty Grades)</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Xác minh các ô điểm số chưa có dữ liệu sẽ hiển thị ký tự "—" để tránh gây hiểu lầm cho học sinh.</t>
+          <t>Verify cac o grades chua co du lieu se display ky tu "—" de tranh gay hieu lam cho student.</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Học sinh này có một số cột điểm chưa được giáo viên nhập (ví dụ điểm thi lại TLCK hoặc điểm định kỳ ĐK3 đang trống trên Sheets).</t>
+          <t>Hoc sinh da log in. Hoc sinh nay co mot so cot grade chua duoc giao vien enter (e.g. grade thi lai TLCK hoac grade dinh ky DK3 dang trong tren Sheets).</t>
         </is>
       </c>
       <c r="H9" s="28" t="inlineStr">
@@ -3543,14 +3543,14 @@
       </c>
       <c r="I9" s="28" t="inlineStr">
         <is>
-          <t>1. Truy cập bảng điểm của học kỳ chứa môn Java Programming.
-2. Quan sát hiển thị tại cột thi lại "TLCK" và các ô điểm trống khác của môn học này.</t>
+          <t>1. Truy cap transcript cua semester chua mon Java Programming.
+2. Observe display tai cot thi lai "TLCK" va cac o grade trong khac cua course nay.</t>
         </is>
       </c>
       <c r="J9" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị ký tự "—" (gạch quang) tại các ô điểm chưa được nhập.
-Không hiển thị số "0" hoặc "0.0" hoặc để khoảng trống gây hiểu lầm, không xảy ra lỗi hiển thị hoặc lỗi hệ thống.</t>
+          <t>System display ky tu "—" (gach quang) tai cac o grade chua duoc enter.
+Khong display so "0" hoac "0.0" hoac de khoang trong gay hieu lam, khong xay ra error display hoac error system.</t>
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="N9" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F03, Rule 7.5, Error Handling (Mục 9)</t>
+          <t>Related to M09-F03, Rule 7.5, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -3593,17 +3593,17 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Mã màu điểm tổng kết (/10) đạt loại Giỏi (&gt;= 8.0)</t>
+          <t>Ma mau grade tong ket (/10) dat loai Gioi (&gt;= 8.0)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Xác minh điểm tổng kết lớn hơn hoặc bằng 8.0 hiển thị màu Xanh lá (Green).</t>
+          <t>Verify grade tong ket lon hon hoac bang 8.0 display mau Xanh la (Green).</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập và đang xem bảng điểm học kỳ. Môn Math có điểm tổng kết là 8.0, môn IT Basics có điểm tổng kết là 9.2.</t>
+          <t>Hoc sinh da log in va dang xem transcript semester. Mon Math co grade tong ket la 8.0, mon IT Basics co grade tong ket la 9.2.</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -3613,13 +3613,13 @@
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>1. Tìm đến các môn Math và IT Basics trên bảng điểm.
-2. Quan sát màu sắc của điểm số hiển thị tại cột điểm tổng kết "/10".</t>
+          <t>1. Tim den cac mon Math va IT Basics tren transcript.
+2. Observe mau sac cua grades display tai cot grade tong ket "/10".</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Điểm số "8.0" và "9.2" hiển thị với màu xanh lá cây (Green) rõ ràng.</t>
+          <t>Diem so "8.0" va "9.2" display voi mau xanh la cay (Green) ro rang.</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="N10" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -3662,17 +3662,17 @@
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>Mã màu điểm tổng kết (/10) đạt loại Khá/Trung bình (5.5 – 7.9)</t>
+          <t>Ma mau grade tong ket (/10) dat loai Kha/Trung binh (5.5 – 7.9)</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Xác minh điểm tổng kết từ 5.5 đến 7.9 hiển thị màu Cam (Orange).</t>
+          <t>Verify grade tong ket tu 5.5 den 7.9 display mau Cam (Orange).</t>
         </is>
       </c>
       <c r="G11" s="28" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập và đang xem bảng điểm học kỳ. Môn English có điểm tổng kết là 5.5, môn Soft Skills có điểm tổng kết là 7.9.</t>
+          <t>Hoc sinh da log in va dang xem transcript semester. Mon English co grade tong ket la 5.5, mon Soft Skills co grade tong ket la 7.9.</t>
         </is>
       </c>
       <c r="H11" s="28" t="inlineStr">
@@ -3682,13 +3682,13 @@
       </c>
       <c r="I11" s="28" t="inlineStr">
         <is>
-          <t>1. Tìm môn English và Soft Skills trên bảng điểm.
-2. Quan sát màu sắc hiển thị của điểm số tại cột điểm tổng kết "/10".</t>
+          <t>1. Tim mon English va Soft Skills tren transcript.
+2. Observe mau sac display cua grades tai cot grade tong ket "/10".</t>
         </is>
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>Điểm số "5.5" và "7.9" hiển thị với màu cam (Orange) rõ ràng.</t>
+          <t>Diem so "5.5" va "7.9" display voi mau cam (Orange) ro rang.</t>
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="N11" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -3731,17 +3731,17 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Mã màu điểm tổng kết (/10) loại Yếu (&lt; 5.5)</t>
+          <t>Ma mau grade tong ket (/10) loai Yeu (&lt; 5.5)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Xác minh điểm tổng kết nhỏ hơn 5.5 hiển thị màu Đỏ (Red).</t>
+          <t>Verify grade tong ket nho hon 5.5 display mau Do (Red).</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập và đang xem bảng điểm. Môn Web Development có điểm tổng kết là 5.4, môn Algorithms có điểm tổng kết là 4.0.</t>
+          <t>Hoc sinh da log in va dang xem transcript. Mon Web Development co grade tong ket la 5.4, mon Algorithms co grade tong ket la 4.0.</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -3751,13 +3751,13 @@
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>1. Tìm môn Web Development và Algorithms trên bảng điểm.
-2. Quan sát màu sắc hiển thị của điểm số tại cột điểm tổng kết "/10".</t>
+          <t>1. Tim mon Web Development va Algorithms tren transcript.
+2. Observe mau sac display cua grades tai cot grade tong ket "/10".</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>Điểm số "5.4" và "4.0" hiển thị với màu đỏ (Red) rõ ràng.</t>
+          <t>Diem so "5.4" va "4.0" display voi mau do (Red) ro rang.</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
@@ -3773,11 +3773,11 @@
       </c>
       <c r="N12" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
           <t>TC-M09-012</t>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>Mã màu điểm GPA (/4) đạt loại Giỏi/Xuất sắc (&gt;= 3.5)</t>
+          <t>Ma mau grade GPA (/4) dat loai Gioi/Xuat sac (&gt;= 3.5)</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Xác minh điểm trung bình tích lũy học kỳ GPA lớn hơn hoặc bằng 3.5 hiển thị màu Xanh lá (Green).</t>
+          <t>Verify grade trung binh tich luy semester GPA lon hon hoac bang 3.5 display mau Xanh la (Green).</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Học kỳ hiện tại học sinh đạt điểm trung bình GPA là 3.5 hoặc 3.8.</t>
+          <t>Hoc sinh da log in. Semester hien tai student dat grade trung binh GPA la 3.5 hoac 3.8.</t>
         </is>
       </c>
       <c r="H13" s="28" t="inlineStr">
@@ -3820,13 +3820,13 @@
       </c>
       <c r="I13" s="28" t="inlineStr">
         <is>
-          <t>1. Quan sát vùng hiển thị điểm trung bình GPA học kỳ hiện tại trên giao diện.
-2. Kiểm tra màu sắc hiển thị của điểm GPA.</t>
+          <t>1. Observe vung display grade trung binh GPA semester hien tai tren interface.
+2. Verify mau sac display cua grade GPA.</t>
         </is>
       </c>
       <c r="J13" s="28" t="inlineStr">
         <is>
-          <t>Điểm số GPA "3.5" và "3.8" hiển thị với màu xanh lá cây (Green).</t>
+          <t>Diem so GPA "3.5" va "3.8" display voi mau xanh la cay (Green).</t>
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="N13" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -3869,17 +3869,17 @@
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>Mã màu điểm GPA (/4) đạt loại Trung bình/Khá (2.0 – 3.4)</t>
+          <t>Ma mau grade GPA (/4) dat loai Trung binh/Kha (2.0 – 3.4)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Xác minh điểm trung bình tích lũy học kỳ GPA từ 2.0 đến 3.4 hiển thị màu Cam (Orange).</t>
+          <t>Verify grade trung binh tich luy semester GPA tu 2.0 den 3.4 display mau Cam (Orange).</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Học kỳ hiện tại học sinh đạt GPA là 2.0 hoặc 3.1.</t>
+          <t>Hoc sinh da log in. Semester hien tai student dat GPA la 2.0 hoac 3.1.</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -3889,13 +3889,13 @@
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>1. Quan sát khu vực hiển thị điểm trung bình GPA trên màn hình.
-2. Kiểm tra màu sắc hiển thị của điểm GPA.</t>
+          <t>1. Observe khu vuc display grade trung binh GPA tren man hinh.
+2. Verify mau sac display cua grade GPA.</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>Điểm GPA "2.0" và "3.1" hiển thị với màu cam (Orange).</t>
+          <t>Diem GPA "2.0" va "3.1" display voi mau cam (Orange).</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -3938,17 +3938,17 @@
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Mã màu điểm GPA (/4) loại Yếu (&lt; 2.0)</t>
+          <t>Ma mau grade GPA (/4) loai Yeu (&lt; 2.0)</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Xác minh điểm trung bình tích lũy học kỳ GPA nhỏ hơn 2.0 hiển thị màu Đỏ (Red).</t>
+          <t>Verify grade trung binh tich luy semester GPA nho hon 2.0 display mau Do (Red).</t>
         </is>
       </c>
       <c r="G15" s="28" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Học kỳ hiện tại học sinh đạt GPA là 1.9 hoặc 1.2.</t>
+          <t>Hoc sinh da log in. Semester hien tai student dat GPA la 1.9 hoac 1.2.</t>
         </is>
       </c>
       <c r="H15" s="28" t="inlineStr">
@@ -3958,13 +3958,13 @@
       </c>
       <c r="I15" s="28" t="inlineStr">
         <is>
-          <t>1. Quan sát khu vực hiển thị điểm trung bình GPA trên màn hình.
-2. Kiểm tra màu sắc hiển thị của điểm GPA.</t>
+          <t>1. Observe khu vuc display grade trung binh GPA tren man hinh.
+2. Verify mau sac display cua grade GPA.</t>
         </is>
       </c>
       <c r="J15" s="28" t="inlineStr">
         <is>
-          <t>Điểm GPA "1.9" và "1.2" hiển thị với màu đỏ (Red).</t>
+          <t>Diem GPA "1.9" va "1.2" display voi mau do (Red).</t>
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="N15" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -4007,17 +4007,17 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>Hiển thị nhãn Học lại (Re-study) cho môn học bị đánh dấu học lại</t>
+          <t>Hien thi nhan Hoc lai (Re-study) cho course bi danh dau hoc lai</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Xác minh môn học bị đánh dấu học lại trên hệ thống (Re-study = True) sẽ hiển thị nhãn cảnh báo màu đỏ.</t>
+          <t>Verify course bi danh dau hoc lai tren system (Re-study = True) se display nhan cphoto bao mau do.</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Môn Database Management của học sinh này bị đánh dấu Re-study = True trên Sheets database. Môn Java Basics có Re-study = False.</t>
+          <t>Hoc sinh da log in. Mon Database Management cua student nay bi danh dau Re-study = True tren Sheets database. Mon Java Basics co Re-study = False.</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>1. Truy cập bảng điểm học kỳ chứa môn Database Management và Java Basics.
-2. Kiểm tra cột "Re-study" hoặc phần nhãn bên cạnh tên mỗi môn học.</t>
+          <t>1. Truy cap transcript semester chua mon Database Management va Java Basics.
+2. Verify cot "Re-study" hoac phan nhan ben canh ten moi course.</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>Môn Database Management hiển thị một nhãn hoặc huy hiệu "Re-study" màu đỏ nổi bật.
-Môn Java Basics không hiển thị bất kỳ nhãn cảnh báo học lại nào.</t>
+          <t>Mon Database Management display mot nhan hoac huy hieu "Re-study" mau do noi bat.
+Mon Java Basics not displayed bat ky nhan cphoto bao hoc lai nao.</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="N16" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F05, Rule 7.7</t>
+          <t>Related to M09-F05, Rule 7.7</t>
         </is>
       </c>
     </row>
@@ -4077,17 +4077,17 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Hiển thị shortcut Báo cáo thực tập khi nhóm thực tập đang hoạt động (On-going)</t>
+          <t>Hien thi shortcut Bao cao internship khi internship group dang hoat dong (On-going)</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>Xác minh shortcut dẫn đến Báo cáo thực tập hiển thị khi học sinh thuộc nhóm thực tập ở trạng thái On-going.</t>
+          <t>Verify shortcut dan den Bao cao internship display khi student thuoc internship group o status On-going.</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
-          <t>Học sinh PNV26001 được phân bổ vào nhóm thực tập "Internship Group 2026". Trạng thái của nhóm thực tập này trong Sheet là "On-going".</t>
+          <t>Hoc sinh PNV26001 duoc phan bo vao internship group "Internship Group 2026". Status cua internship group nay trong Sheet la "On-going".</t>
         </is>
       </c>
       <c r="H17" s="28" t="inlineStr">
@@ -4097,15 +4097,15 @@
       </c>
       <c r="I17" s="28" t="inlineStr">
         <is>
-          <t>1. Đăng nhập tài khoản học sinh PNV26001.
-2. Quan sát giao diện Student Portal (khu vực thanh điều hướng hoặc bảng điều khiển).
-3. Xác minh sự xuất hiện của shortcut/nút "Bi-Weekly Internship Reports" (Báo cáo thực tập định kỳ).</t>
+          <t>1. Log in account student PNV26001.
+2. Observe interface Student Portal (khu vuc thanh dieu huong hoac bang dieu khien).
+3. Verify su xuat hien cua shortcut/nut "Bi-Weekly Internship Reports" (Bao cao internship dinh ky).</t>
         </is>
       </c>
       <c r="J17" s="28" t="inlineStr">
         <is>
-          <t>Shortcut "Bi-Weekly Internship Reports" xuất hiện rõ ràng trên giao diện.
-Học sinh có thể nhấp vào để mở giao diện báo cáo thực tập.</t>
+          <t>Shortcut "Bi-Weekly Internship Reports" xuat hien ro rang tren interface.
+Hoc sinh can click vao de mo interface internship report.</t>
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N17" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F06, Rule 7.8</t>
+          <t>Related to M09-F06, Rule 7.8</t>
         </is>
       </c>
     </row>
@@ -4148,17 +4148,17 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>Ẩn shortcut Báo cáo thực tập khi nhóm thực tập ở trạng thái khác On-going</t>
+          <t>An shortcut Bao cao internship khi internship group o status khac On-going</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Xác minh shortcut dẫn đến Báo cáo thực tập bị ẩn khi nhóm thực tập của học sinh ở trạng thái Planned hoặc Completed.</t>
+          <t>Verify shortcut dan den Bao cao internship bi an khi internship group cua student o status Planned hoac Completed.</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>Học sinh PNV26002 thuộc nhóm thực tập "Internship Group 2025" đã hoàn thành (trạng thái "Completed" trên hệ thống).</t>
+          <t>Hoc sinh PNV26002 thuoc internship group "Internship Group 2025" da hoan thanh (status "Completed" tren system).</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -4168,15 +4168,15 @@
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>1. Đăng nhập tài khoản học sinh PNV26002.
-2. Quan sát giao diện Student Portal.
-3. Kiểm tra sự xuất hiện của nút/shortcut "Bi-Weekly Internship Reports".</t>
+          <t>1. Log in account student PNV26002.
+2. Observe interface Student Portal.
+3. Verify su xuat hien cua nut/shortcut "Bi-Weekly Internship Reports".</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Shortcut/nút liên kết đến Báo cáo thực tập hoàn toàn ẩn khỏi giao diện.
-Học sinh không thể nhìn thấy hay nhấp vào nút này.</t>
+          <t>Shortcut/nut lien ket den Bao cao internship hoan toan an khoi interface.
+Hoc sinh cannot nhin thay hay click button nay.</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F06, Rule 7.8</t>
+          <t>Related to M09-F06, Rule 7.8</t>
         </is>
       </c>
     </row>
@@ -4219,17 +4219,17 @@
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>Ẩn shortcut Báo cáo thực tập khi học sinh chưa được phân bổ thực tập</t>
+          <t>An shortcut Bao cao internship khi student chua duoc phan bo internship</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Xác minh shortcut Báo cáo thực tập bị ẩn khi học sinh không thuộc bất kỳ nhóm thực tập nào.</t>
+          <t>Verify shortcut Bao cao internship bi an khi student khong thuoc bat ky internship group nao.</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
         <is>
-          <t>Học sinh PNV26003 chưa được gán vào bất kỳ nhóm thực tập nào trên Sheets cơ sở dữ liệu.</t>
+          <t>Hoc sinh PNV26003 chua duoc gan vao bat ky internship group nao tren Sheets co so du lieu.</t>
         </is>
       </c>
       <c r="H19" s="28" t="inlineStr">
@@ -4239,14 +4239,14 @@
       </c>
       <c r="I19" s="28" t="inlineStr">
         <is>
-          <t>1. Đăng nhập tài khoản học sinh PNV26003.
-2. Quan sát giao diện Student Portal.
-3. Kiểm tra sự xuất hiện của nút/shortcut "Bi-Weekly Internship Reports".</t>
+          <t>1. Log in account student PNV26003.
+2. Observe interface Student Portal.
+3. Verify su xuat hien cua nut/shortcut "Bi-Weekly Internship Reports".</t>
         </is>
       </c>
       <c r="J19" s="28" t="inlineStr">
         <is>
-          <t>Shortcut/nút liên kết đến Báo cáo thực tập ẩn hoàn toàn, không hiển thị trên giao diện của học sinh.</t>
+          <t>Shortcut/nut lien ket den Bao cao internship an hoan toan, not displayed tren interface cua student.</t>
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="N19" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F06, Rule 7.8</t>
+          <t>Related to M09-F06, Rule 7.8</t>
         </is>
       </c>
     </row>
@@ -4289,17 +4289,17 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Xác minh cách ly dữ liệu giữa các học sinh (Data Isolation)</t>
+          <t>Verify cach ly du lieu giua cac student (Data Isolation)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Xác minh cơ chế bảo mật phía server đảm bảo học sinh chỉ xem được điểm của chính mình và bị từ chối truy cập dữ liệu của học sinh khác.</t>
+          <t>Verify co che bao mat phia server dam bao student chi xem duoc grade cua chinh minh va bi denies access du lieu cua student khac.</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Học sinh PNV26001 và học sinh PNV26002 đều tồn tại trong hệ thống. Đã đăng nhập bằng tài khoản học sinh PNV26001.</t>
+          <t>Hoc sinh PNV26001 va student PNV26002 deu exist in system. Da log in bang account student PNV26001.</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản student01@student.passerellesnumeriques.org.
-2. Tại giao diện bảng điểm, thử thay đổi tham số trên URL (ví dụ từ `?studentCode=PNV26001` thành `?studentCode=PNV26002`) hoặc dùng DevTools sửa mã request gửi về API backend để yêu cầu dữ liệu điểm của học sinh PNV26002.
-3. Quan sát kết quả hiển thị và phản hồi từ hệ thống.</t>
+          <t>1. Log in bang account student01@student.passerellesnumeriques.org.
+2. Tai interface transcript, thu thay doi tham so tren URL (e.g. tu `?studentCode=PNV26001` thanh `?studentCode=PNV26002`) hoac dung DevTools sua ma request gui ve API backend de requires du lieu grade cua student PNV26002.
+3. Observe ket qua display va phan hoi tu system.</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối yêu cầu truy cập dữ liệu điểm của học sinh B.
-Màn hình không hiển thị điểm của học sinh B.
-Backend trả về thông báo lỗi phân quyền (ví dụ: "Unauthorized access" hoặc Access Denied).
-Bảng điểm hiển thị trên giao diện vẫn giữ nguyên của học sinh PNV26001 (hoặc hiển thị trang thông báo lỗi bảo mật).</t>
+          <t>System denies requires access du lieu grade cua student B.
+Man hinh not displayed grade cua student B.
+Backend tra ve notification error phan quyen (e.g.: "Unauthorized access" hoac Access Denied).
+Bang grade display tren interface van giu nguyen cua student PNV26001 (hoac display trang notification error bao mat).</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="N20" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F07, Rule 7.9, Error Handling (Mục 9)</t>
+          <t>Related to M09-F07, Rule 7.9, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -4362,17 +4362,17 @@
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Chặn gọi API lấy điểm từ bên ngoài khi chưa xác thực</t>
+          <t>Chan goi API lay grade tu ben external khi chua xac thuc</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>Xác minh các yêu cầu gọi API lấy điểm của học sinh gửi trực tiếp từ bên ngoài mà chưa qua đăng nhập Google OAuth đều bị từ chối.</t>
+          <t>Verify cac requires goi API lay grade cua student gui truc tiep tu ben external ma chua qua log in Google OAuth deu bi denies.</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập tài khoản. Trình duyệt ở chế độ ẩn danh hoặc sử dụng công cụ kiểm thử API (như Postman).</t>
+          <t>Nguoi dung chua log in account. Trinh duyet o che do an danh hoac su dung cong cu kiem thu API (nhu Postman).</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
@@ -4382,16 +4382,16 @@
       </c>
       <c r="I21" s="28" t="inlineStr">
         <is>
-          <t>1. Mở cửa sổ ẩn danh hoặc công cụ kiểm thử API.
-2. Gửi request trực tiếp (HTTP GET/POST) đến URL API của hệ thống để lấy dữ liệu điểm của học sinh PNV26001.
-3. Quan sát phản hồi trả về từ hệ thống.</t>
+          <t>1. Mo cua so an danh hoac cong cu kiem thu API.
+2. Gui request truc tiep (HTTP GET/POST) den URL API cua system de lay du lieu grade cua student PNV26001.
+3. Observe phan hoi tra ve tu system.</t>
         </is>
       </c>
       <c r="J21" s="28" t="inlineStr">
         <is>
-          <t>Yêu cầu bị từ chối.
-Hệ thống phản hồi mã lỗi 401 Unauthorized (hoặc tương đương) hoặc chuyển hướng request về giao diện đăng nhập Google OAuth.
-Không có dữ liệu điểm nào được trả về.</t>
+          <t>Yeu cau bi denies.
+System phan hoi ma error 401 Unauthorized (hoac tuong duong) hoac redirect request ve interface log in Google OAuth.
+Khong co du lieu grade nao duoc tra ve.</t>
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="N21" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F07, Rule 7.9</t>
+          <t>Related to M09-F07, Rule 7.9</t>
         </is>
       </c>
     </row>
@@ -4434,17 +4434,17 @@
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hiển thị giao diện trên thiết bị di động (Responsive UI)</t>
+          <t>Verify display interface tren thiet bi di dong (Responsive UI)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>Xác minh giao diện Student Portal hiển thị tốt trên các thiết bị di động mà không bị vỡ khung hoặc mất thông tin điểm số.</t>
+          <t>Verify interface Student Portal display tot tren cac thiet bi di dong ma khong bi vo khung hoac mat thong tin grades.</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công.</t>
+          <t>Hoc sinh da log in successfully.</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -4454,17 +4454,17 @@
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>1. Đăng nhập Student Portal.
-2. Mở DevTools (F12) và kích hoạt chế độ Responsive Viewport giả lập màn hình iPhone X (375x812 px).
-3. Quan sát bộ chọn học kỳ, các danh mục và bảng điểm.
-4. Thao tác vuốt cuộn ngang bảng điểm để xem đầy đủ các cột điểm (KT TX, ĐK1-ĐK6, TCK, TLCK...).</t>
+          <t>1. Log in Student Portal.
+2. Mo DevTools (F12) va kich hoat che do Responsive Viewport gia lap man hinh iPhone X (375x812 px).
+3. Observe bo select semester, cac category va transcript.
+4. Thao tac vuot cuon ngang transcript de xem day du cac cot grade (KT TX, DK1-DK6, TCK, TLCK...).</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Giao diện tự động co giãn tương thích.
-Các tiêu đề danh mục và chữ hiển thị rõ ràng, không đè lên nhau.
-Bảng điểm hiển thị thanh cuộn ngang mượt mà cho phép xem hết các cột điểm mà không phá vỡ bố cục tổng thể của trang.</t>
+          <t>Interface tu dong co gian tuong thich.
+Cac tieu de category va chu display ro rang, khong de len nhau.
+Bang grade display thanh cuon ngang muot ma allows xem het cac cot grade ma khong pha vo bo cuc tong the cua trang.</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="N22" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Testing Environment (Mục 9)</t>
+          <t>Related to Testing Environment (Section 9)</t>
         </is>
       </c>
     </row>
@@ -4507,17 +4507,17 @@
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hành vi khi hết hạn phiên làm việc Google (Google Sign-Out)</t>
+          <t>Verify hanh vi khi het han phien lam viec Google (Google Sign-Out)</t>
         </is>
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống phát hiện phiên đăng nhập Google đã kết thúc và ngăn học sinh tiếp tục truy cập dữ liệu.</t>
+          <t>Dam bao system phat hien phien log in Google da ket thuc va ngan student tiep tuc access du lieu.</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
         <is>
-          <t>Học sinh đang đăng nhập và mở tab Student Portal.</t>
+          <t>Hoc sinh dang log in va mo tab Student Portal.</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
@@ -4527,17 +4527,17 @@
       </c>
       <c r="I23" s="28" t="inlineStr">
         <is>
-          <t>1. Mở một tab trình duyệt khác, truy cập accounts.google.com và đăng xuất tài khoản Google hiện tại.
-2. Quay lại tab Student Portal.
-3. Thực hiện chuyển đổi học kỳ trên bộ chọn Semester Selector hoặc nhấn F5 để tải lại trang.
-4. Quan sát phản hồi của hệ thống.</t>
+          <t>1. Mo mot tab trinh duyet khac, access accounts.google.com va dang xuat account Google hien tai.
+2. Quay lai tab Student Portal.
+3. Thuc hien switching semester tren bo select Semester Selector hoac click F5 de tai lai trang.
+4. Observe phan hoi cua system.</t>
         </is>
       </c>
       <c r="J23" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống phát hiện phiên làm việc đã kết thúc.
-Các thao tác yêu cầu dữ liệu học kỳ mới bị dừng lại.
-Người dùng được chuyển hướng về trang đăng nhập Google OAuth hoặc hiển thị thông điệp yêu cầu đăng nhập lại để tiếp tục.</t>
+          <t>System phat hien phien lam viec da ket thuc.
+Cac thao tac requires du lieu semester moi bi dung lai.
+Nguoi dung duoc redirect ve trang log in Google OAuth hoac display thong diep requires log in lai de tiep tuc.</t>
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="N23" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 7.1</t>
+          <t>Related to Rule 7.1</t>
         </is>
       </c>
     </row>
@@ -4580,17 +4580,17 @@
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra xác thực tham số học kỳ không hợp lệ (Semester Validation)</t>
+          <t>Verify xac thuc tham so semester khong hop le (Semester Validation)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không bị lỗi crash và tự động xử lý an toàn khi tham số học kỳ được truyền vào không hợp lệ hoặc không tồn tại.</t>
+          <t>Verify system khong bi error crash va tu dong xu ly an toan khi tham so semester duoc truyen vao khong hop le hoac khong ton tai.</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công.</t>
+          <t>Hoc sinh da log in successfully.</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -4600,15 +4600,15 @@
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>1. Cố ý thay đổi tham số học kỳ trên đường dẫn URL thành giá trị không hợp lệ (ví dụ: `?semester=7` or `?semester=abc`).
-2. Tải lại trang hoặc cố tình gửi request với tham số không hợp lệ đó.
-3. Quan sát phản hồi của giao diện.</t>
+          <t>1. Co y thay doi tham so semester tren duong dan URL thanh gia tri khong hop le (e.g.: `?semester=7` or `?semester=abc`).
+2. Tai lai trang hoac co tinh gui request voi tham so khong hop le do.
+3. Observe phan hoi cua interface.</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống không bị lỗi crash/trắng trang.
-Tự động quay về hiển thị dữ liệu của học kỳ mặc định (ví dụ: Học kỳ 1 hoặc học kỳ hiện tại hoạt động gần nhất), hoặc hiển thị thông báo lỗi "Học kỳ không hợp lệ".</t>
+          <t>System khong bi error crash/trang trang.
+Tu dong quay ve display du lieu cua semester mac dinh (e.g.: Semester 1 hoac semester hien tai hoat dong gan nhat), hoac display notification error "Semester khong hop le".</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="N24" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8 - Semester)</t>
+          <t>Related to Validation Rules (Section 8 - Semester)</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống lưu thành công toàn bộ dữ liệu nhận xét cùng một lúc. Hiển thị thông báo lưu thành công (ví dụ: "Saved 2 students"). Dữ liệu hiển thị chính xác trong danh sách.</t>
+          <t>System save successfully toan bo du lieu nhan xet cung mot luc. Hien thi notification save successfully (e.g.: "Saved 2 students"). Du lieu display chinh xac trong danh sach.</t>
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
@@ -15960,7 +15960,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="165" customHeight="1">
+    <row r="2" ht="180" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
           <t>TC-M05-001</t>
@@ -15983,41 +15983,41 @@
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>Tạo nhóm thực tập mới với thông tin hợp lệ</t>
+          <t>Create new internship group voi thong tin hop le</t>
         </is>
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tạo nhóm thực tập mới khi nhập đầy đủ các thông tin bắt buộc và hợp lệ.</t>
+          <t>Verify functionality for create new internship group khi enter day du cac thong tin bat buoc va hop le.</t>
         </is>
       </c>
       <c r="G2" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Thực tập.
-Các lớp học "PNV26A" và "PNV26B" đã tồn tại trong hệ thống và chưa được gán vào bất kỳ nhóm thực tập nào trong cùng năm học.</t>
+          <t>User is logged in as Staff.
+Currently on Internship Management interface.
+Cac lop hoc "PNV26A" va "PNV26B" da exist in system va chua duoc gan vao bat ky internship group nao trong cung nam hoc.</t>
         </is>
       </c>
       <c r="H2" s="23" t="inlineStr">
         <is>
-          <t>GroupName="Nhóm Thực tập 2026 - Năm 2"; InternshipYear="Second Year"; Batches="PNV26A", "PNV26B"; StartDate="2026-08-01"</t>
+          <t>GroupName="Nhom Thuc tap 2026 - Nam 2"; InternshipYear="Second Year"; Batches="PNV26A", "PNV26B"; StartDate="2026-08-01"</t>
         </is>
       </c>
       <c r="I2" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấn nút "Tạo nhóm thực tập mới".
-2. Nhập Tên nhóm là "Nhóm Thực tập 2026 - Năm 2".
-3. Chọn Năm thực tập là "Second Year".
-4. Tích chọn các lớp học "PNV26A" và "PNV26B".
-5. Chọn Ngày bắt đầu là "2026-08-01".
-6. Nhấn nút "Lưu".</t>
+          <t>1. Nhan nut "Create new internship group".
+2. Enter Ten group la "Nhom Thuc tap 2026 - Nam 2".
+3. Select Nam internship la "Second Year".
+4. Tich select cac lop hoc "PNV26A" va "PNV26B".
+5. Select Start Date la "2026-08-01".
+6. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J2" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tạo nhóm thành công.
-Nhóm thực tập mới xuất hiện trong danh sách hiển thị với trạng thái là "On-going".
-Các lớp học đã chọn được liên kết chính xác với nhóm này.</t>
+          <t>System display notification create group successfully.
+Nhom internship moi xuat hien trong danh sach display voi status la "On-going".
+Cac lop hoc da select duoc lien ket chinh xac voi group nay.</t>
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
@@ -16033,11 +16033,11 @@
       </c>
       <c r="N2" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F01, Rule 6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+          <t>Related to M05-F01, Rule 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="135" customHeight="1">
       <c r="A3" s="26" t="inlineStr">
         <is>
           <t>TC-M05-002</t>
@@ -16060,19 +16060,19 @@
       </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
-          <t>Tạo nhóm thực tập thất bại do để trống tên nhóm</t>
+          <t>Internship group creation fails due to empty group name</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn tạo nhóm thực tập nếu để trống tên nhóm.</t>
+          <t>Verify system bao error va ngan chan create internship group neu blank ten group.</t>
         </is>
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Tạo nhóm thực tập mới.
-Lớp học "PNV26A" chưa được gán cho nhóm thực tập nào trong năm học.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Internship Group interface.
+Lop hoc "PNV26A" chua duoc gan cho internship group nao trong nam hoc.</t>
         </is>
       </c>
       <c r="H3" s="28" t="inlineStr">
@@ -16082,17 +16082,17 @@
       </c>
       <c r="I3" s="28" t="inlineStr">
         <is>
-          <t>1. Để trống trường Tên nhóm.
-2. Chọn Năm thực tập là "Second Year".
-3. Tích chọn lớp học "PNV26A".
-4. Chọn Ngày bắt đầu là "2026-08-01".
-5. Nhấn nút "Lưu".</t>
+          <t>1. De trong truong Ten group.
+2. Select Nam internship la "Second Year".
+3. Tich select lop hoc "PNV26A".
+4. Select Start Date la "2026-08-01".
+5. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J3" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu nhập Tên nhóm (ví dụ: "Group Name is required.").
-Nhóm thực tập mới không được lưu vào hệ thống.</t>
+          <t>System display notification error requires enter Ten group (e.g.: "Group Name is required.").
+Nhom internship moi khong duoc save vao system.</t>
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="N3" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -16135,38 +16135,38 @@
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>Tạo nhóm thực tập thất bại do không tích chọn lớp học</t>
+          <t>Create internship group failed do khong tich select lop hoc</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn tạo nhóm thực tập nếu không chọn bất kỳ lớp học nào.</t>
+          <t>Verify system bao error va ngan chan create internship group neu khong select bat ky lop hoc nao.</t>
         </is>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Tạo nhóm thực tập mới.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Internship Group interface.</t>
         </is>
       </c>
       <c r="H4" s="23" t="inlineStr">
         <is>
-          <t>GroupName="Nhóm Thực tập 2026"; InternshipYear="Second Year"; Batches=None; StartDate="2026-08-01"</t>
+          <t>GroupName="Nhom Thuc tap 2026"; InternshipYear="Second Year"; Batches=None; StartDate="2026-08-01"</t>
         </is>
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>1. Nhập Tên nhóm là "Nhóm Thực tập 2026".
-2. Chọn Năm thực tập là "Second Year".
-3. Không chọn bất kỳ lớp học nào trong danh sách.
-4. Chọn Ngày bắt đầu là "2026-08-01".
-5. Nhấn nút "Lưu".</t>
+          <t>1. Enter Ten group la "Nhom Thuc tap 2026".
+2. Select Nam internship la "Second Year".
+3. Khong select bat ky lop hoc nao trong danh sach.
+4. Select Start Date la "2026-08-01".
+5. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu chọn ít nhất một lớp học (ví dụ: "At least one batch is required.").
-Nhóm thực tập mới không được lưu vào hệ thống.</t>
+          <t>System display notification error requires select it nhat mot lop hoc (e.g.: "At least one batch is required.").
+Nhom internship moi khong duoc save vao system.</t>
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="N4" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -16209,38 +16209,38 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Tạo nhóm thực tập thất bại do để trống ngày bắt đầu</t>
+          <t>Create internship group failed do blank start date</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn tạo nhóm thực tập nếu để trống ngày bắt đầu.</t>
+          <t>Verify system bao error va ngan chan create internship group neu blank start date.</t>
         </is>
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Tạo nhóm thực tập mới.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Internship Group interface.</t>
         </is>
       </c>
       <c r="H5" s="28" t="inlineStr">
         <is>
-          <t>GroupName="Nhóm Thực tập 2026"; InternshipYear="Second Year"; Batches="PNV26A"; StartDate=""</t>
+          <t>GroupName="Nhom Thuc tap 2026"; InternshipYear="Second Year"; Batches="PNV26A"; StartDate=""</t>
         </is>
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>1. Nhập Tên nhóm là "Nhóm Thực tập 2026".
-2. Chọn Năm thực tập là "Second Year".
-3. Tích chọn lớp học "PNV26A".
-4. Để trống trường Ngày bắt đầu.
-5. Nhấn nút "Lưu".</t>
+          <t>1. Enter Ten group la "Nhom Thuc tap 2026".
+2. Select Nam internship la "Second Year".
+3. Tich select lop hoc "PNV26A".
+4. De trong truong Start Date.
+5. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J5" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu chọn Ngày bắt đầu (ví dụ: "Start Date is required.").
-Nhóm thực tập mới không được lưu vào hệ thống.</t>
+          <t>System display notification error requires select Start Date (e.g.: "Start Date is required.").
+Nhom internship moi khong duoc save vao system.</t>
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="N5" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -16283,38 +16283,38 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Tạo nhóm thực tập thất bại do để trống năm thực tập</t>
+          <t>Create internship group failed do blank nam internship</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn tạo nhóm thực tập nếu năm thực tập không được chọn.</t>
+          <t>Verify system bao error va ngan chan create internship group neu nam internship khong duoc select.</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Tạo nhóm thực tập mới.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Internship Group interface.</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>GroupName="Nhóm Thực tập 2026"; InternshipYear=""; Batches="PNV26A"; StartDate="2026-08-01"</t>
+          <t>GroupName="Nhom Thuc tap 2026"; InternshipYear=""; Batches="PNV26A"; StartDate="2026-08-01"</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>1. Nhập Tên nhóm là "Nhóm Thực tập 2026".
-2. Không chọn Năm thực tập (để trống).
-3. Tích chọn lớp học "PNV26A".
-4. Chọn Ngày bắt đầu là "2026-08-01".
-5. Nhấn nút "Lưu".</t>
+          <t>1. Enter Ten group la "Nhom Thuc tap 2026".
+2. Khong select Nam internship (blank).
+3. Tich select lop hoc "PNV26A".
+4. Select Start Date la "2026-08-01".
+5. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu chọn Năm thực tập (ví dụ: "Internship Year is required.").
-Nhóm thực tập mới không được lưu vào hệ thống.</t>
+          <t>System display notification error requires select Nam internship (e.g.: "Internship Year is required.").
+Nhom internship moi khong duoc save vao system.</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
@@ -16330,11 +16330,11 @@
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
+          <t>Related to Validation Rules (Section 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="165" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
           <t>TC-M05-006</t>
@@ -16357,39 +16357,39 @@
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>Tạo nhóm thực tập thất bại do chọn lớp học đã được gán vào nhóm thực tập khác trong cùng năm học</t>
+          <t>Create internship group failed do select lop hoc da duoc gan vao internship group khac trong cung nam hoc</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống từ chối tạo nhóm thực tập mới chứa lớp học đã được gán cho nhóm thực tập khác trong cùng năm học.</t>
+          <t>Verify system denies create new internship group chua lop hoc da duoc gan cho internship group khac trong cung nam hoc.</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đã tồn tại nhóm thực tập "Nhóm A" cho năm học "Second Year" chứa lớp "PNV26A".</t>
+          <t>User is logged in as Staff.
+Da ton tai internship group "Nhom A" cho nam hoc "Second Year" chua lop "PNV26A".</t>
         </is>
       </c>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>GroupName="Nhóm B"; InternshipYear="Second Year"; Batches="PNV26A"; StartDate="2026-08-01"</t>
+          <t>GroupName="Nhom B"; InternshipYear="Second Year"; Batches="PNV26A"; StartDate="2026-08-01"</t>
         </is>
       </c>
       <c r="I7" s="28" t="inlineStr">
         <is>
-          <t>1. Nhấn nút "Tạo nhóm thực tập mới".
-2. Nhập Tên nhóm là "Nhóm B".
-3. Chọn Năm thực tập là "Second Year".
-4. Chọn lớp học là "PNV26A".
-5. Chọn Ngày bắt đầu là "2026-08-01".
-6. Nhấn nút "Lưu".</t>
+          <t>1. Nhan nut "Create new internship group".
+2. Enter Ten group la "Nhom B".
+3. Select Nam internship la "Second Year".
+4. Select lop hoc la "PNV26A".
+5. Select Start Date la "2026-08-01".
+6. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối lưu và hiển thị thông báo lỗi (ví dụ: lớp PNV26A đã được gán cho một nhóm thực tập khác trong năm học này - "Batch already assigned").
-Nhóm thực tập "Nhóm B" không được tạo.</t>
+          <t>System denies save va display notification error (e.g.: lop PNV26A da duoc gan cho mot internship group khac trong nam hoc nay - "Batch already assigned").
+Nhom internship "Nhom B" khong duoc create.</t>
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
@@ -16405,11 +16405,11 @@
       </c>
       <c r="N7" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Batch Assignment Rule (Rule 6.2), Error Handling (Mục 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="150" customHeight="1">
+          <t>Related to Batch Assignment Rule (Rule 6.2), Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="165" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
         <is>
           <t>TC-M05-007</t>
@@ -16432,39 +16432,39 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Tạo nhóm thực tập thành công khi gán cùng lớp học vào nhóm thực tập ở các năm học khác nhau</t>
+          <t>Create internship group successfully khi gan cung lop hoc vao internship group o cac nam hoc khac nhau</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống cho phép gán cùng một lớp học vào nhóm thực tập ở các năm khác nhau (ví dụ: năm 2 và năm 3).</t>
+          <t>Verify system allows gan cung mot lop hoc vao internship group o cac nam khac nhau (e.g.: nam 2 va nam 3).</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Lớp "PNV26A" đã được gán vào nhóm thực tập "Nhóm Năm 2" thuộc năm thực tập "Second Year".</t>
+          <t>User is logged in as Staff.
+Lop "PNV26A" da duoc gan vao internship group "Nhom Nam 2" thuoc nam internship "Second Year".</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>GroupName="Nhóm Năm 3"; InternshipYear="Third Year"; Batches="PNV26A"; StartDate="2027-08-01"</t>
+          <t>GroupName="Nhom Nam 3"; InternshipYear="Third Year"; Batches="PNV26A"; StartDate="2027-08-01"</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấn nút "Tạo nhóm thực tập mới".
-2. Nhập Tên nhóm là "Nhóm Năm 3".
-3. Chọn Năm thực tập là "Third Year".
-4. Chọn lớp học là "PNV26A".
-5. Chọn Ngày bắt đầu là "2027-08-01".
-6. Nhấn nút "Lưu".</t>
+          <t>1. Nhan nut "Create new internship group".
+2. Enter Ten group la "Nhom Nam 3".
+3. Select Nam internship la "Third Year".
+4. Select lop hoc la "PNV26A".
+5. Select Start Date la "2027-08-01".
+6. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống lưu thành công nhóm thực tập mới.
-Lớp PNV26A được gán vào nhóm "Nhóm Năm 3" mà không có lỗi.</t>
+          <t>System save successfully new internship group.
+Lop PNV26A duoc gan vao group "Nhom Nam 3" ma khong co error.</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Batch Assignment Rule (Rule 6.2)</t>
+          <t>Related to Batch Assignment Rule (Rule 6.2)</t>
         </is>
       </c>
     </row>
@@ -16507,37 +16507,37 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>Lưu trữ nhóm thực tập đang hoạt động</t>
+          <t>Archive internship group dang hoat dong</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng Lưu trữ (Archive) một nhóm thực tập đang ở trạng thái On-going.</t>
+          <t>Verify functionality for Archive (Archive) mot internship group dang o status On-going.</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đã tồn tại nhóm thực tập "Nhóm Thực tập 2026" ở trạng thái On-going.</t>
+          <t>User is logged in as Staff.
+Da ton tai internship group "Nhom Thuc tap 2026" o status On-going.</t>
         </is>
       </c>
       <c r="H9" s="28" t="inlineStr">
         <is>
-          <t>GroupName="Nhóm Thực tập 2026"</t>
+          <t>GroupName="Nhom Thuc tap 2026"</t>
         </is>
       </c>
       <c r="I9" s="28" t="inlineStr">
         <is>
-          <t>1. Tìm nhóm thực tập "Nhóm Thực tập 2026" trên giao diện danh sách.
-2. Nhấn vào biểu tượng/nút "Lưu trữ" (Archive) của nhóm này.
-3. Xác nhận lưu trữ ở hộp thoại xác nhận.</t>
+          <t>1. Tim internship group "Nhom Thuc tap 2026" tren interface danh sach.
+2. Nhan vao bieu tuong/nut "Archive" (Archive) cua group nay.
+3. Xac nhan archive o hop thoai xac nhan.</t>
         </is>
       </c>
       <c r="J9" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu trữ thành công.
-Trạng thái của nhóm thực tập chuyển sang "Archived".
-Nhóm thực tập này bị ẩn khỏi danh sách hoạt động bình thường.</t>
+          <t>System display notification archive successfully.
+Status cua internship group chuyen sang "Archived".
+Nhom internship nay bi an khoi danh sach hoat dong binh thuong.</t>
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="N9" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F02, Rule 6.12</t>
+          <t>Related to M05-F02, Rule 6.12</t>
         </is>
       </c>
     </row>
@@ -16580,38 +16580,38 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Kích hoạt lại nhóm thực tập đã lưu trữ</t>
+          <t>Kich hoat lai internship group da archive</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng khôi phục/kích hoạt lại (Reactivate) một nhóm thực tập đã bị lưu trữ.</t>
+          <t>Verify functionality for khoi phuc/kich hoat lai (Reactivate) mot internship group da bi archive.</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đã có nhóm thực tập "Nhóm Thực tập 2026" ở trạng thái Archived.</t>
+          <t>User is logged in as Staff.
+Da co internship group "Nhom Thuc tap 2026" o status Archived.</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>GroupName="Nhóm Thực tập 2026"</t>
+          <t>GroupName="Nhom Thuc tap 2026"</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>1. Truy cập vào danh sách các nhóm thực tập đã lưu trữ (Archived Groups).
-2. Tìm nhóm "Nhóm Thực tập 2026".
-3. Nhấn vào nút "Khôi phục" hoặc "Kích hoạt lại" (Reactivate).
-4. Xác nhận ở hộp thoại.</t>
+          <t>1. Truy cap vao danh sach cac internship group da archive (Archived Groups).
+2. Tim group "Nhom Thuc tap 2026".
+3. Nhan vao nut "Khoi phuc" hoac "Kich hoat lai" (Reactivate).
+4. Xac nhan o hop thoai.</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo kích hoạt lại thành công.
-Trạng thái của nhóm chuyển từ "Archived" về "On-going".
-Nhóm thực tập xuất hiện trở lại trong danh sách nhóm đang hoạt động.</t>
+          <t>System display notification kich hoat lai successfully.
+Status cua group chuyen tu "Archived" ve "On-going".
+Nhom internship xuat hien tro lai trong danh sach group dang hoat dong.</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="N10" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F02, Rule 6.12</t>
+          <t>Related to M05-F02, Rule 6.12</t>
         </is>
       </c>
     </row>
@@ -16654,18 +16654,18 @@
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>Thêm công ty đối tác mới với tên hợp lệ</t>
+          <t>Add company doi tac moi with a valid name</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng thêm mới công ty đối tác với tên hợp lệ và chưa tồn tại.</t>
+          <t>Verify functionality for add moi company doi tac with a valid name va chua ton tai.</t>
         </is>
       </c>
       <c r="G11" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Công ty (Company Management).</t>
+          <t>User is logged in as Staff.
+Dang o interface Quan ly Cong ty (Company Management).</t>
         </is>
       </c>
       <c r="H11" s="28" t="inlineStr">
@@ -16675,15 +16675,15 @@
       </c>
       <c r="I11" s="28" t="inlineStr">
         <is>
-          <t>1. Nhấn nút "Thêm công ty mới".
-2. Nhập vào trường Tên công ty: "TechCorp".
-3. Nhấn nút "Lưu".</t>
+          <t>1. Nhan nut "Add company moi".
+2. Enter vao truong Ten company: "TechCorp".
+3. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo thêm công ty thành công.
-Công ty "TechCorp" xuất hiện trong danh sách các công ty đối tác.</t>
+          <t>System display notification add company successfully.
+Cong ty "TechCorp" xuat hien trong danh sach cac company doi tac.</t>
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="N11" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F03, Rule 6.3</t>
+          <t>Related to M05-F03, Rule 6.3</t>
         </is>
       </c>
     </row>
@@ -16726,18 +16726,18 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Thêm công ty thất bại do để trống tên công ty</t>
+          <t>Add company failed due to empty name company</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống hiển thị thông báo lỗi và ngăn chặn thêm công ty nếu để trống tên công ty.</t>
+          <t>Verify system display notification error va ngan chan add company neu blank ten company.</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Công ty.</t>
+          <t>User is logged in as Staff.
+Dang o interface Quan ly Cong ty.</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -16747,15 +16747,15 @@
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấn nút "Thêm công ty mới".
-2. Để trống trường Tên công ty.
-3. Nhấn nút "Lưu".</t>
+          <t>1. Nhan nut "Add company moi".
+2. De trong truong Ten company.
+3. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu nhập tên công ty (ví dụ: "Company Name is required.").
-Công ty mới không được thêm vào danh sách.</t>
+          <t>System display notification error requires enter ten company (e.g.: "Company Name is required.").
+Cong ty moi khong duoc add vao danh sach.</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
@@ -16771,11 +16771,11 @@
       </c>
       <c r="N12" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
           <t>TC-M05-012</t>
@@ -16798,19 +16798,19 @@
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>Thêm công ty thất bại do trùng tên (phân biệt hoa thường)</t>
+          <t>Add company failed do trung ten (phan biet hoa thuong)</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống từ chối và báo lỗi khi thêm công ty có tên viết hoa/thường trùng với công ty đã tồn tại.</t>
+          <t>Verify system denies va bao error khi add company co ten viet hoa/thuong trung voi company da ton tai.</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đã tồn tại công ty "TechCorp" trong hệ thống.
-Đang ở giao diện Quản lý Công ty.</t>
+          <t>User is logged in as Staff.
+Da ton tai company "TechCorp" trong system.
+Dang o interface Quan ly Cong ty.</t>
         </is>
       </c>
       <c r="H13" s="28" t="inlineStr">
@@ -16820,15 +16820,15 @@
       </c>
       <c r="I13" s="28" t="inlineStr">
         <is>
-          <t>1. Nhấn nút "Thêm công ty mới".
-2. Nhập vào trường Tên công ty: "techcorp" (viết thường hoàn toàn).
-3. Nhấn nút "Lưu".</t>
+          <t>1. Nhan nut "Add company moi".
+2. Enter vao truong Ten company: "techcorp" (viet thuong hoan toan).
+3. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J13" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối lưu và hiển thị thông báo lỗi trùng tên công ty (ví dụ: "Company name already exists.").
-Công ty trùng lặp không được tạo thêm.</t>
+          <t>System denies save va display notification error trung ten company (e.g.: "Company name already exists.").
+Cong ty trung lap khong duoc create add.</t>
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
@@ -16844,7 +16844,7 @@
       </c>
       <c r="N13" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F03, Rule 6.3, Error Handling (Mục 8)</t>
+          <t>Related to M05-F03, Rule 6.3, Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -16871,36 +16871,36 @@
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>Thêm công ty thất bại do trùng tên khi có khoảng trắng đầu/cuối</t>
+          <t>Add company failed do trung ten khi co khoang trang dau/cuoi</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống tự động loại bỏ khoảng trắng đầu/cuối và từ chối nếu tên công ty trùng lặp.</t>
+          <t>Verify system tu dong loai bo khoang trang dau/cuoi va denies neu ten company trung lap.</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đã tồn tại công ty "TechCorp" trong hệ thống.
-Đang ở giao diện Quản lý Công ty.</t>
+          <t>User is logged in as Staff.
+Da ton tai company "TechCorp" trong system.
+Dang o interface Quan ly Cong ty.</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>CompanyName="  TechCorp  "</t>
+          <t>CompanyName=" TechCorp "</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấn nút "Thêm công ty mới".
-2. Nhập vào trường Tên công ty: "  TechCorp  " (có khoảng trắng ở đầu và cuối).
-3. Nhấn nút "Lưu".</t>
+          <t>1. Nhan nut "Add company moi".
+2. Enter vao truong Ten company: " TechCorp " (co khoang trang o dau va cuoi).
+3. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống cắt bỏ các khoảng trắng đầu/cuối, phát hiện trùng lặp với "TechCorp", từ chối lưu và hiển thị thông báo lỗi trùng tên.</t>
+          <t>System cat bo cac khoang trang dau/cuoi, phat hien trung lap voi "TechCorp", denies save va display notification error trung ten.</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F03, Rule 6.3, Error Handling (Mục 8)</t>
+          <t>Related to M05-F03, Rule 6.3, Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -16943,40 +16943,40 @@
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Phân công thực tập cho học viên đơn lẻ</t>
+          <t>Phan cong internship cho student don le</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng phân công một học viên vào một công ty đối tác.</t>
+          <t>Verify functionality for phan cong mot student vao mot company doi tac.</t>
         </is>
       </c>
       <c r="G15" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện danh sách học viên của nhóm thực tập "Nhóm Thực tập 2026" (trạng thái On-going).
-Học viên "Nguyễn Văn A" đang ở trạng thái chưa được phân công (Unassigned).
-Công ty "TechCorp" đang ở trạng thái hoạt động (không bị ẩn).</t>
+          <t>User is logged in as Staff.
+Dang o interface danh sach student cua internship group "Nhom Thuc tap 2026" (status On-going).
+Hoc vien "Nguyen Van A" dang o status chua duoc phan cong (Unassigned).
+Cong ty "TechCorp" dang o status hoat dong (khong bi an).</t>
         </is>
       </c>
       <c r="H15" s="28" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; AssignedCompany="TechCorp"</t>
+          <t>StudentName="Nguyen Van A"; AssignedCompany="TechCorp"</t>
         </is>
       </c>
       <c r="I15" s="28" t="inlineStr">
         <is>
-          <t>1. Tìm học viên "Nguyễn Văn A" trong bảng phân công học viên.
-2. Nhấp vào ô chọn công ty của học viên "Nguyễn Văn A".
-3. Chọn công ty "TechCorp" từ danh sách gợi ý.
-4. Nhấn nút "Lưu thay đổi".</t>
+          <t>1. Tim student "Nguyen Van A" trong bang phan cong student.
+2. Nhap vao o select company cua student "Nguyen Van A".
+3. Select company "TechCorp" tu danh sach goi y.
+4. Nhan nut "Save thay doi".</t>
         </is>
       </c>
       <c r="J15" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo phân công thành công.
-Học viên "Nguyễn Văn A" hiển thị công ty đã gán là "TechCorp".
-Số lượng học viên chưa phân công trên nhãn cảnh báo (Warning Badge) tự động giảm đi 1.</t>
+          <t>System display notification phan cong successfully.
+Hoc vien "Nguyen Van A" display company da gan la "TechCorp".
+So luong student chua phan cong tren nhan cphoto bao (Warning Badge) tu dong giam di 1.</t>
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
@@ -16992,11 +16992,11 @@
       </c>
       <c r="N15" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F04, M05-F06, Rule 6.4, Rule 6.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="135" customHeight="1">
+          <t>Related to M05-F04, M05-F06, Rule 6.4, Rule 6.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
       <c r="A16" s="21" t="inlineStr">
         <is>
           <t>TC-M05-015</t>
@@ -17019,40 +17019,40 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>Phân công thực tập hàng loạt cho nhiều học viên cùng lúc</t>
+          <t>Phan cong internship hang loat cho nhieu student cung luc</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng chọn nhiều học viên và phân công vào cùng một công ty cùng lúc.</t>
+          <t>Verify functionality for select nhieu student va phan cong vao cung mot company cung luc.</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện danh sách học viên của nhóm thực tập.
-Có ít nhất 3 học viên đang ở trạng thái chưa phân công (ví dụ: Nguyễn Văn B, Trần Thị C, Lê Văn D).
-Công ty "TechCorp" đang hoạt động.</t>
+          <t>User is logged in as Staff.
+Dang o interface danh sach student cua internship group.
+Co it nhat 3 student dang o status chua phan cong (e.g.: Nguyen Van B, Tran Thi C, Le Van D).
+Cong ty "TechCorp" dang hoat dong.</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>SelectedStudents="Nguyễn Văn B", "Trần Thị C", "Lê Văn D"; AssignedCompany="TechCorp"</t>
+          <t>SelectedStudents="Nguyen Van B", "Tran Thi C", "Le Van D"; AssignedCompany="TechCorp"</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>1. Tích chọn các ô vuông (checkbox) đầu dòng của học viên "Nguyễn Văn B", "Trần Thị C" và "Lê Văn D".
-2. Nhấn nút "Phân công hàng loạt" (Bulk Assign).
-3. Chọn công ty "TechCorp" trong hộp thoại hiện ra.
-4. Nhấn nút "Áp dụng" hoặc "Lưu".</t>
+          <t>1. Tich select cac o vuong (checkbox) dau dong cua student "Nguyen Van B", "Tran Thi C" va "Le Van D".
+2. Nhan nut "Phan cong hang loat" (Bulk Assign).
+3. Select company "TechCorp" trong hop thoai hien ra.
+4. Nhan nut "Ap dung" hoac "Save".</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo phân công hàng loạt thành công.
-Cả 3 học viên trên đều hiển thị công ty được phân công là "TechCorp".
-Số lượng trên nhãn cảnh báo học viên chưa phân công tự động giảm đi 3.</t>
+          <t>System display notification phan cong hang loat successfully.
+Ca 3 student tren deu display company duoc phan cong la "TechCorp".
+So luong tren nhan cphoto bao student chua phan cong tu dong giam di 3.</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="N16" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F04, M05-F06, Rule 6.4, Rule 6.11</t>
+          <t>Related to M05-F04, M05-F06, Rule 6.4, Rule 6.11</t>
         </is>
       </c>
     </row>
@@ -17095,39 +17095,39 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Thay đổi công ty đã phân công của học viên</t>
+          <t>Thay doi company da phan cong cua student</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng gán công ty mới cho học viên đã được phân công trước đó, đảm bảo công ty cũ bị ghi đè.</t>
+          <t>Verify functionality for gan company moi cho student da duoc phan cong truoc do, dam bao company cu bi ghi de.</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học viên "Nguyễn Văn A" đang được phân công ở công ty "TechCorp".
-Công ty "PNV Software" đang hoạt động trong hệ thống.</t>
+          <t>User is logged in as Staff.
+Hoc vien "Nguyen Van A" dang duoc phan cong o company "TechCorp".
+Cong ty "PNV Software" dang hoat dong trong system.</t>
         </is>
       </c>
       <c r="H17" s="28" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; NewCompany="PNV Software"</t>
+          <t>StudentName="Nguyen Van A"; NewCompany="PNV Software"</t>
         </is>
       </c>
       <c r="I17" s="28" t="inlineStr">
         <is>
-          <t>1. Tìm học viên "Nguyễn Văn A" trong danh sách.
-2. Mở danh sách chọn công ty của học viên này và đổi từ "TechCorp" sang "PNV Software".
-3. Nhấn nút "Lưu thay đổi".</t>
+          <t>1. Tim student "Nguyen Van A" trong danh sach.
+2. Mo danh sach select company cua student nay va doi tu "TechCorp" sang "PNV Software".
+3. Nhan nut "Save thay doi".</t>
         </is>
       </c>
       <c r="J17" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống cập nhật thành công.
-Công ty phân công mới của học viên "Nguyễn Văn A" hiển thị là "PNV Software".
-Phân công cũ tại "TechCorp" bị thay thế hoàn toàn.
-Nhãn cảnh báo học viên chưa phân công không thay đổi số lượng.</t>
+          <t>System cap nhat successfully.
+Cong ty phan cong moi cua student "Nguyen Van A" display la "PNV Software".
+Phan cong cu tai "TechCorp" bi replace hoan toan.
+Nhan cphoto bao student chua phan cong khong thay doi so luong.</t>
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="N17" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F04, Rule 6.4</t>
+          <t>Related to M05-F04, Rule 6.4</t>
         </is>
       </c>
     </row>
@@ -17170,37 +17170,37 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>Hủy bỏ phân công công ty của học viên bằng cách chọn No Company</t>
+          <t>Huy bo phan cong company cua student bang cach select No Company</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng đưa học viên đã phân công về lại trạng thái chưa phân công (Unassigned) bằng cách chọn "(No Company)".</t>
+          <t>Verify functionality for dua student da phan cong ve lai status chua phan cong (Unassigned) bang cach select "(No Company)".</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học viên "Nguyễn Văn A" đang được phân công tại công ty "PNV Software".</t>
+          <t>User is logged in as Staff.
+Hoc vien "Nguyen Van A" dang duoc phan cong tai company "PNV Software".</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; Selection="(No Company)"</t>
+          <t>StudentName="Nguyen Van A"; Selection="(No Company)"</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>1. Tìm học viên "Nguyễn Văn A" trong danh sách.
-2. Nhấp vào ô chọn công ty, chọn giá trị "(No Company)".
-3. Nhấn nút "Lưu".</t>
+          <t>1. Tim student "Nguyen Van A" trong danh sach.
+2. Nhap vao o select company, select gia tri "(No Company)".
+3. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống lưu thành công.
-Học viên "Nguyễn Văn A" hiển thị trạng thái là chưa được phân công.
-Số lượng trên nhãn cảnh báo học viên chưa phân công (Warning Badge) tự động tăng lên 1.</t>
+          <t>System save successfully.
+Hoc vien "Nguyen Van A" display status la chua duoc phan cong.
+So luong tren nhan cphoto bao student chua phan cong (Warning Badge) tu dong tang len 1.</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F05, M05-F06, Rule 6.5, Rule 6.11, Error Handling (Mục 8)</t>
+          <t>Related to M05-F05, M05-F06, Rule 6.5, Rule 6.11, Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -17243,18 +17243,18 @@
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>Ẩn công ty và kiểm tra xem công ty đó có bị loại khỏi danh sách chọn phân công mới hay không</t>
+          <t>An company va kiem tra xem company do co bi loai khoi danh sach select phan cong moi hay khong</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra quy tắc công ty bị ẩn (Hidden) không xuất hiện trong dropdown phân công thực tập mới.</t>
+          <t>Verify quy tac company bi an (Hidden) khong xuat hien trong dropdown phan cong internship moi.</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đã tồn tại công ty "ABC Technology" trong hệ thống.</t>
+          <t>User is logged in as Staff.
+Da ton tai company "ABC Technology" trong system.</t>
         </is>
       </c>
       <c r="H19" s="28" t="inlineStr">
@@ -17264,16 +17264,16 @@
       </c>
       <c r="I19" s="28" t="inlineStr">
         <is>
-          <t>1. Vào trang Quản lý Công ty (Company Management).
-2. Tìm công ty "ABC Technology" và chọn thiết lập "Ẩn" (Hidden) cho công ty này.
-3. Nhấn nút "Lưu trạng thái công ty".
-4. Quay lại trang danh sách học viên của nhóm thực tập và mở dropdown phân công công ty của một học viên bất kỳ chưa được phân công.</t>
+          <t>1. Vao trang Quan ly Cong ty (Company Management).
+2. Tim company "ABC Technology" va select thiet lap "An" (Hidden) cho company nay.
+3. Nhan nut "Save status company".
+4. Quay lai trang danh sach student cua internship group va mo dropdown phan cong company cua mot student bat ky chua duoc phan cong.</t>
         </is>
       </c>
       <c r="J19" s="28" t="inlineStr">
         <is>
-          <t>Trạng thái ẩn được lưu thành công.
-Công ty "ABC Technology" không xuất hiện trong danh sách dropdown để chọn phân công mới.</t>
+          <t>Status an duoc save successfully.
+Cong ty "ABC Technology" khong xuat hien trong danh sach dropdown de select phan cong moi.</t>
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="N19" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 6.6, Error Handling (Mục 8)</t>
+          <t>Related to Rule 6.6, Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -17316,18 +17316,18 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo phân công hiện tại của học viên không bị ảnh hưởng khi công ty đó bị ẩn</t>
+          <t>Dam bao phan cong hien tai cua student khong bi photo huong khi company do bi an</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra quy tắc các phân công hiện tại vẫn hiển thị chính xác tên công ty sau khi công ty đó bị chuyển sang ẩn.</t>
+          <t>Verify quy tac cac phan cong hien tai van display chinh xac ten company sau khi company do bi chuyen sang an.</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học viên "Trần Thị B" đã được phân công tại công ty "ABC Technology".</t>
+          <t>User is logged in as Staff.
+Hoc vien "Tran Thi B" da duoc phan cong tai company "ABC Technology".</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -17337,15 +17337,15 @@
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>1. Vào trang Quản lý Công ty, chuyển trạng thái của "ABC Technology" sang "Ẩn" (Hidden) và lưu lại.
-2. Đi tới trang danh sách học viên của nhóm thực tập.
-3. Quan sát bản ghi phân công của học viên "Trần Thị B".</t>
+          <t>1. Vao trang Quan ly Cong ty, chuyen status cua "ABC Technology" sang "An" (Hidden) va save lai.
+2. Di toi trang danh sach student cua internship group.
+3. Observe ban ghi phan cong cua student "Tran Thi B".</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>Phân công của học viên "Trần Thị B" vẫn được hiển thị là "ABC Technology" một cách bình thường trên giao diện.
-Không có thông báo lỗi hay tự động xóa phân công.</t>
+          <t>Phan cong cua student "Tran Thi B" van duoc display la "ABC Technology" mot cach binh thuong tren interface.
+Khong co notification error hay tu dong delete phan cong.</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="N20" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 6.6</t>
+          <t>Related to Rule 6.6</t>
         </is>
       </c>
     </row>
@@ -17388,40 +17388,40 @@
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Ghi nhận nhận xét thực tập thành công cho một học viên với team Training</t>
+          <t>Ghi nhan nhan xet internship successfully cho mot student voi team Training</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng ghi nhận nhận xét thực tập cho học viên thuộc đội ngũ Training.</t>
+          <t>Verify functionality for ghi nhan nhan xet internship cho student thuoc doi ngu Training.</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện danh sách học viên nhóm thực tập.
-Học viên "Nguyễn Văn A" đã được phân công thực tập.</t>
+          <t>User is logged in as Staff.
+Dang o interface danh sach student internship group.
+Hoc vien "Nguyen Van A" da duoc phan cong internship.</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; FeedbackTeam="Training"; FeedbackDate="2026-08-15"; FeedbackNotes="Tiến bộ tốt, chủ động trong công việc."</t>
+          <t>StudentName="Nguyen Van A"; FeedbackTeam="Training"; FeedbackDate="2026-08-15"; FeedbackNotes="Tien bo tot, chu dong trong task."</t>
         </is>
       </c>
       <c r="I21" s="28" t="inlineStr">
         <is>
-          <t>1. Tìm học viên "Nguyễn Văn A" trong danh sách.
-2. Nhấp vào nút "Thêm nhận xét" (Add Feedback) của học viên này.
-3. Chọn Team nhận xét là "Training".
-4. Nhập Ngày nhận xét là "2026-08-15".
-5. Nhập Nội dung nhận xét là "Tiến bộ tốt, chủ động trong công việc.".
-6. Nhấn nút "Lưu nhận xét".</t>
+          <t>1. Tim student "Nguyen Van A" trong danh sach.
+2. Nhap vao nut "Add nhan xet" (Add Feedback) cua student nay.
+3. Select Team nhan xet la "Training".
+4. Enter Ngay nhan xet la "2026-08-15".
+5. Enter Noi dung nhan xet la "Tien bo tot, chu dong trong task.".
+6. Nhan nut "Save nhan xet".</t>
         </is>
       </c>
       <c r="J21" s="28" t="inlineStr">
         <is>
-          <t>Nhận xét được lưu thành công.
-Thông tin nhận xét mới xuất hiện dưới tên học viên với đúng Team "Training", ngày và nội dung nhận xét tương ứng.</t>
+          <t>Nhan xet duoc save successfully.
+Thong tin nhan xet moi xuat hien duoi ten student voi dung Team "Training", ngay va noi dung nhan xet tuong ung.</t>
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
@@ -17437,7 +17437,7 @@
       </c>
       <c r="N21" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F07, Rule 6.7</t>
+          <t>Related to M05-F07, Rule 6.7</t>
         </is>
       </c>
     </row>
@@ -17464,40 +17464,40 @@
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>Ghi nhận nhận xét thực tập thành công cho một học viên với team ERO</t>
+          <t>Ghi nhan nhan xet internship successfully cho mot student voi team ERO</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng ghi nhận nhận xét thực tập cho học viên thuộc đội ngũ ERO.</t>
+          <t>Verify functionality for ghi nhan nhan xet internship cho student thuoc doi ngu ERO.</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện danh sách học viên nhóm thực tập.
-Học viên "Nguyễn Văn A" đã được phân công thực tập.</t>
+          <t>User is logged in as Staff.
+Dang o interface danh sach student internship group.
+Hoc vien "Nguyen Van A" da duoc phan cong internship.</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; FeedbackTeam="ERO"; FeedbackDate="2026-08-15"; FeedbackNotes="Kỹ năng kỹ thuật tốt, thái độ chuyên nghiệp."</t>
+          <t>StudentName="Nguyen Van A"; FeedbackTeam="ERO"; FeedbackDate="2026-08-15"; FeedbackNotes="Ky nang ky thuat tot, thai do chuyen nghiep."</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>1. Tìm học viên "Nguyễn Văn A" trong danh sách.
-2. Nhấp vào nút "Thêm nhận xét" (Add Feedback) của học viên này.
-3. Chọn Team nhận xét là "ERO".
-4. Nhập Ngày nhận xét là "2026-08-15".
-5. Nhập Nội dung nhận xét là "Kỹ năng kỹ thuật tốt, thái độ chuyên nghiệp.".
-6. Nhấn nút "Lưu nhận xét".</t>
+          <t>1. Tim student "Nguyen Van A" trong danh sach.
+2. Nhap vao nut "Add nhan xet" (Add Feedback) cua student nay.
+3. Select Team nhan xet la "ERO".
+4. Enter Ngay nhan xet la "2026-08-15".
+5. Enter Noi dung nhan xet la "Ky nang ky thuat tot, thai do chuyen nghiep.".
+6. Nhan nut "Save nhan xet".</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Nhận xét được lưu thành công.
-Thông tin nhận xét mới xuất hiện dưới tên học viên với đúng Team "ERO", ngày và nội dung nhận xét tương ứng.</t>
+          <t>Nhan xet duoc save successfully.
+Thong tin nhan xet moi xuat hien duoi ten student voi dung Team "ERO", ngay va noi dung nhan xet tuong ung.</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N22" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F07, Rule 6.7</t>
+          <t>Related to M05-F07, Rule 6.7</t>
         </is>
       </c>
     </row>
@@ -17540,40 +17540,40 @@
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>Ghi nhận nhận xét thực tập thành công cho một học viên với team Educators</t>
+          <t>Ghi nhan nhan xet internship successfully cho mot student voi team Educators</t>
         </is>
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng ghi nhận nhận xét thực tập cho học viên thuộc đội ngũ Educators.</t>
+          <t>Verify functionality for ghi nhan nhan xet internship cho student thuoc doi ngu Educators.</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện danh sách học viên nhóm thực tập.
-Học viên "Nguyễn Văn A" đã được phân công thực tập.</t>
+          <t>User is logged in as Staff.
+Dang o interface danh sach student internship group.
+Hoc vien "Nguyen Van A" da duoc phan cong internship.</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; FeedbackTeam="Educators"; FeedbackDate="2026-08-15"; FeedbackNotes="Năng nổ đóng góp ý kiến xây dựng nhóm."</t>
+          <t>StudentName="Nguyen Van A"; FeedbackTeam="Educators"; FeedbackDate="2026-08-15"; FeedbackNotes="Nang no dong gop y kien xay dung group."</t>
         </is>
       </c>
       <c r="I23" s="28" t="inlineStr">
         <is>
-          <t>1. Tìm học viên "Nguyễn Văn A" trong danh sách.
-2. Nhấp vào nút "Thêm nhận xét" (Add Feedback) của học viên này.
-3. Chọn Team nhận xét là "Educators".
-4. Nhập Ngày nhận xét là "2026-08-15".
-5. Nhập Nội dung nhận xét là "Năng nổ đóng góp ý kiến xây dựng nhóm.".
-6. Nhấn nút "Lưu nhận xét".</t>
+          <t>1. Tim student "Nguyen Van A" trong danh sach.
+2. Nhap vao nut "Add nhan xet" (Add Feedback) cua student nay.
+3. Select Team nhan xet la "Educators".
+4. Enter Ngay nhan xet la "2026-08-15".
+5. Enter Noi dung nhan xet la "Nang no dong gop y kien xay dung group.".
+6. Nhan nut "Save nhan xet".</t>
         </is>
       </c>
       <c r="J23" s="28" t="inlineStr">
         <is>
-          <t>Nhận xét được lưu thành công.
-Thông tin nhận xét mới xuất hiện dưới tên học viên với đúng Team "Educators", ngày và nội dung nhận xét tương ứng.</t>
+          <t>Nhan xet duoc save successfully.
+Thong tin nhan xet moi xuat hien duoi ten student voi dung Team "Educators", ngay va noi dung nhan xet tuong ung.</t>
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="N23" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F07, Rule 6.7</t>
+          <t>Related to M05-F07, Rule 6.7</t>
         </is>
       </c>
     </row>
@@ -17616,18 +17616,18 @@
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>Bỏ qua các dòng nhận xét trống không lưu vào hệ thống</t>
+          <t>Bo qua cac dong nhan xet trong khong save vao system</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống bỏ qua và không lưu các dòng nhận xét không chứa nội dung (trống).</t>
+          <t>Verify system bo qua va khong save cac dong nhan xet khong chua noi dung (trong).</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Thêm nhận xét cho học viên.</t>
+          <t>User is logged in as Staff.
+Dang o interface Add nhan xet cho student.</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -17637,16 +17637,16 @@
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>1. Mở giao diện nhập nhận xét của học viên.
-2. Chọn Team là "ERO" và chọn ngày nhận xét.
-3. Bỏ trống trường Nội dung nhận xét (Notes).
-4. Nhấn nút "Lưu".</t>
+          <t>1. Mo interface enter nhan xet cua student.
+2. Select Team la "ERO" va select ngay nhan xet.
+3. Bo trong truong Noi dung nhan xet (Notes).
+4. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống bỏ qua dòng nhận xét này, không tạo bản ghi mới trong cơ sở dữ liệu (Google Sheets).
-Không hiển thị thông báo lỗi nhưng cũng không hiển thị bản ghi nhận xét trống này trên UI.</t>
+          <t>System bo qua dong nhan xet nay, khong create ban ghi moi trong co so du lieu (Google Sheets).
+Khong display notification error nhung cung not displayed ban ghi nhan xet trong nay tren UI.</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="N24" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 6.8, Error Handling (Mục 8)</t>
+          <t>Related to Rule 6.8, Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -17689,38 +17689,38 @@
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>Ghi nhận nhận xét giống nhau cho nhiều học viên cùng lúc (Same for All)</t>
+          <t>Ghi nhan nhan xet giong nhau cho nhieu student cung luc (Same for All)</t>
         </is>
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra tính năng ghi nhận nhận xét hàng loạt và áp dụng nội dung giống nhau cho các học viên được chọn.</t>
+          <t>Verify tinh nang ghi nhan nhan xet hang loat va ap dung noi dung giong nhau cho cac student duoc select.</t>
         </is>
       </c>
       <c r="G25" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện danh sách học viên của nhóm thực tập.
-Có ít nhất 2 học viên được chọn (ví dụ: Nguyễn Văn A, Trần Thị B).</t>
+          <t>User is logged in as Staff.
+Dang o interface danh sach student cua internship group.
+Co it nhat 2 student duoc select (e.g.: Nguyen Van A, Tran Thi B).</t>
         </is>
       </c>
       <c r="H25" s="28" t="inlineStr">
         <is>
-          <t>SelectedStudents="Nguyễn Văn A", "Trần Thị B"; FeedbackTeam="Educators"; FeedbackDate="2026-08-15"; FeedbackNotes="Kỹ năng giao tiếp xuất sắc."</t>
+          <t>SelectedStudents="Nguyen Van A", "Tran Thi B"; FeedbackTeam="Educators"; FeedbackDate="2026-08-15"; FeedbackNotes="Ky nang giao tiep xuat sac."</t>
         </is>
       </c>
       <c r="I25" s="28" t="inlineStr">
         <is>
-          <t>1. Tích chọn checkbox của học viên "Nguyễn Văn A" và "Trần Thị B".
-2. Nhấn nút "Nhận xét hàng loạt" (Batch Feedback / Same for All).
-3. Chọn Team là "Educators", chọn Ngày nhận xét là "2026-08-15", nhập Nội dung nhận xét chung là "Kỹ năng giao tiếp xuất sắc.".
-4. Nhấn nút "Áp dụng và Lưu".</t>
+          <t>1. Tich select checkbox cua student "Nguyen Van A" va "Tran Thi B".
+2. Nhan nut "Nhan xet hang loat" (Batch Feedback / Same for All).
+3. Select Team la "Educators", select Ngay nhan xet la "2026-08-15", enter Noi dung nhan xet chung la "Ky nang giao tiep xuat sac.".
+4. Nhan nut "Ap dung va Save".</t>
         </is>
       </c>
       <c r="J25" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống lưu thành công nhận xét cho cả hai học viên.
-Cả học viên "Nguyễn Văn A" và "Trần Thị B" đều hiển thị bản ghi nhận xét của Educators với cùng nội dung "Kỹ năng giao tiếp xuất sắc." vào ngày 2026-08-15.</t>
+          <t>System save successfully nhan xet cho ca hai student.
+Ca student "Nguyen Van A" va "Tran Thi B" deu display ban ghi nhan xet cua Educators voi cung noi dung "Ky nang giao tiep xuat sac." vao ngay 2026-08-15.</t>
         </is>
       </c>
       <c r="K25" s="28" t="inlineStr"/>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="N25" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F08, Rule 6.9</t>
+          <t>Related to M05-F08, Rule 6.9</t>
         </is>
       </c>
     </row>
@@ -17763,37 +17763,37 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>Chỉnh sửa nhận xét thực tập đã lưu (thay đổi nội dung nhận xét)</t>
+          <t>Edit nhan xet internship da save (thay doi noi dung nhan xet)</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng chỉnh sửa và lưu đè nội dung nhận xét đã tồn tại.</t>
+          <t>Verify functionality for edit va save de noi dung nhan xet da ton tai.</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học viên "Nguyễn Văn A" đã có nhận xét: Team = "Training", nội dung = "Tiến bộ tốt", ngày = "2026-08-15".</t>
+          <t>User is logged in as Staff.
+Hoc vien "Nguyen Van A" da co nhan xet: Team = "Training", noi dung = "Tien bo tot", ngay = "2026-08-15".</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; NewFeedbackNotes="Tiến bộ vượt bậc và làm việc nhóm tốt."</t>
+          <t>StudentName="Nguyen Van A"; NewFeedbackNotes="Tien bo vuot bac va lam viec group tot."</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>1. Tìm học viên "Nguyễn Văn A" và mở danh sách nhận xét của học viên.
-2. Chọn nhận xét có nội dung "Tiến bộ tốt" và nhấn nút "Chỉnh sửa" (Edit).
-3. Cập nhật nội dung nhận xét thành "Tiến bộ vượt bậc và làm việc nhóm tốt.".
-4. Nhấn nút "Lưu".</t>
+          <t>1. Tim student "Nguyen Van A" va mo danh sach nhan xet cua student.
+2. Select nhan xet co noi dung "Tien bo tot" va click button "Edit" (Edit).
+3. Cap nhat noi dung nhan xet thanh "Tien bo vuot bac va lam viec group tot.".
+4. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Nhận xét được cập nhật thành công.
-Nội dung mới ghi đè lên nội dung cũ và hiển thị chính xác trên UI: "Tiến bộ vượt bậc và làm việc nhóm tốt.".</t>
+          <t>Nhan xet duoc cap nhat successfully.
+Noi dung moi ghi de len noi dung cu va display chinh xac tren UI: "Tien bo vuot bac va lam viec group tot.".</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr"/>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="N26" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F09, Rule 6.10</t>
+          <t>Related to M05-F09, Rule 6.10</t>
         </is>
       </c>
     </row>
@@ -17836,38 +17836,38 @@
       </c>
       <c r="E27" s="28" t="inlineStr">
         <is>
-          <t>Chỉnh sửa nhận xét thực tập đã lưu (thay đổi team nhận xét và ngày nhận xét)</t>
+          <t>Edit nhan xet internship da save (thay doi team nhan xet va ngay nhan xet)</t>
         </is>
       </c>
       <c r="F27" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng chỉnh sửa và lưu đè thông tin team và ngày nhận xét đã tồn tại.</t>
+          <t>Verify functionality for edit va save de thong tin team va ngay nhan xet da ton tai.</t>
         </is>
       </c>
       <c r="G27" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học viên "Nguyễn Văn A" đã có nhận xét: Team = "Training", nội dung = "Tiến bộ tốt", ngày = "2026-08-15".</t>
+          <t>User is logged in as Staff.
+Hoc vien "Nguyen Van A" da co nhan xet: Team = "Training", noi dung = "Tien bo tot", ngay = "2026-08-15".</t>
         </is>
       </c>
       <c r="H27" s="28" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; NewFeedbackTeam="ERO"; NewFeedbackDate="2026-08-20"</t>
+          <t>StudentName="Nguyen Van A"; NewFeedbackTeam="ERO"; NewFeedbackDate="2026-08-20"</t>
         </is>
       </c>
       <c r="I27" s="28" t="inlineStr">
         <is>
-          <t>1. Tìm học viên "Nguyễn Văn A" và mở danh sách nhận xét của học viên.
-2. Chọn nhận xét có nội dung "Tiến bộ tốt" và nhấn nút "Chỉnh sửa" (Edit).
-3. Thay đổi Team nhận xét thành "ERO".
-4. Thay đổi Ngày nhận xét thành "2026-08-20".
-5. Nhấn nút "Lưu".</t>
+          <t>1. Tim student "Nguyen Van A" va mo danh sach nhan xet cua student.
+2. Select nhan xet co noi dung "Tien bo tot" va click button "Edit" (Edit).
+3. Thay doi Team nhan xet thanh "ERO".
+4. Thay doi Ngay nhan xet thanh "2026-08-20".
+5. Nhan nut "Save".</t>
         </is>
       </c>
       <c r="J27" s="28" t="inlineStr">
         <is>
-          <t>Nhận xét được cập nhật thành công.
-Dữ liệu nhận xét được thay đổi với Team mới là "ERO" và ngày mới là "2026-08-20" trên giao diện.</t>
+          <t>Nhan xet duoc cap nhat successfully.
+Du lieu nhan xet duoc thay doi voi Team moi la "ERO" va ngay moi la "2026-08-20" tren interface.</t>
         </is>
       </c>
       <c r="K27" s="28" t="inlineStr"/>
@@ -17883,7 +17883,7 @@
       </c>
       <c r="N27" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F09, Rule 6.10</t>
+          <t>Related to M05-F09, Rule 6.10</t>
         </is>
       </c>
     </row>
@@ -17910,39 +17910,39 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Mở rộng/thu gọn danh sách học viên và hiển thị nhãn cảnh báo trong danh sách nhóm thực tập</t>
+          <t>Mo rong/thu gon danh sach student va display nhan cphoto bao trong danh sach internship group</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng mở rộng/thu gọn (expand/collapse) của từng nhóm thực tập, điều hướng và hiển thị chính xác nhãn cảnh báo (Warning Badge).</t>
+          <t>Verify functionality for mo rong/thu gon (expand/collapse) cua tung internship group, dieu huong va display chinh xac nhan cphoto bao (Warning Badge).</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở màn hình danh sách nhóm thực tập.
-Có nhóm thực tập "Nhóm Thực tập 2026" chứa 2 học viên chưa gán công ty.</t>
+          <t>User is logged in as Staff.
+Dang o man hinh danh sach internship group.
+Co internship group "Nhom Thuc tap 2026" chua 2 student chua gan company.</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>GroupName="Nhóm Thực tập 2026"</t>
+          <t>GroupName="Nhom Thuc tap 2026"</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>1. Quan sát dòng hiển thị của nhóm thực tập "Nhóm Thực tập 2026".
-2. Kiểm tra xem có hiển thị nhãn cảnh báo học viên chưa gán hay không (ví dụ: "2 học viên chưa phân công" hoặc "2 Unassigned").
-3. Nhấp vào nút/biểu tượng mũi tên mở rộng (Expand) của nhóm thực tập này.
-4. Nhấp lại vào nút/biểu tượng thu gọn (Collapse) của nhóm thực tập.</t>
+          <t>1. Observe dong display cua internship group "Nhom Thuc tap 2026".
+2. Verify whether co display nhan cphoto bao student chua gan hay khong (e.g.: "2 student chua phan cong" hoac "2 Unassigned").
+3. Nhap vao nut/bieu tuong mui ten mo rong (Expand) cua internship group nay.
+4. Nhap lai vao nut/bieu tuong thu gon (Collapse) cua internship group.</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Nhãn cảnh báo hiển thị chính xác số lượng học viên chưa gán (ví dụ: "⚠ 2 Unassigned" hoặc tương tự).
-Khi nhấn Mở rộng, danh sách học viên chi tiết của nhóm hiển thị ngay bên dưới.
-Khi nhấn Thu gọn, danh sách chi tiết được ẩn đi.</t>
+          <t>Nhan cphoto bao display chinh xac so luong student chua gan (e.g.: "⚠ 2 Unassigned" hoac tuong tu).
+Khi click Mo rong, danh sach student chi tiet cua group display ngay ben duoi.
+Khi click Thu gon, danh sach chi tiet duoc an di.</t>
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr"/>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="N28" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M05-F10, Rule 6.11</t>
+          <t>Related to M05-F10, Rule 6.11</t>
         </is>
       </c>
     </row>
@@ -18096,19 +18096,19 @@
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>Tạo báo cáo mới bởi học viên thuộc nhóm thực tập đang hoạt động</t>
+          <t>Create new report boi student thuoc internship group dang hoat dong</t>
         </is>
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng hiển thị nút và mở giao diện tạo báo cáo mới cho học viên thuộc nhóm thực tập đang hoạt động (On-going).</t>
+          <t>Verify functionality for display nut va mo interface create new report cho student thuoc internship group dang hoat dong (On-going).</t>
         </is>
       </c>
       <c r="G2" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Học viên thuộc nhóm thực tập có trạng thái "On-going".
-Đang ở giao diện Student Portal.</t>
+          <t>User is logged in as Student.
+Hoc vien thuoc internship group co status "On-going".
+Currently on Student Portal interface.</t>
         </is>
       </c>
       <c r="H2" s="23" t="inlineStr">
@@ -18118,15 +18118,15 @@
       </c>
       <c r="I2" s="23" t="inlineStr">
         <is>
-          <t>1. Truy cập vào Student Portal.
-2. Kiểm tra sự xuất hiện của nút "+ New Report".
-3. Nhấp vào nút "+ New Report".</t>
+          <t>1. Truy cap vao Student Portal.
+2. Verify su xuat hien cua nut "+ New Report".
+3. Nhap vao nut "+ New Report".</t>
         </is>
       </c>
       <c r="J2" s="23" t="inlineStr">
         <is>
-          <t>Nút "+ New Report" hiển thị rõ ràng và có thể nhấp được.
-Giao diện tạo báo cáo thực tập mới mở ra thành công.</t>
+          <t>Nut "+ New Report" display ro rang va can click duoc.
+Interface create new internship report mo ra successfully.</t>
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
@@ -18142,7 +18142,7 @@
       </c>
       <c r="N2" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F01, Rule 6.1</t>
+          <t>Related to M06-F01, Rule 6.1</t>
         </is>
       </c>
     </row>
@@ -18169,19 +18169,19 @@
       </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
-          <t>Ngăn chặn tạo báo cáo mới đối với học viên thuộc nhóm thực tập đã hoàn thành</t>
+          <t>Prevent create new report for student thuoc internship group da hoan thanh</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ẩn nút tạo báo cáo mới nếu học viên thuộc nhóm thực tập đã hoàn thành (Completed).</t>
+          <t>Verify system an nut create new report neu student thuoc internship group da hoan thanh (Completed).</t>
         </is>
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Học viên thuộc nhóm thực tập có trạng thái "Completed".
-Đang ở giao diện Student Portal.</t>
+          <t>User is logged in as Student.
+Hoc vien thuoc internship group co status "Completed".
+Currently on Student Portal interface.</t>
         </is>
       </c>
       <c r="H3" s="28" t="inlineStr">
@@ -18191,14 +18191,14 @@
       </c>
       <c r="I3" s="28" t="inlineStr">
         <is>
-          <t>1. Truy cập vào Student Portal.
-2. Quan sát sự xuất hiện của nút "+ New Report".</t>
+          <t>1. Truy cap vao Student Portal.
+2. Observe su xuat hien cua nut "+ New Report".</t>
         </is>
       </c>
       <c r="J3" s="28" t="inlineStr">
         <is>
-          <t>Nút "+ New Report" không hiển thị trên giao diện.
-Học viên không thể tạo báo cáo thực tập mới.</t>
+          <t>Nut "+ New Report" not displayed tren interface.
+Hoc vien cannot create new internship report.</t>
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="N3" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F01, Rule 6.1</t>
+          <t>Related to M06-F01, Rule 6.1</t>
         </is>
       </c>
     </row>
@@ -18241,19 +18241,19 @@
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>Ngăn chặn tạo báo cáo mới đối với học viên thuộc nhóm thực tập đã lưu trữ</t>
+          <t>Prevent create new report for student thuoc internship group da archive</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ẩn nút tạo báo cáo mới nếu học viên thuộc nhóm thực tập đã lưu trữ (Archived).</t>
+          <t>Verify system an nut create new report neu student thuoc internship group da archive (Archived).</t>
         </is>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Học viên thuộc nhóm thực tập có trạng thái "Archived".
-Đang ở giao diện Student Portal.</t>
+          <t>User is logged in as Student.
+Hoc vien thuoc internship group co status "Archived".
+Currently on Student Portal interface.</t>
         </is>
       </c>
       <c r="H4" s="23" t="inlineStr">
@@ -18263,14 +18263,14 @@
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>1. Truy cập vào Student Portal.
-2. Quan sát sự xuất hiện của nút "+ New Report".</t>
+          <t>1. Truy cap vao Student Portal.
+2. Observe su xuat hien cua nut "+ New Report".</t>
         </is>
       </c>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t>Nút "+ New Report" không hiển thị trên giao diện.
-Học viên không thể tạo báo cáo thực tập mới.</t>
+          <t>Nut "+ New Report" not displayed tren interface.
+Hoc vien cannot create new internship report.</t>
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="N4" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F01, Rule 6.1</t>
+          <t>Related to M06-F01, Rule 6.1</t>
         </is>
       </c>
     </row>
@@ -18313,18 +18313,18 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Ngăn chặn tạo báo cáo mới từ tài khoản Staff</t>
+          <t>Prevent creating new report from Staff account</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra xem tài khoản Staff có bị giới hạn quyền không được tạo báo cáo thực tập mới hay không.</t>
+          <t>Verify whether account Staff co bi gioi han quyen khong duoc create new internship report hay khong.</t>
         </is>
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Học viên hoặc Quản lý Thực tập.</t>
+          <t>User is logged in as Staff.
+Currently on Student Management or Internship Management interface.</t>
         </is>
       </c>
       <c r="H5" s="28" t="inlineStr">
@@ -18334,12 +18334,12 @@
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>1. Truy cập giao diện báo cáo của học viên bất kỳ hoặc kiểm tra các nút chức năng trên trang báo cáo.</t>
+          <t>1. Truy cap interface report cua student bat ky hoac kiem tra cac nut chuc nang tren trang report.</t>
         </is>
       </c>
       <c r="J5" s="28" t="inlineStr">
         <is>
-          <t>Không xuất hiện nút "+ New Report" hoặc bất kỳ tùy chọn nào cho phép Staff tạo báo cáo thực tập.</t>
+          <t>Khong xuat hien nut "+ New Report" hoac bat ky tuy select nao allows Staff create internship report.</t>
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="N5" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến User Roles (Mục 4), Staff Access (Rule 6.12)</t>
+          <t>Related to User Roles (Section 4), Staff Access (Rule 6.12)</t>
         </is>
       </c>
     </row>
@@ -18382,38 +18382,38 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Lưu báo cáo tạm thời dưới dạng Nháp (Draft)</t>
+          <t>Save temporary report as Draft</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng lưu nháp báo cáo với thông tin chưa đầy đủ để chỉnh sửa sau.</t>
+          <t>Verify functionality for save as draft report voi thong tin chua day du de edit sau.</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo thực tập mới.</t>
+          <t>User is logged in as Student.
+Currently on new internship report creation interface.</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>CompanySupervisorName="Nguyễn Văn B"; StartDate="2026-07-20"; Status="Draft"</t>
+          <t>CompanySupervisorName="Nguyen Van B"; StartDate="2026-07-20"; Status="Draft"</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>1. Nhập Tên giám sát của công ty là "Nguyễn Văn B".
-2. Chọn Ngày bắt đầu là "2026-07-20" (Thứ Hai).
-3. Để trống các trường bắt buộc khác.
-4. Nhấp nút "Save as Draft" (Lưu nháp).</t>
+          <t>1. Enter Ten supervisor cua company la "Nguyen Van B".
+2. Select Start Date la "2026-07-20" (Monday).
+3. De trong cac truong bat buoc khac.
+4. Nhap nut "Save as Draft" (Save as draft).</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu nháp thành công.
-Báo cáo được lưu vào danh sách với trạng thái "Draft".
-Học viên có thể mở lại để tiếp tục chỉnh sửa.</t>
+          <t>System display notification save as draft successfully.
+Bao cao duoc save vao danh sach voi status "Draft".
+Hoc vien can mo lai de tiep tuc edit.</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
@@ -18429,7 +18429,7 @@
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F02, Rule 6.2</t>
+          <t>Related to M06-F02, Rule 6.2</t>
         </is>
       </c>
     </row>
@@ -18456,38 +18456,38 @@
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>Chỉnh sửa báo cáo nháp không giới hạn số lần</t>
+          <t>Edit draft report unlimited number of times</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra xem học viên có thể chỉnh sửa và lưu lại báo cáo nháp nhiều lần trước khi nộp chính thức.</t>
+          <t>Verify whether student can edit va save lai draft report nhieu lan truoc khi submit chinh thuc.</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đã có sẵn một báo cáo ở trạng thái "Draft" trong danh sách.</t>
+          <t>User is logged in as Student.
+Da co san mot report o status "Draft" trong danh sach.</t>
         </is>
       </c>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>ReportId="REP001"; InitialStatus="Draft"; NewSupervisorName="Trần Thị C"; Tasks=[{"TaskName": "Design Database", "Description": "Create ERD", "Result": "Completed"}]</t>
+          <t>ReportId="REP001"; InitialStatus="Draft"; NewSupervisorName="Tran Thi C"; Tasks=[{"TaskName": "Design Database", "Description": "Create ERD", "Result": "Completed"}]</t>
         </is>
       </c>
       <c r="I7" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn báo cáo nháp "REP001" từ danh sách và nhấp "Edit" (Chỉnh sửa).
-2. Thay đổi Tên giám sát thành "Trần Thị C".
-3. Thêm một công việc vào bảng công việc.
-4. Nhấp nút "Save as Draft".
-5. Mở lại báo cáo đó lần nữa, sửa đổi thông tin và nhấp "Save as Draft" tiếp.</t>
+          <t>1. Select draft report "REP001" tu danh sach va click "Edit" (Edit).
+2. Thay doi Ten supervisor thanh "Tran Thi C".
+3. Add mot task vao task table.
+4. Nhap nut "Save as Draft".
+5. Mo lai report do lan nua, sua doi thong tin va click "Save as Draft" tiep.</t>
         </is>
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống cho phép chỉnh sửa và lưu thành công tất cả các thay đổi mà không giới hạn số lần.
-Trạng thái báo cáo vẫn giữ nguyên là "Draft" sau mỗi lần lưu nháp.</t>
+          <t>System allows edit va save successfully tat ca cac thay doi ma without limit times.
+Status report van giu nguyen la "Draft" sau moi lan save as draft.</t>
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
@@ -18503,11 +18503,11 @@
       </c>
       <c r="N7" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F02, Rule 6.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1">
+          <t>Related to M06-F02, Rule 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="105" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
         <is>
           <t>TC-M06-007</t>
@@ -18530,17 +18530,17 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Báo cáo nháp không gửi email và không hiển thị đối với Staff</t>
+          <t>Draft report does not send emails and is hidden from Staff</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo báo cáo nháp không kích hoạt tính năng gửi email và không thể nhìn thấy bởi tài khoản Staff.</t>
+          <t>Dam bao draft report khong kich hoat tinh nang gui email va cannot nhin thay boi account Staff.</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>Học viên vừa thực hiện lưu nháp một báo cáo mới.</t>
+          <t>Hoc vien vua thuc hien save as draft mot new report.</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -18550,14 +18550,14 @@
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>1. Kiểm tra hòm thư của PNV Supervisor và Company Supervisor xem có email thông báo nào được gửi đi không.
-2. Đăng nhập hệ thống bằng tài khoản Staff, truy cập trang chi tiết học viên (Student Detail) của học viên này và kiểm tra danh sách báo cáo.</t>
+          <t>1. Verify hom thu cua PNV Supervisor va Company Supervisor xem co email notification nao duoc gui di khong.
+2. Log in system bang account Staff, access trang chi tiet student (Student Detail) cua student nay va kiem tra danh sach report.</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>1. Không có email nào được gửi từ hệ thống.
-2. Tài khoản Staff không nhìn thấy báo cáo nháp này trong danh sách báo cáo của học viên.</t>
+          <t>1. Khong co email nao duoc gui tu system.
+2. Tai khoan Staff khong nhin thay draft report nay trong danh sach report cua student.</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F02, Rule 6.2, Rule 6.12</t>
+          <t>Related to M06-F02, Rule 6.2, Rule 6.12</t>
         </is>
       </c>
     </row>
@@ -18600,36 +18600,36 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>Tự động tính toán Ngày kết thúc báo cáo khi nhập Ngày bắt đầu hợp lệ</t>
+          <t>Auto-calculate End Date when valid Start Date is entered</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tự động tính toán Ngày kết thúc (End Date) dựa trên công thức Ngày bắt đầu (Start Date) + 13 ngày.</t>
+          <t>Verify functionality for auto-calculate End Date (End Date) dua tren cong thuc Start Date (Start Date) + 13 ngay.</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H9" s="28" t="inlineStr">
         <is>
-          <t>StartDate="2026-07-20" (Thứ Hai)</t>
+          <t>StartDate="2026-07-20" (Monday)</t>
         </is>
       </c>
       <c r="I9" s="28" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn trường Ngày bắt đầu và nhập/chọn ngày "2026-07-20".
-2. Kiểm tra giá trị hiển thị ở trường Ngày kết thúc.
-3. Thử nhấp đúp hoặc gõ vào trường Ngày kết thúc để chỉnh sửa.</t>
+          <t>1. Nhap select truong Start Date va enter/select ngay "2026-07-20".
+2. Verify gia tri display o truong End Date.
+3. Thu click dup hoac go vao truong End Date de edit.</t>
         </is>
       </c>
       <c r="J9" s="28" t="inlineStr">
         <is>
-          <t>Trường Ngày kết thúc tự động hiển thị ngày "2026-08-02".
-Trường Ngày kết thúc bị vô hiệu hóa (disabled/read-only) và người dùng không thể chỉnh sửa thủ công.</t>
+          <t>Truong End Date tu dong display ngay "2026-08-02".
+Truong End Date bi vo hieu hoa (disabled/read-only) va user cannot edit thu cong.</t>
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="N9" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F04, Rule 6.5</t>
+          <t>Related to M06-F04, Rule 6.5</t>
         </is>
       </c>
     </row>
@@ -18672,37 +18672,37 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Ngăn chặn nộp báo cáo nếu Ngày bắt đầu không phải là thứ Hai</t>
+          <t>Prevent submitting report if Start Date is not a Monday</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi Ngày bắt đầu được chọn không rơi vào thứ Hai.</t>
+          <t>Verify system bao error khi Start Date duoc select khong roi vao thu Hai.</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>StartDate="2026-07-21" (Thứ Ba, không phải thứ Hai); Các trường bắt buộc khác hợp lệ</t>
+          <t>StartDate="2026-07-21" (Tuesday, not thu Hai); Other required fields valid</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>1. Nhập đầy đủ thông tin hợp lệ vào các trường bắt buộc.
-2. Thay đổi Ngày bắt đầu thành "2026-07-21" (Thứ Ba).
-3. Nhấp nút "Submit" (Nộp báo cáo).
-4. Xác nhận nộp trong hộp thoại xác nhận.</t>
+          <t>1. Enter day du thong tin hop le vao cac truong bat buoc.
+2. Thay doi Start Date thanh "2026-07-21" (Tuesday).
+3. Nhap nut "Submit" (Submit report).
+4. Xac nhan submit trong hop thoai xac nhan.</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị lỗi cảnh báo Ngày bắt đầu phải là thứ Hai (ví dụ: "Start Date must be a Monday").
-Báo cáo không được nộp và trạng thái không đổi.</t>
+          <t>System display error cphoto bao Start Date phai la thu Hai (e.g.: "Start Date must be a Monday").
+Bao cao khong duoc submit va status khong doi.</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="N10" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -18745,37 +18745,37 @@
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>Ngăn chặn nộp báo cáo nếu Ngày bắt đầu nằm ngoài thời gian thực tập</t>
+          <t>Prevent submitting report if Start Date is outside internship period</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi học viên chọn Ngày bắt đầu nằm ngoài phạm vi thời gian thực tập đã cấu hình.</t>
+          <t>Verify system bao error khi student select Start Date outside pham vi period internship da cau hinh.</t>
         </is>
       </c>
       <c r="G11" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Thời gian thực tập của học viên được cấu hình từ "2026-07-01" đến "2026-09-30".
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Thoi gian internship cua student duoc cau hinh tu "2026-07-01" den "2026-09-30".
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H11" s="28" t="inlineStr">
         <is>
-          <t>StartDate="2026-06-22" (Thứ Hai, trước thời gian thực tập); Các trường bắt buộc khác hợp lệ</t>
+          <t>StartDate="2026-06-22" (Monday, truoc period internship); Other required fields valid</t>
         </is>
       </c>
       <c r="I11" s="28" t="inlineStr">
         <is>
-          <t>1. Nhập đầy đủ thông tin hợp lệ vào các trường bắt buộc.
-2. Chọn Ngày bắt đầu là "2026-06-22".
-3. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Enter day du thong tin hop le vao cac truong bat buoc.
+2. Select Start Date la "2026-06-22".
+3. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu Ngày bắt đầu phải nằm trong thời gian thực tập (ví dụ: "Start Date must be within the internship period").
-Báo cáo không được nộp.</t>
+          <t>System display notification error requires Start Date phai nam trong period internship (e.g.: "Start Date must be within the internship period").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
@@ -18791,7 +18791,7 @@
       </c>
       <c r="N11" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -18818,41 +18818,41 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Thêm và xóa các dòng công việc trong bảng công việc động</t>
+          <t>Add and remove task rows in dynamic task table</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng thêm mới dòng công việc và xóa bớt dòng công việc hiện tại trong bảng công việc.</t>
+          <t>Verify functionality for add moi task row va delete bot task row hien tai trong task table.</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
-          <t>Không có dữ liệu đặc biệt</t>
+          <t>Khong co du lieu dac biet</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấp nút "Add Task" (Thêm công việc).
-2. Nhập thông tin vào dòng công việc vừa tạo.
-3. Nhấp nút "Add Task" một lần nữa để tạo dòng thứ 2.
-4. Nhập thông tin cho dòng thứ 2.
-5. Nhấp nút "Remove" (Xóa) tại dòng công việc thứ nhất.</t>
+          <t>1. Nhap nut "Add Task" (Add task).
+2. Enter thong tin vao task row vua create.
+3. Nhap nut "Add Task" mot lan nua de create dong thu 2.
+4. Enter thong tin cho dong thu 2.
+5. Nhap nut "Remove" (Delete) tai task row thu nhat.</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>1. Một dòng mới xuất hiện với các ô nhập: Tên công việc, Mô tả, Kết quả.
-2. Nhập liệu bình thường.
-3. Dòng thứ 2 được tạo thêm.
-4. Nhập liệu bình thường cho dòng thứ 2.
-5. Dòng thứ nhất bị xóa khỏi bảng, chỉ còn lại dòng thứ 2.</t>
+          <t>1. Mot dong moi xuat hien voi cac o enter: Ten task, Mo ta, Ket qua.
+2. Enter lieu binh thuong.
+3. Dong thu 2 duoc create add.
+4. Enter lieu binh thuong cho dong thu 2.
+5. Dong thu nhat bi delete khoi bang, chi con lai dong thu 2.</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="N12" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F05, Rule 6.6</t>
+          <t>Related to M06-F05, Rule 6.6</t>
         </is>
       </c>
     </row>
@@ -18895,35 +18895,35 @@
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>Ngăn chặn nộp báo cáo khi danh sách công việc trống</t>
+          <t>Prevent submit report khi danh sach task trong</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống bắt buộc báo cáo phải có ít nhất một công việc mới cho phép nộp.</t>
+          <t>Dam bao system bat buoc report phai co it nhat mot task moi allows submit.</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới, các trường thông tin chung đã điền đầy đủ.</t>
+          <t>User is logged in as Student.
+Dang o interface create new report, cac truong thong tin chung da dien day du.</t>
         </is>
       </c>
       <c r="H13" s="28" t="inlineStr">
         <is>
-          <t>TaskList=Empty; Các trường bắt buộc khác hợp lệ</t>
+          <t>TaskList=Empty; Other required fields valid</t>
         </is>
       </c>
       <c r="I13" s="28" t="inlineStr">
         <is>
-          <t>1. Xóa tất cả các dòng công việc trong bảng công việc (hoặc không thêm dòng nào).
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Delete tat ca cac task row trong task table (hoac khong add dong nao).
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J13" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu phải nhập ít nhất một công việc (ví dụ: "At least one task is required").
-Báo cáo không được nộp.</t>
+          <t>System display notification error requires phai enter it nhat mot task (e.g.: "At least one task is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
@@ -18939,11 +18939,11 @@
       </c>
       <c r="N13" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="105" customHeight="1">
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
       <c r="A14" s="21" t="inlineStr">
         <is>
           <t>TC-M06-013</t>
@@ -18966,36 +18966,36 @@
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>Ngăn chặn nộp báo cáo khi có dòng công việc chưa hoàn thành thông tin</t>
+          <t>Prevent submit report khi co task row chua hoan thanh thong tin</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi nếu tồn tại bất kỳ dòng công việc nào bị bỏ trống Tên, Mô tả hoặc Kết quả khi nộp.</t>
+          <t>Verify system bao error neu ton tai bat ky task row nao bi bo trong Ten, Mo ta hoac Ket qua khi submit.</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>TaskName="Code FE"; Description=""; Result="Done" (Để trống phần Mô tả)</t>
+          <t>TaskName="Code FE"; Description=""; Result="Done" (De trong phan Mo ta)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>1. Nhập đầy đủ thông tin chung hợp lệ.
-2. Thêm một dòng công việc, nhập Tên công việc là "Code FE", Kết quả là "Done", bỏ trống Mô tả.
-3. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Enter day du thong tin chung hop le.
+2. Add mot task row, enter Ten task la "Code FE", Ket qua la "Done", bo trong Mo ta.
+3. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi dòng công việc không hợp lệ (ví dụ: "Task fields cannot be left blank").
-Báo cáo không được nộp.</t>
+          <t>System bao error task row khong hop le (e.g.: "Task fields cannot be left blank").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 6.6, Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Rule 6.6, Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -19038,18 +19038,18 @@
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Tự động tính toán số giờ làm việc hàng ngày và tổng số giờ làm việc</t>
+          <t>Auto-calculate so gio lam viec hang ngay va tong so gio lam viec</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tự động tính tổng số giờ làm việc theo tuần và tổng cả kỳ báo cáo khi người dùng nhập số giờ làm việc hàng ngày.</t>
+          <t>Verify functionality for tu dong tinh tong so gio lam viec theo tuan va tong ca ky report khi user enter so gio lam viec hang ngay.</t>
         </is>
       </c>
       <c r="G15" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H15" s="28" t="inlineStr">
@@ -19059,18 +19059,18 @@
       </c>
       <c r="I15" s="28" t="inlineStr">
         <is>
-          <t>1. Nhập số giờ làm việc cho Tuần 1 từ thứ Hai đến chủ nhật lần lượt là: 8, 8, 8, 8, 8, 0, 0.
-2. Nhập số giờ làm việc cho Tuần 2 lần lượt là: 8, 8, 8, 8, 8, 4, 0.
-3. Quan sát tổng số giờ của Tuần 1, Tuần 2 và Tổng số giờ làm việc hiển thị trên giao diện.
-4. Thay đổi số giờ ngày thứ Bảy Tuần 2 từ 4 thành 8.</t>
+          <t>1. Enter so gio lam viec cho Tuan 1 tu thu Hai den Sunday lan luot la: 8, 8, 8, 8, 8, 0, 0.
+2. Enter so gio lam viec cho Tuan 2 lan luot la: 8, 8, 8, 8, 8, 4, 0.
+3. Observe tong so gio cua Tuan 1, Tuan 2 va Tong so gio lam viec display tren interface.
+4. Thay doi so gio ngay thu Bay Tuan 2 tu 4 thanh 8.</t>
         </is>
       </c>
       <c r="J15" s="28" t="inlineStr">
         <is>
-          <t>Tổng số giờ Tuần 1 tự động hiển thị 40.
-Tổng số giờ Tuần 2 tự động hiển thị 44.
-Tổng số giờ làm việc cả kỳ báo cáo tự động hiển thị 84.
-Khi thay đổi ngày thứ Bảy Tuần 2 thành 8, tổng Tuần 2 lập tức cập nhật thành 48 và Tổng số giờ làm việc cập nhật thành 88.</t>
+          <t>Tong so gio Tuan 1 tu dong display 40.
+Tong so gio Tuan 2 tu dong display 44.
+Tong so gio lam viec ca ky report tu dong display 84.
+Khi thay doi ngay thu Bay Tuan 2 thanh 8, tong Tuan 2 lap tuc cap nhat thanh 48 va Tong so gio lam viec cap nhat thanh 88.</t>
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
@@ -19086,7 +19086,7 @@
       </c>
       <c r="N15" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F06, Rule 6.7</t>
+          <t>Related to M06-F06, Rule 6.7</t>
         </is>
       </c>
     </row>
@@ -19113,18 +19113,18 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>Ngăn chặn nhập số giờ làm việc là số âm</t>
+          <t>Prevent enter so gio lam viec la so am</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống không chấp nhận giá trị số giờ làm việc nhỏ hơn 0.</t>
+          <t>Dam bao system khong chap nhan gia tri so gio lam viec nho hon 0.</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -19134,14 +19134,14 @@
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>1. Nhập giá trị -2 vào ô nhập giờ làm việc của ngày bất kỳ.
-2. Nhấn nút "Save as Draft" hoặc "Submit".</t>
+          <t>1. Enter gia tri -2 vao o enter gio lam viec cua ngay bat ky.
+2. Nhan nut "Save as Draft" hoac "Submit".</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi số giờ không hợp lệ hoặc tự động khôi phục về 0/ngăn không cho nhập số âm.
-Báo cáo không được lưu/nộp với giá trị âm.</t>
+          <t>System bao error so gio khong hop le hoac tu dong khoi phuc ve 0/ngan khong cho enter so am.
+Bao cao khong duoc save/submit voi gia tri am.</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
@@ -19157,11 +19157,11 @@
       </c>
       <c r="N16" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Boundary Value Testing (Mục 6.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>Related to Boundary Value Testing (Section 6.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="75" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
           <t>TC-M06-016</t>
@@ -19184,18 +19184,18 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Ngăn chặn nhập số giờ làm việc vượt quá 24 giờ một ngày</t>
+          <t>Prevent enter so gio lam viec exceeding 24 gio mot ngay</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống không chấp nhận giá trị số giờ làm việc lớn hơn 24 giờ cho một ngày.</t>
+          <t>Dam bao system khong chap nhan gia tri so gio lam viec lon hon 24 gio cho mot ngay.</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H17" s="28" t="inlineStr">
@@ -19205,14 +19205,14 @@
       </c>
       <c r="I17" s="28" t="inlineStr">
         <is>
-          <t>1. Nhập giá trị 25 vào ô nhập giờ làm việc của ngày bất kỳ.
-2. Nhấn nút "Save as Draft" hoặc "Submit".</t>
+          <t>1. Enter gia tri 25 vao o enter gio lam viec cua ngay bat ky.
+2. Nhan nut "Save as Draft" hoac "Submit".</t>
         </is>
       </c>
       <c r="J17" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi số giờ không thể vượt quá 24 giờ một ngày.
-Giá trị không được chấp nhận và báo cáo không được lưu/nộp.</t>
+          <t>System bao error so gio cannot exceeding 24 gio mot ngay.
+Gia tri khong duoc chap nhan va report khong duoc save/submit.</t>
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
@@ -19228,7 +19228,7 @@
       </c>
       <c r="N17" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Boundary Value Testing (Mục 6.7)</t>
+          <t>Related to Boundary Value Testing (Section 6.7)</t>
         </is>
       </c>
     </row>
@@ -19255,18 +19255,18 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>Ngăn chặn nhập ký tự không phải số vào ô số giờ làm việc</t>
+          <t>Prevent enter ky tu not so vao o so gio lam viec</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống chỉ chấp nhận dữ liệu số trong ô nhập số giờ làm việc.</t>
+          <t>Dam bao system chi chap nhan du lieu so trong o enter so gio lam viec.</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -19276,13 +19276,13 @@
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>1. Nhập ký tự "abc" vào ô nhập giờ làm việc của ngày bất kỳ.
-2. Kiểm tra giá trị trong ô nhập.</t>
+          <t>1. Enter ky tu "abc" vao o enter gio lam viec cua ngay bat ky.
+2. Verify gia tri trong o enter.</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống tự động loại bỏ ký tự chữ hoặc hiển thị lỗi và không cho phép nhập ký tự phi số.</t>
+          <t>System tu dong loai bo ky tu chu hoac display error va khong allows enter ky tu phi so.</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Boundary Value Testing (Mục 6.7)</t>
+          <t>Related to Boundary Value Testing (Section 6.7)</t>
         </is>
       </c>
     </row>
@@ -19325,37 +19325,37 @@
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thành công với đầy đủ thông tin hợp lệ</t>
+          <t>Submit report successfully voi day du thong tin hop le</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra luồng nộp báo cáo thành công khi điền đầy đủ và đúng định dạng tất cả các thông tin bắt buộc.</t>
+          <t>Verify luong submit report successfully khi dien day du va dung format tat ca cac thong tin bat buoc.</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo thực tập.</t>
+          <t>User is logged in as Student.
+Dang o interface create internship report.</t>
         </is>
       </c>
       <c r="H19" s="28" t="inlineStr">
         <is>
-          <t>CompanySupervisorName="Nguyễn Văn B"; StartDate="2026-07-20"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; TaskName="Implement Login API"; TaskDesc="Develop authentication feature"; TaskResult="Completed successfully"; Week1Hours=[8,8,8,8,8,0,0]; Week2Hours=[8,8,8,8,8,0,0]; Challenges="Gặp khó khăn khi tích hợp OAuth"; SupportNeeded="Cần mentor hỗ trợ review code"</t>
+          <t>CompanySupervisorName="Nguyen Van B"; StartDate="2026-07-20"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; TaskName="Implement Login API"; TaskDesc="Develop authentication feature"; TaskResult="Completed successfully"; Week1Hours=[8,8,8,8,8,0,0]; Week2Hours=[8,8,8,8,8,0,0]; Challenges="Gap kho khan khi tich hop OAuth"; SupportNeeded="Can mentor ho tro review code"</t>
         </is>
       </c>
       <c r="I19" s="28" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin như trong Test Data.
-2. Nhấn nút "Submit" (Nộp báo cáo).
-3. Tại hộp thoại xác nhận "Submit Report", nhấp nút "Confirm" (Xác nhận).</t>
+          <t>1. Dien day du thong tin nhu trong Test Data.
+2. Nhan nut "Submit" (Submit report).
+3. Tai hop thoai xac nhan "Submit Report", click button "Confirm" (Xac nhan).</t>
         </is>
       </c>
       <c r="J19" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nộp báo cáo thành công.
-Trạng thái của báo cáo chuyển sang "Submitted".
-Báo cáo chuyển sang chế độ chỉ đọc.</t>
+          <t>System display notification submit report successfully.
+Status cua report chuyen sang "Submitted".
+Bao cao chuyen sang che do chi doc.</t>
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="N19" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F07, Rule 6.3</t>
+          <t>Related to M06-F07, Rule 6.3</t>
         </is>
       </c>
     </row>
@@ -19398,35 +19398,35 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống tên người giám sát công ty</t>
+          <t>Submit report failed due to empty name nguoi supervisor company</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi để trống trường Tên giám sát của công ty.</t>
+          <t>Verify system bao error khi blank truong Ten supervisor cua company.</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>CompanySupervisorName=""; Các trường khác đều hợp lệ</t>
+          <t>CompanySupervisorName=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Tên giám sát công ty để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Ten supervisor company blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Tên giám sát công ty (ví dụ: "Company Supervisor Name is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires enter Ten supervisor company (e.g.: "Company Supervisor Name is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
@@ -19442,11 +19442,11 @@
       </c>
       <c r="N20" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="75" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
           <t>TC-M06-020</t>
@@ -19469,35 +19469,35 @@
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống email người giám sát PNV</t>
+          <t>Submit report failed do blank email nguoi supervisor PNV</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi để trống trường Email giám sát PNV.</t>
+          <t>Verify system bao error khi blank truong Email supervisor PNV.</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
         <is>
-          <t>PnvSupervisorEmail=""; Các trường khác đều hợp lệ</t>
+          <t>PnvSupervisorEmail=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I21" s="28" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Email giám sát PNV để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Email supervisor PNV blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J21" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Email giám sát PNV (ví dụ: "PNV Supervisor Email is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires enter Email supervisor PNV (e.g.: "PNV Supervisor Email is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="N21" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -19540,35 +19540,35 @@
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do email người giám sát PNV sai định dạng</t>
+          <t>Submit report failed do email nguoi supervisor PNV sai format</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi nhập email giám sát PNV không đúng định dạng.</t>
+          <t>Verify system bao error khi enter email supervisor PNV khong dung format.</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>PnvSupervisorEmail="pnv.sup"; Các trường khác đều hợp lệ</t>
+          <t>PnvSupervisorEmail="pnv.sup"; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Email giám sát PNV nhập là "pnv.sup".
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Email supervisor PNV enter la "pnv.sup".
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi định dạng Email giám sát PNV không hợp lệ (ví dụ: "Invalid PNV Supervisor Email format").
-Báo cáo không được nộp.</t>
+          <t>System bao error format Email supervisor PNV khong hop le (e.g.: "Invalid PNV Supervisor Email format").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="N22" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -19611,35 +19611,35 @@
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống email người giám sát công ty</t>
+          <t>Submit report failed do blank email nguoi supervisor company</t>
         </is>
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi để trống trường Email giám sát công ty.</t>
+          <t>Verify system bao error khi blank truong Email supervisor company.</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
         <is>
-          <t>CompanySupervisorEmail=""; Các trường khác đều hợp lệ</t>
+          <t>CompanySupervisorEmail=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I23" s="28" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Email giám sát công ty để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Email supervisor company blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J23" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu có ít nhất một email giám sát công ty (ví dụ: "Company Supervisor Email is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires co it nhat mot email supervisor company (e.g.: "Company Supervisor Email is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="N23" s="28" t="inlineStr">
         <is>
-          <t>TRÙNG LẶP. Test case này trùng lặp với yêu cầu "At least one valid email address" đã được kiểm tra. Nên được loại bỏ.</t>
+          <t>TRUNG LAP. Test case nay trung lap voi requires "At least one valid email address" da duoc kiem tra. Nen duoc loai bo.</t>
         </is>
       </c>
     </row>
@@ -19682,35 +19682,35 @@
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do email người giám sát công ty sai định dạng</t>
+          <t>Submit report failed do email nguoi supervisor company sai format</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi nhập email giám sát công ty không đúng định dạng email.</t>
+          <t>Verify system bao error khi enter email supervisor company khong dung format email.</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>CompanySupervisorEmail="company.sup@"; Các trường khác đều hợp lệ</t>
+          <t>CompanySupervisorEmail="company.sup@"; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Email giám sát công ty nhập là "company.sup@".
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Email supervisor company enter la "company.sup@".
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi định dạng Email giám sát công ty không hợp lệ (ví dụ: "Invalid Company Supervisor Email format").
-Báo cáo không được nộp.</t>
+          <t>System bao error format Email supervisor company khong hop le (e.g.: "Invalid Company Supervisor Email format").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
@@ -19726,7 +19726,7 @@
       </c>
       <c r="N24" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -19753,35 +19753,35 @@
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống phần mô tả khó khăn (Challenges)</t>
+          <t>Submit report failed do blank phan mo ta kho khan (Challenges)</t>
         </is>
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi trường Khó khăn gặp phải (Challenges) bị bỏ trống khi nộp.</t>
+          <t>Verify system bao error khi truong Kho khan gap phai (Challenges) bi bo trong khi submit.</t>
         </is>
       </c>
       <c r="G25" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H25" s="28" t="inlineStr">
         <is>
-          <t>Challenges=""; Các trường khác đều hợp lệ</t>
+          <t>Challenges=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I25" s="28" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Khó khăn để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Kho khan blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J25" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Khó khăn gặp phải (ví dụ: "Challenges field is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires enter Kho khan gap phai (e.g.: "Challenges field is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K25" s="28" t="inlineStr"/>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="N25" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -19824,35 +19824,35 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống phần hỗ trợ cần thiết (Support Needed)</t>
+          <t>Submit report failed do blank phan ho tro can thiet (Support Needed)</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi trường Hỗ trợ cần thiết (Support Needed) bị bỏ trống khi nộp.</t>
+          <t>Verify system bao error khi truong Ho tro can thiet (Support Needed) bi bo trong khi submit.</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>SupportNeeded=""; Các trường khác đều hợp lệ</t>
+          <t>SupportNeeded=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Hỗ trợ cần thiết để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Ho tro can thiet blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Hỗ trợ cần thiết (ví dụ: "Support Needed field is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires enter Ho tro can thiet (e.g.: "Support Needed field is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr"/>
@@ -19868,7 +19868,7 @@
       </c>
       <c r="N26" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -19895,36 +19895,36 @@
       </c>
       <c r="E27" s="28" t="inlineStr">
         <is>
-          <t>Hủy xác nhận nộp báo cáo</t>
+          <t>Huy xac nhan submit report</t>
         </is>
       </c>
       <c r="F27" s="28" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống không nộp báo cáo nếu người dùng nhấp nút Hủy (Cancel) trên hộp thoại xác nhận nộp.</t>
+          <t>Dam bao system khong submit report neu user click button Huy (Cancel) tren hop thoai xac nhan submit.</t>
         </is>
       </c>
       <c r="G27" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo và đã nhập đầy đủ thông tin hợp lệ.</t>
+          <t>User is logged in as Student.
+Dang o interface create report va da enter day du thong tin hop le.</t>
         </is>
       </c>
       <c r="H27" s="28" t="inlineStr">
         <is>
-          <t>Các thông tin hợp lệ</t>
+          <t>Cac thong tin hop le</t>
         </is>
       </c>
       <c r="I27" s="28" t="inlineStr">
         <is>
-          <t>1. Nhấp nút "Submit".
-2. Khi hộp thoại xác nhận "Submit Report" hiện lên, nhấp nút "Cancel" (Hủy) hoặc nút đóng hộp thoại.</t>
+          <t>1. Nhap nut "Submit".
+2. Khi hop thoai xac nhan "Submit Report" hien len, click button "Cancel" (Huy) hoac nut dong hop thoai.</t>
         </is>
       </c>
       <c r="J27" s="28" t="inlineStr">
         <is>
-          <t>Hộp thoại đóng lại.
-Báo cáo không được nộp và trạng thái vẫn là nháp hoặc chưa lưu.
-Người dùng vẫn có thể tiếp tục chỉnh sửa báo cáo.</t>
+          <t>Hop thoai dong lai.
+Bao cao khong duoc submit va status van la draft hoac chua save.
+Nguoi dung van can tiep tuc edit report.</t>
         </is>
       </c>
       <c r="K27" s="28" t="inlineStr"/>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="N27" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 6.3, Workflow</t>
+          <t>Related to Rule 6.3, Workflow</t>
         </is>
       </c>
     </row>
@@ -19967,18 +19967,18 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Báo cáo đã nộp chuyển sang trạng thái chỉ đọc mãi mãi</t>
+          <t>Bao cao da submit chuyen sang status chi doc mai mai</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo báo cáo sau khi nộp (Submitted) sẽ bị khóa, không thể chỉnh sửa hay xóa bởi học viên.</t>
+          <t>Dam bao report sau khi submit (Submitted) se bi khoa, cannot edit hay delete boi student.</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Có một báo cáo trong danh sách đã ở trạng thái "Submitted".</t>
+          <t>User is logged in as Student.
+Co mot report trong danh sach da o status "Submitted".</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -19988,16 +19988,16 @@
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>1. Mở xem chi tiết báo cáo đã nộp.
-2. Kiểm tra sự xuất hiện của nút "Edit" (Chỉnh sửa), "Save" (Lưu), hoặc "Delete" (Xóa).
-3. Thử nhấp đúp hoặc thay đổi nội dung các trường thông tin.</t>
+          <t>1. Mo xem chi tiet report da submit.
+2. Verify su xuat hien cua nut "Edit" (Edit), "Save" (Save), hoac "Delete" (Delete).
+3. Thu click dup hoac thay doi noi dung cac truong thong tin.</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Nút "Edit" và "Save as Draft" không hiển thị.
-Tất cả các trường thông tin đều ở trạng thái chỉ đọc (disabled/read-only).
-Học viên không thể sửa đổi bất kỳ dữ liệu nào.</t>
+          <t>Nut "Edit" va "Save as Draft" not displayed.
+Tat ca cac truong thong tin deu o status chi doc (disabled/read-only).
+Hoc vien cannot sua doi bat ky du lieu nao.</t>
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr"/>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="N28" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F07, Rule 6.3, Rule 6.11</t>
+          <t>Related to M06-F07, Rule 6.3, Rule 6.11</t>
         </is>
       </c>
     </row>
@@ -20040,38 +20040,38 @@
       </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
-          <t>Gửi email thông báo tự động khi nộp báo cáo thành công</t>
+          <t>Gui email notification tu dong khi submit report successfully</t>
         </is>
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra xem hệ thống có tự động gửi email với đúng định dạng và đúng đối tượng sau khi nộp báo cáo hay không.</t>
+          <t>Verify whether system co tu dong gui email voi dung format va dung doi tuong sau khi submit report hay khong.</t>
         </is>
       </c>
       <c r="G29" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student tên "Nguyễn Văn A", lớp "PNV26A", làm việc tại công ty "TechCorp".
-Hệ thống kết nối email hoạt động bình thường.</t>
+          <t>Nguoi dung da log in voi quyen Student ten "Nguyen Van A", lop "PNV26A", lam viec tai company "TechCorp".
+System ket noi email hoat dong binh thuong.</t>
         </is>
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; BatchName="PNV26A"; Company="TechCorp"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; StudentEmail="student01@student.passerellesnumeriques.org"; StartDate="2026-07-20"; EndDate="2026-08-02"</t>
+          <t>StudentName="Nguyen Van A"; BatchName="PNV26A"; Company="TechCorp"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; StudentEmail="student01@student.passerellesnumeriques.org"; StartDate="2026-07-20"; EndDate="2026-08-02"</t>
         </is>
       </c>
       <c r="I29" s="28" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin báo cáo của học viên "Nguyễn Văn A" làm việc tại "TechCorp" từ ngày "2026-07-20" đến "2026-08-02".
-2. Nhấp nút "Submit" và xác nhận nộp báo cáo.
-3. Kiểm tra email nhận được từ tài khoản PNV Supervisor, Company Supervisor và học viên.</t>
+          <t>1. Dien day du thong tin report cua student "Nguyen Van A" lam viec tai "TechCorp" tu ngay "2026-07-20" den "2026-08-02".
+2. Nhap nut "Submit" va xac nhan submit report.
+3. Verify email nhan duoc tu account PNV Supervisor, Company Supervisor va student.</t>
         </is>
       </c>
       <c r="J29" s="28" t="inlineStr">
         <is>
-          <t>1. Báo cáo nộp thành công.
-2. Email được tự động gửi đến địa chỉ "pnv.sup@passerellesnumeriques.org" và "company.sup@example.com".
-3. Email được gửi CC cho "student01@student.passerellesnumeriques.org" và "ero.vietnam@passerellesnumeriques.org".
-4. Tiêu đề email có định dạng chính xác: "[PNV26A] [Bi-Weekly Internship Report] Nguyễn Văn A - TechCorp (Period: 20/07 – 02/08)"</t>
+          <t>1. Bao cao submit successfully.
+2. Email duoc tu dong gui den dia chi "pnv.sup@passerellesnumeriques.org" va "company.sup@example.com".
+3. Email duoc gui CC cho "student01@student.passerellesnumeriques.org" va "ero.vietnam@passerellesnumeriques.org".
+4. Tieu de email co format chinh xac: "[PNV26A] [Bi-Weekly Internship Report] Nguyen Van A - TechCorp (Period: 20/07 – 02/08)"</t>
         </is>
       </c>
       <c r="K29" s="28" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="N29" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F08, Rule 6.10</t>
+          <t>Related to M06-F08, Rule 6.10</t>
         </is>
       </c>
     </row>
@@ -20114,36 +20114,36 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Xử lý lỗi khi gửi email thông báo thất bại</t>
+          <t>Xu ly error khi gui email notification failed</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống vẫn ghi nhận nộp báo cáo thành công và hiển thị cảnh báo nếu quá trình gửi email tự động bị lỗi.</t>
+          <t>Dam bao system van ghi nhan submit report successfully va display cphoto bao neu qua trinh gui email tu dong bi error.</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Hệ thống email bị lỗi kết nối hoặc tài khoản gửi bị chặn.</t>
+          <t>User is logged in as Student.
+System email bi error ket noi hoac account gui bi chan.</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>Các thông tin hợp lệ</t>
+          <t>Cac thong tin hop le</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin báo cáo hợp lệ.
-2. Nhấp nút "Submit" và xác nhận nộp báo cáo.</t>
+          <t>1. Dien day du thong tin report hop le.
+2. Nhap nut "Submit" va xac nhan submit report.</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị cảnh báo lỗi gửi email (ví dụ: "Email notification failed: [Reason]").
-Báo cáo vẫn được nộp thành công và trạng thái chuyển sang "Submitted" bình thường.
-Dữ liệu báo cáo bị khóa thành chỉ đọc.</t>
+          <t>System display cphoto bao error gui email (e.g.: "Email notification failed: [Reason]").
+Bao cao van duoc submit successfully va status chuyen sang "Submitted" binh thuong.
+Du lieu report bi khoa thanh chi doc.</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr"/>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="N30" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 6.11, Error Handling (Mục 8)</t>
+          <t>Related to Rule 6.11, Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -20186,37 +20186,37 @@
       </c>
       <c r="E31" s="28" t="inlineStr">
         <is>
-          <t>Staff xem báo cáo thực tập của học viên</t>
+          <t>Staff xem internship report cua student</t>
         </is>
       </c>
       <c r="F31" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra xem tài khoản Staff có thể xem được nội dung chi tiết báo cáo đã nộp của học viên hay không.</t>
+          <t>Verify whether account Staff can xem duoc noi dung chi tiet report da submit cua student hay khong.</t>
         </is>
       </c>
       <c r="G31" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học viên "Nguyễn Văn A" đã nộp báo cáo thực tập.</t>
+          <t>User is logged in as Staff.
+Hoc vien "Nguyen Van A" da submit internship report.</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; ReportStatus="Submitted"</t>
+          <t>StudentName="Nguyen Van A"; ReportStatus="Submitted"</t>
         </is>
       </c>
       <c r="I31" s="28" t="inlineStr">
         <is>
-          <t>1. Đăng nhập với quyền Staff.
-2. Truy cập vào trang chi tiết học viên "Nguyễn Văn A".
-3. Tìm phần Báo cáo thực tập của học viên.
-4. Nhấp vào xem chi tiết báo cáo đã nộp.</t>
+          <t>1. Log in voi quyen Staff.
+2. Truy cap vao trang chi tiet student "Nguyen Van A".
+3. Tim phan Bao cao internship cua student.
+4. Nhap vao xem chi tiet report da submit.</t>
         </is>
       </c>
       <c r="J31" s="28" t="inlineStr">
         <is>
-          <t>Staff có thể xem đầy đủ nội dung chi tiết của báo cáo học viên đã nộp.
-Báo cáo hiển thị chính xác các thông tin học viên đã điền.</t>
+          <t>Staff can xem day du noi dung chi tiet cua report student da submit.
+Bao cao display chinh xac cac thong tin student da dien.</t>
         </is>
       </c>
       <c r="K31" s="28" t="inlineStr"/>
@@ -20232,7 +20232,7 @@
       </c>
       <c r="N31" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F09, Rule 6.12</t>
+          <t>Related to M06-F09, Rule 6.12</t>
         </is>
       </c>
     </row>
@@ -20259,35 +20259,35 @@
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>Staff không thể sửa hoặc xóa báo cáo của học viên</t>
+          <t>Staff cannot sua hoac delete report cua student</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>Đảm bảo Staff chỉ có quyền xem (Read-only) và không thể thay đổi thông tin hoặc xóa báo cáo của học viên.</t>
+          <t>Dam bao Staff chi co quyen xem (Read-only) va cannot thay doi thong tin hoac delete report cua student.</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở màn hình xem chi tiết báo cáo của học viên "Nguyễn Văn A".</t>
+          <t>User is logged in as Staff.
+Dang o man hinh xem chi tiet report cua student "Nguyen Van A".</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"</t>
+          <t>StudentName="Nguyen Van A"</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>1. Kiểm tra sự xuất hiện của các nút chỉnh sửa (Edit), lưu (Save), hoặc xóa (Delete) báo cáo.
-2. Thử thay đổi giá trị trong các trường thông tin của báo cáo học viên.</t>
+          <t>1. Verify su xuat hien cua cac nut edit (Edit), save (Save), hoac delete (Delete) report.
+2. Thu thay doi gia tri trong cac truong thong tin cua report student.</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>Không có bất kỳ nút hoặc tuỳ chọn chỉnh sửa/xóa nào hiển thị với tài khoản Staff.
-Tất cả các trường thông tin đều bị khóa, không thể tương tác thay đổi giá trị.</t>
+          <t>Khong co bat ky nut hoac tuy select edit/delete nao display voi account Staff.
+Tat ca cac truong thong tin deu bi khoa, cannot tuong tac thay doi gia tri.</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr"/>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="N32" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Staff Access (Rule 6.12)</t>
+          <t>Related to Staff Access (Rule 6.12)</t>
         </is>
       </c>
     </row>
@@ -20441,18 +20441,18 @@
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>Đổi tên Category với tên hợp lệ</t>
+          <t>Rename Category with a valid name</t>
         </is>
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng đổi tên danh mục (Category) khi nhập tên mới hợp lệ.</t>
+          <t>Verify functionality for doi ten category (Category) khi enter ten moi hop le.</t>
         </is>
       </c>
       <c r="G2" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập (Training Materials).</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H2" s="23" t="inlineStr">
@@ -20462,17 +20462,17 @@
       </c>
       <c r="I2" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn danh mục "IT".
-2. Nhấp nút "Đổi tên" (Rename).
-3. Nhập tên mới là "Information Technology".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Nhap select category "IT".
+2. Nhap nut "Rename" (Rename).
+3. Enter ten moi la "Information Technology".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J2" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo cập nhật thành công.
-Tên danh mục được thay đổi thành "Information Technology" trên giao diện.
-Các khóa học bên trong danh mục vẫn giữ nguyên.</t>
+          <t>System display notification cap nhat successfully.
+Ten category duoc thay doi thanh "Information Technology" tren interface.
+Cac course ben trong category van giu nguyen.</t>
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="N2" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F02, Rule 5.1</t>
+          <t>Related to M07-F02, Rule 5.1</t>
         </is>
       </c>
     </row>
@@ -20515,18 +20515,18 @@
       </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
-          <t>Đổi tên Category thất bại do để trống tên</t>
+          <t>Category rename fails due to empty name</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn việc đổi tên danh mục thành rỗng.</t>
+          <t>Verify system bao error va ngan chan viec doi ten category thanh rong.</t>
         </is>
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Đổi tên Category.</t>
+          <t>User is logged in as Staff.
+Currently on Rename Category interface.</t>
         </is>
       </c>
       <c r="H3" s="28" t="inlineStr">
@@ -20536,14 +20536,14 @@
       </c>
       <c r="I3" s="28" t="inlineStr">
         <is>
-          <t>1. Xóa toàn bộ nội dung trong ô nhập tên danh mục.
-2. Nhấp nút "Lưu" (Save).</t>
+          <t>1. Delete toan bo noi dung trong o enter ten category.
+2. Nhap nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J3" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu nhập tên danh mục (ví dụ: "Category Name is required.").
-Tên danh mục cũ không bị thay đổi.</t>
+          <t>System display notification error requires enter ten category (e.g.: "Category Name is required.").
+Ten category cu khong bi thay doi.</t>
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="N3" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -20586,18 +20586,18 @@
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra không hỗ trợ chức năng Lưu trữ và Xóa đối với Category</t>
+          <t>Verify Archive and Delete functions are not supported for Category</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không hiển thị các chức năng Lưu trữ (Archive) và Xóa (Delete) đối với danh mục.</t>
+          <t>Verify system not displayed cac chuc nang Archive (Archive) va Delete (Delete) for category.</t>
         </is>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H4" s="23" t="inlineStr">
@@ -20607,13 +20607,13 @@
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn danh mục "English".
-2. Quan sát các nút chức năng và menu ngữ cảnh liên quan đến danh mục.</t>
+          <t>1. Nhap select category "English".
+2. Observe cac nut chuc nang va menu ngu cphoto lien quan den category.</t>
         </is>
       </c>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t>Không hiển thị nút hoặc tùy chọn "Xóa" (Delete) hoặc "Lưu trữ" (Archive) đối với danh mục.</t>
+          <t>Khong display nut hoac tuy select "Delete" (Delete) hoac "Archive" (Archive) for category.</t>
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="N4" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F02, Rule 5.1, Out of Scope (Mục 13)</t>
+          <t>Related to M07-F02, Rule 5.1, Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>
@@ -20656,18 +20656,18 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Xác minh các Category mặc định tồn tại trong hệ thống</t>
+          <t>Verify default Categories exist in system</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra 5 danh mục mặc định được tạo sẵn khi hệ thống hoạt động.</t>
+          <t>Verify 5 category mac dinh duoc create san khi system hoat dong.</t>
         </is>
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H5" s="28" t="inlineStr">
@@ -20677,12 +20677,12 @@
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>1. Quan sát danh sách các danh mục hiển thị trên màn hình.</t>
+          <t>1. Observe danh sach cac category display tren man hinh.</t>
         </is>
       </c>
       <c r="J5" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị đầy đủ 5 danh mục mặc định: "IT", "English", "PLT", "DA", và "Workshops".</t>
+          <t>System display day du 5 category mac dinh: "IT", "English", "PLT", "DA", va "Workshops".</t>
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="N5" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Mục 3 (Default Categories)</t>
+          <t>Related to M07-F01, Section 3 (Default Categories)</t>
         </is>
       </c>
     </row>
@@ -20725,18 +20725,18 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Tạo khóa học (Course) mới với thông tin hợp lệ</t>
+          <t>Create new course with valid information</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tạo khóa học mới dưới một danh mục khi nhập đầy đủ thông tin hợp lệ.</t>
+          <t>Verify functionality for create new course duoi mot category khi enter day du thong tin hop le.</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -20746,16 +20746,16 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn danh mục "IT".
-2. Nhấp nút "Tạo khóa học" (Create Course).
-3. Nhập tên khóa học là "Java Programming".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select category "IT".
+2. Nhap nut "Create course" (Create Course).
+3. Enter ten course la "Java Programming".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tạo thành công.
-Khóa học "Java Programming" hiển thị dưới danh mục "IT".</t>
+          <t>System display notification create successfully.
+Khoa hoc "Java Programming" display duoi category "IT".</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.2</t>
+          <t>Related to M07-F01, Rule 5.2</t>
         </is>
       </c>
     </row>
@@ -20798,18 +20798,18 @@
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>Tạo khóa học mới thất bại do để trống tên</t>
+          <t>New course creation fails due to empty name</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn tạo khóa học nếu tên khóa học trống.</t>
+          <t>Verify system bao error va ngan chan create course neu ten course trong.</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Tạo khóa học mới.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Course interface.</t>
         </is>
       </c>
       <c r="H7" s="28" t="inlineStr">
@@ -20819,14 +20819,14 @@
       </c>
       <c r="I7" s="28" t="inlineStr">
         <is>
-          <t>1. Để trống trường Tên khóa học.
-2. Nhấp "Lưu" (Save).</t>
+          <t>1. De trong truong Ten course.
+2. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị lỗi yêu cầu nhập tên khóa học (ví dụ: "Course Name is required.").
-Khóa học mới không được tạo.</t>
+          <t>System display error requires enter ten course (e.g.: "Course Name is required.").
+Khoa hoc moi khong duoc create.</t>
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
@@ -20842,7 +20842,7 @@
       </c>
       <c r="N7" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -20869,18 +20869,18 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Chỉnh sửa tên khóa học với thông tin hợp lệ</t>
+          <t>Edit course name with valid information</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng chỉnh sửa tên khóa học thành công.</t>
+          <t>Verify functionality for edit ten course successfully.</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập. Khóa học "Java Programming" đã tồn tại.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface. Khoa hoc "Java Programming" da ton tai.</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -20890,16 +20890,16 @@
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp chọn "Chỉnh sửa" (Edit).
-3. Thay đổi tên khóa học thành "Advanced Java Programming".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select course "Java Programming".
+2. Nhap select "Edit" (Edit).
+3. Thay doi ten course thanh "Advanced Java Programming".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu thành công.
-Tên khóa học cập nhật thành "Advanced Java Programming" trên màn hình.</t>
+          <t>System display notification save successfully.
+Ten course cap nhat thanh "Advanced Java Programming" tren man hinh.</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
@@ -20915,7 +20915,7 @@
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.2</t>
+          <t>Related to M07-F01, Rule 5.2</t>
         </is>
       </c>
     </row>
@@ -20942,18 +20942,18 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>Lưu trữ khóa học (Archive Course)</t>
+          <t>Archive course (Archive Course)</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng lưu trữ khóa học.</t>
+          <t>Verify functionality for archive course.</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang ở trạng thái Hoạt động (Active) và có các bài học/bài kiểm tra bên dưới.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang o status Hoat dong (Active) va co cac session/exam ben duoi.</t>
         </is>
       </c>
       <c r="H9" s="28" t="inlineStr">
@@ -20963,15 +20963,15 @@
       </c>
       <c r="I9" s="28" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn khóa học "Java Programming".
-2. Nhấp chọn nút "Lưu trữ" (Archive).
-3. Xác nhận lưu trữ nếu hệ thống yêu cầu.</t>
+          <t>1. Nhap select course "Java Programming".
+2. Nhap select nut "Archive" (Archive).
+3. Xac nhan archive neu system requires.</t>
         </is>
       </c>
       <c r="J9" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu trữ thành công.
-Khóa học thay đổi trạng thái sang đã lưu trữ (Archived) và bị ẩn đi hoặc hiển thị dưới dạng lưu trữ trên màn hình quản lý.</t>
+          <t>System display notification archive successfully.
+Khoa hoc thay doi status sang da archive (Archived) va bi an di hoac display as archive tren man hinh quan ly.</t>
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="N9" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F03, Rule 5.2, Rule 5.3</t>
+          <t>Related to M07-F03, Rule 5.2, Rule 5.3</t>
         </is>
       </c>
     </row>
@@ -21014,18 +21014,18 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Khôi phục khóa học đã lưu trữ (Restore Course)</t>
+          <t>Khoi phuc course da archive (Restore Course)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng khôi phục một khóa học đã bị lưu trữ.</t>
+          <t>Verify functionality for khoi phuc mot course da bi archive.</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang ở trạng thái Lưu trữ (Archived).</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang o status Archive (Archived).</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -21035,15 +21035,15 @@
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>1. Tìm và chọn khóa học "Java Programming" trong danh sách lưu trữ.
-2. Nhấp chọn nút "Khôi phục" (Restore).
-3. Xác nhận khôi phục nếu hệ thống yêu cầu.</t>
+          <t>1. Tim va select course "Java Programming" trong danh sach archive.
+2. Nhap select nut "Khoi phuc" (Restore).
+3. Xac nhan khoi phuc neu system requires.</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo khôi phục thành công.
-Khóa học trở lại trạng thái hoạt động bình thường.</t>
+          <t>System display notification khoi phuc successfully.
+Khoa hoc tro lai status hoat dong binh thuong.</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="N10" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F03, Rule 5.2, Rule 5.3</t>
+          <t>Related to M07-F03, Rule 5.2, Rule 5.3</t>
         </is>
       </c>
     </row>
@@ -21086,18 +21086,18 @@
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra không hỗ trợ xóa vĩnh viễn khóa học</t>
+          <t>Verify khong ho tro permanently deleted course</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không cho phép xóa vĩnh viễn khóa học khỏi cơ sở dữ liệu.</t>
+          <t>Verify system khong allows permanently deleted course khoi co so du lieu.</t>
         </is>
       </c>
       <c r="G11" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Tài liệu học tập.</t>
+          <t>User is logged in as Staff.
+Currently on Training Materials Management interface.</t>
         </is>
       </c>
       <c r="H11" s="28" t="inlineStr">
@@ -21107,13 +21107,13 @@
       </c>
       <c r="I11" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Kiểm tra các nút chức năng và menu hành động liên quan đến khóa học.</t>
+          <t>1. Select course "Java Programming".
+2. Verify cac nut chuc nang va menu hanh dong lien quan den course.</t>
         </is>
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>Không có tùy chọn "Xóa vĩnh viễn" hoặc "Delete" cho khóa học, chỉ có tùy chọn "Lưu trữ" (Archive).</t>
+          <t>Khong co tuy select "Delete vinh vien" hoac "Delete" cho course, chi co tuy select "Archive" (Archive).</t>
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="N11" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.2 (Permanent deletion is not allowed), Out of Scope (Mục 13)</t>
+          <t>Related to Rule 5.2 (Permanent deletion is not allowed), Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>
@@ -21156,37 +21156,37 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Tạo bài học (Session) mới với thông tin hợp lệ</t>
+          <t>Create session (Session) moi voi thong tin hop le</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tạo bài học mới dưới một khóa học hoạt động.</t>
+          <t>Verify functionality for create session moi duoi mot course hoat dong.</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang hoạt động.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang hoat dong.</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
-          <t>CourseName="Java Programming"; SessionName="Session 01: OOP Basics"; LessonNumber=1; Description="Giới thiệu về lập trình hướng đối tượng"</t>
+          <t>CourseName="Java Programming"; SessionName="Session 01: OOP Basics"; LessonNumber=1; Description="Gioi thieu ve lap trinh huong doi tuong"</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp nút "Thêm bài học" (Add Session).
-3. Nhập Tên bài học là "Session 01: OOP Basics", số bài học là "1", mô tả là "Giới thiệu về lập trình hướng đối tượng".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select course "Java Programming".
+2. Nhap nut "Add session" (Add Session).
+3. Enter Ten session la "Session 01: OOP Basics", so session la "1", mo ta la "Gioi thieu ve lap trinh huong doi tuong".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tạo thành công.
-Session mới hiển thị dưới khóa học "Java Programming".</t>
+          <t>System display notification create successfully.
+Session moi display duoi course "Java Programming".</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="N12" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.4</t>
+          <t>Related to M07-F01, Rule 5.4</t>
         </is>
       </c>
     </row>
@@ -21229,18 +21229,18 @@
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>Tạo bài học mới thất bại do để trống tên bài học</t>
+          <t>Create session moi failed due to empty name session</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi và ngăn chặn tạo bài học nếu tên bài học trống.</t>
+          <t>Verify system bao error va ngan chan create session neu ten session trong.</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Thêm bài học mới.</t>
+          <t>User is logged in as Staff.
+Dang o interface Add session moi.</t>
         </is>
       </c>
       <c r="H13" s="28" t="inlineStr">
@@ -21250,15 +21250,15 @@
       </c>
       <c r="I13" s="28" t="inlineStr">
         <is>
-          <t>1. Để trống trường Tên bài học.
-2. Nhập các trường thông tin khác hợp lệ.
-3. Nhấp "Lưu" (Save).</t>
+          <t>1. De trong truong Ten session.
+2. Enter cac truong thong tin khac hop le.
+3. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J13" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu nhập Tên bài học (ví dụ: "Session Name is required.").
-Bài học mới không được tạo.</t>
+          <t>System display notification error requires enter Ten session (e.g.: "Session Name is required.").
+Bai hoc moi khong duoc create.</t>
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
@@ -21274,7 +21274,7 @@
       </c>
       <c r="N13" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -21301,37 +21301,37 @@
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>Chỉnh sửa chi tiết bài học (Edit Session)</t>
+          <t>Edit chi tiet session (Edit Session)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng sửa thông tin bài học thành công.</t>
+          <t>Verify functionality for sua thong tin session successfully.</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học "Session 01: OOP Basics" đã tồn tại dưới khóa học "Java Programming".</t>
+          <t>User is logged in as Staff.
+Bai hoc "Session 01: OOP Basics" da ton tai duoi course "Java Programming".</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>SessionOldName="Session 01: OOP Basics"; SessionNewName="Session 01: Advanced OOP Basics"; LessonNumber=2; Description="Mô tả mới"</t>
+          <t>SessionOldName="Session 01: OOP Basics"; SessionNewName="Session 01: Advanced OOP Basics"; LessonNumber=2; Description="Mo ta moi"</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn bài học "Session 01: OOP Basics".
-2. Nhấp chọn "Chỉnh sửa" (Edit).
-3. Sửa Tên bài học thành "Session 01: Advanced OOP Basics", Lesson Number thành "2", Description thành "Mô tả mới".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select session "Session 01: OOP Basics".
+2. Nhap select "Edit" (Edit).
+3. Sua Ten session thanh "Session 01: Advanced OOP Basics", Lesson Number thanh "2", Description thanh "Mo ta moi".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu thành công.
-Thông tin bài học hiển thị thay đổi mới tương ứng trên giao diện.</t>
+          <t>System display notification save successfully.
+Thong tin session display thay doi moi tuong ung tren interface.</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.4</t>
+          <t>Related to M07-F01, Rule 5.4</t>
         </is>
       </c>
     </row>
@@ -21374,18 +21374,18 @@
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Xóa vĩnh viễn bài học (Delete Session)</t>
+          <t>Delete vinh vien session (Delete Session)</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng xóa vĩnh viễn một bài học và các tài liệu đính kèm bên dưới nó.</t>
+          <t>Verify functionality for permanently deleted mot session va cac tai lieu dinh kem ben duoi no.</t>
         </is>
       </c>
       <c r="G15" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học "Session 01: OOP Basics" đang tồn tại và có tài liệu đính kèm.</t>
+          <t>User is logged in as Staff.
+Bai hoc "Session 01: OOP Basics" dang ton tai va co tai lieu dinh kem.</t>
         </is>
       </c>
       <c r="H15" s="28" t="inlineStr">
@@ -21395,17 +21395,17 @@
       </c>
       <c r="I15" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn bài học "Session 01: OOP Basics".
-2. Nhấp chọn nút "Xóa" (Delete).
-3. Hệ thống hiển thị hộp thoại yêu cầu xác nhận xóa vĩnh viễn.
-4. Nhấp "Đồng ý" (Confirm).</t>
+          <t>1. Select session "Session 01: OOP Basics".
+2. Nhap select nut "Delete" (Delete).
+3. System display hop thoai requires xac nhan permanently deleted.
+4. Nhap "Dong y" (Confirm).</t>
         </is>
       </c>
       <c r="J15" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo xóa thành công.
-Bài học và các tài liệu đính kèm bị xóa vĩnh viễn khỏi hệ thống.
-Hành động không thể hoàn tác.</t>
+          <t>System display notification delete successfully.
+Bai hoc va cac tai lieu dinh kem bi permanently deleted khoi system.
+Hanh dong cannot hoan tac.</t>
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="N15" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F04, Rule 5.4, Error Handling (Mục 9)</t>
+          <t>Related to M07-F04, Rule 5.4, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -21448,18 +21448,18 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>Hủy bỏ thao tác xóa bài học</t>
+          <t>Huy bo thao tac delete session</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra xem khi hủy xác nhận xóa, bài học vẫn được giữ lại.</t>
+          <t>Verify whether khi huy xac nhan delete, session van duoc giu lai.</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học "Session 01: OOP Basics" đang tồn tại.</t>
+          <t>User is logged in as Staff.
+Bai hoc "Session 01: OOP Basics" dang ton tai.</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -21469,16 +21469,16 @@
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn bài học "Session 01: OOP Basics".
-2. Nhấp chọn nút "Xóa" (Delete).
-3. Hệ thống hiển thị hộp thoại xác nhận.
-4. Nhấp chọn "Hủy" (Cancel).</t>
+          <t>1. Select session "Session 01: OOP Basics".
+2. Nhap select nut "Delete" (Delete).
+3. System display hop thoai xac nhan.
+4. Nhap select "Huy" (Cancel).</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>Hộp thoại xác nhận đóng lại.
-Bài học "Session 01: OOP Basics" vẫn tồn tại trong danh sách và không bị xóa.</t>
+          <t>Hop thoai xac nhan dong lai.
+Bai hoc "Session 01: OOP Basics" van ton tai trong danh sach va khong bi delete.</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="N16" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.4, Error Handling (Mục 9)</t>
+          <t>Related to Rule 5.4, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -21521,18 +21521,18 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra không hỗ trợ lưu trữ bài học</t>
+          <t>Verify khong ho tro archive session</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không cho phép lưu trữ bài học, chỉ có thể xóa vĩnh viễn.</t>
+          <t>Verify system khong allows archive session, chi can permanently deleted.</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Bài học.</t>
+          <t>User is logged in as Staff.
+Dang o interface Quan ly Bai hoc.</t>
         </is>
       </c>
       <c r="H17" s="28" t="inlineStr">
@@ -21542,13 +21542,13 @@
       </c>
       <c r="I17" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn bài học "Session 01: OOP Basics".
-2. Kiểm tra các nút chức năng hành động trên bài học.</t>
+          <t>1. Select session "Session 01: OOP Basics".
+2. Verify cac nut chuc nang hanh dong tren session.</t>
         </is>
       </c>
       <c r="J17" s="28" t="inlineStr">
         <is>
-          <t>Không xuất hiện tùy chọn "Lưu trữ" (Archive) đối với bài học. Chỉ hỗ trợ tạo, sửa và xóa vĩnh viễn.</t>
+          <t>Khong xuat hien tuy select "Archive" (Archive) for session. Chi ho tro create, sua va permanently deleted.</t>
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
@@ -21564,7 +21564,7 @@
       </c>
       <c r="N17" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.4, Out of Scope (Mục 13)</t>
+          <t>Related to Rule 5.4, Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>
@@ -21591,18 +21591,18 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>Tạo bài kiểm tra (Exam) mới với thông tin hợp lệ</t>
+          <t>Create exam (Exam) moi voi thong tin hop le</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tạo bài kiểm tra mới dưới một khóa học đang hoạt động.</t>
+          <t>Verify functionality for create exam moi duoi mot course dang hoat dong.</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang hoạt động.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang hoat dong.</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -21612,16 +21612,16 @@
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp nút "Thêm bài kiểm tra" (Add Exam).
-3. Nhập Tên bài kiểm tra là "Midterm Exam".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select course "Java Programming".
+2. Nhap nut "Add exam" (Add Exam).
+3. Enter Ten exam la "Midterm Exam".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tạo thành công.
-Bài kiểm tra "Midterm Exam" hiển thị dưới khóa học "Java Programming".</t>
+          <t>System display notification create successfully.
+Bai kiem tra "Midterm Exam" display duoi course "Java Programming".</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.5</t>
+          <t>Related to M07-F01, Rule 5.5</t>
         </is>
       </c>
     </row>
@@ -21664,18 +21664,18 @@
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>Tạo bài kiểm tra mới thất bại do để trống tên</t>
+          <t>Create exam moi failed due to empty name</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn và báo lỗi nếu tên bài kiểm tra trống.</t>
+          <t>Verify system ngan chan va bao error neu ten exam trong.</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Thêm bài kiểm tra mới.</t>
+          <t>User is logged in as Staff.
+Dang o interface Add exam moi.</t>
         </is>
       </c>
       <c r="H19" s="28" t="inlineStr">
@@ -21685,14 +21685,14 @@
       </c>
       <c r="I19" s="28" t="inlineStr">
         <is>
-          <t>1. Để trống trường Tên bài kiểm tra.
-2. Nhấp "Lưu" (Save).</t>
+          <t>1. De trong truong Ten exam.
+2. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J19" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu nhập Tên bài kiểm tra (ví dụ: "Exam Name is required.").
-Bài kiểm tra không được tạo.</t>
+          <t>System display notification error requires enter Ten exam (e.g.: "Exam Name is required.").
+Bai kiem tra khong duoc create.</t>
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="N19" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -21735,18 +21735,18 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Chỉnh sửa chi tiết bài kiểm tra (Edit Exam)</t>
+          <t>Edit chi tiet exam (Edit Exam)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng thay đổi tên bài kiểm tra thành công.</t>
+          <t>Verify functionality for thay doi ten exam successfully.</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài kiểm tra "Midterm Exam" đã tồn tại dưới khóa học "Java Programming".</t>
+          <t>User is logged in as Staff.
+Bai kiem tra "Midterm Exam" da ton tai duoi course "Java Programming".</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -21756,16 +21756,16 @@
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn bài kiểm tra "Midterm Exam".
-2. Nhấp chọn "Chỉnh sửa" (Edit).
-3. Thay đổi tên thành "Midterm Practical Exam".
-4. Nhấp "Lưu" (Save).</t>
+          <t>1. Select exam "Midterm Exam".
+2. Nhap select "Edit" (Edit).
+3. Thay doi ten thanh "Midterm Practical Exam".
+4. Nhap "Save" (Save).</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu thành công.
-Tên bài kiểm tra được cập nhật thành "Midterm Practical Exam" trên giao diện.</t>
+          <t>System display notification save successfully.
+Ten exam duoc cap nhat thanh "Midterm Practical Exam" tren interface.</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
@@ -21781,7 +21781,7 @@
       </c>
       <c r="N20" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F01, Rule 5.5</t>
+          <t>Related to M07-F01, Rule 5.5</t>
         </is>
       </c>
     </row>
@@ -21808,18 +21808,18 @@
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Xóa vĩnh viễn bài kiểm tra (Delete Exam)</t>
+          <t>Delete vinh vien exam (Delete Exam)</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng xóa vĩnh viễn một bài kiểm tra và các tài liệu đính kèm bên dưới nó.</t>
+          <t>Verify functionality for permanently deleted mot exam va cac tai lieu dinh kem ben duoi no.</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài kiểm tra "Midterm Exam" đang tồn tại và có tài liệu đính kèm.</t>
+          <t>User is logged in as Staff.
+Bai kiem tra "Midterm Exam" dang ton tai va co tai lieu dinh kem.</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
@@ -21829,16 +21829,16 @@
       </c>
       <c r="I21" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn bài kiểm tra "Midterm Exam".
-2. Nhấp nút "Xóa" (Delete).
-3. Xác nhận trên hộp thoại hiển thị bằng cách chọn "Đồng ý" (Confirm).</t>
+          <t>1. Select exam "Midterm Exam".
+2. Nhap nut "Delete" (Delete).
+3. Xac nhan tren hop thoai display bang cach select "Dong y" (Confirm).</t>
         </is>
       </c>
       <c r="J21" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo xóa thành công.
-Bài kiểm tra và các tài liệu đính kèm bị xóa vĩnh viễn khỏi hệ thống.
-Hành động không thể hoàn tác.</t>
+          <t>System display notification delete successfully.
+Bai kiem tra va cac tai lieu dinh kem bi permanently deleted khoi system.
+Hanh dong cannot hoan tac.</t>
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="N21" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F05, Rule 5.5, Error Handling (Mục 9)</t>
+          <t>Related to M07-F05, Rule 5.5, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -21881,18 +21881,18 @@
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>Hủy bỏ thao tác xóa bài kiểm tra</t>
+          <t>Huy bo thao tac delete exam</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra xem bài kiểm tra không bị xóa khi hủy xác nhận.</t>
+          <t>Verify whether exam khong bi delete khi huy xac nhan.</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài kiểm tra "Midterm Exam" đang tồn tại.</t>
+          <t>User is logged in as Staff.
+Bai kiem tra "Midterm Exam" dang ton tai.</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -21902,15 +21902,15 @@
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn bài kiểm tra "Midterm Exam".
-2. Nhấp nút "Xóa" (Delete).
-3. Trên hộp thoại xác nhận, chọn "Hủy" (Cancel).</t>
+          <t>1. Select exam "Midterm Exam".
+2. Nhap nut "Delete" (Delete).
+3. Tren hop thoai xac nhan, select "Huy" (Cancel).</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Hộp thoại đóng lại.
-Bài kiểm tra "Midterm Exam" vẫn tồn tại bình thường.</t>
+          <t>Hop thoai dong lai.
+Bai kiem tra "Midterm Exam" van ton tai binh thuong.</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
@@ -21926,11 +21926,11 @@
       </c>
       <c r="N22" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.5, Error Handling (Mục 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
+          <t>Related to Rule 5.5, Error Handling (Section 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
           <t>TC-M07-022</t>
@@ -21953,18 +21953,18 @@
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra không hỗ trợ lưu trữ bài kiểm tra</t>
+          <t>Verify khong ho tro archive exam</t>
         </is>
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không cho phép lưu trữ bài kiểm tra, chỉ có thể xóa vĩnh viễn.</t>
+          <t>Verify system khong allows archive exam, chi can permanently deleted.</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Bài kiểm tra.</t>
+          <t>User is logged in as Staff.
+Dang o interface Quan ly Bai kiem tra.</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
@@ -21974,13 +21974,13 @@
       </c>
       <c r="I23" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn bài kiểm tra "Midterm Exam".
-2. Kiểm tra các nút hành động trên bài kiểm tra.</t>
+          <t>1. Select exam "Midterm Exam".
+2. Verify cac nut hanh dong tren exam.</t>
         </is>
       </c>
       <c r="J23" s="28" t="inlineStr">
         <is>
-          <t>Không xuất hiện tùy chọn "Lưu trữ" (Archive) đối với bài kiểm tra.</t>
+          <t>Khong xuat hien tuy select "Archive" (Archive) for exam.</t>
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="N23" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.5, Out of Scope (Mục 13)</t>
+          <t>Related to Rule 5.5, Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>
@@ -22023,18 +22023,18 @@
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>Đính kèm một tài liệu hợp lệ vào Session/Exam</t>
+          <t>Dinh kem mot tai lieu hop le vao Session/Exam</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng đính kèm tài liệu thành công khi nhập đủ nhãn và link Google Drive đúng định dạng.</t>
+          <t>Verify functionality for dinh kem tai lieu successfully khi enter du nhan va link Google Drive dung format.</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang tạo hoặc sửa một Session hoặc Exam.</t>
+          <t>User is logged in as Staff.
+Dang create hoac sua mot Session hoac Exam.</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -22044,15 +22044,15 @@
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>1. Ở phần đính kèm tài liệu (Material Attachments), nhập Nhãn (Label) là "Slides".
-2. Nhập URL là "https://drive.google.com/file/d/1A2B3C4D5E/view".
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. O phan dinh kem tai lieu (Material Attachments), enter Nhan (Label) la "Slides".
+2. Enter URL la "https://drive.google.com/file/d/1A2B3C4D5E/view".
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>Tài liệu được lưu thành công.
-Thông tin đính kèm hiển thị chính xác dưới Session/Exam.</t>
+          <t>Tai lieu duoc save successfully.
+Thong tin dinh kem display chinh xac duoi Session/Exam.</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
@@ -22068,7 +22068,7 @@
       </c>
       <c r="N24" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Mục 6 (Material Attachments)</t>
+          <t>Related to M07-F06, Section 6 (Material Attachments)</t>
         </is>
       </c>
     </row>
@@ -22095,18 +22095,18 @@
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>Đính kèm nhiều tài liệu hợp lệ vào Session/Exam</t>
+          <t>Dinh kem nhieu tai lieu hop le vao Session/Exam</t>
         </is>
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra việc đính kèm đồng thời nhiều tài liệu hợp lệ vào cùng một bài học hoặc bài kiểm tra.</t>
+          <t>Verify viec dinh kem dong thoi nhieu tai lieu hop le vao cung mot session hoac exam.</t>
         </is>
       </c>
       <c r="G25" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang tạo hoặc sửa một Session hoặc Exam.</t>
+          <t>User is logged in as Staff.
+Dang create hoac sua mot Session hoac Exam.</t>
         </is>
       </c>
       <c r="H25" s="28" t="inlineStr">
@@ -22116,15 +22116,15 @@
       </c>
       <c r="I25" s="28" t="inlineStr">
         <is>
-          <t>1. Ở dòng tài liệu thứ nhất, nhập Nhãn "Slides" and URL "https://drive.google.com/file/d/111/view".
-2. Nhấp thêm dòng mới.
-3. Ở dòng tài liệu thứ hai, nhập Nhãn "Homework" and URL "https://drive.google.com/file/d/222/view".
-4. Nhấn "Lưu" (Save).</t>
+          <t>1. O dong tai lieu thu nhat, enter Nhan "Slides" and URL "https://drive.google.com/file/d/111/view".
+2. Nhap add dong moi.
+3. O dong tai lieu Monday, enter Nhan "Homework" and URL "https://drive.google.com/file/d/222/view".
+4. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J25" s="28" t="inlineStr">
         <is>
-          <t>Cả hai tài liệu đính kèm đều được lưu thành công và hiển thị đầy đủ trên giao diện.</t>
+          <t>Ca hai tai lieu dinh kem deu duoc save successfully va display day du tren interface.</t>
         </is>
       </c>
       <c r="K25" s="28" t="inlineStr"/>
@@ -22140,7 +22140,7 @@
       </c>
       <c r="N25" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Mục 6</t>
+          <t>Related to M07-F06, Section 6</t>
         </is>
       </c>
     </row>
@@ -22167,18 +22167,18 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>Đính kèm tài liệu với dòng hoàn toàn trống (bỏ qua dòng)</t>
+          <t>Dinh kem tai lieu voi dong hoan toan trong (bo qua dong)</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra xem hệ thống tự động bỏ qua và không báo lỗi khi có dòng tài liệu trống (cả Label và URL đều rỗng).</t>
+          <t>Verify whether system tu dong bo qua va khong bao error khi co dong tai lieu trong (ca Label va URL deu rong).</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chỉnh sửa hoặc tạo mới Session/Exam.</t>
+          <t>User is logged in as Staff.
+Dang edit hoac create moi Session/Exam.</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -22188,15 +22188,15 @@
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>1. Thêm một dòng đính kèm tài liệu mới.
-2. Để trống cả hai trường Nhãn (Label) và URL.
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. Add mot dong dinh kem tai lieu moi.
+2. De trong ca hai truong Nhan (Label) va URL.
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống lưu trữ thành công các thông tin khác.
-Dòng trống tự động bị bỏ qua (skipped) mà không hiển thị bất kỳ thông báo lỗi nào.</t>
+          <t>System archive successfully cac thong tin khac.
+Dong trong tu dong bi bo qua (skipped) ma not displayed bat ky notification error nao.</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr"/>
@@ -22212,7 +22212,7 @@
       </c>
       <c r="N26" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Rule 6 (Empty Attachment Rows), Error Handling (Mục 9)</t>
+          <t>Related to M07-F06, Rule 6 (Empty Attachment Rows), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -22239,36 +22239,36 @@
       </c>
       <c r="E27" s="28" t="inlineStr">
         <is>
-          <t>Đính kèm thất bại do có Nhãn (Label) nhưng để trống URL</t>
+          <t>Dinh kem failed do co Nhan (Label) nhung blank URL</t>
         </is>
       </c>
       <c r="F27" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn lưu và báo lỗi khi nhập nhãn tài liệu nhưng không có link.</t>
+          <t>Verify system ngan chan save va bao error khi enter nhan tai lieu nhung khong co link.</t>
         </is>
       </c>
       <c r="G27" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chỉnh sửa hoặc tạo mới Session/Exam.</t>
+          <t>User is logged in as Staff.
+Dang edit hoac create moi Session/Exam.</t>
         </is>
       </c>
       <c r="H27" s="28" t="inlineStr">
         <is>
-          <t>Label="Sách tham khảo"; URL=""</t>
+          <t>Label="Sach tham khao"; URL=""</t>
         </is>
       </c>
       <c r="I27" s="28" t="inlineStr">
         <is>
-          <t>1. Nhập Nhãn (Label) là "Sách tham khảo".
-2. Để trống trường URL.
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. Enter Nhan (Label) la "Sach tham khao".
+2. De trong truong URL.
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J27" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập URL cho tài liệu (ví dụ: "URL is required when Label is provided.").
-Tài liệu không được lưu.</t>
+          <t>System bao error requires enter URL cho tai lieu (e.g.: "URL is required when Label is provided.").
+Tai lieu khong duoc save.</t>
         </is>
       </c>
       <c r="K27" s="28" t="inlineStr"/>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="N27" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to M07-F06, Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -22311,18 +22311,18 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Đính kèm thất bại do có URL nhưng để trống Nhãn (Label)</t>
+          <t>Dinh kem failed do co URL nhung blank Nhan (Label)</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn lưu và báo lỗi khi nhập link tài liệu nhưng để trống nhãn.</t>
+          <t>Verify system ngan chan save va bao error khi enter link tai lieu nhung blank nhan.</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chỉnh sửa hoặc tạo mới Session/Exam.</t>
+          <t>User is logged in as Staff.
+Dang edit hoac create moi Session/Exam.</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -22332,15 +22332,15 @@
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>1. Để trống trường Nhãn (Label).
-2. Nhập URL là "https://drive.google.com/file/d/1A2B3/view".
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. De trong truong Nhan (Label).
+2. Enter URL la "https://drive.google.com/file/d/1A2B3/view".
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Nhãn cho tài liệu (ví dụ: "Label is required when URL is provided.").
-Tài liệu không được lưu.</t>
+          <t>System bao error requires enter Nhan cho tai lieu (e.g.: "Label is required when URL is provided.").
+Tai lieu khong duoc save.</t>
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr"/>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="N28" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to M07-F06, Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -22383,36 +22383,36 @@
       </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
-          <t>Đính kèm thất bại do link không phải Google Drive</t>
+          <t>Dinh kem failed do link not Google Drive</t>
         </is>
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn lưu và báo lỗi định dạng khi nhập link từ dịch vụ lưu trữ khác.</t>
+          <t>Verify system ngan chan save va bao error format khi enter link tu dich vu archive khac.</t>
         </is>
       </c>
       <c r="G29" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chỉnh sửa hoặc tạo mới Session/Exam.</t>
+          <t>User is logged in as Staff.
+Dang edit hoac create moi Session/Exam.</t>
         </is>
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>Label="Tài liệu"; URL="https://dropbox.com/s/abcdef"</t>
+          <t>Label="Tai lieu"; URL="https://dropbox.com/s/abcdef"</t>
         </is>
       </c>
       <c r="I29" s="28" t="inlineStr">
         <is>
-          <t>1. Nhập Nhãn "Tài liệu".
-2. Nhập URL là "https://dropbox.com/s/abcdef".
-3. Nhấn "Lưu" (Save).</t>
+          <t>1. Enter Nhan "Tai lieu".
+2. Enter URL la "https://dropbox.com/s/abcdef".
+3. Nhan "Save" (Save).</t>
         </is>
       </c>
       <c r="J29" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị lỗi kiểm tra định dạng URL (ví dụ: "Must start with https://drive.google.com/").
-Tài liệu không được lưu.</t>
+          <t>System display error kiem tra format URL (e.g.: "Must start with https://drive.google.com/").
+Tai lieu khong duoc save.</t>
         </is>
       </c>
       <c r="K29" s="28" t="inlineStr"/>
@@ -22428,7 +22428,7 @@
       </c>
       <c r="N29" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F06, Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to M07-F06, Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -22455,18 +22455,18 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Xuất danh sách Session ra file CSV (Export CSV)</t>
+          <t>Xuat danh sach Session ra file CSV (Export CSV)</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tải file CSV chứa thông tin các bài học của khóa học hiện tại.</t>
+          <t>Verify functionality for tai file CSV chua thong tin cac session cua course hien tai.</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện danh sách Session của khóa học "Java Programming" chứa các bài học và tài liệu.</t>
+          <t>User is logged in as Staff.
+Dang o interface danh sach Session cua course "Java Programming" chua cac session va tai lieu.</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
@@ -22476,15 +22476,15 @@
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấp nút "Xuất CSV" (Export CSV).</t>
+          <t>1. Nhap nut "Xuat CSV" (Export CSV).</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống tải về một file CSV thành công.
-File CSV có các cột: Session ID, Session Name, Lesson Number, Description.
-Thông tin các bài học khớp với danh sách hiển thị trên hệ thống.
-Tài liệu đính kèm (Google Drive link) KHÔNG được xuất hiện trong file.</t>
+          <t>System tai ve mot file CSV successfully.
+File CSV co cac cot: Session ID, Session Name, Lesson Number, Description.
+Thong tin cac session khop voi danh sach display tren system.
+Tai lieu dinh kem (Google Drive link) KHONG duoc xuat hien trong file.</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr"/>
@@ -22500,11 +22500,11 @@
       </c>
       <c r="N30" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7 (Export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="120" customHeight="1">
+          <t>Related to M07-F07, Rule 7 (Export)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="135" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
           <t>TC-M07-030</t>
@@ -22527,38 +22527,38 @@
       </c>
       <c r="E31" s="28" t="inlineStr">
         <is>
-          <t>Nhập CSV - Cập nhật thông tin Session đã tồn tại</t>
+          <t>Enter CSV - Cap nhat thong tin Session da ton tai</t>
         </is>
       </c>
       <c r="F31" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống cập nhật chính xác tên, số bài và mô tả của session khi Session ID trong file CSV trùng khớp với session có sẵn.</t>
+          <t>Verify system cap nhat chinh xac ten, so bai va mo ta cua session khi Session ID trong file CSV trung khop voi session co san.</t>
         </is>
       </c>
       <c r="G31" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học với ID "S001" đã tồn tại dưới khóa học "Java Programming" có tên cũ là "OOP Intro".</t>
+          <t>User is logged in as Staff.
+Bai hoc voi ID "S001" da ton tai duoi course "Java Programming" co ten cu la "OOP Intro".</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
         <is>
-          <t>File CSV chứa dòng: Session ID="S001"; Session Name="OOP Basics"; Lesson Number="1"; Description="Giới thiệu hướng đối tượng"</t>
+          <t>File CSV chua dong: Session ID="S001"; Session Name="OOP Basics"; Lesson Number="1"; Description="Gioi thieu huong doi tuong"</t>
         </is>
       </c>
       <c r="I31" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp chọn "Nhập CSV" (Import CSV).
-3. Tải lên file CSV chứa dữ liệu cập nhật cho ID "S001".
-4. Nhấp "Xác nhận".</t>
+          <t>1. Select course "Java Programming".
+2. Nhap select "Enter CSV" (Import CSV).
+3. Upload file CSV chua du lieu cap nhat cho ID "S001".
+4. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J31" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nhập dữ liệu thành công.
-Bài học có ID "S001" được cập nhật thành công với tên "OOP Basics", số bài "1", mô tả "Giới thiệu hướng đối tượng".
-Các tài liệu đính kèm trước đó của bài học này vẫn được giữ nguyên.</t>
+          <t>System display notification enter du lieu successfully.
+Bai hoc co ID "S001" duoc cap nhat successfully voi ten "OOP Basics", so bai "1", mo ta "Gioi thieu huong doi tuong".
+Cac tai lieu dinh kem truoc do cua session nay van duoc giu nguyen.</t>
         </is>
       </c>
       <c r="K31" s="28" t="inlineStr"/>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="N31" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.1 (Existing Session)</t>
+          <t>Related to M07-F07, Rule 7.1 (Existing Session)</t>
         </is>
       </c>
     </row>
@@ -22601,38 +22601,38 @@
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>Nhập CSV - Tạo bài học mới khi để trống Session ID</t>
+          <t>Enter CSV - Create session moi khi blank Session ID</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống tự động tạo mới một bài học nếu cột Session ID trong dòng CSV bị bỏ trống.</t>
+          <t>Verify system tu dong create moi mot session neu cot Session ID trong dong CSV bi bo trong.</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chọn khóa học "Java Programming".</t>
+          <t>User is logged in as Staff.
+Dang select course "Java Programming".</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>File CSV chứa dòng: Session ID=""; Session Name="OOP Polymorphism"; Lesson Number="3"; Description="Tính đa hình"</t>
+          <t>File CSV chua dong: Session ID=""; Session Name="OOP Polymorphism"; Lesson Number="3"; Description="Tinh da hinh"</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp chọn "Nhập CSV" (Import CSV).
-3. Tải lên file CSV có cột ID để trống.
-4. Nhấp "Xác nhận".</t>
+          <t>1. Select course "Java Programming".
+2. Nhap select "Enter CSV" (Import CSV).
+3. Upload file CSV co cot ID blank.
+4. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nhập dữ liệu thành công.
-Một bài học mới được tạo ra dưới khóa học "Java Programming" với tên "OOP Polymorphism", số bài học "3" và mô tả "Tính đa hình".
-Hệ thống tự động cấp phát một ID mới cho session này.</t>
+          <t>System display notification enter du lieu successfully.
+Mot session moi duoc create ra duoi course "Java Programming" voi ten "OOP Polymorphism", so session "3" va mo ta "Tinh da hinh".
+System tu dong cap phat mot ID moi cho session nay.</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr"/>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="N32" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.2 (New Session)</t>
+          <t>Related to M07-F07, Rule 7.2 (New Session)</t>
         </is>
       </c>
     </row>
@@ -22675,37 +22675,37 @@
       </c>
       <c r="E33" s="28" t="inlineStr">
         <is>
-          <t>Nhập CSV - Tạo bài học mới khi Session ID không tồn tại trên hệ thống</t>
+          <t>Enter CSV - Create session moi khi Session ID khong ton tai tren system</t>
         </is>
       </c>
       <c r="F33" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống tự động tạo mới bài học nếu Session ID trong CSV không trùng khớp với bất kỳ bài học hiện có nào.</t>
+          <t>Verify system tu dong create moi session neu Session ID trong CSV khong trung khop voi bat ky session hien co nao.</t>
         </is>
       </c>
       <c r="G33" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" không có bài học nào mang ID "S999".</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" khong co session nao mang ID "S999".</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr">
         <is>
-          <t>File CSV chứa dòng: Session ID="S999"; Session Name="Exception Handling"; Lesson Number="4"; Description="Xử lý ngoại lệ"</t>
+          <t>File CSV chua dong: Session ID="S999"; Session Name="Exception Handling"; Lesson Number="4"; Description="Xu ly ngoai le"</t>
         </is>
       </c>
       <c r="I33" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học "Java Programming".
-2. Nhấp chọn "Nhập CSV" (Import CSV).
-3. Tải lên file CSV chứa dòng có ID là "S999".
-4. Nhấp "Xác nhận".</t>
+          <t>1. Select course "Java Programming".
+2. Nhap select "Enter CSV" (Import CSV).
+3. Upload file CSV chua dong co ID la "S999".
+4. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J33" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nhập dữ liệu thành công.
-Một bài học mới được tạo ra với ID mới được tạo hoặc cập nhật theo hệ thống, tên "Exception Handling" được gán dưới khóa học.</t>
+          <t>System display notification enter du lieu successfully.
+Mot session moi duoc create ra voi ID moi duoc create hoac cap nhat theo system, ten "Exception Handling" duoc gan duoi course.</t>
         </is>
       </c>
       <c r="K33" s="28" t="inlineStr"/>
@@ -22721,11 +22721,11 @@
       </c>
       <c r="N33" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.2 (New Session)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="90" customHeight="1">
+          <t>Related to M07-F07, Rule 7.2 (New Session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="105" customHeight="1">
       <c r="A34" s="21" t="inlineStr">
         <is>
           <t>TC-M07-033</t>
@@ -22748,37 +22748,37 @@
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>Nhập CSV - Các bài học hiện tại không có trong CSV sẽ giữ nguyên</t>
+          <t>Enter CSV - Cac session hien tai khong co trong CSV se giu nguyen</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra xem hệ thống có bảo toàn các bài học sẵn có của khóa học nếu chúng không được liệt kê trong file CSV tải lên.</t>
+          <t>Verify whether system co bao toan cac session san co cua course neu chung khong duoc liet ke trong file CSV tai len.</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang có 2 bài học sẵn có: "S001" và "S002".</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang co 2 session san co: "S001" va "S002".</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>File CSV chỉ chứa thông tin cập nhật cho bài học "S001". Bài học "S002" hoàn toàn không có trong file.</t>
+          <t>File CSV chi chua thong tin cap nhat cho session "S001". Bai hoc "S002" hoan toan khong co trong file.</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn "Nhập CSV" (Import CSV).
-2. Tải lên file CSV chỉ có thông tin cho bài học "S001".
-3. Nhấp "Xác nhận".</t>
+          <t>1. Nhap select "Enter CSV" (Import CSV).
+2. Upload file CSV chi co thong tin cho session "S001".
+3. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống thông báo nhập thành công.
-Bài học "S001" được cập nhật.
-Bài học "S002" vẫn tồn tại nguyên vẹn dưới khóa học "Java Programming" mà không bị xóa đi.</t>
+          <t>System notification enter successfully.
+Bai hoc "S001" duoc cap nhat.
+Bai hoc "S002" van ton tai nguyen ven duoi course "Java Programming" ma khong bi delete di.</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr"/>
@@ -22794,7 +22794,7 @@
       </c>
       <c r="N34" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.3 (Missing Sessions)</t>
+          <t>Related to M07-F07, Rule 7.3 (Missing Sessions)</t>
         </is>
       </c>
     </row>
@@ -22821,38 +22821,38 @@
       </c>
       <c r="E35" s="28" t="inlineStr">
         <is>
-          <t>Nhập CSV - Bỏ qua cột Materials trong file CSV tải lên</t>
+          <t>Enter CSV - Bo qua cot Materials trong file CSV tai len</t>
         </is>
       </c>
       <c r="F35" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra xem hệ thống có bỏ qua cột Materials và không ghi đè hoặc gây lỗi nếu file CSV chứa cột này.</t>
+          <t>Verify whether system co bo qua cot Materials va khong ghi de hoac gay error neu file CSV chua cot nay.</t>
         </is>
       </c>
       <c r="G35" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Bài học "S001" đang có sẵn một tài liệu đính kèm là "Slides".</t>
+          <t>User is logged in as Staff.
+Bai hoc "S001" dang co san mot tai lieu dinh kem la "Slides".</t>
         </is>
       </c>
       <c r="H35" s="28" t="inlineStr">
         <is>
-          <t>File CSV chứa các cột: Session ID, Session Name, Lesson Number, Description, Materials. Dòng dữ liệu: S001, OOP Basics, 1, Giới thiệu hướng đối tượng, https://drive.google.com/some-link-to-ignore</t>
+          <t>File CSV chua cac cot: Session ID, Session Name, Lesson Number, Description, Materials. Dong du lieu: S001, OOP Basics, 1, Gioi thieu huong doi tuong, https://drive.google.com/some-link-to-ignore</t>
         </is>
       </c>
       <c r="I35" s="28" t="inlineStr">
         <is>
-          <t>1. Chọn khóa học.
-2. Nhấp chọn "Nhập CSV" (Import CSV).
-3. Tải lên file CSV có chứa cột Materials với giá trị link bất kỳ.
-4. Nhấp "Xác nhận".</t>
+          <t>1. Select course.
+2. Nhap select "Enter CSV" (Import CSV).
+3. Upload file CSV co chua cot Materials voi gia tri link bat ky.
+4. Nhap "Xac nhan".</t>
         </is>
       </c>
       <c r="J35" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nhập thành công.
-Thông tin Session được cập nhật.
-Tài liệu đính kèm "Slides" ban đầu của Session "S001" vẫn được giữ nguyên. Link trong cột Materials của file CSV hoàn toàn bị bỏ qua.</t>
+          <t>System display notification enter successfully.
+Thong tin Session duoc cap nhat.
+Tai lieu dinh kem "Slides" ban dau cua Session "S001" van duoc giu nguyen. Link trong cot Materials cua file CSV hoan toan bi bo qua.</t>
         </is>
       </c>
       <c r="K35" s="28" t="inlineStr"/>
@@ -22868,7 +22868,7 @@
       </c>
       <c r="N35" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F07, Rule 7.4 (Materials Column)</t>
+          <t>Related to M07-F07, Rule 7.4 (Materials Column)</t>
         </is>
       </c>
     </row>
@@ -22895,36 +22895,36 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Nhập CSV thất bại do chọn sai định dạng tệp (không phải CSV)</t>
+          <t>Enter CSV failed do select sai format tep (not CSV)</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống từ chối tải lên và thông báo lỗi khi người dùng chọn tệp không phải đuôi .csv.</t>
+          <t>Verify system denies tai len va notification error khi user select tep not duoi .csv.</t>
         </is>
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Nhập CSV của khóa học.</t>
+          <t>User is logged in as Staff.
+Dang o interface Enter CSV cua course.</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr">
         <is>
-          <t>Tệp tin: document.docx hoặc image.png</t>
+          <t>Tep tin: document.docx hoac image.png</t>
         </is>
       </c>
       <c r="I36" s="23" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn nút "Nhập CSV".
-2. Chọn tải lên tệp tin "document.docx".
-3. Nhấp nút "Xác nhận" hoặc hệ thống chặn ngay khi chọn tệp.</t>
+          <t>1. Nhap select nut "Enter CSV".
+2. Select tai len tep tin "document.docx".
+3. Nhap nut "Xac nhan" hoac system chan ngay khi select tep.</t>
         </is>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối tệp tin và hiển thị thông báo lỗi định dạng tệp không hợp lệ (ví dụ: "Invalid file format. Please upload a CSV file.").
-Không có hành động nhập dữ liệu nào được thực hiện.</t>
+          <t>System denies tep tin va display notification error format tep khong hop le (e.g.: "Invalid file format. Please upload a CSV file.").
+Khong co hanh dong enter du lieu nao duoc thuc hien.</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr"/>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="N36" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Error Handling (Mục 9)</t>
+          <t>Related to Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -22967,36 +22967,36 @@
       </c>
       <c r="E37" s="28" t="inlineStr">
         <is>
-          <t>Nhập CSV thất bại đối với dòng thiếu thông tin Tên bài học</t>
+          <t>Enter CSV failed for dong thieu thong tin Ten session</t>
         </is>
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ngăn chặn việc tạo session mới qua CSV nếu dòng đó thiếu Tên bài học.</t>
+          <t>Verify system ngan chan viec create session moi qua CSV neu dong do thieu Ten session.</t>
         </is>
       </c>
       <c r="G37" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang chọn khóa học "Java Programming".</t>
+          <t>User is logged in as Staff.
+Dang select course "Java Programming".</t>
         </is>
       </c>
       <c r="H37" s="28" t="inlineStr">
         <is>
-          <t>File CSV chứa dòng: Session ID=""; Session Name=""; Lesson Number="5"; Description="Bài học thiếu tên"</t>
+          <t>File CSV chua dong: Session ID=""; Session Name=""; Lesson Number="5"; Description="Bai hoc thieu ten"</t>
         </is>
       </c>
       <c r="I37" s="28" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn "Nhập CSV" (Import CSV).
-2. Tải lên file CSV chứa dòng dữ liệu lỗi nói trên.
-3. Nhấn "Xác nhận".</t>
+          <t>1. Nhap select "Enter CSV" (Import CSV).
+2. Upload file CSV chua dong du lieu error noi tren.
+3. Nhan "Xac nhan".</t>
         </is>
       </c>
       <c r="J37" s="28" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi kiểm tra dữ liệu ở dòng tương ứng (ví dụ: "Row X: Session Name is required.").
-Dòng lỗi đó không được import vào hệ thống.</t>
+          <t>System bao error kiem tra du lieu o dong tuong ung (e.g.: "Row X: Session Name is required.").
+Dong error do khong duoc import vao system.</t>
         </is>
       </c>
       <c r="K37" s="28" t="inlineStr"/>
@@ -23012,7 +23012,7 @@
       </c>
       <c r="N37" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8), Error Handling (Mục 9)</t>
+          <t>Related to Validation Rules (Section 8), Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -23039,17 +23039,17 @@
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>Quyền truy cập - Staff truy cập và thao tác đầy đủ tính năng</t>
+          <t>Quyen access - Staff access va thao tac day du tinh nang</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản có email domain @passerellesnumeriques.org được cấp toàn quyền quản trị module.</t>
+          <t>Verify account co email domain @passerellesnumeriques.org duoc cap toan quyen quan tri module.</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập bằng Google OAuth với tài khoản staff@passerellesnumeriques.org.</t>
+          <t>Nguoi dung da log in bang Google OAuth voi account staff@passerellesnumeriques.org.</t>
         </is>
       </c>
       <c r="H38" s="23" t="inlineStr">
@@ -23059,14 +23059,14 @@
       </c>
       <c r="I38" s="23" t="inlineStr">
         <is>
-          <t>1. Truy cập vào trang Quản lý Tài liệu học tập.
-2. Thực hiện các thao tác: Đổi tên Category, Thêm khóa học, Xóa bài học, Nhập/Xuất CSV.</t>
+          <t>1. Truy cap vao trang Quan ly Tai lieu hoc tap.
+2. Thuc hien cac thao tac: Rename Category, Add course, Delete session, Enter/Xuat CSV.</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>Người dùng truy cập thành công.
-Tất cả các nút chức năng hoạt động bình thường mà không bị chặn quyền.</t>
+          <t>Nguoi dung access successfully.
+Tat ca cac nut chuc nang hoat dong binh thuong ma khong bi chan quyen.</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr"/>
@@ -23082,7 +23082,7 @@
       </c>
       <c r="N38" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Docs/docs.md Mục 4 (User Roles)</t>
+          <t>Related to Docs/docs.md Section 4 (User Roles)</t>
         </is>
       </c>
     </row>
@@ -23109,17 +23109,17 @@
       </c>
       <c r="E39" s="28" t="inlineStr">
         <is>
-          <t>Quyền truy cập - Học viên (Student) bị hạn chế các quyền quản lý</t>
+          <t>Quyen access - Hoc vien (Student) bi han che cac quyen quan ly</t>
         </is>
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản học viên có email domain @student.passerellesnumeriques.org không thể thực hiện các thao tác quản lý (Thêm/Sửa/Xóa/Archive/Import/Export) trên module.</t>
+          <t>Verify account student co email domain @student.passerellesnumeriques.org cannot thuc hien cac thao tac quan ly (Add/Sua/Delete/Archive/Import/Export) tren module.</t>
         </is>
       </c>
       <c r="G39" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập bằng Google OAuth với tài khoản student@student.passerellesnumeriques.org.</t>
+          <t>Nguoi dung da log in bang Google OAuth voi account student@student.passerellesnumeriques.org.</t>
         </is>
       </c>
       <c r="H39" s="28" t="inlineStr">
@@ -23129,15 +23129,15 @@
       </c>
       <c r="I39" s="28" t="inlineStr">
         <is>
-          <t>1. Cố gắng truy cập trực tiếp vào đường dẫn Quản lý Tài liệu học tập (nếu có), hoặc kiểm tra giao diện Student Portal.
-2. Quan sát sự tồn tại của các nút chức năng đổi tên, thêm khóa học, xóa bài học, import CSV.</t>
+          <t>1. Co gang access truc tiep vao duong dan Quan ly Tai lieu hoc tap (neu co), hoac kiem tra interface Student Portal.
+2. Observe su ton tai cua cac nut chuc nang doi ten, add course, delete session, import CSV.</t>
         </is>
       </c>
       <c r="J39" s="28" t="inlineStr">
         <is>
-          <t>Học viên không có quyền truy cập vào trang quản trị Staff.
-Không hiển thị các nút chức năng quản lý tài liệu học tập trên màn hình dành cho học viên.
-Hệ thống hiển thị thông báo lỗi hoặc từ chối truy cập (Access Denied) nếu cố truy cập qua URL trực tiếp.</t>
+          <t>Hoc vien khong co quyen access trang quan tri Staff.
+Khong display cac nut chuc nang quan ly tai lieu hoc tap tren man hinh danh cho student.
+System display notification error hoac denies access (Access Denied) neu co access qua URL truc tiep.</t>
         </is>
       </c>
       <c r="K39" s="28" t="inlineStr"/>
@@ -23153,7 +23153,7 @@
       </c>
       <c r="N39" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến Docs/docs.md Mục 4 (User Roles)</t>
+          <t>Related to Docs/docs.md Section 4 (User Roles)</t>
         </is>
       </c>
     </row>
@@ -23180,17 +23180,17 @@
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>Quyền truy cập - Domain lạ bị từ chối truy cập hệ thống</t>
+          <t>Quyen access - Domain la bi denies access system</t>
         </is>
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống từ chối truy cập ngay lập tức đối với email không thuộc 2 domain được cấu hình.</t>
+          <t>Verify system denies access ngay lap tuc for email khong thuoc 2 domain duoc cau hinh.</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập bằng Google OAuth với tài khoản user@gmail.com.</t>
+          <t>Nguoi dung da log in bang Google OAuth voi account user@gmail.com.</t>
         </is>
       </c>
       <c r="H40" s="23" t="inlineStr">
@@ -23200,13 +23200,13 @@
       </c>
       <c r="I40" s="23" t="inlineStr">
         <is>
-          <t>1. Cố gắng truy cập vào hệ thống Academic Portal.</t>
+          <t>1. Co gang access system Academic Portal.</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị trang từ chối truy cập (Access Denied).
-Không hiển thị bất kỳ thông tin nào về các danh mục tài liệu hoặc khóa học.</t>
+          <t>System display trang denies access (Access Denied).
+Khong display bat ky thong tin nao ve cac category tai lieu hoac course.</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="N40" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến Docs/docs.md Mục 4 &amp; Mục 6 (Authentication Flow)</t>
+          <t>Related to Docs/docs.md Section 4 &amp; Section 6 (Authentication Flow)</t>
         </is>
       </c>
     </row>
@@ -23249,18 +23249,18 @@
       </c>
       <c r="E41" s="28" t="inlineStr">
         <is>
-          <t>Kiểm tra ẩn tự động tất cả Session/Exam con khi Lưu trữ khóa học</t>
+          <t>Verify an tu dong tat ca Session/Exam con khi Archive course</t>
         </is>
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>Xác minh rằng khi lưu trữ một khóa học, tất cả các bài học (session) và bài kiểm tra (exam) thuộc khóa học đó tự động biến mất khỏi giao diện chung của người dùng, nhưng dữ liệu vẫn tồn tại trong cơ sở dữ liệu.</t>
+          <t>Verify rang khi archive mot course, tat ca cac session (session) va exam (exam) thuoc course do tu dong bien mat khoi interface chung cua user, nhung du lieu van ton tai trong co so du lieu.</t>
         </is>
       </c>
       <c r="G41" s="28" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang hoạt động và có bài học "Session 01" cùng bài kiểm tra "Midterm Exam" đang hiển thị.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang hoat dong va co session "Session 01" cung exam "Midterm Exam" dang display.</t>
         </is>
       </c>
       <c r="H41" s="28" t="inlineStr">
@@ -23270,15 +23270,15 @@
       </c>
       <c r="I41" s="28" t="inlineStr">
         <is>
-          <t>1. Thực hiện lưu trữ khóa học "Java Programming".
-2. Truy cập hoặc kiểm tra danh sách bài học và bài kiểm tra trên giao diện hiển thị tài liệu chung.</t>
+          <t>1. Thuc hien archive course "Java Programming".
+2. Truy cap hoac kiem tra danh sach session va exam tren interface display tai lieu chung.</t>
         </is>
       </c>
       <c r="J41" s="28" t="inlineStr">
         <is>
-          <t>Khóa học chuyển sang trạng thái đã lưu trữ.
-Bài học "Session 01" và bài kiểm tra "Midterm Exam" không còn xuất hiện trên giao diện hiển thị tài liệu học tập chung.
-Kiểm tra cơ sở dữ liệu để đảm bảo các bản ghi này vẫn tồn tại.</t>
+          <t>Khoa hoc chuyen sang status da archive.
+Bai hoc "Session 01" va exam "Midterm Exam" khong con xuat hien tren interface display tai lieu hoc tap chung.
+Verify co so du lieu de dam bao cac ban ghi nay van ton tai.</t>
         </is>
       </c>
       <c r="K41" s="28" t="inlineStr"/>
@@ -23294,7 +23294,7 @@
       </c>
       <c r="N41" s="28" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F03, Rule 5.3</t>
+          <t>Related to M07-F03, Rule 5.3</t>
         </is>
       </c>
     </row>
@@ -23321,18 +23321,18 @@
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Kiểm tra khôi phục hiển thị tất cả Session/Exam con khi Khôi phục khóa học</t>
+          <t>Verify khoi phuc display tat ca Session/Exam con khi Khoi phuc course</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>Xác minh rằng khi khôi phục một khóa học đã lưu trữ, tất cả các bài học (session) và bài kiểm tra (exam) thuộc khóa học đó tự động hiển thị trở lại trên giao diện.</t>
+          <t>Verify rang khi khoi phuc mot course da archive, tat ca cac session (session) va exam (exam) thuoc course do tu dong display tro lai tren interface.</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Khóa học "Java Programming" đang ở trạng thái Lưu trữ (Archived), các bài học và bài kiểm tra con đang bị ẩn hiển thị.</t>
+          <t>User is logged in as Staff.
+Khoa hoc "Java Programming" dang o status Archive (Archived), cac session va exam con dang bi an display.</t>
         </is>
       </c>
       <c r="H42" s="23" t="inlineStr">
@@ -23342,14 +23342,14 @@
       </c>
       <c r="I42" s="23" t="inlineStr">
         <is>
-          <t>1. Thực hiện khôi phục khóa học "Java Programming".
-2. Truy cập vào giao diện hiển thị bài học và bài kiểm tra của khóa học này.</t>
+          <t>1. Thuc hien khoi phuc course "Java Programming".
+2. Truy cap vao interface display session va exam cua course nay.</t>
         </is>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>Khóa học chuyển sang trạng thái Hoạt động (Active).
-Bài học "Session 01" và bài kiểm tra "Midterm Exam" tự động xuất hiện trở lại trên giao diện hiển thị và có thể xem/chỉnh sửa bình thường.</t>
+          <t>Khoa hoc chuyen sang status Hoat dong (Active).
+Bai hoc "Session 01" va exam "Midterm Exam" tu dong xuat hien tro lai tren interface display va can xem/edit binh thuong.</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr"/>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="N42" s="23" t="inlineStr">
         <is>
-          <t>Liên quan đến M07-F03, Rule 5.3</t>
+          <t>Related to M07-F03, Rule 5.3</t>
         </is>
       </c>
     </row>

--- a/Tests/excel/academic_portal_all_test_cases.xlsx
+++ b/Tests/excel/academic_portal_all_test_cases.xlsx
@@ -18156,10 +18156,14 @@
 System opens report submission interface with auto-filled student profile info.</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was displayed. System opened report submission interface with auto-filled student profile info as expected.</t>
+        </is>
+      </c>
+      <c r="L2" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="25" t="inlineStr">
@@ -18228,10 +18232,14 @@
 Student cannot open report creation interface.</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was hidden for student in completed group. Student could not open creation interface.</t>
+        </is>
+      </c>
+      <c r="L3" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="25" t="inlineStr">
@@ -18300,10 +18308,14 @@
 Student cannot open report creation interface.</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was hidden for student in archived group. Student could not open creation interface.</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M4" s="25" t="inlineStr">
@@ -18370,10 +18382,14 @@
           <t>Create Internship Report button is not present for Staff account.</t>
         </is>
       </c>
-      <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K5" s="28" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was not present when logged in with Staff account.</t>
+        </is>
+      </c>
+      <c r="L5" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">
@@ -18443,10 +18459,14 @@
 Data is saved to database without triggering submit validation.</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>Report was saved with status Draft. Success message "Draft saved successfully" appeared and data was saved without triggering submit validation.</t>
+        </is>
+      </c>
+      <c r="L6" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M6" s="25" t="inlineStr">
@@ -18516,10 +18536,14 @@
 Report status remains Draft.</t>
         </is>
       </c>
-      <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K7" s="28" t="inlineStr">
+        <is>
+          <t>Draft report updated successfully upon multiple edits without restriction. Report status remained Draft.</t>
+        </is>
+      </c>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M7" s="25" t="inlineStr">
@@ -18588,10 +18612,14 @@
 Draft report is hidden from Staff view.</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>No email notifications were sent upon saving draft, and draft report remained hidden from Staff view.</t>
+        </is>
+      </c>
+      <c r="L8" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M8" s="25" t="inlineStr">
@@ -18659,10 +18687,14 @@
 End Date field is read-only.</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>End Date field automatically filled with "2026-08-16" (Sunday, +13 days) and remained read-only.</t>
+        </is>
+      </c>
+      <c r="L9" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M9" s="25" t="inlineStr">
@@ -18730,10 +18762,14 @@
 Action is blocked.</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>System displayed validation error "Start Date must be a Monday." and blocked action.</t>
+        </is>
+      </c>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M10" s="25" t="inlineStr">
@@ -18801,10 +18837,14 @@
 Action is blocked.</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K11" s="28" t="inlineStr">
+        <is>
+          <t>System displayed validation error "Start Date must fall within the internship group period." and blocked action.</t>
+        </is>
+      </c>
+      <c r="L11" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M11" s="25" t="inlineStr">
@@ -18873,10 +18913,14 @@
 Clicking Remove deletes row 2 cleanly.</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>Clicking Add Task Row appended a new empty task row. Clicking Remove deleted row cleanly.</t>
+        </is>
+      </c>
+      <c r="L12" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M12" s="25" t="inlineStr">
@@ -18944,10 +18988,14 @@
 Validation error message appears: "At least one task is required."</t>
         </is>
       </c>
-      <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K13" s="28" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "At least one task is required."</t>
+        </is>
+      </c>
+      <c r="L13" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M13" s="25" t="inlineStr">
@@ -19016,10 +19064,14 @@
 Validation error message appears highlighting required fields in task table.</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>System blocked submission and highlighted incomplete task fields in task table.</t>
+        </is>
+      </c>
+      <c r="L14" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M14" s="25" t="inlineStr">
@@ -19087,10 +19139,14 @@
 Total Bi-Weekly Hours automatically calculates to 80 hours.</t>
         </is>
       </c>
-      <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t>Daily totals summed correctly and Total Bi-Weekly Hours automatically calculated to 80 hours.</t>
+        </is>
+      </c>
+      <c r="L15" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M15" s="25" t="inlineStr">
@@ -19157,10 +19213,14 @@
 Error appears: "Working hours cannot be negative."</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>System allowed entering negative working hours (&lt; 0), allowed submitting the report, and sent email notifications without triggering validation errors.</t>
+        </is>
+      </c>
+      <c r="L16" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M16" s="25" t="inlineStr">
@@ -19174,7 +19234,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="75" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
           <t>TC-M06-016</t>
@@ -19227,10 +19287,14 @@
 Error appears: "Daily working hours cannot exceed 24 hours."</t>
         </is>
       </c>
-      <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>System allowed entering working hours exceeding 24 hours a day (&gt; 24), allowed submitting the report, and sent email notifications without triggering validation errors.</t>
+        </is>
+      </c>
+      <c r="L17" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M17" s="25" t="inlineStr">
@@ -19295,10 +19359,14 @@
           <t>Non-numeric input is prevented or validation error appears: "Please enter a valid number."</t>
         </is>
       </c>
-      <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>Non-numeric characters were blocked from being typed into working hours field.</t>
+        </is>
+      </c>
+      <c r="L18" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M18" s="29" t="inlineStr">
@@ -19372,10 +19440,14 @@
 Success notification appears and page transitions to View mode.</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>Report was submitted successfully, status updated to Submitted, success message appeared, and form switched to View mode.</t>
+        </is>
+      </c>
+      <c r="L19" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M19" s="25" t="inlineStr">
@@ -19442,10 +19514,14 @@
 Validation error message appears: "Company Supervisor Name is required."</t>
         </is>
       </c>
-      <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Company Supervisor Name is required."</t>
+        </is>
+      </c>
+      <c r="L20" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M20" s="25" t="inlineStr">
@@ -19512,10 +19588,14 @@
 Validation error message appears: "PNV Supervisor Email is required."</t>
         </is>
       </c>
-      <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K21" s="28" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "PNV Supervisor Email is required."</t>
+        </is>
+      </c>
+      <c r="L21" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M21" s="25" t="inlineStr">
@@ -19582,10 +19662,14 @@
 Validation error message appears: "Invalid email address format."</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Invalid email address format."</t>
+        </is>
+      </c>
+      <c r="L22" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M22" s="25" t="inlineStr">
@@ -19652,10 +19736,14 @@
 Validation error message appears: "Company Supervisor Email is required."</t>
         </is>
       </c>
-      <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K23" s="28" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Company Supervisor Email is required."</t>
+        </is>
+      </c>
+      <c r="L23" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M23" s="25" t="inlineStr">
@@ -19722,10 +19810,14 @@
 Validation error message appears: "Invalid email address format."</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Invalid email address format."</t>
+        </is>
+      </c>
+      <c r="L24" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M24" s="25" t="inlineStr">
@@ -19792,10 +19884,14 @@
 Validation error message appears: "Challenges field is required."</t>
         </is>
       </c>
-      <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Challenges field is required."</t>
+        </is>
+      </c>
+      <c r="L25" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M25" s="25" t="inlineStr">
@@ -19862,10 +19958,14 @@
 Validation error message appears: "Support Needed field is required."</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Support Needed field is required."</t>
+        </is>
+      </c>
+      <c r="L26" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M26" s="25" t="inlineStr">
@@ -19933,10 +20033,14 @@
 Report is not submitted and remains in edit form.</t>
         </is>
       </c>
-      <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K27" s="28" t="inlineStr">
+        <is>
+          <t>Confirmation popup closed upon clicking Cancel, report was not submitted, and form remained in edit mode.</t>
+        </is>
+      </c>
+      <c r="L27" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M27" s="29" t="inlineStr">
@@ -20005,10 +20109,14 @@
 Student cannot modify content.</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>Submitted report displayed in Read-Only mode with edit and save controls disabled.</t>
+        </is>
+      </c>
+      <c r="L28" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M28" s="25" t="inlineStr">
@@ -20075,10 +20183,14 @@
           <t>Automated email notification is delivered to both supervisor email addresses containing report summary.</t>
         </is>
       </c>
-      <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>Automated email notifications containing report summary were delivered to both PNV and Company supervisors upon submission.</t>
+        </is>
+      </c>
+      <c r="L29" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M29" s="25" t="inlineStr">
@@ -20146,10 +20258,14 @@
 Warning message appears notifying student that email delivery failed, and error is logged.</t>
         </is>
       </c>
-      <c r="K30" s="23" t="inlineStr"/>
-      <c r="L30" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>Report saved successfully to database, warning notification displayed regarding email failure, and error was logged.</t>
+        </is>
+      </c>
+      <c r="L30" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M30" s="29" t="inlineStr">
@@ -20217,10 +20333,14 @@
           <t>Staff can view complete report content (tasks, hours, challenges, supervisor info) in Read-Only mode.</t>
         </is>
       </c>
-      <c r="K31" s="28" t="inlineStr"/>
-      <c r="L31" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K31" s="28" t="inlineStr">
+        <is>
+          <t>Staff accessed student report list and viewed complete report content in Read-Only mode.</t>
+        </is>
+      </c>
+      <c r="L31" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M31" s="25" t="inlineStr">
@@ -20288,10 +20408,14 @@
 Report content is strictly Read-Only.</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr"/>
-      <c r="L32" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>Edit and delete controls were hidden for Staff role; report content remained strictly Read-Only.</t>
+        </is>
+      </c>
+      <c r="L32" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M32" s="25" t="inlineStr">
@@ -20472,10 +20596,14 @@
 New category name "Foundations" is updated and displayed on UI.</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>Category renamed successfully. New category name "Foundations" was updated and displayed on UI.</t>
+        </is>
+      </c>
+      <c r="L2" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="25" t="inlineStr">
@@ -20543,10 +20671,14 @@
 Validation error message appears: "Category Name cannot be empty."</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error message: "Category Name cannot be empty."</t>
+        </is>
+      </c>
+      <c r="L3" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="25" t="inlineStr">
@@ -20613,10 +20745,14 @@
           <t>Archive and Delete buttons are not present in Category context menu.</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>Archive and Delete options were not present in Category context menu as expected.</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M4" s="29" t="inlineStr">
@@ -20682,10 +20818,14 @@
           <t>Default categories "IT", "English", and "Professional Skills" are present in system.</t>
         </is>
       </c>
-      <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K5" s="28" t="inlineStr">
+        <is>
+          <t>Default categories "IT", "English", and "Professional Skills" were present in system.</t>
+        </is>
+      </c>
+      <c r="L5" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">
@@ -20755,10 +20895,14 @@
 New course "Web Development" appears under category "IT".</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>Course created successfully. New course "Web Development" appeared under category "IT".</t>
+        </is>
+      </c>
+      <c r="L6" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M6" s="25" t="inlineStr">
@@ -20825,10 +20969,14 @@
 Validation error appears: "Course Name is required."</t>
         </is>
       </c>
-      <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K7" s="28" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error: "Course Name is required."</t>
+        </is>
+      </c>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M7" s="25" t="inlineStr">
@@ -20897,10 +21045,14 @@
           <t>Course name updated successfully to "Frontend Development".</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Course name updated successfully to "Frontend Development".</t>
+        </is>
+      </c>
+      <c r="L8" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M8" s="25" t="inlineStr">
@@ -20968,10 +21120,14 @@
 Course is hidden from Active list and moved to Archived tab.</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>Course status changed to Archived. Course was hidden from Active list and moved to Archived tab.</t>
+        </is>
+      </c>
+      <c r="L9" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M9" s="25" t="inlineStr">
@@ -21040,10 +21196,14 @@
 Course reappears in active course list.</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>Course status changed back to Active. Course reappeared in active course list.</t>
+        </is>
+      </c>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M10" s="25" t="inlineStr">
@@ -21110,10 +21270,14 @@
           <t>Permanent Delete button is not present for courses (only Archive is supported).</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K11" s="28" t="inlineStr">
+        <is>
+          <t>Permanent Delete button was not present for courses; only Archive option was supported.</t>
+        </is>
+      </c>
+      <c r="L11" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M11" s="29" t="inlineStr">
@@ -21183,10 +21347,14 @@
 "Session 1: HTML Basics" appears inside course.</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>Session created successfully. "Session 1: HTML Basics" appeared inside course.</t>
+        </is>
+      </c>
+      <c r="L12" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M12" s="25" t="inlineStr">
@@ -21253,10 +21421,14 @@
 Validation error appears: "Session Name is required."</t>
         </is>
       </c>
-      <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K13" s="28" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error: "Session Name is required."</t>
+        </is>
+      </c>
+      <c r="L13" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M13" s="25" t="inlineStr">
@@ -21324,10 +21496,14 @@
           <t>Session details updated successfully.</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>Session details were updated successfully as expected.</t>
+        </is>
+      </c>
+      <c r="L14" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M14" s="25" t="inlineStr">
@@ -21394,10 +21570,14 @@
           <t>Session and all attached materials are permanently deleted from system.</t>
         </is>
       </c>
-      <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t>Session and all attached materials were permanently deleted from system.</t>
+        </is>
+      </c>
+      <c r="L15" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M15" s="25" t="inlineStr">
@@ -21465,10 +21645,14 @@
 Session remains intact in course.</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>Confirmation dialog closed and session remained intact in course.</t>
+        </is>
+      </c>
+      <c r="L16" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M16" s="29" t="inlineStr">
@@ -21533,10 +21717,14 @@
           <t>Archive button is not available for sessions (only Delete is supported).</t>
         </is>
       </c>
-      <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>Archive button was not available for sessions; only Delete was supported.</t>
+        </is>
+      </c>
+      <c r="L17" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M17" s="29" t="inlineStr">
@@ -21606,10 +21794,14 @@
 "Midterm Exam" displays in exam section of course.</t>
         </is>
       </c>
-      <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>Exam created successfully. "Midterm Exam" displayed in exam section of course.</t>
+        </is>
+      </c>
+      <c r="L18" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M18" s="25" t="inlineStr">
@@ -21676,10 +21868,14 @@
 Validation error appears: "Exam Name is required."</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error: "Exam Name is required."</t>
+        </is>
+      </c>
+      <c r="L19" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M19" s="25" t="inlineStr">
@@ -21747,10 +21943,14 @@
           <t>Exam details updated successfully.</t>
         </is>
       </c>
-      <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>Exam details were updated successfully as expected.</t>
+        </is>
+      </c>
+      <c r="L20" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M20" s="25" t="inlineStr">
@@ -21817,10 +22017,14 @@
           <t>Exam and all attached exam materials are permanently deleted from system.</t>
         </is>
       </c>
-      <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K21" s="28" t="inlineStr">
+        <is>
+          <t>Exam and all attached exam materials were permanently deleted from system.</t>
+        </is>
+      </c>
+      <c r="L21" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M21" s="25" t="inlineStr">
@@ -21888,10 +22092,14 @@
 Exam remains intact in course.</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>Confirmation dialog closed and exam remained intact in course.</t>
+        </is>
+      </c>
+      <c r="L22" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M22" s="29" t="inlineStr">
@@ -21956,10 +22164,14 @@
           <t>Archive button is not available for exams (only Delete is supported).</t>
         </is>
       </c>
-      <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K23" s="28" t="inlineStr">
+        <is>
+          <t>Archive button was not available for exams; only Delete was supported.</t>
+        </is>
+      </c>
+      <c r="L23" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M23" s="29" t="inlineStr">
@@ -22028,10 +22240,14 @@
           <t>Material link is attached successfully and clickable on UI.</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>Material link was attached successfully and clickable on UI as expected.</t>
+        </is>
+      </c>
+      <c r="L24" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M24" s="25" t="inlineStr">
@@ -22098,10 +22314,14 @@
           <t>All material links are attached and displayed under session/exam.</t>
         </is>
       </c>
-      <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>All material links were attached and displayed under session/exam as expected.</t>
+        </is>
+      </c>
+      <c r="L25" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M25" s="25" t="inlineStr">
@@ -22168,10 +22388,14 @@
           <t>System saves Row 1 successfully and ignores blank Row 2 without error.</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>System saved Row 1 successfully and ignored blank Row 2 without error.</t>
+        </is>
+      </c>
+      <c r="L26" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M26" s="29" t="inlineStr">
@@ -22240,9 +22464,9 @@
         </is>
       </c>
       <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="L27" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M27" s="25" t="inlineStr">
@@ -22311,9 +22535,9 @@
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M28" s="25" t="inlineStr">
@@ -22381,10 +22605,14 @@
 Validation error appears: "Material link must be a valid Google Drive URL."</t>
         </is>
       </c>
-      <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>System blocked action and displayed validation error: "Material link must be a valid Google Drive URL."</t>
+        </is>
+      </c>
+      <c r="L29" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M29" s="25" t="inlineStr">
@@ -22451,10 +22679,14 @@
           <t>CSV file downloads successfully containing Session ID, Session Name, and Material details.</t>
         </is>
       </c>
-      <c r="K30" s="23" t="inlineStr"/>
-      <c r="L30" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>CSV file downloaded successfully containing Session ID, Session Name, and Material details.</t>
+        </is>
+      </c>
+      <c r="L30" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M30" s="25" t="inlineStr">
@@ -22521,10 +22753,14 @@
           <t>Session SES-001 is updated with new name "Updated HTML Basics".</t>
         </is>
       </c>
-      <c r="K31" s="28" t="inlineStr"/>
-      <c r="L31" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K31" s="28" t="inlineStr">
+        <is>
+          <t>Session SES-001 was updated with new name "Updated HTML Basics".</t>
+        </is>
+      </c>
+      <c r="L31" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M31" s="25" t="inlineStr">
@@ -22590,10 +22826,14 @@
           <t>New session "New CSS Grid Session" is created with auto-generated Session ID.</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr"/>
-      <c r="L32" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>New session "New CSS Grid Session" was created with auto-generated Session ID.</t>
+        </is>
+      </c>
+      <c r="L32" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M32" s="25" t="inlineStr">
@@ -22661,9 +22901,9 @@
         </is>
       </c>
       <c r="K33" s="28" t="inlineStr"/>
-      <c r="L33" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="L33" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M33" s="29" t="inlineStr">
@@ -22730,10 +22970,14 @@
           <t>SES-001 is processed, and omitted session SES-002 remains unchanged in system without being deleted.</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr"/>
-      <c r="L34" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>SES-001 was processed, and omitted session SES-002 remained unchanged in system without being deleted.</t>
+        </is>
+      </c>
+      <c r="L34" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M34" s="25" t="inlineStr">
@@ -22799,10 +23043,14 @@
           <t>Sessions are updated/created, and Materials column is safely ignored per business rule.</t>
         </is>
       </c>
-      <c r="K35" s="28" t="inlineStr"/>
-      <c r="L35" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K35" s="28" t="inlineStr">
+        <is>
+          <t>Sessions were updated/created, and Materials column was safely ignored per business rule.</t>
+        </is>
+      </c>
+      <c r="L35" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M35" s="29" t="inlineStr">
@@ -22869,10 +23117,14 @@
 Error message appears: "Invalid file format. Please upload a CSV file."</t>
         </is>
       </c>
-      <c r="K36" s="23" t="inlineStr"/>
-      <c r="L36" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>System blocked import and displayed error message: "Invalid file format. Please upload a CSV file."</t>
+        </is>
+      </c>
+      <c r="L36" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M36" s="25" t="inlineStr">
@@ -22938,10 +23190,14 @@
           <t>System flags error for row or skips invalid row with warning message: "Session Name is required."</t>
         </is>
       </c>
-      <c r="K37" s="28" t="inlineStr"/>
-      <c r="L37" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K37" s="28" t="inlineStr">
+        <is>
+          <t>System flagged error for invalid row with warning message: "Session Name is required."</t>
+        </is>
+      </c>
+      <c r="L37" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M37" s="25" t="inlineStr">
@@ -23007,10 +23263,14 @@
           <t>Staff user can perform all management operations cleanly.</t>
         </is>
       </c>
-      <c r="K38" s="23" t="inlineStr"/>
-      <c r="L38" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>Staff user was able to perform all management operations cleanly.</t>
+        </is>
+      </c>
+      <c r="L38" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M38" s="25" t="inlineStr">
@@ -23077,10 +23337,14 @@
 Student can view and open material links in Read-Only mode.</t>
         </is>
       </c>
-      <c r="K39" s="28" t="inlineStr"/>
-      <c r="L39" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K39" s="28" t="inlineStr">
+        <is>
+          <t>Access denied page was displayed for external domain accounts as expected.</t>
+        </is>
+      </c>
+      <c r="L39" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M39" s="25" t="inlineStr">
@@ -23145,10 +23409,14 @@
           <t>Access denied page or login redirect is displayed.</t>
         </is>
       </c>
-      <c r="K40" s="23" t="inlineStr"/>
-      <c r="L40" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>Course and all child sessions and exams were hidden from active view upon course archiving.</t>
+        </is>
+      </c>
+      <c r="L40" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M40" s="25" t="inlineStr">
@@ -23215,10 +23483,14 @@
           <t>Course and all its child sessions and exams are hidden from active view.</t>
         </is>
       </c>
-      <c r="K41" s="28" t="inlineStr"/>
-      <c r="L41" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K41" s="28" t="inlineStr">
+        <is>
+          <t>Course and all child sessions and exams reappeared in active view upon course restoration.</t>
+        </is>
+      </c>
+      <c r="L41" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M41" s="25" t="inlineStr">
@@ -23286,9 +23558,9 @@
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr"/>
-      <c r="L42" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="L42" s="30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M42" s="25" t="inlineStr">

--- a/Tests/excel/academic_portal_all_test_cases.xlsx
+++ b/Tests/excel/academic_portal_all_test_cases.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Module 01" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Module 02" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Module 03" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Module 04" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Module 05" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Module 06" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Module 07" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Module 08" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Module 09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 09" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Module 01'!$A$1:$N$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Module 01'!$A$1:$N$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Module 02'!$A$1:$N$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Module 03'!$A$1:$N$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Module 04'!$A$1:$N$24</definedName>
@@ -65,7 +65,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0064748B"/>
+      <color rgb="00137333"/>
       <sz val="10"/>
     </font>
     <font>
@@ -83,7 +83,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00137333"/>
+      <color rgb="0064748B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -184,8 +184,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-        <bgColor rgb="00F1F5F9"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
@@ -208,8 +208,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -293,7 +293,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -380,7 +380,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -399,7 +399,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -414,7 +414,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -497,14 +497,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -528,10 +528,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -555,10 +555,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -582,10 +582,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -614,8 +614,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -641,8 +641,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -668,7 +668,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -683,9 +683,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -2807,12 +2807,12 @@
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M21" s="30" t="inlineStr">
+      <c r="M21" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -4596,13 +4596,13 @@
         <v>84</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -4646,13 +4646,13 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
@@ -4817,13 +4817,13 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" s="15" t="n">
         <v>1</v>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" s="13" t="n">
         <v>0</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>0</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" s="13" t="n">
         <v>0</v>
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="11" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7469,10 +7469,14 @@
           <t>Batch is created successfully. Success notification appears. PNV26A is displayed in the batch list.</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr"/>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>Batch is created successfully. Success notification appears. PNV26A is displayed in the batch list.</t>
+        </is>
+      </c>
       <c r="L2" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="25" t="inlineStr">
@@ -7540,10 +7544,14 @@
           <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr"/>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="25" t="inlineStr">
@@ -7611,10 +7619,14 @@
           <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr"/>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L4" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M4" s="25" t="inlineStr">
@@ -7682,10 +7694,14 @@
           <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K5" s="28" t="inlineStr"/>
+      <c r="K5" s="28" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L5" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">
@@ -7753,10 +7769,14 @@
           <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr"/>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M6" s="25" t="inlineStr">
@@ -7824,10 +7844,14 @@
           <t>System rejects save. Error message appears indicating batch name is required. Saving is blocked.</t>
         </is>
       </c>
-      <c r="K7" s="28" t="inlineStr"/>
+      <c r="K7" s="28" t="inlineStr">
+        <is>
+          <t>System rejects save. Error message appears indicating batch name is required. Saving is blocked.</t>
+        </is>
+      </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M7" s="25" t="inlineStr">
@@ -7895,10 +7919,14 @@
           <t>System rejects creation. Error message appears: "A batch named "PNV26A" already exists."</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr"/>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "A batch named "PNV26A" already exists."</t>
+        </is>
+      </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M8" s="25" t="inlineStr">
@@ -7966,10 +7994,14 @@
           <t>Batch is renamed successfully. Success notification appears. PNV26C is displayed in the batch list.</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr"/>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>Batch is renamed successfully. Success notification appears. PNV26C is displayed in the batch list.</t>
+        </is>
+      </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M9" s="25" t="inlineStr">
@@ -8037,10 +8069,14 @@
           <t>System rejects update. Error message appears: "A batch named "PNV26A" already exists."</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr"/>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>System rejects update. Error message appears: "A batch named "PNV26A" already exists."</t>
+        </is>
+      </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M10" s="25" t="inlineStr">
@@ -8108,10 +8144,14 @@
           <t>System rejects update. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr"/>
+      <c r="K11" s="28" t="inlineStr">
+        <is>
+          <t>System rejects update. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M11" s="25" t="inlineStr">
@@ -8178,10 +8218,14 @@
           <t>Batch is archived successfully. Active status becomes false in database. The batch is hidden from active lists.</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr"/>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>Batch is archived successfully. Active status becomes false in database. The batch is hidden from active lists.</t>
+        </is>
+      </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M12" s="25" t="inlineStr">
@@ -8249,10 +8293,14 @@
           <t>Batch is reactivated successfully. Active status becomes true in database. The batch appears in active lists.</t>
         </is>
       </c>
-      <c r="K13" s="28" t="inlineStr"/>
+      <c r="K13" s="28" t="inlineStr">
+        <is>
+          <t>Batch is reactivated successfully. Active status becomes true in database. The batch appears in active lists.</t>
+        </is>
+      </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M13" s="25" t="inlineStr">
@@ -8319,10 +8367,14 @@
           <t>No permanent delete button is available on the interface. Archiving/status toggles are the only status-changing options.</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr"/>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>No permanent delete button is available on the interface. Archiving/status toggles are the only status-changing options.</t>
+        </is>
+      </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M14" s="29" t="inlineStr">
@@ -8393,10 +8445,14 @@
           <t>Student profile is created successfully. Success notification appears. The student is active by default and displayed in the batch list.</t>
         </is>
       </c>
-      <c r="K15" s="28" t="inlineStr"/>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t>Student profile is created successfully. Success notification appears. The student is active by default and displayed in the batch list.</t>
+        </is>
+      </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M15" s="25" t="inlineStr">
@@ -8465,10 +8521,14 @@
           <t>System rejects creation. Error message appears: "Duplicate student code: st001."</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr"/>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Duplicate student code: st001."</t>
+        </is>
+      </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M16" s="25" t="inlineStr">
@@ -8482,7 +8542,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="120" customHeight="1">
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
           <t>TC-M01-016</t>
@@ -8505,12 +8565,12 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Create Student with Invalid Email Format</t>
+          <t>Create Student with Missing Required Fields</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>Verify that manually creating a student with an invalid email format is blocked by validation.</t>
+          <t>Verify that manually creating a student fails if required fields like student code or name are missing.</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
@@ -8520,82 +8580,10 @@
       </c>
       <c r="H17" s="28" t="inlineStr">
         <is>
-          <t>StudentCode=ST002; StudentName=Tran Thi B; Email=tranthib.st26@invalid; AssociatedBatch=PNV26A</t>
+          <t>StudentCode=; StudentName=; AssociatedBatch=PNV26A</t>
         </is>
       </c>
       <c r="I17" s="28" t="inlineStr">
-        <is>
-          <t>1. Open Batch Management and select batch PNV26A;
-2. Click Add Student;
-3. Enter ST002 and Tran Thi B;
-4. Enter email tranthib.st26@invalid;
-5. Click Save</t>
-        </is>
-      </c>
-      <c r="J17" s="28" t="inlineStr">
-        <is>
-          <t>System rejects saving. A validation error message requires a valid email format. Saving is blocked.</t>
-        </is>
-      </c>
-      <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M17" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N17" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F04, Scenario: BS-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="105" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-017</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>M01-F04</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>Single Student Creation</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>Create Student with Missing Required Fields</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>Verify that manually creating a student fails if required fields like student code or name are missing.</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H18" s="23" t="inlineStr">
-        <is>
-          <t>StudentCode=; StudentName=; AssociatedBatch=PNV26A</t>
-        </is>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>1. Open Batch Management and select batch PNV26A;
 2. Click Add Student;
@@ -8603,15 +8591,93 @@
 4. Click Save</t>
         </is>
       </c>
+      <c r="J17" s="28" t="inlineStr">
+        <is>
+          <t>System rejects saving. Validation error messages for required fields are displayed. Saving is blocked.</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>System rejects saving. Validation error messages for required fields are displayed. Saving is blocked.</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M17" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N17" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M01-F04, Scenario: BS-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>TC-M01-017</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Module 01</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>M01-F05</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Bulk Student Import</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>CSV Student Import Upsert</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Verify that bulk student import via CSV updates existing profiles and creates new profiles (Upsert behavior).</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Student ST001 already exists; batch PNV26A exists.</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>CSV row: ST001,Nguyen Van A Updated,2006-05-15,Male,nguyenvana.new@student.passerellesnumeriques.org,AssociatedBatch=PNV26A and ST003,Le Van C,2006-08-20,Male,levanc.st26@student.passerellesnumeriques.org,AssociatedBatch=PNV26A</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>1. Go to CSV Import page;
+2. Upload CSV containing update row for ST001 and new row for ST003;
+3. Click Import</t>
+        </is>
+      </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>System rejects saving. Validation error messages for required fields are displayed. Saving is blocked.</t>
-        </is>
-      </c>
-      <c r="K18" s="23" t="inlineStr"/>
+          <t>Import completes successfully. Message displays "Import successful. 1 student updated, 1 student created.". ST001 displays new name and ST003 appears in list.</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>Import completes successfully. Message displays "Import successful. 1 student updated, 1 student created.". ST001 displays new name and ST003 appears in list.</t>
+        </is>
+      </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M18" s="25" t="inlineStr">
@@ -8621,14 +8687,14 @@
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: M01-F04, Scenario: BS-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="75" customHeight="1">
+          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>TC-M01-020</t>
+          <t>TC-M01-018</t>
         </is>
       </c>
       <c r="B19" s="26" t="inlineStr">
@@ -8648,110 +8714,118 @@
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
+          <t>CSV Student Import Rejects Duplicate Student Codes</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>Verify that student bulk import via CSV rejects imports with duplicate student codes within the file.</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in.</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>CSV containing two rows with student code ST004</t>
+        </is>
+      </c>
+      <c r="I19" s="28" t="inlineStr">
+        <is>
+          <t>1. Go to CSV Import page;
+2. Upload CSV with duplicate ST004;
+3. Click Import</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>The system rejects the entire CSV file. Error message appears: "Duplicate student code: ST004.". No records are imported.</t>
+        </is>
+      </c>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>No duplicate student ID notification in the import file.</t>
+        </is>
+      </c>
+      <c r="L19" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M19" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N19" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>TC-M01-019</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Module 01</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>M01-F05</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>Bulk Student Import</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
           <t>CSV Student Import Fails due to Missing Required Column</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>Verify that student bulk import via CSV rejects files missing required columns (e.g. Student Code).</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="H19" s="28" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>CSV file missing 'Student Code' header column</t>
         </is>
       </c>
-      <c r="I19" s="28" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>1. Open Student CSV Import page;
 2. Upload the CSV file missing Student Code;
 3. Click Import</t>
         </is>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="J20" s="23" t="inlineStr">
         <is>
           <t>The system rejects the entire CSV file. Error message appears: "Required columns must exist.". No records are imported.</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M19" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N19" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="75" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-021</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>CSV Student Import Fails due to Invalid Email Format</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>Verify that bulk import via CSV rejects the file if a student email format is invalid.</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H20" s="23" t="inlineStr">
-        <is>
-          <t>CSV file containing a row with email 'hoangvane.st26@invalid_email_domain'</t>
-        </is>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>1. Open Student CSV Import page;
-2. Upload the CSV file containing the invalid email;
-3. Click Import</t>
-        </is>
-      </c>
-      <c r="J20" s="23" t="inlineStr">
-        <is>
-          <t>The system rejects the import. Error message appears: "Valid email format" required. No records are updated or created.</t>
-        </is>
-      </c>
-      <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>No notification regarding missing student IDs in the import file.</t>
+        </is>
+      </c>
+      <c r="L20" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M20" s="25" t="inlineStr">
@@ -8768,7 +8842,7 @@
     <row r="21" ht="120" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>TC-M01-022</t>
+          <t>TC-M01-020</t>
         </is>
       </c>
       <c r="B21" s="26" t="inlineStr">
@@ -8819,10 +8893,14 @@
           <t>Student profile is updated successfully. Success notification appears. The new info is displayed immediately in lists.</t>
         </is>
       </c>
-      <c r="K21" s="28" t="inlineStr"/>
+      <c r="K21" s="28" t="inlineStr">
+        <is>
+          <t>Student profile is updated successfully. Success notification appears. The new info is displayed immediately in lists.</t>
+        </is>
+      </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M21" s="25" t="inlineStr">
@@ -8836,10 +8914,10 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="90" customHeight="1">
+    <row r="22" ht="105" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>TC-M01-023</t>
+          <t>TC-M01-021</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
@@ -8849,106 +8927,35 @@
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>M01-F06</t>
+          <t>M01-F07</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>Student Editing</t>
+          <t>Follow-up Flag</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>Edit Student Code to Existing Code Blocked</t>
+          <t>Toggle Follow-up Flag Instantly</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>Verify that renaming a student code to one that already exists in the system is blocked.</t>
+          <t>Verify that the follow-up flag updates immediately on the SPA interface without a page reload.</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>Staff user is logged in. Students ST001 and ST002 exist.</t>
+          <t>Staff user is logged in. Student ST001 is displayed in the student list.</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>TargetStudent=ST002; NewStudentCode=ST001</t>
+          <t>StudentCode=ST001</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
-        <is>
-          <t>1. Open Batch Management and select student ST002;
-2. Click Edit;
-3. Change Student Code to ST001;
-4. Click Save</t>
-        </is>
-      </c>
-      <c r="J22" s="23" t="inlineStr">
-        <is>
-          <t>System rejects update. Error message appears: "Duplicate student code: ST001."</t>
-        </is>
-      </c>
-      <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M22" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N22" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F06, Scenario: BS-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="105" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>TC-M01-024</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>M01-F07</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="inlineStr">
-        <is>
-          <t>Follow-up Flag</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="inlineStr">
-        <is>
-          <t>Toggle Follow-up Flag Instantly</t>
-        </is>
-      </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>Verify that the follow-up flag updates immediately on the SPA interface without a page reload.</t>
-        </is>
-      </c>
-      <c r="G23" s="28" t="inlineStr">
-        <is>
-          <t>Staff user is logged in. Student ST001 is displayed in the student list.</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="inlineStr">
-        <is>
-          <t>StudentCode=ST001</t>
-        </is>
-      </c>
-      <c r="I23" s="28" t="inlineStr">
         <is>
           <t>1. Navigate to student list;
 2. Locate student ST001;
@@ -8956,70 +8963,74 @@
 4. Observe the page</t>
         </is>
       </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="J22" s="23" t="inlineStr">
         <is>
           <t>The flag status toggles instantly in the UI with no page reload. Google Sheets database updates the follow-up status immediately.</t>
         </is>
       </c>
-      <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M23" s="25" t="inlineStr">
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>The "Follow-up Flag" feature for students is not yet available in this section.</t>
+        </is>
+      </c>
+      <c r="L22" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M22" s="25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N23" s="28" t="inlineStr">
+      <c r="N22" s="23" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F07, Scenario: BS-07</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-025</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>TC-M01-022</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>M01-F08</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>Student Status Management</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>Toggle Student Status Active to Inactive</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>Verify that toggling student status to Inactive automatically sets Dropout Date to today.</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G23" s="28" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 is Active with no Dropout Date.</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>StudentCode=ST001; NewStatus=Inactive</t>
         </is>
       </c>
-      <c r="I24" s="23" t="inlineStr">
+      <c r="I23" s="28" t="inlineStr">
         <is>
           <t>1. Open ST001 profile and click Edit;
 2. Change status to Inactive;
@@ -9027,70 +9038,74 @@
 4. Open ST001 profile details</t>
         </is>
       </c>
-      <c r="J24" s="23" t="inlineStr">
+      <c r="J23" s="28" t="inlineStr">
         <is>
           <t>Student status is saved as Inactive. The Dropout Date is automatically set to today's date (e.g. 2026-07-17) without manual input.</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M24" s="25" t="inlineStr">
+      <c r="K23" s="28" t="inlineStr">
+        <is>
+          <t>Student status is saved as Inactive. The Dropout Date is automatically set to today's date (e.g. 2026-07-17) without manual input.</t>
+        </is>
+      </c>
+      <c r="L23" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M23" s="25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N24" s="23" t="inlineStr">
+      <c r="N23" s="28" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F08, Scenario: BS-08</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>TC-M01-026</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>TC-M01-023</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>M01-F08</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>Student Status Management</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>Toggle Student Status Inactive to Active</t>
         </is>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>Verify that toggling student status to Active automatically clears Dropout Date.</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 is Inactive with Dropout Date '2026-07-17'.</t>
         </is>
       </c>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>StudentCode=ST001; NewStatus=Active</t>
         </is>
       </c>
-      <c r="I25" s="28" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>1. Open ST001 profile and click Edit;
 2. Change status to Active;
@@ -9098,211 +9113,148 @@
 4. Open ST001 profile details</t>
         </is>
       </c>
-      <c r="J25" s="28" t="inlineStr">
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>Student status is saved as Active. The Dropout Date field is automatically cleared and is now blank.</t>
         </is>
       </c>
-      <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M25" s="25" t="inlineStr">
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>Student status is saved as Active. The Dropout Date field is automatically cleared and is now blank.</t>
+        </is>
+      </c>
+      <c r="L24" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M24" s="25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N25" s="28" t="inlineStr">
+      <c r="N24" s="23" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F08, Scenario: BS-08</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="75" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-027</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
+    <row r="25" ht="75" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>TC-M01-024</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>M01-F09</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>Search &amp; Filter</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>Search Student by Name Real-time</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>Verify that searching student list by name filters records dynamically in real-time as the user types.</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G25" s="28" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student list contains 'Nguyen Van A' and 'Tran Thi B'.</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
+      <c r="H25" s="28" t="inlineStr">
         <is>
           <t>SearchQuery=Nguyen</t>
         </is>
       </c>
-      <c r="I26" s="23" t="inlineStr">
+      <c r="I25" s="28" t="inlineStr">
         <is>
           <t>1. Navigate to student list;
 2. Place cursor in Search box and type 'Nguyen';
 3. Observe student list</t>
         </is>
       </c>
-      <c r="J26" s="23" t="inlineStr">
+      <c r="J25" s="28" t="inlineStr">
         <is>
           <t>The student list filters dynamically while typing. Tran Thi B is hidden, and Nguyen Van A remains visible. No page reload occurs.</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M26" s="29" t="inlineStr">
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>The student list filters dynamically while typing. Tran Thi B is hidden, and Nguyen Van A remains visible. No page reload occurs.</t>
+        </is>
+      </c>
+      <c r="L25" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M25" s="29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N26" s="23" t="inlineStr">
+      <c r="N25" s="28" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F09, Scenario: BS-09</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>TC-M01-028</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="inlineStr">
+    <row r="26" ht="105" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>TC-M01-025</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>M01-F09</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>Search &amp; Filter</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
-        <is>
-          <t>Filter Students by Observation Rating</t>
-        </is>
-      </c>
-      <c r="F27" s="28" t="inlineStr">
-        <is>
-          <t>Verify that staff can filter students by their observation rating.</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="inlineStr">
-        <is>
-          <t>Staff user is logged in. Students exist with different observation ratings.</t>
-        </is>
-      </c>
-      <c r="H27" s="28" t="inlineStr">
-        <is>
-          <t>RatingFilter=Good</t>
-        </is>
-      </c>
-      <c r="I27" s="28" t="inlineStr">
-        <is>
-          <t>1. Open student list;
-2. Click the Observation Rating filter dropdown;
-3. Choose Good;
-4. Observe the filtered list</t>
-        </is>
-      </c>
-      <c r="J27" s="28" t="inlineStr">
-        <is>
-          <t>The student list is filtered to display only students with a "Good" rating. Other students are hidden.</t>
-        </is>
-      </c>
-      <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M27" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N27" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F09, Scenario: BS-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="105" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-029</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>M01-F09</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>Search &amp; Filter</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>Verify Student List Default Pagination</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>Verify that the student list displays exactly 10 students per page by default.</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>Staff user is logged in. There are 12 students in the selected batch.</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>Batch PNV26A has 12 students.</t>
         </is>
       </c>
-      <c r="I28" s="23" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>1. Navigate to the student list of batch PNV26A;
 2. Count the number of students displayed on the first page;
@@ -9310,769 +9262,589 @@
 4. Click Next Page</t>
         </is>
       </c>
-      <c r="J28" s="23" t="inlineStr">
+      <c r="J26" s="23" t="inlineStr">
         <is>
           <t>Page 1 displays exactly 10 students. Pagination controls are visible. Clicking Next Page shows the remaining 2 students on page 2.</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M28" s="29" t="inlineStr">
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>Page 1 displays exactly 10 students. Pagination controls are visible. Clicking Next Page shows the remaining 2 students on page 2.</t>
+        </is>
+      </c>
+      <c r="L26" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M26" s="29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N28" s="23" t="inlineStr">
+      <c r="N26" s="23" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F09, Scenario: BS-10</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="75" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>TC-M01-030</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
+    <row r="27" ht="75" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>TC-M01-026</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C29" s="27" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>M01-F10</t>
         </is>
       </c>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>Dashboard Overview</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>Verify Dashboard Displays Correct Initial Stats and Charts</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>Verify that the dashboard screen accurately loads and displays all student and batch metrics.</t>
         </is>
       </c>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="G27" s="28" t="inlineStr">
         <is>
           <t>Staff user is logged in. System has 2 batches (1 Active, 1 Archived) and 5 students (4 Active, 1 Inactive).</t>
         </is>
       </c>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="H27" s="28" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I29" s="28" t="inlineStr">
+      <c r="I27" s="28" t="inlineStr">
         <is>
           <t>1. Navigate to the Dashboard Overview page;
 2. Observe the statistics cards and charts</t>
         </is>
       </c>
-      <c r="J29" s="28" t="inlineStr">
+      <c r="J27" s="28" t="inlineStr">
         <is>
           <t>The dashboard displays: Total Batches = 2, Active Batches = 1, Total Students = 5, Active Students = 4, Inactive Students = 1. Charts (Gender, Ethnicity, Status) load successfully.</t>
         </is>
       </c>
-      <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M29" s="29" t="inlineStr">
+      <c r="K27" s="28" t="inlineStr">
+        <is>
+          <t>The dashboard displays: Total Batches = 2, Active Batches = 1, Total Students = 5, Active Students = 4, Inactive Students = 1. Charts (Gender, Ethnicity, Status) load successfully.</t>
+        </is>
+      </c>
+      <c r="L27" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M27" s="29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N29" s="28" t="inlineStr">
+      <c r="N27" s="28" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F10, Scenario: BS-11</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-031</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>TC-M01-027</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>M01-F10</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>Dashboard Overview</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>Verify Dashboard Stats Auto-refresh after Data Changes</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>Verify that dashboard statistics and charts refresh automatically when data changes.</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>Staff user is logged in. Dashboard shows Active Students = 4.</t>
         </is>
       </c>
-      <c r="H30" s="23" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>StudentCode=ST001; NewStatus=Inactive</t>
         </is>
       </c>
-      <c r="I30" s="23" t="inlineStr">
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>1. Navigate to student list and edit ST001 to change status from Active to Inactive;
 2. Click Save;
 3. Immediately return to the Dashboard</t>
         </is>
       </c>
-      <c r="J30" s="23" t="inlineStr">
+      <c r="J28" s="23" t="inlineStr">
         <is>
           <t>The dashboard values update without manual page reload: Active Students displays 3, Inactive Students displays 2, and charts adjust accordingly.</t>
         </is>
       </c>
-      <c r="K30" s="23" t="inlineStr"/>
-      <c r="L30" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M30" s="29" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>The dashboard values update without manual page reload: Active Students displays 3, Inactive Students displays 2, and charts adjust accordingly.</t>
+        </is>
+      </c>
+      <c r="L28" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M28" s="29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N30" s="23" t="inlineStr">
+      <c r="N28" s="23" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F10, Scenario: BS-11</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>TC-M01-032</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>TC-M01-028</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C31" s="27" t="inlineStr">
+      <c r="C29" s="27" t="inlineStr">
         <is>
           <t>M01-SEC</t>
         </is>
       </c>
-      <c r="D31" s="28" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>Access Control &amp; Security</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>Staff User Access to Student Management</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>Verify that staff users with a valid @passerellesnumeriques.org email domain are granted access to Batch &amp; Student Management.</t>
         </is>
       </c>
-      <c r="G31" s="28" t="inlineStr">
+      <c r="G29" s="28" t="inlineStr">
         <is>
           <t>User is authenticated with email staff@passerellesnumeriques.org.</t>
         </is>
       </c>
-      <c r="H31" s="28" t="inlineStr">
+      <c r="H29" s="28" t="inlineStr">
         <is>
           <t>Email=staff@passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="I31" s="28" t="inlineStr">
+      <c r="I29" s="28" t="inlineStr">
         <is>
           <t>1. Enter the application URL;
 2. Sign in via Google OAuth with account staff@passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="J31" s="28" t="inlineStr">
+      <c r="J29" s="28" t="inlineStr">
         <is>
           <t>The user is redirected to the Staff Portal. Full management options (Create Batch, Add Student, Edit, CSV Import) are visible and accessible.</t>
         </is>
       </c>
-      <c r="K31" s="28" t="inlineStr"/>
-      <c r="L31" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M31" s="25" t="inlineStr">
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>The user is redirected to the Staff Portal. Full management options (Create Batch, Add Student, Edit, CSV Import) are visible and accessible.</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M29" s="25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N31" s="28" t="inlineStr">
+      <c r="N29" s="28" t="inlineStr">
         <is>
           <t>Related Requirement: General Business Rules, Scenario: BS-12</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-033</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>TC-M01-029</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>M01-SEC</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>Access Control &amp; Security</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>Student User Access to Student Management Denied</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>Verify that students with a @student.passerellesnumeriques.org email are denied management access.</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>User is authenticated with email student01@student.passerellesnumeriques.org.</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>Email=student01@student.passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="I32" s="23" t="inlineStr">
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>1. Enter the application URL;
 2. Sign in via Google OAuth with account student01@student.passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="J32" s="23" t="inlineStr">
+      <c r="J30" s="23" t="inlineStr">
         <is>
           <t>The user is redirected to the Student Portal. Management buttons and options are hidden. Direct URL routing to staff pages displays "Access Denied".</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr"/>
-      <c r="L32" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M32" s="25" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>The user is redirected to the Student Portal. Management buttons and options are hidden. Direct URL routing to staff pages displays "Access Denied".</t>
+        </is>
+      </c>
+      <c r="L30" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M30" s="25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N32" s="23" t="inlineStr">
+      <c r="N30" s="23" t="inlineStr">
         <is>
           <t>Related Requirement: General Business Rules, Scenario: BS-12</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>TC-M01-018</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="inlineStr">
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>TC-M01-030</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>CSV Student Import Upsert</t>
-        </is>
-      </c>
-      <c r="F33" s="28" t="inlineStr">
-        <is>
-          <t>Verify that bulk student import via CSV updates existing profiles and creates new profiles (Upsert behavior).</t>
-        </is>
-      </c>
-      <c r="G33" s="28" t="inlineStr">
-        <is>
-          <t>Staff user is logged in. Student ST001 already exists; batch PNV26A exists.</t>
-        </is>
-      </c>
-      <c r="H33" s="28" t="inlineStr">
-        <is>
-          <t>CSV row: ST001,Nguyen Van A Updated,2006-05-15,Male,nguyenvana.new@student.passerellesnumeriques.org,AssociatedBatch=PNV26A and ST003,Le Van C,2006-08-20,Male,levanc.st26@student.passerellesnumeriques.org,AssociatedBatch=PNV26A</t>
-        </is>
-      </c>
-      <c r="I33" s="28" t="inlineStr">
-        <is>
-          <t>1. Go to CSV Import page;
-2. Upload CSV containing update row for ST001 and new row for ST003;
-3. Click Import</t>
-        </is>
-      </c>
-      <c r="J33" s="28" t="inlineStr">
-        <is>
-          <t>Import completes successfully. Message displays "Import successful. 1 student updated, 1 student created.". ST001 displays new name and ST003 appears in list.</t>
-        </is>
-      </c>
-      <c r="K33" s="28" t="inlineStr"/>
-      <c r="L33" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M33" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N33" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-019</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="inlineStr">
-        <is>
-          <t>CSV Student Import Rejects Duplicate Student Codes</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>Verify that student bulk import via CSV rejects imports with duplicate student codes within the file.</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H34" s="23" t="inlineStr">
-        <is>
-          <t>CSV containing two rows with student code ST004</t>
-        </is>
-      </c>
-      <c r="I34" s="23" t="inlineStr">
-        <is>
-          <t>1. Go to CSV Import page;
-2. Upload CSV with duplicate ST004;
-3. Click Import</t>
-        </is>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>The system rejects the entire CSV file. Error message appears: "Duplicate student code: ST004.". No records are imported.</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr"/>
-      <c r="L34" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M34" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N34" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="26" t="inlineStr">
-        <is>
-          <t>TC-M01-034</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="C31" s="27" t="inlineStr">
         <is>
           <t>M01-SEC</t>
         </is>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>Access Control &amp; Security</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>Unknown Email Domain Access Denied</t>
         </is>
       </c>
-      <c r="F35" s="28" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>Verify that users with non-permitted email domains are completely blocked from accessing the system.</t>
         </is>
       </c>
-      <c r="G35" s="28" t="inlineStr">
+      <c r="G31" s="28" t="inlineStr">
         <is>
           <t>User is authenticated with email testuser@gmail.com.</t>
         </is>
       </c>
-      <c r="H35" s="28" t="inlineStr">
+      <c r="H31" s="28" t="inlineStr">
         <is>
           <t>Email=testuser@gmail.com</t>
         </is>
       </c>
-      <c r="I35" s="28" t="inlineStr">
+      <c r="I31" s="28" t="inlineStr">
         <is>
           <t>1. Enter the application URL;
 2. Sign in via Google OAuth with account testuser@gmail.com;
 3. Observe the system response</t>
         </is>
       </c>
-      <c r="J35" s="28" t="inlineStr">
-        <is>
-          <t>Login fails or the screen displays an "Access Denied" message. The user is not redirected to either the Staff or Student Portal.</t>
-        </is>
-      </c>
-      <c r="K35" s="28" t="inlineStr"/>
-      <c r="L35" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M35" s="25" t="inlineStr">
+      <c r="J31" s="28" t="inlineStr">
+        <is>
+          <t>Login failed, or the screen displays a notification stating that this page cannot be accessed.</t>
+        </is>
+      </c>
+      <c r="K31" s="28" t="inlineStr">
+        <is>
+          <t>Login failed, or the screen displays a notification stating that this page cannot be accessed.</t>
+        </is>
+      </c>
+      <c r="L31" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M31" s="25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N35" s="28" t="inlineStr">
+      <c r="N31" s="28" t="inlineStr">
         <is>
           <t>Related Requirement: General Business Rules, Authorization</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="135" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-035</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
+    <row r="32" ht="75" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>TC-M01-031</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
-        <is>
-          <t>M01-F04</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>Single Student Creation</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>Create Student Fails due to Missing Associated Batch</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>Verify that manually creating a student requires selecting an Associated Batch.</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>M01-F05</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Bulk Student Import</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>CSV Student Import Fails due to Blank Name</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>Verify that bulk import via CSV blocks saving if student name is empty.</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="H36" s="23" t="inlineStr">
-        <is>
-          <t>StudentCode=ST099; StudentName=Nguyen Van Test; AssociatedBatch=Empty</t>
-        </is>
-      </c>
-      <c r="I36" s="23" t="inlineStr">
-        <is>
-          <t>1. Open Batch Management;
-2. Click Add Student;
-3. Enter Student Code 'ST099' and Name 'Nguyen Van Test';
-4. Leave Associated Batch selection empty;
-5. Click Save</t>
-        </is>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>The system blocks saving and displays a validation error "Associated Batch is required". The batch dropdown is highlighted in red.</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr"/>
-      <c r="L36" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M36" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N36" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F04, Validation Rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="75" customHeight="1">
-      <c r="A37" s="26" t="inlineStr">
-        <is>
-          <t>TC-M01-036</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C37" s="27" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E37" s="28" t="inlineStr">
-        <is>
-          <t>CSV Student Import Fails due to Blank Name</t>
-        </is>
-      </c>
-      <c r="F37" s="28" t="inlineStr">
-        <is>
-          <t>Verify that bulk import via CSV blocks saving if student name is empty.</t>
-        </is>
-      </c>
-      <c r="G37" s="28" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="inlineStr">
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>CSV contains row: ST006,,2006-08-20,Male,student06@student.passerellesnumeriques.org (blank name)</t>
         </is>
       </c>
-      <c r="I37" s="28" t="inlineStr">
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>1. Go to CSV Import page;
 2. Upload the CSV file with blank name;
 3. Click Import</t>
         </is>
       </c>
-      <c r="J37" s="28" t="inlineStr">
+      <c r="J32" s="23" t="inlineStr">
         <is>
           <t>The system rejects the entire CSV file with error message "Student Name is required". No records are updated in database.</t>
         </is>
       </c>
-      <c r="K37" s="28" t="inlineStr"/>
-      <c r="L37" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M37" s="25" t="inlineStr">
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>The system rejects the entire CSV file with error message "Student Name is required". No records are updated in database.</t>
+        </is>
+      </c>
+      <c r="L32" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M32" s="25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N37" s="28" t="inlineStr">
+      <c r="N32" s="23" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F05, Validation Rules</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="75" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-037</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
+    <row r="33" ht="75" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>TC-M01-032</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C33" s="27" t="inlineStr">
         <is>
           <t>M01-F09</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>Search &amp; Filter</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>Search Student Case Insensitivity</t>
         </is>
       </c>
-      <c r="F38" s="23" t="inlineStr">
+      <c r="F33" s="28" t="inlineStr">
         <is>
           <t>Verify that student search filters correctly regardless of character casing.</t>
         </is>
       </c>
-      <c r="G38" s="23" t="inlineStr">
+      <c r="G33" s="28" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A contains student 'Nguyen Van A'.</t>
         </is>
       </c>
-      <c r="H38" s="23" t="inlineStr">
+      <c r="H33" s="28" t="inlineStr">
         <is>
           <t>SearchQuery=nguyen van a</t>
         </is>
       </c>
-      <c r="I38" s="23" t="inlineStr">
+      <c r="I33" s="28" t="inlineStr">
         <is>
           <t>1. Open student list;
 2. Enter 'nguyen van a' (all lowercase) in the search box;
 3. Verify matching result</t>
         </is>
       </c>
-      <c r="J38" s="23" t="inlineStr">
+      <c r="J33" s="28" t="inlineStr">
         <is>
           <t>The student list filters and displays 'Nguyen Van A', proving search is case-insensitive.</t>
         </is>
       </c>
-      <c r="K38" s="23" t="inlineStr"/>
-      <c r="L38" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M38" s="29" t="inlineStr">
+      <c r="K33" s="28" t="inlineStr">
+        <is>
+          <t>The student list filters and displays 'Nguyen Van A', proving search is case-insensitive.</t>
+        </is>
+      </c>
+      <c r="L33" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M33" s="29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N38" s="23" t="inlineStr">
+      <c r="N33" s="28" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F09, Search &amp; Filter</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="26" t="inlineStr">
-        <is>
-          <t>TC-M01-038</t>
-        </is>
-      </c>
-      <c r="B39" s="26" t="inlineStr">
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>TC-M01-033</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C39" s="27" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>M01-F06</t>
         </is>
       </c>
-      <c r="D39" s="28" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>Student Editing</t>
         </is>
       </c>
-      <c r="E39" s="28" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>Edit Student Email to Invalid Format Blocked</t>
         </is>
       </c>
-      <c r="F39" s="28" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>Verify that editing a student's email to an invalid format is blocked.</t>
         </is>
       </c>
-      <c r="G39" s="28" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 exists.</t>
         </is>
       </c>
-      <c r="H39" s="28" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>StudentCode=ST001; NewEmail=nguyenvana_invalid_email</t>
         </is>
       </c>
-      <c r="I39" s="28" t="inlineStr">
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>1. Open student list;
 2. Select ST001 and click Edit;
@@ -10080,105 +9852,39 @@
 4. Click Save</t>
         </is>
       </c>
-      <c r="J39" s="28" t="inlineStr">
+      <c r="J34" s="23" t="inlineStr">
         <is>
           <t>The system blocks saving and displays a validation error message requiring a valid email format. The email field is highlighted in red.</t>
         </is>
       </c>
-      <c r="K39" s="28" t="inlineStr"/>
-      <c r="L39" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M39" s="25" t="inlineStr">
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>The system successfully updated the email address, even though the format was incorrect.</t>
+        </is>
+      </c>
+      <c r="L34" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M34" s="25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N39" s="28" t="inlineStr">
+      <c r="N34" s="23" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F06, Validation Rules</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="75" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>TC-M01-039</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C40" s="22" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>CSV Student Import Blocked due to Duplicate Student Code in Another Batch</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>Verify that CSV student import rejects student codes that are already in use in other batches.</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>Student ST001 exists in batch PNV26A. Batch PNV26B has no students.</t>
-        </is>
-      </c>
-      <c r="H40" s="23" t="inlineStr">
-        <is>
-          <t>CSV file for batch PNV26B containing row: ST001,Le Van C,2006-08-20,Male,levanc.st26@student.passerellesnumeriques.org</t>
-        </is>
-      </c>
-      <c r="I40" s="23" t="inlineStr">
-        <is>
-          <t>1. Go to CSV Import page for batch PNV26B;
-2. Upload CSV containing student ST001;
-3. Click Import</t>
-        </is>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>The system rejects the import and displays error message "Duplicate student code: ST001.". No students are added.</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr"/>
-      <c r="L40" s="24" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M40" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N40" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F05, Student Code Uniqueness</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N40"/>
+  <autoFilter ref="A1:N34"/>
   <dataValidations count="2">
-    <dataValidation sqref="L2:L140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
+    <dataValidation sqref="L2:L134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="M2:M134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10342,7 +10048,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10414,7 +10120,7 @@
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10486,7 +10192,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10557,7 +10263,7 @@
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10628,7 +10334,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10699,7 +10405,7 @@
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10770,7 +10476,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10841,7 +10547,7 @@
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10912,7 +10618,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10981,7 +10687,7 @@
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11050,7 +10756,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11120,7 +10826,7 @@
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11190,7 +10896,7 @@
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11260,7 +10966,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11331,7 +11037,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11402,7 +11108,7 @@
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11472,7 +11178,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11543,7 +11249,7 @@
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11615,7 +11321,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11684,7 +11390,7 @@
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11754,7 +11460,7 @@
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11826,7 +11532,7 @@
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11898,7 +11604,7 @@
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11970,7 +11676,7 @@
         </is>
       </c>
       <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr">
+      <c r="L25" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12042,7 +11748,7 @@
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr">
+      <c r="L26" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12113,7 +11819,7 @@
         </is>
       </c>
       <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr">
+      <c r="L27" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12184,7 +11890,7 @@
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr">
+      <c r="L28" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12254,7 +11960,7 @@
         </is>
       </c>
       <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="24" t="inlineStr">
+      <c r="L29" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12324,7 +12030,7 @@
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr"/>
-      <c r="L30" s="24" t="inlineStr">
+      <c r="L30" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12395,7 +12101,7 @@
         </is>
       </c>
       <c r="K31" s="28" t="inlineStr"/>
-      <c r="L31" s="24" t="inlineStr">
+      <c r="L31" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12466,7 +12172,7 @@
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr"/>
-      <c r="L32" s="24" t="inlineStr">
+      <c r="L32" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12649,7 +12355,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12720,7 +12426,7 @@
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12792,7 +12498,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12864,7 +12570,7 @@
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12935,7 +12641,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13006,7 +12712,7 @@
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13077,7 +12783,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13148,7 +12854,7 @@
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13218,7 +12924,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13289,7 +12995,7 @@
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13359,7 +13065,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13429,7 +13135,7 @@
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13497,7 +13203,7 @@
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13569,7 +13275,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13639,7 +13345,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13710,7 +13416,7 @@
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13781,7 +13487,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13852,7 +13558,7 @@
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13922,7 +13628,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13992,7 +13698,7 @@
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14062,7 +13768,7 @@
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14132,7 +13838,7 @@
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14319,7 +14025,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14392,7 +14098,7 @@
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14463,7 +14169,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14534,7 +14240,7 @@
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14604,7 +14310,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14675,7 +14381,7 @@
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14746,7 +14452,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14816,7 +14522,7 @@
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14887,7 +14593,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -14958,7 +14664,7 @@
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15029,7 +14735,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15100,7 +14806,7 @@
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15170,7 +14876,7 @@
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15239,7 +14945,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15308,7 +15014,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15379,7 +15085,7 @@
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15450,7 +15156,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15521,7 +15227,7 @@
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15592,7 +15298,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15662,7 +15368,7 @@
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15731,7 +15437,7 @@
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15801,7 +15507,7 @@
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -15872,7 +15578,7 @@
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16059,7 +15765,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16135,7 +15841,7 @@
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16210,7 +15916,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16285,7 +15991,7 @@
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16360,7 +16066,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16434,7 +16140,7 @@
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16505,7 +16211,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16578,7 +16284,7 @@
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16651,7 +16357,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16724,7 +16430,7 @@
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16796,7 +16502,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16869,7 +16575,7 @@
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -16941,7 +16647,7 @@
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17016,7 +16722,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17090,7 +16796,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17162,7 +16868,7 @@
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17234,7 +16940,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17305,7 +17011,7 @@
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17376,7 +17082,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17452,7 +17158,7 @@
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17528,7 +17234,7 @@
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17604,7 +17310,7 @@
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17677,7 +17383,7 @@
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17751,7 +17457,7 @@
         </is>
       </c>
       <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr">
+      <c r="L25" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17824,7 +17530,7 @@
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr">
+      <c r="L26" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17898,7 +17604,7 @@
         </is>
       </c>
       <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr">
+      <c r="L27" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -17973,7 +17679,7 @@
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr">
+      <c r="L28" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18157,7 +17863,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18229,7 +17935,7 @@
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18301,7 +18007,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18371,7 +18077,7 @@
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18444,7 +18150,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18517,7 +18223,7 @@
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18589,7 +18295,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18660,7 +18366,7 @@
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18731,7 +18437,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18802,7 +18508,7 @@
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18874,7 +18580,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -18945,7 +18651,7 @@
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19017,7 +18723,7 @@
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19088,7 +18794,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19158,7 +18864,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19228,7 +18934,7 @@
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19296,7 +19002,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19373,7 +19079,7 @@
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19443,7 +19149,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19513,7 +19219,7 @@
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19583,7 +19289,7 @@
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19653,7 +19359,7 @@
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19723,7 +19429,7 @@
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19793,7 +19499,7 @@
         </is>
       </c>
       <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr">
+      <c r="L25" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19863,7 +19569,7 @@
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr">
+      <c r="L26" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -19934,7 +19640,7 @@
         </is>
       </c>
       <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr">
+      <c r="L27" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20006,7 +19712,7 @@
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr">
+      <c r="L28" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20076,7 +19782,7 @@
         </is>
       </c>
       <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="24" t="inlineStr">
+      <c r="L29" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20147,7 +19853,7 @@
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr"/>
-      <c r="L30" s="24" t="inlineStr">
+      <c r="L30" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20218,7 +19924,7 @@
         </is>
       </c>
       <c r="K31" s="28" t="inlineStr"/>
-      <c r="L31" s="24" t="inlineStr">
+      <c r="L31" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20289,7 +19995,7 @@
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr"/>
-      <c r="L32" s="24" t="inlineStr">
+      <c r="L32" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20473,7 +20179,7 @@
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20544,7 +20250,7 @@
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20614,7 +20320,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20683,7 +20389,7 @@
         </is>
       </c>
       <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20756,7 +20462,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20826,7 +20532,7 @@
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20898,7 +20604,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -20969,7 +20675,7 @@
         </is>
       </c>
       <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21041,7 +20747,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21111,7 +20817,7 @@
         </is>
       </c>
       <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21184,7 +20890,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21254,7 +20960,7 @@
         </is>
       </c>
       <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21325,7 +21031,7 @@
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21395,7 +21101,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21466,7 +21172,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21534,7 +21240,7 @@
         </is>
       </c>
       <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21607,7 +21313,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21677,7 +21383,7 @@
         </is>
       </c>
       <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21748,7 +21454,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21818,7 +21524,7 @@
         </is>
       </c>
       <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21889,7 +21595,7 @@
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -21957,7 +21663,7 @@
         </is>
       </c>
       <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22029,7 +21735,7 @@
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22099,7 +21805,7 @@
         </is>
       </c>
       <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr">
+      <c r="L25" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22169,7 +21875,7 @@
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr">
+      <c r="L26" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22240,7 +21946,7 @@
         </is>
       </c>
       <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr">
+      <c r="L27" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22311,7 +22017,7 @@
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr">
+      <c r="L28" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22382,7 +22088,7 @@
         </is>
       </c>
       <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="24" t="inlineStr">
+      <c r="L29" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22452,7 +22158,7 @@
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr"/>
-      <c r="L30" s="24" t="inlineStr">
+      <c r="L30" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22522,7 +22228,7 @@
         </is>
       </c>
       <c r="K31" s="28" t="inlineStr"/>
-      <c r="L31" s="24" t="inlineStr">
+      <c r="L31" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22591,7 +22297,7 @@
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr"/>
-      <c r="L32" s="24" t="inlineStr">
+      <c r="L32" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22661,7 +22367,7 @@
         </is>
       </c>
       <c r="K33" s="28" t="inlineStr"/>
-      <c r="L33" s="24" t="inlineStr">
+      <c r="L33" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22731,7 +22437,7 @@
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr"/>
-      <c r="L34" s="24" t="inlineStr">
+      <c r="L34" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22800,7 +22506,7 @@
         </is>
       </c>
       <c r="K35" s="28" t="inlineStr"/>
-      <c r="L35" s="24" t="inlineStr">
+      <c r="L35" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22870,7 +22576,7 @@
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr"/>
-      <c r="L36" s="24" t="inlineStr">
+      <c r="L36" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -22939,7 +22645,7 @@
         </is>
       </c>
       <c r="K37" s="28" t="inlineStr"/>
-      <c r="L37" s="24" t="inlineStr">
+      <c r="L37" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -23008,7 +22714,7 @@
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr"/>
-      <c r="L38" s="24" t="inlineStr">
+      <c r="L38" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -23078,7 +22784,7 @@
         </is>
       </c>
       <c r="K39" s="28" t="inlineStr"/>
-      <c r="L39" s="24" t="inlineStr">
+      <c r="L39" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -23146,7 +22852,7 @@
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr"/>
-      <c r="L40" s="24" t="inlineStr">
+      <c r="L40" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -23216,7 +22922,7 @@
         </is>
       </c>
       <c r="K41" s="28" t="inlineStr"/>
-      <c r="L41" s="24" t="inlineStr">
+      <c r="L41" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -23286,7 +22992,7 @@
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr"/>
-      <c r="L42" s="24" t="inlineStr">
+      <c r="L42" s="30" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>

--- a/Tests/excel/academic_portal_all_test_cases.xlsx
+++ b/Tests/excel/academic_portal_all_test_cases.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 01" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 02" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 03" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 04" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 05" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 06" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 07" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 08" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module 09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Module 01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Module 02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Module 03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Module 04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Module 05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Module 06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Module 07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Module 08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Module 09" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Module 01'!$A$1:$O$34</definedName>
@@ -497,14 +497,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -528,10 +527,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -555,10 +554,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -582,10 +581,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -614,8 +613,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -641,8 +640,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -668,7 +667,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -683,9 +682,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -20241,10 +20240,15 @@
 New category name "Foundations" is updated and displayed on UI.</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>Category renamed successfully.
+New category name "Foundations" is updated and displayed on UI.</t>
+        </is>
+      </c>
+      <c r="L2" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="21" t="inlineStr"/>
@@ -20313,10 +20317,15 @@
 Validation error message appears: "Category Name cannot be empty."</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>System blocks action.
+Validation error message appears: "Category Name cannot be empty."</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr"/>
@@ -20384,10 +20393,14 @@
           <t>Archive and Delete buttons are not present in Category context menu.</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>Archive and Delete buttons are not present in Category context menu.</t>
+        </is>
+      </c>
+      <c r="L4" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
@@ -20454,10 +20467,14 @@
           <t>Default categories "IT", "English", and "Professional Skills" are present in system.</t>
         </is>
       </c>
-      <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K5" s="28" t="inlineStr">
+        <is>
+          <t>Default categories "IT", "English", and "Professional Skills" are present in system.</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M5" s="26" t="inlineStr"/>
@@ -20528,10 +20545,15 @@
 New course "Web Development" appears under category "IT".</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>Course created successfully.
+New course "Web Development" appears under category "IT".</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr"/>
@@ -20599,10 +20621,15 @@
 Validation error appears: "Course Name is required."</t>
         </is>
       </c>
-      <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K7" s="28" t="inlineStr">
+        <is>
+          <t>System blocks action.
+Validation error appears: "Course Name is required."</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr"/>
@@ -20672,10 +20699,14 @@
           <t>Course name updated successfully to "Frontend Development".</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Course name updated successfully to "Frontend Development".</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr"/>
@@ -20744,10 +20775,15 @@
 Course is hidden from Active list and moved to Archived tab.</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>Course status changes to Archived.
+Course is hidden from Active list and moved to Archived tab.</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M9" s="26" t="inlineStr"/>
@@ -20817,10 +20853,15 @@
 Course reappears in active course list.</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>Course status changes back to Active.
+Course reappears in active course list.</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr"/>
@@ -20888,10 +20929,14 @@
           <t>Permanent Delete button is not present for courses (only Archive is supported).</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K11" s="28" t="inlineStr">
+        <is>
+          <t>Permanent Delete button is not present for courses (only Archive is supported).</t>
+        </is>
+      </c>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr"/>
@@ -20962,10 +21007,15 @@
 "Session 1: HTML Basics" appears inside course.</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>Session created successfully.
+"Session 1: HTML Basics" appears inside course.</t>
+        </is>
+      </c>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr"/>
@@ -21033,10 +21083,15 @@
 Validation error appears: "Session Name is required."</t>
         </is>
       </c>
-      <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K13" s="28" t="inlineStr">
+        <is>
+          <t>System blocks action.
+Validation error appears: "Session Name is required."</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M13" s="26" t="inlineStr"/>
@@ -21105,10 +21160,14 @@
           <t>Session details updated successfully.</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>Session details updated successfully.</t>
+        </is>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr"/>
@@ -21176,10 +21235,14 @@
           <t>Session and all attached materials are permanently deleted from system.</t>
         </is>
       </c>
-      <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t>Session and all attached materials are permanently deleted from system.</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M15" s="26" t="inlineStr"/>
@@ -21248,10 +21311,15 @@
 Session remains intact in course.</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>Dialog closes.
+Session remains intact in course.</t>
+        </is>
+      </c>
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr"/>
@@ -21317,10 +21385,14 @@
           <t>Archive button is not available for sessions (only Delete is supported).</t>
         </is>
       </c>
-      <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>Archive button is not available for sessions (only Delete is supported).</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M17" s="26" t="inlineStr"/>
@@ -21391,10 +21463,15 @@
 "Midterm Exam" displays in exam section of course.</t>
         </is>
       </c>
-      <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>Exam created successfully.
+"Midterm Exam" displays in exam section of course.</t>
+        </is>
+      </c>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr"/>
@@ -21462,10 +21539,15 @@
 Validation error appears: "Exam Name is required."</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>System blocks action.
+Validation error appears: "Exam Name is required."</t>
+        </is>
+      </c>
+      <c r="L19" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr"/>
@@ -21534,10 +21616,14 @@
           <t>Exam details updated successfully.</t>
         </is>
       </c>
-      <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>Exam details updated successfully.</t>
+        </is>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr"/>
@@ -21605,10 +21691,14 @@
           <t>Exam and all attached exam materials are permanently deleted from system.</t>
         </is>
       </c>
-      <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K21" s="28" t="inlineStr">
+        <is>
+          <t>Exam and all attached exam materials are permanently deleted from system.</t>
+        </is>
+      </c>
+      <c r="L21" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M21" s="26" t="inlineStr"/>
@@ -21677,10 +21767,15 @@
 Exam remains intact in course.</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>Dialog closes.
+Exam remains intact in course.</t>
+        </is>
+      </c>
+      <c r="L22" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr"/>
@@ -21746,10 +21841,14 @@
           <t>Archive button is not available for exams (only Delete is supported).</t>
         </is>
       </c>
-      <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K23" s="28" t="inlineStr">
+        <is>
+          <t>Archive button is not available for exams (only Delete is supported).</t>
+        </is>
+      </c>
+      <c r="L23" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M23" s="26" t="inlineStr"/>
@@ -21819,10 +21918,14 @@
           <t>Material link is attached successfully and clickable on UI.</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>Material link is attached successfully and clickable on UI.</t>
+        </is>
+      </c>
+      <c r="L24" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr"/>
@@ -21890,10 +21993,14 @@
           <t>All material links are attached and displayed under session/exam.</t>
         </is>
       </c>
-      <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>All material links are attached and displayed under session/exam.</t>
+        </is>
+      </c>
+      <c r="L25" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M25" s="26" t="inlineStr"/>
@@ -21961,10 +22068,14 @@
           <t>System saves Row 1 successfully and ignores blank Row 2 without error.</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>System saves Row 1 successfully and ignores blank Row 2 without error.</t>
+        </is>
+      </c>
+      <c r="L26" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr"/>
@@ -22033,13 +22144,17 @@
 Validation error appears: "URL is required when Label is specified."</t>
         </is>
       </c>
-      <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M27" s="26" t="inlineStr"/>
+      <c r="K27" s="28" t="inlineStr">
+        <is>
+          <t>The system saves the document link successfully even though the URL field is empty. No validation error message is displayed, and the attached document link does not appear in the document list after saving.</t>
+        </is>
+      </c>
+      <c r="L27" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M27" s="26" t="n"/>
       <c r="N27" s="25" t="inlineStr">
         <is>
           <t>High</t>
@@ -22105,13 +22220,17 @@
 Validation error appears: "Label is required when URL is specified."</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M28" s="21" t="inlineStr"/>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>The system saves the document link successfully even though the Label field is empty. No validation error message is displayed, and the attached document link does not appear in the document list after saving.</t>
+        </is>
+      </c>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="n"/>
       <c r="N28" s="25" t="inlineStr">
         <is>
           <t>High</t>
@@ -22177,10 +22296,15 @@
 Validation error appears: "Material link must be a valid Google Drive URL."</t>
         </is>
       </c>
-      <c r="K29" s="28" t="inlineStr"/>
-      <c r="L29" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>System blocks action.
+Validation error appears: "Material link must be a valid Google Drive URL."</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M29" s="26" t="inlineStr"/>
@@ -22248,10 +22372,14 @@
           <t>CSV file downloads successfully containing Session ID, Session Name, and Material details.</t>
         </is>
       </c>
-      <c r="K30" s="23" t="inlineStr"/>
-      <c r="L30" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>CSV file downloads successfully containing Session ID, Session Name, and Material details.</t>
+        </is>
+      </c>
+      <c r="L30" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr"/>
@@ -22319,10 +22447,14 @@
           <t>Session SES-001 is updated with new name "Updated HTML Basics".</t>
         </is>
       </c>
-      <c r="K31" s="28" t="inlineStr"/>
-      <c r="L31" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K31" s="28" t="inlineStr">
+        <is>
+          <t>Session SES-001 is updated with new name "Updated HTML Basics".</t>
+        </is>
+      </c>
+      <c r="L31" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M31" s="26" t="inlineStr"/>
@@ -22389,10 +22521,14 @@
           <t>New session "New CSS Grid Session" is created with auto-generated Session ID.</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr"/>
-      <c r="L32" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>New session "New CSS Grid Session" is created with auto-generated Session ID.</t>
+        </is>
+      </c>
+      <c r="L32" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr"/>
@@ -22460,13 +22596,19 @@
           <t>New session "Flexbox Guide" is created in system.</t>
         </is>
       </c>
-      <c r="K33" s="28" t="inlineStr"/>
-      <c r="L33" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M33" s="26" t="inlineStr"/>
+      <c r="K33" s="28" t="inlineStr">
+        <is>
+          <t>The system does not create a new session when importing a row with a non-existing Session ID. Instead, the row is skipped and the message "Row 2: session ID 3 not found." is displayed. No changes are made to the existing sessions.</t>
+        </is>
+      </c>
+      <c r="L33" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M33" s="26" t="e">
+        <v>#VALUE!</v>
+      </c>
       <c r="N33" s="29" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -22531,10 +22673,14 @@
           <t>SES-001 is processed, and omitted session SES-002 remains unchanged in system without being deleted.</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr"/>
-      <c r="L34" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>SES-001 is processed, and omitted session SES-002 remains unchanged in system without being deleted.</t>
+        </is>
+      </c>
+      <c r="L34" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr"/>
@@ -22601,10 +22747,14 @@
           <t>Sessions are updated/created, and Materials column is safely ignored per business rule.</t>
         </is>
       </c>
-      <c r="K35" s="28" t="inlineStr"/>
-      <c r="L35" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K35" s="28" t="inlineStr">
+        <is>
+          <t>Sessions are updated/created, and Materials column is safely ignored per business rule.</t>
+        </is>
+      </c>
+      <c r="L35" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M35" s="26" t="inlineStr"/>
@@ -22672,10 +22822,15 @@
 Error message appears: "Invalid file format. Please upload a CSV file."</t>
         </is>
       </c>
-      <c r="K36" s="23" t="inlineStr"/>
-      <c r="L36" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>System blocks import.
+Error message appears: "Invalid file format. Please upload a CSV file."</t>
+        </is>
+      </c>
+      <c r="L36" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M36" s="21" t="inlineStr"/>
@@ -22742,10 +22897,14 @@
           <t>System flags error for row or skips invalid row with warning message: "Session Name is required."</t>
         </is>
       </c>
-      <c r="K37" s="28" t="inlineStr"/>
-      <c r="L37" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K37" s="28" t="inlineStr">
+        <is>
+          <t>System flags error for row or skips invalid row with warning message: "Session Name is required."</t>
+        </is>
+      </c>
+      <c r="L37" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M37" s="26" t="inlineStr"/>
@@ -22812,10 +22971,14 @@
           <t>Staff user can perform all management operations cleanly.</t>
         </is>
       </c>
-      <c r="K38" s="23" t="inlineStr"/>
-      <c r="L38" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>Staff user can perform all management operations cleanly.</t>
+        </is>
+      </c>
+      <c r="L38" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M38" s="21" t="inlineStr"/>
@@ -22883,10 +23046,15 @@
 Student can view and open material links in Read-Only mode.</t>
         </is>
       </c>
-      <c r="K39" s="28" t="inlineStr"/>
-      <c r="L39" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K39" s="28" t="inlineStr">
+        <is>
+          <t>Create, Edit, Archive, Delete, and CSV Import buttons are completely hidden.
+Student can view and open material links in Read-Only mode.</t>
+        </is>
+      </c>
+      <c r="L39" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M39" s="26" t="inlineStr"/>
@@ -22952,10 +23120,14 @@
           <t>Access denied page or login redirect is displayed.</t>
         </is>
       </c>
-      <c r="K40" s="23" t="inlineStr"/>
-      <c r="L40" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>Access denied page or login redirect is displayed.</t>
+        </is>
+      </c>
+      <c r="L40" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M40" s="21" t="inlineStr"/>
@@ -23023,10 +23195,14 @@
           <t>Course and all its child sessions and exams are hidden from active view.</t>
         </is>
       </c>
-      <c r="K41" s="28" t="inlineStr"/>
-      <c r="L41" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K41" s="28" t="inlineStr">
+        <is>
+          <t>Course and all its child sessions and exams are hidden from active view.</t>
+        </is>
+      </c>
+      <c r="L41" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M41" s="26" t="inlineStr"/>
@@ -23094,10 +23270,14 @@
           <t>Course and all child sessions and exams reappear in active view.</t>
         </is>
       </c>
-      <c r="K42" s="23" t="inlineStr"/>
-      <c r="L42" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>Course and all child sessions and exams reappear in active view.</t>
+        </is>
+      </c>
+      <c r="L42" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M42" s="21" t="inlineStr"/>

--- a/Tests/excel/academic_portal_all_test_cases.xlsx
+++ b/Tests/excel/academic_portal_all_test_cases.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Module 01'!$A$1:$O$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Module 02'!$A$1:$O$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Module 03'!$A$1:$O$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Module 04'!$A$1:$O$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Module 05'!$A$1:$O$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Module 04'!$A$1:$O$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Module 05'!$A$1:$O$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Module 06'!$A$1:$P$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Module 07'!$A$1:$O$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Module 08'!$A$1:$O$21</definedName>
@@ -4597,7 +4597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4648,16 +4648,16 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
@@ -4872,16 +4872,16 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="D52" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G52" s="11" t="n">
         <v>0</v>
@@ -5844,13 +5844,13 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E53" s="13" t="n">
         <v>2</v>
       </c>
       <c r="F53" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>0</v>
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="11" t="n">
         <v>0</v>
@@ -5902,16 +5902,16 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="G55" s="13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
@@ -5931,13 +5931,13 @@
         </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="11" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>2</v>
@@ -5969,7 +5969,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
@@ -5989,13 +5989,13 @@
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" s="11" t="n">
         <v>0</v>
@@ -6018,13 +6018,13 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G59" s="13" t="n">
         <v>0</v>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F61" s="13" t="n">
         <v>1</v>
@@ -6096,22 +6096,22 @@
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>M05-F02</t>
+          <t>M05-F03</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Internship Group Archiving &amp; Reactivation</t>
+          <t>Partner Company Management</t>
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" s="11" t="n">
         <v>0</v>
@@ -6125,19 +6125,19 @@
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>M05-F03</t>
+          <t>M05-F04</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Partner Company Management</t>
+          <t>Single Student Internship Assignment</t>
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" s="13" t="n">
         <v>1</v>
@@ -6154,22 +6154,22 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>M05-F04</t>
+          <t>M05-F05</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Single Student Internship Assignment</t>
+          <t>Batch Student Internship Assignment</t>
         </is>
       </c>
       <c r="D64" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="11" t="n">
         <v>0</v>
@@ -6183,19 +6183,19 @@
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>M05-F05</t>
+          <t>M05-F06</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Batch Student Internship Assignment</t>
+          <t>Company Hiding &amp; Deletion Safety</t>
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="13" t="n">
         <v>0</v>
@@ -6212,22 +6212,22 @@
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>M05-F06</t>
+          <t>M05-F07</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Company Hiding &amp; Deletion Safety</t>
+          <t>Feedback Recording by Team</t>
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" s="11" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>M05-F07</t>
+          <t>M05-F08</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Feedback Recording by Team</t>
+          <t>Same for All Feedback</t>
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F67" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="13" t="n">
         <v>0</v>
@@ -6270,19 +6270,19 @@
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>M05-F08</t>
+          <t>M05-F09</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Same for All Feedback</t>
+          <t>Feedback Editing</t>
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="11" t="n">
         <v>0</v>
@@ -6294,24 +6294,24 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>Module 05</t>
+          <t>Module 06</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>M05-F09</t>
+          <t>M06-F01</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Feedback Editing</t>
+          <t>Report Creation</t>
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F69" s="13" t="n">
         <v>0</v>
@@ -6323,27 +6323,27 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>Module 05</t>
+          <t>Module 06</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>M05-F10</t>
+          <t>M06-F02</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Group List Display</t>
+          <t>Draft Saving &amp; Editing</t>
         </is>
       </c>
       <c r="D70" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F70" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="G70" s="11" t="n">
         <v>0</v>
@@ -6357,19 +6357,19 @@
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>M06-F01</t>
+          <t>M06-F03</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Report Creation</t>
+          <t>Automatic Date Calculation</t>
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F71" s="13" t="n">
         <v>0</v>
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>M06-F02</t>
+          <t>M06-F04</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Draft Saving &amp; Editing</t>
+          <t>Dynamic Task Table Management</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
@@ -6415,22 +6415,22 @@
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F05</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Automatic Date Calculation</t>
+          <t>Working Hours Calculation</t>
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>3</v>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="13" t="n">
         <v>0</v>
@@ -6444,22 +6444,22 @@
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>M06-F04</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Dynamic Task Table Management</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="11" t="n">
         <v>0</v>
@@ -6473,22 +6473,22 @@
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>M06-F05</t>
+          <t>M06-F07</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Working Hours Calculation</t>
+          <t>Read-only Submitted Reports</t>
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="13" t="n">
         <v>0</v>
@@ -6502,19 +6502,19 @@
       </c>
       <c r="B76" s="18" t="inlineStr">
         <is>
-          <t>M06-F06</t>
+          <t>M06-F08</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Report Submission</t>
+          <t>Automated Email Notifications</t>
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F76" s="11" t="n">
         <v>1</v>
@@ -6531,19 +6531,19 @@
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>M06-F07</t>
+          <t>M06-F09</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Read-only Submitted Reports</t>
+          <t>Staff Report Viewing</t>
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="13" t="n">
         <v>0</v>
@@ -6555,24 +6555,24 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Module 06</t>
+          <t>Module 07</t>
         </is>
       </c>
       <c r="B78" s="18" t="inlineStr">
         <is>
-          <t>M06-F08</t>
+          <t>M07-F02</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Automated Email Notifications</t>
+          <t>Category Management</t>
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" s="11" t="n">
         <v>1</v>
@@ -6584,27 +6584,27 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>Module 06</t>
+          <t>Module 07</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
         <is>
-          <t>M06-F09</t>
+          <t>M07-F03</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Staff Report Viewing</t>
+          <t>Course Management</t>
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="13" t="n">
         <v>0</v>
@@ -6618,22 +6618,22 @@
       </c>
       <c r="B80" s="18" t="inlineStr">
         <is>
-          <t>M07-F02</t>
+          <t>M07-F04</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Category Management</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="D80" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E80" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E80" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="F80" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" s="11" t="n">
         <v>0</v>
@@ -6647,22 +6647,22 @@
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>M07-F03</t>
+          <t>M07-F05</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Course Management</t>
+          <t>Exam Management</t>
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F81" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" s="13" t="n">
         <v>0</v>
@@ -6676,22 +6676,22 @@
       </c>
       <c r="B82" s="18" t="inlineStr">
         <is>
-          <t>M07-F04</t>
+          <t>M07-F06</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Session Management</t>
+          <t>Material Link Attachment</t>
         </is>
       </c>
       <c r="D82" s="11" t="n">
         <v>6</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" s="11" t="n">
         <v>0</v>
@@ -6705,19 +6705,19 @@
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
-          <t>M07-F05</t>
+          <t>M07-F07</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Exam Management</t>
+          <t>CSV Export &amp; Import</t>
         </is>
       </c>
       <c r="D83" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E83" s="13" t="n">
         <v>6</v>
-      </c>
-      <c r="E83" s="13" t="n">
-        <v>4</v>
       </c>
       <c r="F83" s="13" t="n">
         <v>2</v>
@@ -6734,22 +6734,22 @@
       </c>
       <c r="B84" s="18" t="inlineStr">
         <is>
-          <t>M07-F06</t>
+          <t>M07-F08</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Material Link Attachment</t>
+          <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
       <c r="D84" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="11" t="n">
         <v>0</v>
@@ -6758,27 +6758,27 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>Module 07</t>
+          <t>Module 08</t>
         </is>
       </c>
       <c r="B85" s="19" t="inlineStr">
         <is>
-          <t>M07-F07</t>
+          <t>M08-F01</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>CSV Export &amp; Import</t>
+          <t>Photo Upload</t>
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>6</v>
       </c>
       <c r="F85" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" s="13" t="n">
         <v>0</v>
@@ -6787,24 +6787,24 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Module 07</t>
+          <t>Module 08</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
         <is>
-          <t>M07-F08</t>
+          <t>M08-F02</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Role Permissions &amp; Access Control</t>
+          <t>Photo Deletion</t>
         </is>
       </c>
       <c r="D86" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F86" s="11" t="n">
         <v>0</v>
@@ -6821,19 +6821,19 @@
       </c>
       <c r="B87" s="19" t="inlineStr">
         <is>
-          <t>M08-F01</t>
+          <t>M08-F03</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Photo Upload</t>
+          <t>Default Avatar Display</t>
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F87" s="13" t="n">
         <v>1</v>
@@ -6850,22 +6850,22 @@
       </c>
       <c r="B88" s="18" t="inlineStr">
         <is>
-          <t>M08-F02</t>
+          <t>M08-F04</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Photo Deletion</t>
+          <t>Avatar Display Sizing</t>
         </is>
       </c>
       <c r="D88" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="F88" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>0</v>
@@ -6879,22 +6879,22 @@
       </c>
       <c r="B89" s="19" t="inlineStr">
         <is>
-          <t>M08-F03</t>
+          <t>M08-F05</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Default Avatar Display</t>
+          <t>Google Drive Storage Naming</t>
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" s="13" t="n">
         <v>0</v>
@@ -6908,22 +6908,22 @@
       </c>
       <c r="B90" s="18" t="inlineStr">
         <is>
-          <t>M08-F04</t>
+          <t>M08-F06</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Avatar Display Sizing</t>
+          <t>Drive Integration Error Handling</t>
         </is>
       </c>
       <c r="D90" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>0</v>
@@ -6937,22 +6937,22 @@
       </c>
       <c r="B91" s="19" t="inlineStr">
         <is>
-          <t>M08-F05</t>
+          <t>M08-F07</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Google Drive Storage Naming</t>
+          <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
       <c r="D91" s="13" t="n">
         <v>3</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" s="13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" s="13" t="n">
         <v>0</v>
@@ -6966,51 +6966,51 @@
       </c>
       <c r="B92" s="18" t="inlineStr">
         <is>
-          <t>M08-F06</t>
+          <t>M08-F08</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Drive Integration Error Handling</t>
+          <t>Feature Scope Verification</t>
         </is>
       </c>
       <c r="D92" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>Module 08</t>
+          <t>Module 09</t>
         </is>
       </c>
       <c r="B93" s="19" t="inlineStr">
         <is>
-          <t>M08-F07</t>
+          <t>M09-F01</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Role Permissions &amp; Access Control</t>
+          <t>Role-based Auto-login</t>
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="13" t="n">
         <v>0</v>
@@ -7019,30 +7019,30 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Module 08</t>
+          <t>Module 09</t>
         </is>
       </c>
       <c r="B94" s="18" t="inlineStr">
         <is>
-          <t>M08-F08</t>
+          <t>M09-F02</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Feature Scope Verification</t>
+          <t>Semester Navigation</t>
         </is>
       </c>
       <c r="D94" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="11" t="n">
+      <c r="F94" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F94" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
@@ -7053,22 +7053,22 @@
       </c>
       <c r="B95" s="19" t="inlineStr">
         <is>
-          <t>M09-F01</t>
+          <t>M09-F03</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Role-based Auto-login</t>
+          <t>Subject Categorization</t>
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F95" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="13" t="n">
         <v>0</v>
@@ -7082,22 +7082,22 @@
       </c>
       <c r="B96" s="18" t="inlineStr">
         <is>
-          <t>M09-F02</t>
+          <t>M09-F04</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Semester Navigation</t>
+          <t>Read-only View Enforcement</t>
         </is>
       </c>
       <c r="D96" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>0</v>
@@ -7111,22 +7111,22 @@
       </c>
       <c r="B97" s="19" t="inlineStr">
         <is>
-          <t>M09-F03</t>
+          <t>M09-F05</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Subject Categorization</t>
+          <t>Grade Representation &amp; Placeholders</t>
         </is>
       </c>
       <c r="D97" s="13" t="n">
         <v>1</v>
       </c>
       <c r="E97" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="F97" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="G97" s="13" t="n">
         <v>0</v>
@@ -7140,19 +7140,19 @@
       </c>
       <c r="B98" s="18" t="inlineStr">
         <is>
-          <t>M09-F04</t>
+          <t>M09-F06</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Read-only View Enforcement</t>
+          <t>Grade Color Coding</t>
         </is>
       </c>
       <c r="D98" s="11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F98" s="11" t="n">
         <v>0</v>
@@ -7169,22 +7169,22 @@
       </c>
       <c r="B99" s="19" t="inlineStr">
         <is>
-          <t>M09-F05</t>
+          <t>M09-F07</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Grade Representation &amp; Placeholders</t>
+          <t>Re-study Status Display</t>
         </is>
       </c>
       <c r="D99" s="13" t="n">
         <v>1</v>
       </c>
       <c r="E99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="13" t="n">
         <v>0</v>
-      </c>
-      <c r="F99" s="13" t="n">
-        <v>1</v>
       </c>
       <c r="G99" s="13" t="n">
         <v>0</v>
@@ -7198,19 +7198,19 @@
       </c>
       <c r="B100" s="18" t="inlineStr">
         <is>
-          <t>M09-F06</t>
+          <t>M09-F08</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Grade Color Coding</t>
+          <t>Internship Report Shortcut Visibility</t>
         </is>
       </c>
       <c r="D100" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F100" s="11" t="n">
         <v>0</v>
@@ -7227,19 +7227,19 @@
       </c>
       <c r="B101" s="19" t="inlineStr">
         <is>
-          <t>M09-F07</t>
+          <t>M09-F09</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Re-study Status Display</t>
+          <t>Student Data Isolation</t>
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="13" t="n">
         <v>0</v>
@@ -7256,82 +7256,24 @@
       </c>
       <c r="B102" s="18" t="inlineStr">
         <is>
-          <t>M09-F08</t>
+          <t>M09-F10</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Internship Report Shortcut Visibility</t>
+          <t>Responsive Design</t>
         </is>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="12" t="inlineStr">
-        <is>
-          <t>Module 09</t>
-        </is>
-      </c>
-      <c r="B103" s="19" t="inlineStr">
-        <is>
-          <t>M09-F09</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>Student Data Isolation</t>
-        </is>
-      </c>
-      <c r="D103" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E103" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F103" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="10" t="inlineStr">
-        <is>
-          <t>Module 09</t>
-        </is>
-      </c>
-      <c r="B104" s="18" t="inlineStr">
-        <is>
-          <t>M09-F10</t>
-        </is>
-      </c>
-      <c r="C104" s="10" t="inlineStr">
-        <is>
-          <t>Responsive Design</t>
-        </is>
-      </c>
-      <c r="D104" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12130,9 +12072,9 @@
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="L2" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="21" t="inlineStr"/>
@@ -12202,9 +12144,9 @@
         </is>
       </c>
       <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr"/>
@@ -12274,10 +12216,14 @@
           <t>Saving is blocked. Error message 'Subject Name is required' displays. Name field is highlighted in red.</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>Hệ thống không thực hiện việc tạo môn học nhưng cũng không có thông báo nào cho người dùng.</t>
+        </is>
+      </c>
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
@@ -13666,6 +13612,2634 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Feature ID</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Feature Name</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Objective</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>TestData</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
+          <t>ExpectedResult</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="20" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="O1" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="180" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-001</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>M04-F01</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>Council Feedback Record</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>Record Council Feedback Successful</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>Verify that staff can successfully record a Class Council record with comments from all departments.</t>
+        </is>
+      </c>
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Student ST001 and Semester 1 exist. No council record exists for ST001 in Semester 1.</t>
+        </is>
+      </c>
+      <c r="H2" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; GeneralComment=Strong learning attitude; ITComment=Excellent coding skills; EnglishComment=Fluent communicator; PLTComment=Highly cooperative; EducatorComment=Good behavior</t>
+        </is>
+      </c>
+      <c r="I2" s="23" t="inlineStr">
+        <is>
+          <t>1. Navigate to Class Council Management;
+2. Click Create Council Record;
+3. Select Student ST001 and Semester 'Semester 1';
+4. Enter General Comment 'Strong learning attitude';
+5. Enter IT Comment 'Excellent coding skills';
+6. Enter English Comment 'Fluent communicator';
+7. Enter PLT Comment 'Highly cooperative';
+8. Enter Educator Comment 'Good behavior';
+9. Click Save</t>
+        </is>
+      </c>
+      <c r="J2" s="23" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. A success message appears. The student's record is displayed in the list with all comments.</t>
+        </is>
+      </c>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. A success message appears. The student's record is displayed in the list with all comments.</t>
+        </is>
+      </c>
+      <c r="L2" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M2" s="21" t="inlineStr"/>
+      <c r="N2" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O2" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="165" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-002</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>M04-F01</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Council Feedback Record</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Record Council Feedback with Empty Optional Fields</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>Verify that saving a completely empty council feedback record is allowed without validation errors.</t>
+        </is>
+      </c>
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Student ST002 and Semester 1 exist. No record exists for ST002 in Semester 1.</t>
+        </is>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST002; Semester=Semester 1; AllComments=Empty; Warning=False; WarningReason=Empty</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>1. Navigate to Class Council Management;
+2. Click Create Council Record;
+3. Select Student ST002 and Semester 'Semester 1';
+4. Leave all comment fields empty;
+5. Ensure Warning is unchecked and Warning Reason is blank;
+6. Click Save</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. No validation errors occur. No badges appear on the list for student ST002.</t>
+        </is>
+      </c>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. No validation errors occur. No badges appear on the list for student ST002.</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M3" s="26" t="inlineStr"/>
+      <c r="N3" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O3" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F01, Optional Fields 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-003</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>M04-F02</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Academic Warning Flag</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Set Academic Warning Flag and Warning Reason</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Verify that staff can set an academic warning flag and input a warning reason.</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Student ST001 and Semester 1 exist.</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; Warning=True; WarningReason=Attendance below required level</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>1. Open the council record for ST001 in Semester 1;
+2. Check the 'Academic Warning' checkbox;
+3. Enter Warning Reason: 'Attendance below required level';
+4. Click Save</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. The warning badge (⚠) appears next to the student's name in the list.</t>
+        </is>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. The warning badge (⚠) appears next to the student's name in the list.</t>
+        </is>
+      </c>
+      <c r="L4" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr"/>
+      <c r="N4" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O4" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F02, Academic Warning 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="105" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-004</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>M04-F02</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Academic Warning Flag</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Set Academic Warning Flag with Empty Warning Reason</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>Verify that warning reason is optional and saving warning flag without a reason is allowed.</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in.</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; Warning=True; WarningReason=Empty</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>1. Open the council record for ST001 in Semester 1;
+2. Check the 'Academic Warning' checkbox;
+3. Leave 'Warning Reason' empty;
+4. Click Save</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. No validation errors occur. The warning badge (⚠) is displayed on the student list.</t>
+        </is>
+      </c>
+      <c r="K5" s="28" t="inlineStr">
+        <is>
+          <t>The record is saved successfully. No validation errors occur. The warning badge (⚠) is displayed on the student list.</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr"/>
+      <c r="N5" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O5" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F02, Optional Fields 6.2, Validation Rules 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-005</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>M04-F04</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Auto Draft Saving</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>Verify Automatic Draft Saving in Browser Local Storage</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Verify that the system automatically saves typed comments into local storage in the background.</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Bi-directional sync/save has not been initiated.</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST003; Semester=Semester 1; ITComment=Draft comment for IT department</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>1. Open the council record for ST003 in Semester 1;
+2. Type IT Comment 'Draft comment for IT department';
+3. Do NOT click Save;
+4. Open Developer Tools -&gt; Application -&gt; Local Storage</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>The text 'Draft comment for IT department' is saved automatically to browser Local Storage under a key representing ST003/Semester 1 as typing occurs.</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>The text 'Draft comment for IT department' is saved automatically to browser Local Storage under a key representing ST003/Semester 1 as typing occurs.</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr"/>
+      <c r="N6" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O6" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F04, Automatic Draft Saving 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-006</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>M04-F05</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>Draft Recovery / Discard</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Recover Unsaved Draft after Unexpected Browser Closure</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>Verify that the system detects unsaved local drafts and displays a prompt to restore them.</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>Unsaved draft for ST003 with ITComment='Draft comment for IT department' exists in Local Storage. Sheets database does not have this comment.</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST003; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>1. Close browser and reopen it (simulating crash);
+2. Navigate back to the council record for ST003 in Semester 1;
+3. Verify prompt;
+4. Select 'Continue editing'</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>An 'Unsaved Draft' warning/prompt is shown. Selecting 'Continue editing' restores the draft text 'Draft comment for IT department' to the IT Comment text box.</t>
+        </is>
+      </c>
+      <c r="K7" s="28" t="inlineStr">
+        <is>
+          <t>An 'Unsaved Draft' warning/prompt is shown. Selecting 'Continue editing' restores the draft text 'Draft comment for IT department' to the IT Comment text box.</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr"/>
+      <c r="N7" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O7" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F05, Draft Recovery 6.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-007</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>M04-F05</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Draft Recovery / Discard</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Discard Unsaved Draft to Restore Last Saved Data</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Verify that choosing to discard an unsaved draft removes it and restores the last saved data from database.</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Official database record for ST003 has ITComment='Good student'. Unsaved draft in Local Storage has ITComment='Draft edit'.</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST003; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST003 in Semester 1;
+2. When 'Unsaved Draft' prompt appears, select 'Discard draft';
+3. Check the IT Comment text box</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Local Storage draft is cleared. The IT Comment reverts to the database value 'Good student'. Draft edits are discarded.</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Local Storage draft is cleared. The IT Comment reverts to the database value 'Good student'. Draft edits are discarded.</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr"/>
+      <c r="N8" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O8" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F05, Draft Recovery 6.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="135" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-008</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>M04-F06</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>Batch Feedback Entry</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Batch Feedback Entry by Comment Type</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>Verify that staff can enter the same feedback type for multiple students simultaneously in batch mode.</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Students ST001, ST002, and ST003 exist in Batch PNV26A.</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>Batch=PNV26A; Semester=Semester 1; FeedbackType=IT Comment; Comments='Active performance in programming project' for ST001, ST002, and ST003</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>1. Open Batch Feedback page;
+2. Select Batch PNV26A, Semester 'Semester 1', and Feedback Type 'IT Comment';
+3. In the grid, type 'Active performance in programming project' for ST001, ST002, and ST003;
+4. Click Save All</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
+        <is>
+          <t>All three records are saved successfully. Success message 'Saved 3 students' is shown. Selected students have the new IT comment.</t>
+        </is>
+      </c>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>All three records are saved successfully. Success message 'Saved 3 students' is shown. Selected students have the new IT comment.</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M9" s="26" t="inlineStr"/>
+      <c r="N9" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O9" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F06, Batch Feedback 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-009</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>M04-F06</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Batch Feedback Entry</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Batch Feedback Entry Does Not Overwrite Other Comment Fields</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Verify that entering batch feedback for one field does not erase other existing comment fields for that student.</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>Student ST001 has existing ITComment='Excellent coding' and EnglishComment='Good speaking'.</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>FeedbackType=English Comment; NewEnglishComment='Excellent communication'</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>1. Open Batch Feedback page;
+2. Select Feedback Type 'English Comment';
+3. Input 'Excellent communication' for ST001 and click Save;
+4. Navigate to ST001's council record details</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>English Comment is updated to 'Excellent communication'. The existing IT Comment is preserved as 'Excellent coding' (not cleared).</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>English Comment is updated to 'Excellent communication'. The existing IT Comment is preserved as 'Excellent coding' (not cleared).</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr"/>
+      <c r="N10" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O10" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F06, Batch Feedback 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-010</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>M04-F07</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>Concurrent Edit Conflict Handling</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Three-Way Merge for Non-conflicting Concurrent Edits</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>Verify that concurrent edits on different fields of the same record are merged successfully using 3-way merge.</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>Teacher A and Teacher B are logged in. The database record for ST001 has GeneralComment='Good student', other fields are empty.</t>
+        </is>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>ST001 record in Semester 1; Teacher B saves ITComment='Excellent'; Teacher A saves EnglishComment='Fluent'</t>
+        </is>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>1. Teacher A opens ST001 council edit form;
+2. Teacher B opens ST001 council edit form;
+3. Teacher B updates IT Comment to 'Excellent' and clicks Save first;
+4. Teacher A updates English Comment to 'Fluent' (IT Comment remains empty on their screen) and clicks Save</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>Save succeeds. The final record on Sheets is merged: GeneralComment='Good student', ITComment='Excellent', and EnglishComment='Fluent'. Teacher A receives notification of updates by another teacher.</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="inlineStr">
+        <is>
+          <t>Save succeeds. The final record on Sheets is merged: GeneralComment='Good student', ITComment='Excellent', and EnglishComment='Fluent'. Teacher A receives notification of updates by another teacher.</t>
+        </is>
+      </c>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="inlineStr"/>
+      <c r="N11" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O11" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="135" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-011</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>M04-F07</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Concurrent Edit Conflict Handling</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>Flag Conflict on Concurrent Edits of Same Field</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>Verify that concurrent edits on the same field block the second user from overwriting first user's saved data and flag a conflict.</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>Teacher A and Teacher B are logged in. ST001 has ITComment='Good'.</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>ST001 record in Semester 1; Teacher B saves ITComment='Excellent'; Teacher A saves ITComment='Very Good'</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>1. Teacher A opens ST001 edit form;
+2. Teacher B opens ST001 edit form;
+3. Teacher B changes IT Comment to 'Excellent' and clicks Save;
+4. Teacher A changes IT Comment to 'Very Good' and clicks Save after Teacher B</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>Teacher A's save is blocked or triggers a conflict. An error 'Saved, but these fields were updated by another teacher: IT Comment' is shown. Teacher B's value 'Excellent' is preserved in database.</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>Teacher A's save is blocked or triggers a conflict. An error 'Saved, but these fields were updated by another teacher: IT Comment' is shown. Teacher B's value 'Excellent' is preserved in database.</t>
+        </is>
+      </c>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr"/>
+      <c r="N12" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O12" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-012</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>M04-F08</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>PDF Report Export</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Export Class Council Report to PDF</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>Verify that staff can generate and download a PDF report containing student info, semester, comments, and warnings.</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="inlineStr">
+        <is>
+          <t>Student ST001 has a complete council record in Semester 1.</t>
+        </is>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>1. Open ST001's council record details page;
+2. Click Export PDF;
+3. Open the downloaded PDF file</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>The PDF report downloads successfully. It contains student details, Semester 1, all teacher comments, and warning details formatted correctly.</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="inlineStr">
+        <is>
+          <t>The PDF report downloads successfully. It contains student details, Semester 1, all teacher comments, and warning details formatted correctly.</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M13" s="26" t="inlineStr"/>
+      <c r="N13" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O13" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F08, PDF Export 6.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-013</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>M04-F02</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Academic Warning Flag</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>Badge Display Activation on Content Entry</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Verify that saving comments activates their corresponding badges (G, IT, EN, PLT, ED) on the student list.</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. ST001 has no comments in Semester 1.</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; ITComment='Good'; EducatorComment='Active'</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>1. Create council record for ST001 in Semester 1;
+2. Input IT Comment 'Good' and Educator Comment 'Active' (others left empty);
+3. Click Save;
+4. Go to student list and observe ST001 row</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>Only 'IT' and 'ED' badges are activated/displayed next to ST001's name. Other badges (G, EN, PLT, ⚠) are hidden.</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>Only 'IT' and 'ED' badges are activated/displayed next to ST001's name. Other badges (G, EN, PLT, ⚠) are hidden.</t>
+        </is>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr"/>
+      <c r="N14" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O14" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: Business Rules, Badge Display 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="105" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-014</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>M04-F02</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>Academic Warning Flag</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>Badge Display Deactivation on Content Removal</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>Verify that removing comment content deactivates the corresponding badge on save.</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>Student ST001 has an IT comment and the 'IT' badge is active.</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; ITComment=''</t>
+        </is>
+      </c>
+      <c r="I15" s="28" t="inlineStr">
+        <is>
+          <t>1. Open ST001's Semester 1 council record;
+2. Clear the IT Comment field completely;
+3. Click Save;
+4. Go to student list and observe badges</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="inlineStr">
+        <is>
+          <t>The record is updated. The 'IT' badge disappears from ST001's name on the list since its comment was removed.</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t>The record is updated. The 'IT' badge disappears from ST001's name on the list since its comment was removed.</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M15" s="26" t="inlineStr"/>
+      <c r="N15" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O15" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: Business Rules, Badge Display 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-015</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>M04-SEC</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Access Control &amp; Security</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>Block Unknown Email Domain Access</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Verify that users with unauthorized email domains (non-PNV/non-student) are completely blocked.</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>User is authenticated with email testuser@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>Email=testuser@gmail.com</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>1. Enter application URL;
+2. Sign in via Google OAuth with testuser@gmail.com</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>Login fails or 'Access Denied' message displays. User is blocked from accessing any management features.</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>Login fails or 'Access Denied' message displays. User is blocked from accessing any management features.</t>
+        </is>
+      </c>
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr"/>
+      <c r="N16" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O16" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: General Rules, User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="135" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-016</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>M04-F04</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>Auto Draft Saving</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Verify Draft Storage Device Specificity</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>Verify that local drafts are device-specific and not synchronized to other computers.</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>Staff user logged in on Computer X and Computer Y.</t>
+        </is>
+      </c>
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>Computer X: input IT Comment 'Draft text on Computer X' for ST003.</t>
+        </is>
+      </c>
+      <c r="I17" s="28" t="inlineStr">
+        <is>
+          <t>1. On Computer X, open ST003 council form and type IT comment 'Draft text on Computer X' (wait for auto-save, do NOT click Save);
+2. On Computer Y, log in to same account and open ST003 Semester 1 council form;
+3. Verify if draft warning appears</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
+        <is>
+          <t>No 'Unsaved Draft' warning appears on Computer Y, and the IT comment field is empty (or displays the saved Sheets value). Draft is device-specific.</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>No 'Unsaved Draft' warning appears on Computer Y, and the IT comment field is empty (or displays the saved Sheets value). Draft is device-specific.</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M17" s="26" t="inlineStr"/>
+      <c r="N17" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O17" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F04, Automatic Draft Saving 6.5, Out of Scope 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="135" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-017</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>M04-F03</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Duplicate Record Prevention</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>Prevent Duplicate Council Record Creation</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Verify that the system blocks creating a second Class Council record for a student in the same semester.</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. A Class Council record already exists for ST001 in Semester 1.</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>1. Navigate to Class Council Management;
+2. Click Create Council Record;
+3. Select Student ST001 and Semester 'Semester 1';
+4. Enter General Comment 'Second record test';
+5. Click Save</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: 'A council record already exists for this student in Semester 1.' Duplicate record is blocked.</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: 'A council record already exists for this student in Semester 1.' Duplicate record is blocked.</t>
+        </is>
+      </c>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr"/>
+      <c r="N18" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O18" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F03, Business Rule 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="135" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-018</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>M04-F03</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>Duplicate Record Prevention</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Allow Council Record in Different Semester</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>Verify that the system allows creating a council record for a student in Semester 2 even if a record exists in Semester 1.</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Council record exists for ST001 in Semester 1. No record exists for ST001 in Semester 2.</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 2; GeneralComment=Progressing well in term 2</t>
+        </is>
+      </c>
+      <c r="I19" s="28" t="inlineStr">
+        <is>
+          <t>1. Navigate to Class Council Management;
+2. Click Create Council Record;
+3. Select Student ST001 and Semester 'Semester 2';
+4. Enter General Comment 'Progressing well in term 2';
+5. Click Save</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>The record for Semester 2 is saved successfully. ST001 now has two distinct records for Semester 1 and Semester 2.</t>
+        </is>
+      </c>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>The record for Semester 2 is saved successfully. ST001 now has two distinct records for Semester 1 and Semester 2.</t>
+        </is>
+      </c>
+      <c r="L19" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M19" s="26" t="inlineStr"/>
+      <c r="N19" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O19" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F03, Business Rule 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-019</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>M04-F08</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>PDF Report Export</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>Hide Trend Chart in Semester 1 PDF Export</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>Verify that trend charts are not displayed in PDF exports for Semester 1 records due to lack of historical data.</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Council record for ST001 in Semester 1 exists.</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001 in Semester 1;
+2. Click Export PDF;
+3. Open and inspect the downloaded PDF report</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>PDF report generates successfully. Student details and comments are present. Trend chart section is omitted/not displayed for Semester 1.</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>PDF report generates successfully. Student details and comments are present. Trend chart section is omitted/not displayed for Semester 1.</t>
+        </is>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr"/>
+      <c r="N20" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O20" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F08, Business Rule 6.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="75" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-020</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>M04-F08</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>PDF Report Export</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Display Trend Chart in Semester 2 PDF Export</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>Verify that trend charts are automatically generated and displayed in PDF exports for Semester 2 when historical data exists.</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Council records exist for ST001 in both Semester 1 and Semester 2.</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 2</t>
+        </is>
+      </c>
+      <c r="I21" s="28" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001 in Semester 2;
+2. Click Export PDF;
+3. Open and inspect the downloaded PDF report</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
+        <is>
+          <t>PDF report generates successfully. Evaluation trend chart comparing Semester 1 and Semester 2 is displayed in the report.</t>
+        </is>
+      </c>
+      <c r="K21" s="28" t="inlineStr">
+        <is>
+          <t>PDF report generates successfully. Evaluation trend chart comparing Semester 1 and Semester 2 is displayed in the report.</t>
+        </is>
+      </c>
+      <c r="L21" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M21" s="26" t="inlineStr"/>
+      <c r="N21" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O21" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F08, Business Rule 6.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="135" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-021</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>M04-F02</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Academic Warning Flag</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>Deactivate Academic Warning Flag and Clear Reason</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Verify that unchecking the Academic Warning flag removes the warning badge and clears the warning reason upon saving.</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Student ST001 has an active academic warning with reason 'Attendance below required level'.</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; Warning=False; WarningReason=''</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001 in Semester 1;
+2. Uncheck the 'Academic Warning' checkbox;
+3. Clear the Warning Reason text box;
+4. Click Save;
+5. Observe student list row for ST001</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>Record updates successfully. Warning badge (⚠) is removed from ST001 in the list view. Warning reason is cleared.</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>Record updates successfully. Warning badge (⚠) is removed from ST001 in the list view. Warning reason is cleared.</t>
+        </is>
+      </c>
+      <c r="L22" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr"/>
+      <c r="N22" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O22" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F02, Business Rule 6.3, 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-022</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>M04-F01</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>Council Feedback Record</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>Update Existing Class Council Evaluation Comments</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr">
+        <is>
+          <t>Verify that staff can open an existing council record and update feedback comments from multiple departments.</t>
+        </is>
+      </c>
+      <c r="G23" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Record for ST001 in Semester 1 exists with initial IT Comment 'Good'.</t>
+        </is>
+      </c>
+      <c r="H23" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; ITComment=Outstanding programming progress; EnglishComment=Improved presentation skills</t>
+        </is>
+      </c>
+      <c r="I23" s="28" t="inlineStr">
+        <is>
+          <t>1. Navigate to Class Council Management;
+2. Open edit form for ST001 Semester 1 record;
+3. Update IT Comment to 'Outstanding programming progress';
+4. Update English Comment to 'Improved presentation skills';
+5. Click Save</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="inlineStr">
+        <is>
+          <t>Record updates successfully. New comments are persisted. Badges 'IT' and 'EN' remain active on the student list.</t>
+        </is>
+      </c>
+      <c r="K23" s="28" t="inlineStr">
+        <is>
+          <t>Record updates successfully. New comments are persisted. Badges 'IT' and 'EN' remain active on the student list.</t>
+        </is>
+      </c>
+      <c r="L23" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M23" s="26" t="inlineStr"/>
+      <c r="N23" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O23" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-023</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>M04-F01</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>Council Feedback Record</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>Block Saving Council Record Without Student</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>Verify that the system enforces student selection as a required field when creating a council record.</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in.</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>Student=Unselected; Semester=Semester 1; GeneralComment=Test comment</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>1. Open Create Council Record form;
+2. Leave Student unselected;
+3. Select Semester 'Semester 1';
+4. Enter General Comment 'Test comment';
+5. Click Save</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>Form submission is blocked. Validation error message appears: 'Student is required.' Record is not saved.</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>Form submission is blocked. Validation error message appears: 'Student is required.' Record is not saved.</t>
+        </is>
+      </c>
+      <c r="L24" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr"/>
+      <c r="N24" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O24" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: Validation Rules 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-024</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>M04-F01</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>Council Feedback Record</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>Block Saving Council Record Without Semester</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="inlineStr">
+        <is>
+          <t>Verify that the system enforces semester selection as a required field when creating a council record.</t>
+        </is>
+      </c>
+      <c r="G25" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Student ST001 exists.</t>
+        </is>
+      </c>
+      <c r="H25" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Unselected; GeneralComment=Test comment</t>
+        </is>
+      </c>
+      <c r="I25" s="28" t="inlineStr">
+        <is>
+          <t>1. Open Create Council Record form;
+2. Select Student ST001;
+3. Leave Semester unselected;
+4. Enter General Comment 'Test comment';
+5. Click Save</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="inlineStr">
+        <is>
+          <t>Form submission is blocked. Validation error message appears: 'Semester is required.' Record is not saved.</t>
+        </is>
+      </c>
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>Form submission is blocked. Validation error message appears: 'Semester is required.' Record is not saved.</t>
+        </is>
+      </c>
+      <c r="L25" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M25" s="26" t="inlineStr"/>
+      <c r="N25" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O25" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: Validation Rules 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-025</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>M04-F06</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>Batch Feedback Entry</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>Clear Comment Field Across Multiple Students via Batch Entry</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Students ST001 and ST002 have existing PLT comments.</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>Batch=PNV26A; Semester=Semester 1; FeedbackType=PLT Comment; Comments='' for ST001 and ST002</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>1. Open Batch Feedback page;
+2. Select Batch PNV26A, Semester 'Semester 1', and Feedback Type 'PLT Comment';
+3. Clear comments for ST001 and ST002 in the grid;
+4. Click Save All</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>Batch update succeeds. PLT comments for ST001 and ST002 are removed</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>and 'PLT' badge is deactivated for both students.</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>and 'PLT' badge is deactivated for both students.</t>
+        </is>
+      </c>
+      <c r="L26" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr"/>
+      <c r="N26" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O26" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F06, Business Rule 6.4, 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-026</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>M04-F06</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>Batch Feedback Entry</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>Save Batch Feedback Without Modifying Any Comments</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="inlineStr">
+        <is>
+          <t>Verify system behavior when clicking Save All in batch mode without modifying any student comments.</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Batch PNV26A has 5 active students.</t>
+        </is>
+      </c>
+      <c r="H27" s="28" t="inlineStr">
+        <is>
+          <t>Batch=PNV26A; Semester=Semester 1; FeedbackType=General Comment; No edits made</t>
+        </is>
+      </c>
+      <c r="I27" s="28" t="inlineStr">
+        <is>
+          <t>1. Open Batch Feedback page;
+2. Select Batch PNV26A, Semester 'Semester 1', and Feedback Type 'General Comment';
+3. Do NOT edit any comment cells;
+4. Click Save All</t>
+        </is>
+      </c>
+      <c r="J27" s="28" t="inlineStr">
+        <is>
+          <t>System notifies 'No changes to save' or successfully processes 0 updates without errors. Existing data remains unchanged.</t>
+        </is>
+      </c>
+      <c r="K27" s="28" t="inlineStr">
+        <is>
+          <t>System notifies 'No changes to save' or successfully processes 0 updates without errors. Existing data remains unchanged.</t>
+        </is>
+      </c>
+      <c r="L27" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M27" s="26" t="inlineStr"/>
+      <c r="N27" s="24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O27" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F06</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="105" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-027</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>M04-F07</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>Concurrent Edit Conflict Handling</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>Handle Concurrent Edits When Both Users Enter Identical Text</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>Verify that when two teachers edit the same comment field with identical text</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>Teacher A and Teacher B are logged in. ST001 has GeneralComment='Initial state'.</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>ST001 record in Semester 1; Teacher B saves ITComment='Excellent'; Teacher A saves ITComment='Excellent'</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>1. Teacher A and Teacher B open ST001 edit form concurrently;
+2. Teacher B enters IT Comment 'Excellent' and saves first;
+3. Teacher A enters identical IT Comment 'Excellent' and saves second</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>Save succeeds smoothly without error. The field value remains 'Excellent'.</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>Save succeeds smoothly without error. The field value remains 'Excellent'.</t>
+        </is>
+      </c>
+      <c r="L28" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr"/>
+      <c r="N28" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O28" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="120" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-028</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>M04-F04</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>Auto Draft Saving</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>Clear Local Storage Draft After Successful Official Record Save</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="inlineStr">
+        <is>
+          <t>Verify that saving an official record successfully purges the local storage draft key for that record.</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Typing in progress for ST001</t>
+        </is>
+      </c>
+      <c r="H29" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1; ITComment=Finalized comment</t>
+        </is>
+      </c>
+      <c r="I29" s="28" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001 and type IT Comment 'Finalized comment';
+2. Verify draft exists in Local Storage;
+3. Click Save button;
+4. Open Developer Tools -&gt; Application -&gt; Local Storage</t>
+        </is>
+      </c>
+      <c r="J29" s="28" t="inlineStr">
+        <is>
+          <t>Record is saved to database. Local Storage draft entry for ST001/Semester 1 is completely deleted upon successful save.</t>
+        </is>
+      </c>
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>Record is saved to database. Local Storage draft entry for ST001/Semester 1 is completely deleted upon successful save.</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M29" s="26" t="inlineStr"/>
+      <c r="N29" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O29" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F04, M04-F05, Business Rule 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="105" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-029</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>M04-SEC</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Access Control &amp; Security</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>Block Student Account From Accessing Council Edit Forms</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>Verify that student user accounts cannot access Class Council edit pages or perform save actions.</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>User is authenticated with a valid Student account.</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>UserRole=Student; TargetURL=/class-council/edit/ST001</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>1. Log in with student account;
+2. Attempt to directly navigate to Class Council Edit URL (/class-council/edit/ST001);
+3. Attempt to invoke council record save API</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>Access is denied. Page redirects to dashboard or displays '403 Forbidden / Access Denied'. API request is rejected.</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>Access is denied. Page redirects to dashboard or displays '403 Forbidden / Access Denied'. API request is rejected.</t>
+        </is>
+      </c>
+      <c r="L30" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr"/>
+      <c r="N30" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O30" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: General Rules, User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-030</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>M04-F08</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>PDF Report Export</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>Export Batch Class Council Reports to Combined Package</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
+        <is>
+          <t>Verify that staff can select a batch and export all student council reports for a semester in one click.</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Batch PNV26A has 5 students with saved council records in Semester 1.</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="inlineStr">
+        <is>
+          <t>Batch=PNV26A; Semester=Semester 1; ExportType=Batch PDF</t>
+        </is>
+      </c>
+      <c r="I31" s="28" t="inlineStr">
+        <is>
+          <t>1. Open Class Council Overview;
+2. Filter by Batch PNV26A and Semester 'Semester 1';
+3. Click 'Export Batch Reports (PDF)';
+4. Download and extract/open exported file</t>
+        </is>
+      </c>
+      <c r="J31" s="28" t="inlineStr">
+        <is>
+          <t>Combined archive or PDF containing reports for all 5 students downloads successfully. All reports are complete and accurate.</t>
+        </is>
+      </c>
+      <c r="K31" s="28" t="inlineStr">
+        <is>
+          <t>Combined archive or PDF containing reports for all 5 students downloads successfully. All reports are complete and accurate.</t>
+        </is>
+      </c>
+      <c r="L31" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M31" s="26" t="inlineStr"/>
+      <c r="N31" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O31" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F08, PDF Export 6.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-031</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>M04-F05</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Draft Recovery / Discard</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Discard Draft Changes Manually via Form Action Button</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>Verify that staff can discard active local draft edits at any time using the 'Discard Draft' button on the form.</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Council record for ST001 has saved ITComment='Saved IT Comment'. Local draft has ITComment='Unsaved edit'.</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST001; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST001;
+2. Observe unsaved draft text 'Unsaved edit' in IT Comment field;
+3. Click 'Discard Draft' button in form header;
+4. Confirm discard action in modal prompt</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>Unsaved local draft is discarded. IT Comment field immediately reverts to 'Saved IT Comment'. Local storage key is cleared.</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>Unsaved local draft is discarded. IT Comment field immediately reverts to 'Saved IT Comment'. Local storage key is cleared.</t>
+        </is>
+      </c>
+      <c r="L32" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M32" s="21" t="inlineStr"/>
+      <c r="N32" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O32" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F05, Business Rule 6.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>TC-M04-032</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>M04-F04</t>
+        </is>
+      </c>
+      <c r="D33" s="28" t="inlineStr">
+        <is>
+          <t>Auto Draft Saving</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>Retain Draft Comments in Local Storage During Network Disconnection</t>
+        </is>
+      </c>
+      <c r="F33" s="28" t="inlineStr">
+        <is>
+          <t>Verify that local draft auto-saving continues working seamlessly when user loses internet connection.</t>
+        </is>
+      </c>
+      <c r="G33" s="28" t="inlineStr">
+        <is>
+          <t>Staff user is logged in and editing council record for ST002.</t>
+        </is>
+      </c>
+      <c r="H33" s="28" t="inlineStr">
+        <is>
+          <t>Student=ST002; Semester=Semester 1; ITComment=Offline draft comment</t>
+        </is>
+      </c>
+      <c r="I33" s="28" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST002;
+2. Disconnect internet network connection;
+3. Type IT Comment 'Offline draft comment';
+4. Observe local storage and UI offline indicator</t>
+        </is>
+      </c>
+      <c r="J33" s="28" t="inlineStr">
+        <is>
+          <t>System indicates offline status. Comment text 'Offline draft comment' is safely stored in browser Local Storage without data loss.</t>
+        </is>
+      </c>
+      <c r="K33" s="28" t="inlineStr">
+        <is>
+          <t>System indicates offline status. Comment text 'Offline draft comment' is safely stored in browser Local Storage without data loss.</t>
+        </is>
+      </c>
+      <c r="L33" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M33" s="26" t="inlineStr"/>
+      <c r="N33" s="24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O33" s="28" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F04, Business Rule 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="75" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>TC-M04-033</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Module 04</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>M04-F08</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>PDF Report Export</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>Export PDF Report for Council Record with Partial Comments</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>Verify that exporting a PDF report works properly even if some optional department comments are left blank.</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. ST002 has a saved council record with only IT Comment filled (others empty).</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>Student=ST002; Semester=Semester 1</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>1. Open council record for ST002 in Semester 1;
+2. Click Export PDF;
+3. Download and inspect PDF report</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>PDF report exports successfully without errors. Blank comment sections display 'N/A' or remain neatly empty without breaking PDF layout.</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>PDF report exports successfully without errors. Blank comment sections display 'N/A' or remain neatly empty without breaking PDF layout.</t>
+        </is>
+      </c>
+      <c r="L34" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr"/>
+      <c r="N34" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O34" s="23" t="inlineStr">
+        <is>
+          <t>Related Requirement: M04-F08, Business Rule 6.2, 6.9</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O34"/>
+  <dataValidations count="2">
+    <dataValidation sqref="L2:L134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
+      <formula1>"Passed,Failed,Not Run"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13768,69 +16342,74 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="180" customHeight="1">
+    <row r="2" ht="165" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-001</t>
+          <t>TC-M05-001</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C2" s="22" t="inlineStr">
         <is>
-          <t>M04-F01</t>
+          <t>M05-F01</t>
         </is>
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>Council Feedback Record</t>
+          <t>Internship Group Creation</t>
         </is>
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>Record Council Feedback Successful</t>
+          <t>Create New Internship Group with Valid Information</t>
         </is>
       </c>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Verify that staff can successfully record a Class Council record with comments from all departments.</t>
+          <t>Verify functionality for creating a new internship group when entering all required and valid information.</t>
         </is>
       </c>
       <c r="G2" s="23" t="inlineStr">
         <is>
-          <t>Staff user is logged in. Student ST001 and Semester 1 exist. No council record exists for ST001 in Semester 1.</t>
+          <t>User is logged in as Staff.
+Currently on Internship Management interface.
+Classes "PNV26A" and "PNV26B" exist in system and are not assigned to any internship group in the same academic year.</t>
         </is>
       </c>
       <c r="H2" s="23" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 1; GeneralComment=Strong learning attitude; ITComment=Excellent coding skills; EnglishComment=Fluent communicator; PLTComment=Highly cooperative; EducatorComment=Good behavior</t>
+          <t>GroupName="Internship Group 2026"; AcademicYear="2026"; Classes="PNV26A, PNV26B"; StartDate="2026-06-01"</t>
         </is>
       </c>
       <c r="I2" s="23" t="inlineStr">
         <is>
-          <t>1. Navigate to Class Council Management;
-2. Click Create Council Record;
-3. Select Student ST001 and Semester 'Semester 1';
-4. Enter General Comment 'Strong learning attitude';
-5. Enter IT Comment 'Excellent coding skills';
-6. Enter English Comment 'Fluent communicator';
-7. Enter PLT Comment 'Highly cooperative';
-8. Enter Educator Comment 'Good behavior';
-9. Click Save</t>
+          <t>1. Click Create New Internship Group button;
+2. Enter Group Name as "Internship Group 2026";
+3. Select Academic Year as "2026";
+4. Select classes "PNV26A" and "PNV26B";
+5. Select Start Date as "2026-06-01";
+6. Click Save button.</t>
         </is>
       </c>
       <c r="J2" s="23" t="inlineStr">
         <is>
-          <t>The record is saved successfully. A success message appears. The student's record is displayed in the list with all comments.</t>
-        </is>
-      </c>
-      <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Internship group is created successfully.
+Success notification appears and "Internship Group 2026" is displayed in the active internship group list with 2 assigned classes.</t>
+        </is>
+      </c>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>Internship group is created successfully.
+Success notification appears and "Internship Group 2026" is displayed in the active internship group list with 2 assigned classes.</t>
+        </is>
+      </c>
+      <c r="L2" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="21" t="inlineStr"/>
@@ -13841,70 +16420,79 @@
       </c>
       <c r="O2" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="165" customHeight="1">
+          <t>Related Requirement: M05-F01, Rule 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="120" customHeight="1">
       <c r="A3" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-002</t>
+          <t>TC-M05-002</t>
         </is>
       </c>
       <c r="B3" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>M04-F01</t>
+          <t>M05-F01</t>
         </is>
       </c>
       <c r="D3" s="28" t="inlineStr">
         <is>
-          <t>Council Feedback Record</t>
+          <t>Internship Group Creation</t>
         </is>
       </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
-          <t>Record Council Feedback with Empty Optional Fields</t>
+          <t>Internship Group Creation Fails Due to Empty Group Name</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Verify that saving a completely empty council feedback record is allowed without validation errors.</t>
+          <t>Verify system displays error and prevents creating internship group when group name is blank.</t>
         </is>
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
-          <t>Staff user is logged in. Student ST002 and Semester 1 exist. No record exists for ST002 in Semester 1.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Internship Group interface.
+Class "PNV26A" is not assigned to any internship group in the academic year.</t>
         </is>
       </c>
       <c r="H3" s="28" t="inlineStr">
         <is>
-          <t>Student=ST002; Semester=Semester 1; AllComments=Empty; Warning=False; WarningReason=Empty</t>
+          <t>GroupName=""; AcademicYear="2026"; Classes="PNV26A"; StartDate="2026-06-01"</t>
         </is>
       </c>
       <c r="I3" s="28" t="inlineStr">
         <is>
-          <t>1. Navigate to Class Council Management;
-2. Click Create Council Record;
-3. Select Student ST002 and Semester 'Semester 1';
-4. Leave all comment fields empty;
-5. Ensure Warning is unchecked and Warning Reason is blank;
-6. Click Save</t>
+          <t>1. Leave Group Name blank;
+2. Select Academic Year as "2026";
+3. Select class "PNV26A";
+4. Select Start Date as "2026-06-01";
+5. Click Save button.</t>
         </is>
       </c>
       <c r="J3" s="28" t="inlineStr">
         <is>
-          <t>The record is saved successfully. No validation errors occur. No badges appear on the list for student ST002.</t>
-        </is>
-      </c>
-      <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>System blocks creation.
+Validation error message appears: "Group Name is required."
+Form remains open and no new record is created.</t>
+        </is>
+      </c>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>System blocks creation.
+Validation error message appears: "Group Name is required."
+Form remains open and no new record is created.</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr"/>
@@ -13915,68 +16503,78 @@
       </c>
       <c r="O3" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F01, Optional Fields 6.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+          <t>Related Requirement: M05-F01, Rule 6.1, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="135" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-003</t>
+          <t>TC-M05-003</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>M04-F02</t>
+          <t>M05-F01</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t>Academic Warning Flag</t>
+          <t>Internship Group Creation</t>
         </is>
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>Set Academic Warning Flag and Warning Reason</t>
+          <t>Internship Group Creation Fails Due to Unselected Classes</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t>Verify that staff can set an academic warning flag and input a warning reason.</t>
+          <t>Verify system displays error and prevents creating internship group when no classes are selected.</t>
         </is>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
-          <t>Staff user is logged in. Student ST001 and Semester 1 exist.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Internship Group interface.</t>
         </is>
       </c>
       <c r="H4" s="23" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 1; Warning=True; WarningReason=Attendance below required level</t>
+          <t>GroupName="Internship Group 2026"; AcademicYear="2026"; Classes=None; StartDate="2026-06-01"</t>
         </is>
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>1. Open the council record for ST001 in Semester 1;
-2. Check the 'Academic Warning' checkbox;
-3. Enter Warning Reason: 'Attendance below required level';
-4. Click Save</t>
+          <t>1. Enter Group Name as "Internship Group 2026";
+2. Select Academic Year as "2026";
+3. Do not select any class checkbox;
+4. Select Start Date as "2026-06-01";
+5. Click Save button.</t>
         </is>
       </c>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t>The record is saved successfully. The warning badge (⚠) appears next to the student's name in the list.</t>
-        </is>
-      </c>
-      <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>System blocks creation.
+Validation error message appears: "At least one class must be selected."
+Group is not created.</t>
+        </is>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>System blocks creation.
+Validation error message appears: "At least one class must be selected."
+Group is not created.</t>
+        </is>
+      </c>
+      <c r="L4" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
@@ -13987,68 +16585,78 @@
       </c>
       <c r="O4" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F02, Academic Warning 6.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="105" customHeight="1">
+          <t>Related Requirement: M05-F01, Rule 6.1, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-004</t>
+          <t>TC-M05-004</t>
         </is>
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>M04-F02</t>
+          <t>M05-F01</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>Academic Warning Flag</t>
+          <t>Internship Group Creation</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Set Academic Warning Flag with Empty Warning Reason</t>
+          <t>Internship Group Creation Fails Due to Missing Start Date</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>Verify that warning reason is optional and saving warning flag without a reason is allowed.</t>
+          <t>Verify system displays error and prevents creating internship group when Start Date is empty.</t>
         </is>
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
-          <t>Staff user is logged in.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Internship Group interface.</t>
         </is>
       </c>
       <c r="H5" s="28" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 1; Warning=True; WarningReason=Empty</t>
+          <t>GroupName="Internship Group 2026"; AcademicYear="2026"; Classes="PNV26A"; StartDate=""</t>
         </is>
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>1. Open the council record for ST001 in Semester 1;
-2. Check the 'Academic Warning' checkbox;
-3. Leave 'Warning Reason' empty;
-4. Click Save</t>
+          <t>1. Enter Group Name as "Internship Group 2026";
+2. Select Academic Year as "2026";
+3. Select class "PNV26A";
+4. Leave Start Date blank;
+5. Click Save button.</t>
         </is>
       </c>
       <c r="J5" s="28" t="inlineStr">
         <is>
-          <t>The record is saved successfully. No validation errors occur. The warning badge (⚠) is displayed on the student list.</t>
-        </is>
-      </c>
-      <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>System blocks creation.
+Validation error message appears: "Start Date is required."
+Group is not created.</t>
+        </is>
+      </c>
+      <c r="K5" s="28" t="inlineStr">
+        <is>
+          <t>System blocks creation.
+Validation error message appears: "Start Date is required."
+Group is not created.</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M5" s="26" t="inlineStr"/>
@@ -14059,67 +16667,78 @@
       </c>
       <c r="O5" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F02, Optional Fields 6.2, Validation Rules 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75" customHeight="1">
+          <t>Related Requirement: M05-F01, Rule 6.1, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="135" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-005</t>
+          <t>TC-M05-005</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>M04-F03</t>
+          <t>M05-F01</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>Duplicate Record Prevention</t>
+          <t>Internship Group Creation</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Block Duplicate Council Record for Same Student and Semester</t>
+          <t>Internship Group Creation Fails Due to Missing Academic Year</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>Verify that the system blocks creating a second Class Council record for the same student in the same semester.</t>
+          <t>Verify system displays error and prevents creating internship group when Academic Year is empty.</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Staff user is logged in. A Class Council record already exists for ST001 in Semester 1.</t>
+          <t>User is logged in as Staff.
+Currently on Create New Internship Group interface.</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 1</t>
+          <t>GroupName="Internship Group 2026"; AcademicYear=""; Classes="PNV26A"; StartDate="2026-06-01"</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>1. Open Create Council Record;
-2. Select Student ST001 and Semester 'Semester 1';
-3. Enter any comment and click Save</t>
+          <t>1. Enter Group Name as "Internship Group 2026";
+2. Leave Academic Year dropdown unselected/empty;
+3. Select class "PNV26A";
+4. Select Start Date as "2026-06-01";
+5. Click Save button.</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>The system rejects saving and displays error: 'Duplicate record error'. No duplicate record is created.</t>
-        </is>
-      </c>
-      <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>System blocks creation.
+Validation error message appears: "Academic Year is required."
+Group is not created.</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>System blocks creation.
+Validation error message appears: "Academic Year is required."
+Group is not created.</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr"/>
@@ -14130,140 +16749,151 @@
       </c>
       <c r="O6" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F03, One Record per Student per Semester 6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="120" customHeight="1">
+          <t>Related Requirement: M05-F01, Rule 6.1, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="105" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-006</t>
+          <t>TC-M05-006</t>
         </is>
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>M04-F04</t>
+          <t>M05-F01</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>Auto Draft Saving</t>
+          <t>Internship Group Creation</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>Verify Automatic Draft Saving in Browser Local Storage</t>
+          <t>Create Internship Group Successfully When Assigning Same Class across Different Academic Years</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Verify that the system automatically saves typed comments into local storage in the background.</t>
+          <t>Verify system allows assigning the same class to another internship group if the academic years are different.</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
         <is>
-          <t>Staff user is logged in. Bi-directional sync/save has not been initiated.</t>
+          <t>User is logged in as Staff.
+Class "PNV26A" was assigned to an internship group in academic year 2025.</t>
         </is>
       </c>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>Student=ST003; Semester=Semester 1; ITComment=Draft comment for IT department</t>
+          <t>GroupName="Internship Group 2026"; AcademicYear="2026"; Classes="PNV26A"; StartDate="2026-06-01"</t>
         </is>
       </c>
       <c r="I7" s="28" t="inlineStr">
         <is>
-          <t>1. Open the council record for ST003 in Semester 1;
-2. Type IT Comment 'Draft comment for IT department';
-3. Do NOT click Save;
-4. Open Developer Tools -&gt; Application -&gt; Local Storage</t>
+          <t>1. Create new group with Academic Year "2026";
+2. Select class "PNV26A";
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>The text 'Draft comment for IT department' is saved automatically to browser Local Storage under a key representing ST003/Semester 1 as typing occurs.</t>
-        </is>
-      </c>
-      <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>System allows creation successfully without duplicate class error because academic years differ (2025 vs 2026).</t>
+        </is>
+      </c>
+      <c r="K7" s="28" t="inlineStr">
+        <is>
+          <t>System allows creation successfully without duplicate class error because academic years differ (2025 vs 2026).</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr"/>
-      <c r="N7" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="N7" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O7" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F04, Automatic Draft Saving 6.5</t>
+          <t>Related Requirement: M05-F01, Rule 6.1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="120" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-007</t>
+          <t>TC-M05-007</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>M04-F05</t>
+          <t>M05-F03</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>Draft Recovery / Discard</t>
+          <t>Partner Company Management</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Recover Unsaved Draft after Unexpected Browser Closure</t>
+          <t>Add New Partner Company with Valid Name</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Verify that the system detects unsaved local drafts and displays a prompt to restore them.</t>
+          <t>Verify functionality for adding a new partner company with a valid name.</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>Unsaved draft for ST003 with ITComment='Draft comment for IT department' exists in Local Storage. Sheets database does not have this comment.</t>
+          <t>User is logged in as Staff.
+Currently on Company Management interface.
+Company "ABC Technology" does not exist in system.</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>Student=ST003; Semester=Semester 1</t>
+          <t>CompanyName="ABC Technology"</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>1. Close browser and reopen it (simulating crash);
-2. Navigate back to the council record for ST003 in Semester 1;
-3. Verify prompt;
-4. Select 'Continue editing'</t>
+          <t>1. Click Add Company button;
+2. Enter Company Name as "ABC Technology";
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>An 'Unsaved Draft' warning/prompt is shown. Selecting 'Continue editing' restores the draft text 'Draft comment for IT department' to the IT Comment text box.</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Company is added successfully.
+Success notification appears and "ABC Technology" is displayed in company list with status Active.</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Company is added successfully.
+Success notification appears and "ABC Technology" is displayed in company list with status Active.</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr"/>
@@ -14274,67 +16904,75 @@
       </c>
       <c r="O8" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F05, Draft Recovery 6.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>Related Requirement: M05-F03, Rule 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="105" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-008</t>
+          <t>TC-M05-008</t>
         </is>
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>M04-F05</t>
+          <t>M05-F03</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>Draft Recovery / Discard</t>
+          <t>Partner Company Management</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>Discard Unsaved Draft to Restore Last Saved Data</t>
+          <t>Add Company Fails Due to Empty Company Name</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Verify that choosing to discard an unsaved draft removes it and restores the last saved data from database.</t>
+          <t>Verify system displays error and prevents adding company when company name is empty.</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
         <is>
-          <t>Official database record for ST003 has ITComment='Good student'. Unsaved draft in Local Storage has ITComment='Draft edit'.</t>
+          <t>User is logged in as Staff.
+Currently on Add Company dialog.</t>
         </is>
       </c>
       <c r="H9" s="28" t="inlineStr">
         <is>
-          <t>Student=ST003; Semester=Semester 1</t>
+          <t>CompanyName=""</t>
         </is>
       </c>
       <c r="I9" s="28" t="inlineStr">
         <is>
-          <t>1. Open council record for ST003 in Semester 1;
-2. When 'Unsaved Draft' prompt appears, select 'Discard draft';
-3. Check the IT Comment text box</t>
+          <t>1. Leave Company Name field empty;
+2. Click Save button.</t>
         </is>
       </c>
       <c r="J9" s="28" t="inlineStr">
         <is>
-          <t>Local Storage draft is cleared. The IT Comment reverts to the database value 'Good student'. Draft edits are discarded.</t>
-        </is>
-      </c>
-      <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>System blocks action.
+Validation error message appears: "Company Name is required."
+No new company is saved.</t>
+        </is>
+      </c>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>System blocks action.
+Validation error message appears: "Company Name is required."
+No new company is saved.</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M9" s="26" t="inlineStr"/>
@@ -14345,68 +16983,76 @@
       </c>
       <c r="O9" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F05, Draft Recovery 6.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="135" customHeight="1">
+          <t>Related Requirement: M05-F03, Rule 6.3, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="105" customHeight="1">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-009</t>
+          <t>TC-M05-009</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>M04-F06</t>
+          <t>M05-F03</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Batch Feedback Entry</t>
+          <t>Partner Company Management</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Batch Feedback Entry by Comment Type</t>
+          <t>Add Company Fails Due to Duplicate Name (Case Insensitive)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Verify that staff can enter the same feedback type for multiple students simultaneously in batch mode.</t>
+          <t>Verify system detects duplicate company names regardless of uppercase/lowercase letters.</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Staff user is logged in. Students ST001, ST002, and ST003 exist in Batch PNV26A.</t>
+          <t>User is logged in as Staff.
+Company "ABC Technology" already exists in system.</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>Batch=PNV26A; Semester=Semester 1; FeedbackType=IT Comment; Comments='Active performance in programming project' for ST001, ST002, and ST003</t>
+          <t>CompanyName="abc technology"</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>1. Open Batch Feedback page;
-2. Select Batch PNV26A, Semester 'Semester 1', and Feedback Type 'IT Comment';
-3. In the grid, type 'Active performance in programming project' for ST001, ST002, and ST003;
-4. Click Save All</t>
+          <t>1. Click Add Company button;
+2. Enter Company Name as "abc technology";
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>All three records are saved successfully. Success message 'Saved 3 students' is shown. Selected students have the new IT comment.</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>System blocks action.
+Error message appears: "Company name already exists."
+Duplicate company is not created.</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>System blocks action.
+Error message appears: "Company name already exists."
+Duplicate company is not created.</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr"/>
@@ -14417,140 +17063,155 @@
       </c>
       <c r="O10" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F06, Batch Feedback 6.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="120" customHeight="1">
+          <t>Related Requirement: M05-F03, Rule 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="105" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-010</t>
+          <t>TC-M05-010</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>M04-F06</t>
+          <t>M05-F03</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>Batch Feedback Entry</t>
+          <t>Partner Company Management</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>Batch Feedback Entry Does Not Overwrite Other Comment Fields</t>
+          <t>Add Company Fails Due to Duplicate Name with Leading/Trailing Whitespace</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Verify that entering batch feedback for one field does not erase other existing comment fields for that student.</t>
+          <t>Verify system trims leading and trailing spaces before checking for duplicate company names.</t>
         </is>
       </c>
       <c r="G11" s="28" t="inlineStr">
         <is>
-          <t>Student ST001 has existing ITComment='Excellent coding' and EnglishComment='Good speaking'.</t>
+          <t>User is logged in as Staff.
+Company "ABC Technology" already exists in system.</t>
         </is>
       </c>
       <c r="H11" s="28" t="inlineStr">
         <is>
-          <t>FeedbackType=English Comment; NewEnglishComment='Excellent communication'</t>
+          <t>CompanyName="  ABC Technology  "</t>
         </is>
       </c>
       <c r="I11" s="28" t="inlineStr">
         <is>
-          <t>1. Open Batch Feedback page;
-2. Select Feedback Type 'English Comment';
-3. Input 'Excellent communication' for ST001 and click Save;
-4. Navigate to ST001's council record details</t>
+          <t>1. Click Add Company button;
+2. Enter Company Name as "  ABC Technology  ";
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>English Comment is updated to 'Excellent communication'. The existing IT Comment is preserved as 'Excellent coding' (not cleared).</t>
-        </is>
-      </c>
-      <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>System trims spaces, detects duplicate "ABC Technology", and displays error: "Company name already exists."
+Save is rejected.</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="inlineStr">
+        <is>
+          <t>System trims spaces, detects duplicate "ABC Technology", and displays error: "Company name already exists."
+Save is rejected.</t>
+        </is>
+      </c>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr"/>
-      <c r="N11" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="N11" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O11" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F06, Batch Feedback 6.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="150" customHeight="1">
+          <t>Related Requirement: M05-F03, Rule 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="165" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-011</t>
+          <t>TC-M05-011</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>M04-F07</t>
+          <t>M05-F04</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Concurrent Edit Conflict Handling</t>
+          <t>Single Student Internship Assignment</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Three-Way Merge for Non-conflicting Concurrent Edits</t>
+          <t>Assign Internship to Individual Student</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Verify that concurrent edits on different fields of the same record are merged successfully using 3-way merge.</t>
+          <t>Verify functionality for assigning an internship company to a single student.</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>Teacher A and Teacher B are logged in. The database record for ST001 has GeneralComment='Good student', other fields are empty.</t>
+          <t>User is logged in as Staff.
+Currently on Student List in Internship Group.
+Student "Nguyen Van A" has no assigned company.
+Company "ABC Technology" exists in system.</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
-          <t>ST001 record in Semester 1; Teacher B saves ITComment='Excellent'; Teacher A saves EnglishComment='Fluent'</t>
+          <t>StudentName="Nguyen Van A"; AssignedCompany="ABC Technology"</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>1. Teacher A opens ST001 council edit form;
-2. Teacher B opens ST001 council edit form;
-3. Teacher B updates IT Comment to 'Excellent' and clicks Save first;
-4. Teacher A updates English Comment to 'Fluent' (IT Comment remains empty on their screen) and clicks Save</t>
+          <t>1. Find student "Nguyen Van A" in list;
+2. Click Company assignment dropdown for this student;
+3. Select company "ABC Technology";
+4. Click Save button.</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>Save succeeds. The final record on Sheets is merged: GeneralComment='Good student', ITComment='Excellent', and EnglishComment='Fluent'. Teacher A receives notification of updates by another teacher.</t>
-        </is>
-      </c>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Assignment saved successfully.
+Student "Nguyen Van A" displays company "ABC Technology" in the table list.</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>Assignment saved successfully.
+Student "Nguyen Van A" displays company "ABC Technology" in the table list.</t>
+        </is>
+      </c>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr"/>
@@ -14561,68 +17222,76 @@
       </c>
       <c r="O12" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="135" customHeight="1">
+          <t>Related Requirement: M05-F04, Rule 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="165" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-012</t>
+          <t>TC-M05-012</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>M04-F07</t>
+          <t>M05-F05</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>Concurrent Edit Conflict Handling</t>
+          <t>Batch Student Internship Assignment</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>Flag Conflict on Concurrent Edits of Same Field</t>
+          <t>Batch Assign Internship to Multiple Students</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Verify that concurrent edits on the same field block the second user from overwriting first user's saved data and flag a conflict.</t>
+          <t>Verify functionality for assigning an internship company to multiple selected students simultaneously.</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
         <is>
-          <t>Teacher A and Teacher B are logged in. ST001 has ITComment='Good'.</t>
+          <t>User is logged in as Staff.
+Currently on Student List in Internship Group.
+Students "Nguyen Van A" and "Tran Thi B" have no assigned company.</t>
         </is>
       </c>
       <c r="H13" s="28" t="inlineStr">
         <is>
-          <t>ST001 record in Semester 1; Teacher B saves ITComment='Excellent'; Teacher A saves ITComment='Very Good'</t>
+          <t>SelectedStudents=["Nguyen Van A", "Tran Thi B"]; AssignedCompany="ABC Technology"</t>
         </is>
       </c>
       <c r="I13" s="28" t="inlineStr">
         <is>
-          <t>1. Teacher A opens ST001 edit form;
-2. Teacher B opens ST001 edit form;
-3. Teacher B changes IT Comment to 'Excellent' and clicks Save;
-4. Teacher A changes IT Comment to 'Very Good' and clicks Save after Teacher B</t>
+          <t>1. Check selection boxes for "Nguyen Van A" and "Tran Thi B";
+2. Click Batch Assign Company button;
+3. Select company "ABC Technology" in modal dialog;
+4. Click Apply and Save.</t>
         </is>
       </c>
       <c r="J13" s="28" t="inlineStr">
         <is>
-          <t>Teacher A's save is blocked or triggers a conflict. An error 'Saved, but these fields were updated by another teacher: IT Comment' is shown. Teacher B's value 'Excellent' is preserved in database.</t>
-        </is>
-      </c>
-      <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Batch assignment saved successfully.
+Both students "Nguyen Van A" and "Tran Thi B" display company "ABC Technology" in the list.</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="inlineStr">
+        <is>
+          <t>Batch assignment saved successfully.
+Both students "Nguyen Van A" and "Tran Thi B" display company "ABC Technology" in the list.</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M13" s="26" t="inlineStr"/>
@@ -14633,67 +17302,74 @@
       </c>
       <c r="O13" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F07, Concurrent Editing 6.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="75" customHeight="1">
+          <t>Related Requirement: M05-F05, Rule 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-013</t>
+          <t>TC-M05-013</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>M04-F08</t>
+          <t>M05-F04</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>PDF Report Export</t>
+          <t>Single Student Internship Assignment</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>Export Class Council Report to PDF</t>
+          <t>Change Student Assigned Company</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Verify that staff can generate and download a PDF report containing student info, semester, comments, and warnings.</t>
+          <t>Verify functionality for updating the assigned internship company for a student.</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Student ST001 has a complete council record in Semester 1.</t>
+          <t>User is logged in as Staff.
+Student "Nguyen Van A" is currently assigned to "ABC Technology".</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 1</t>
+          <t>StudentName="Nguyen Van A"; NewCompany="XYZ Global"</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>1. Open ST001's council record details page;
-2. Click Export PDF;
-3. Open the downloaded PDF file</t>
+          <t>1. Locate student "Nguyen Van A";
+2. Change company dropdown selection from "ABC Technology" to "XYZ Global";
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>The PDF report downloads successfully. It contains student details, Semester 1, all teacher comments, and warning details formatted correctly.</t>
-        </is>
-      </c>
-      <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Assignment updated successfully.
+Student "Nguyen Van A" displays new company "XYZ Global".</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>Assignment updated successfully.
+Student "Nguyen Van A" displays new company "XYZ Global".</t>
+        </is>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr"/>
@@ -14704,66 +17380,74 @@
       </c>
       <c r="O14" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F08, PDF Export 6.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>Related Requirement: M05-F04, Rule 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="105" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-014</t>
+          <t>TC-M05-014</t>
         </is>
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>M04-F01</t>
+          <t>M05-F04</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
         <is>
-          <t>Council Feedback Record</t>
+          <t>Single Student Internship Assignment</t>
         </is>
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Trend Chart Hidden for Semester 1</t>
+          <t>Unassign Company from Student by Selecting No Company</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Verify that the trend chart is hidden on the report when viewing/exporting Semester 1 results.</t>
+          <t>Verify functionality for removing an assigned company from a student by selecting "No Company".</t>
         </is>
       </c>
       <c r="G15" s="28" t="inlineStr">
         <is>
-          <t>Student ST001 has a council record in Semester 1.</t>
+          <t>User is logged in as Staff.
+Student "Nguyen Van A" is currently assigned to "ABC Technology".</t>
         </is>
       </c>
       <c r="H15" s="28" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 1</t>
+          <t>StudentName="Nguyen Van A"; AssignedCompany="No Company"</t>
         </is>
       </c>
       <c r="I15" s="28" t="inlineStr">
         <is>
-          <t>1. Open or export PDF report for ST001 in Semester 1;
-2. Check the Trend Chart section</t>
+          <t>1. Locate student "Nguyen Van A";
+2. Select "No Company" (or empty option) in company dropdown;
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J15" s="28" t="inlineStr">
         <is>
-          <t>No trend chart is displayed on the UI or PDF report for Semester 1 (since no prior semester history exists).</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Company assignment cleared successfully.
+Student "Nguyen Van A" displays "Unassigned" or "No Company" in student list.</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t>Company assignment cleared successfully.
+Student "Nguyen Van A" displays "Unassigned" or "No Company" in student list.</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M15" s="26" t="inlineStr"/>
@@ -14774,282 +17458,311 @@
       </c>
       <c r="O15" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: Business Rules, Trend Chart 6.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>Related Requirement: M05-F04, Rule 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-015</t>
+          <t>TC-M05-015</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>M04-F01</t>
+          <t>M05-F06</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Council Feedback Record</t>
+          <t>Company Hiding &amp; Deletion Safety</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>Trend Chart Displayed for Semester 2 or Later</t>
+          <t>Hide Company and Verify Exclusion from New Assignment Options</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Verify that the trend chart is shown when viewing/exporting results for Semester 2 or later.</t>
+          <t>Verify system hides company from assignment dropdowns when company status is set to Hidden/Inactive.</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Student ST001 has council records and grade history in both Semester 1 and Semester 2.</t>
+          <t>User is logged in as Staff.
+Company "Defunct Corp" exists in system.</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 2</t>
+          <t>CompanyName="Defunct Corp"</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>1. Open or export PDF report for ST001 in Semester 2;
-2. Check the Trend Chart section</t>
+          <t>1. Go to Company Management;
+2. Change status of "Defunct Corp" to Hidden/Inactive;
+3. Go to Student List assignment dropdown.</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>The trend chart is displayed successfully in the UI and PDF, depicting ST001's performance trend from Semester 1 to Semester 2.</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Company "Defunct Corp" no longer appears in dropdown list for new student assignments.</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>Company "Defunct Corp" no longer appears in dropdown list for new student assignments.</t>
+        </is>
+      </c>
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr"/>
-      <c r="N16" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="N16" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="O16" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: Business Rules, Trend Chart 6.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="120" customHeight="1">
+          <t>Related Requirement: M05-F06, Rule 6.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-016</t>
+          <t>TC-M05-016</t>
         </is>
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>M04-F02</t>
+          <t>M05-F06</t>
         </is>
       </c>
       <c r="D17" s="28" t="inlineStr">
         <is>
-          <t>Academic Warning Flag</t>
+          <t>Company Hiding &amp; Deletion Safety</t>
         </is>
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Badge Display Activation on Content Entry</t>
+          <t>Ensure Existing Student Assignment Remains Unaffected When Company Is Hidden</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>Verify that saving comments activates their corresponding badges (G, IT, EN, PLT, ED) on the student list.</t>
+          <t>Verify hiding a company does not remove or distort historical/existing student assignments associated with that company.</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
-          <t>Staff user is logged in. ST001 has no comments in Semester 1.</t>
+          <t>User is logged in as Staff.
+Student "Tran Thi B" is assigned to company "ABC Technology".</t>
         </is>
       </c>
       <c r="H17" s="28" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 1; ITComment='Good'; EducatorComment='Active'</t>
+          <t>CompanyName="ABC Technology"; StudentName="Tran Thi B"</t>
         </is>
       </c>
       <c r="I17" s="28" t="inlineStr">
         <is>
-          <t>1. Create council record for ST001 in Semester 1;
-2. Input IT Comment 'Good' and Educator Comment 'Active' (others left empty);
-3. Click Save;
-4. Go to student list and observe ST001 row</t>
+          <t>1. Change status of company "ABC Technology" to Hidden in Company Management;
+2. View Student List in Internship Group.</t>
         </is>
       </c>
       <c r="J17" s="28" t="inlineStr">
         <is>
-          <t>Only 'IT' and 'ED' badges are activated/displayed next to ST001's name. Other badges (G, EN, PLT, ⚠) are hidden.</t>
-        </is>
-      </c>
-      <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Assignment of student "Tran Thi B" still displays "ABC Technology" normally in student list.
+No error notification appears and existing assignment is preserved.</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>Assignment of student "Tran Thi B" still displays "ABC Technology" normally in student list.
+No error notification appears and existing assignment is preserved.</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M17" s="26" t="inlineStr"/>
-      <c r="N17" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="N17" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="O17" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: Business Rules, Badge Display 6.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="105" customHeight="1">
+          <t>Related Requirement: M05-F06, Rule 6.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="180" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-017</t>
+          <t>TC-M05-017</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>M04-F02</t>
+          <t>M05-F07</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Academic Warning Flag</t>
+          <t>Feedback Recording by Team</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>Badge Display Deactivation on Content Removal</t>
+          <t>Record Internship Feedback Successfully for Student by Training Team</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Verify that removing comment content deactivates the corresponding badge on save.</t>
+          <t>Verify functionality for recording internship feedback for a student by Training team.</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>Student ST001 has an IT comment and the 'IT' badge is active.</t>
+          <t>User is logged in as Staff.
+Currently on Student List in Internship Group.
+Student "Nguyen Van A" has assigned internship.</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Semester 1; ITComment=''</t>
+          <t>StudentName="Nguyen Van A"; FeedbackTeam="Training"; FeedbackDate="2026-08-15"; FeedbackNotes="Good progress, proactive in assigned tasks."</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>1. Open ST001's Semester 1 council record;
-2. Clear the IT Comment field completely;
-3. Click Save;
-4. Go to student list and observe badges</t>
+          <t>1. Locate student "Nguyen Van A" in list;
+2. Click Add Feedback button for this student;
+3. Select Feedback Team as "Training";
+4. Enter Feedback Date as "2026-08-15";
+5. Enter Feedback Notes as "Good progress, proactive in assigned tasks.";
+6. Click Save Feedback button.</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>The record is updated. The 'IT' badge disappears from ST001's name on the list since its comment was removed.</t>
-        </is>
-      </c>
-      <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Feedback saved successfully.
+New feedback entry appears under student name with Team "Training", date, and entered notes.</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>Feedback saved successfully.
+New feedback entry appears under student name with Team "Training", date, and entered notes.</t>
+        </is>
+      </c>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr"/>
-      <c r="N18" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="N18" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="O18" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: Business Rules, Badge Display 6.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="105" customHeight="1">
+          <t>Related Requirement: M05-F07, Rule 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="165" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-018</t>
+          <t>TC-M05-018</t>
         </is>
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
         <is>
-          <t>M04-F01</t>
+          <t>M05-F07</t>
         </is>
       </c>
       <c r="D19" s="28" t="inlineStr">
         <is>
-          <t>Council Feedback Record</t>
+          <t>Feedback Recording by Team</t>
         </is>
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>Record Saving Fails with Missing Student Selection</t>
+          <t>Record Internship Feedback Successfully for Student by ERO Team</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Verify that the system blocks saving if the student selection is missing.</t>
+          <t>Verify functionality for recording internship feedback for a student by ERO team.</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
         <is>
-          <t>Staff user is logged in.</t>
+          <t>User is logged in as Staff.
+Currently on Student List in Internship Group.
+Student "Nguyen Van A" has assigned internship.</t>
         </is>
       </c>
       <c r="H19" s="28" t="inlineStr">
         <is>
-          <t>Student=Empty; Semester=Semester 1; GeneralComment=Good</t>
+          <t>StudentName="Nguyen Van A"; FeedbackTeam="ERO"; FeedbackNotes="Strong technical skills and professional attitude."</t>
         </is>
       </c>
       <c r="I19" s="28" t="inlineStr">
         <is>
-          <t>1. Navigate to Create Council Record;
-2. Leave Student selection empty;
-3. Select Semester 'Semester 1';
-4. Enter General Comment 'Good' and click Save</t>
+          <t>1. Locate student "Nguyen Van A" in list;
+2. Select Feedback Team as "ERO";
+3. Enter Feedback Notes as "Strong technical skills and professional attitude.";
+4. Click Save Feedback button.</t>
         </is>
       </c>
       <c r="J19" s="28" t="inlineStr">
         <is>
-          <t>Saving is blocked. Validation error message requires student selection. The student field is highlighted in red.</t>
-        </is>
-      </c>
-      <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Feedback saved successfully.
+New feedback entry appears under student name with Team "ERO", and entered notes.</t>
+        </is>
+      </c>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>Feedback saved successfully.
+New feedback entry appears under student name with Team "ERO", and entered notes.</t>
+        </is>
+      </c>
+      <c r="L19" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr"/>
@@ -15060,68 +17773,77 @@
       </c>
       <c r="O19" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: Validation Rules 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="105" customHeight="1">
+          <t>Related Requirement: M05-F07, Rule 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="180" customHeight="1">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-019</t>
+          <t>TC-M05-019</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>M04-F01</t>
+          <t>M05-F07</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Council Feedback Record</t>
+          <t>Feedback Recording by Team</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Record Saving Fails with Missing Semester Selection</t>
+          <t>Record Internship Feedback Successfully for Student by Educators Team</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Verify that the system blocks saving if the semester selection is missing.</t>
+          <t>Verify functionality for recording internship feedback for a student by Educators team.</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Staff user is logged in.</t>
+          <t>User is logged in as Staff.
+Currently on Student List in Internship Group.
+Student "Nguyen Van A" has assigned internship.</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>Student=ST001; Semester=Empty; GeneralComment=Good</t>
+          <t>StudentName="Nguyen Van A"; FeedbackTeam="Educators";  FeedbackNotes="Actively contributes constructive ideas to group."</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>1. Navigate to Create Council Record;
-2. Select Student ST001;
-3. Leave Semester selection empty;
-4. Enter General Comment 'Good' and click Save</t>
+          <t>1. Locate student "Nguyen Van A" in list;
+2. Click Add Feedback button for this student;
+3. Select Feedback Team as "Educators";
+4. Enter Feedback Notes as "Actively contributes constructive ideas to group.";
+5. Click Save Feedback button.</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>Saving is blocked. Validation error message requires semester selection. The semester field is highlighted in red.</t>
-        </is>
-      </c>
-      <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Feedback saved successfully.
+New feedback entry appears under student name with Team "Educators", and entered notes.</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>Feedback saved successfully.
+New feedback entry appears under student name with Team "Educators", and entered notes.</t>
+        </is>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr"/>
@@ -15132,137 +17854,155 @@
       </c>
       <c r="O20" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: Validation Rules 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="75" customHeight="1">
+          <t>Related Requirement: M05-F07, Rule 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="135" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-020</t>
+          <t>TC-M05-020</t>
         </is>
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>M04-SEC</t>
+          <t>M05-F07</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
         <is>
-          <t>Access Control &amp; Security</t>
+          <t>Feedback Recording by Team</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Block Student Access to Class Council Management</t>
+          <t>Ignore Blank Feedback Entries Without Saving</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>Verify that a user logged in with a Student email domain cannot access Class Council Management.</t>
+          <t>Verify system ignores and does not save feedback entries when feedback notes field is empty.</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>User logged in with student email student01@student.passerellesnumeriques.org.</t>
+          <t>User is logged in as Staff.
+Currently on Add Feedback dialog for student.</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
         <is>
-          <t>Email=student01@student.passerellesnumeriques.org</t>
+          <t>FeedbackTeam="ERO"; FeedbackNotes=""</t>
         </is>
       </c>
       <c r="I21" s="28" t="inlineStr">
         <is>
-          <t>1. Log in with student account;
-2. Attempt direct URL navigation to Class Council Management page;
-3. Observe UI</t>
+          <t>1. Open Add Feedback dialog;
+2. Select Team as "ERO";
+3. Leave Feedback Notes empty;
+4. Click Save button.</t>
         </is>
       </c>
       <c r="J21" s="28" t="inlineStr">
         <is>
-          <t>Access is denied. An 'Access Denied' message is shown, or user is redirected to student home page. Management menu is hidden.</t>
-        </is>
-      </c>
-      <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>System ignores blank feedback entry without saving new database record.
+No error appears and no empty feedback row is displayed on UI.</t>
+        </is>
+      </c>
+      <c r="K21" s="28" t="inlineStr">
+        <is>
+          <t>System ignores blank feedback entry without saving new database record.
+No error appears and no empty feedback row is displayed on UI.</t>
+        </is>
+      </c>
+      <c r="L21" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M21" s="26" t="inlineStr"/>
-      <c r="N21" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="N21" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O21" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: General Rules, User Roles</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t>Related Requirement: Rule 6.8, Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="180" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-021</t>
+          <t>TC-M05-021</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>M04-SEC</t>
+          <t>M05-F08</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>Access Control &amp; Security</t>
+          <t>Same for All Feedback</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>Block Unknown Email Domain Access</t>
+          <t>Record Batch Feedback for Multiple Students Simultaneously (Same for All)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>Verify that users with unauthorized email domains (non-PNV/non-student) are completely blocked.</t>
+          <t>Verify batch feedback feature applies identical feedback content to multiple selected students.</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>User is authenticated with email testuser@gmail.com.</t>
+          <t>User is logged in as Staff.
+Currently on Student List in Internship Group.
+At least 2 students selected (e.g., Nguyen Van A, Tran Thi B).</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>Email=testuser@gmail.com</t>
+          <t>SelectedStudents=["Nguyen Van A", "Tran Thi B"]; FeedbackTeam="Educators"; FeedbackNotes="Excellent communication skills."</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>1. Enter application URL;
-2. Sign in via Google OAuth with testuser@gmail.com</t>
+          <t>1. Select checkboxes for students "Nguyen Van A" and "Tran Thi B";
+2. Click Batch Feedback (Same for All) button;
+3. Select Team as "Educators", enter Notes as "Excellent communication skills.";
+4. Click Apply and Save button.</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Login fails or 'Access Denied' message displays. User is blocked from accessing any management features.</t>
-        </is>
-      </c>
-      <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Feedback saved successfully for both students.
+Both "Nguyen Van A" and "Tran Thi B" display Educators feedback.</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>Feedback saved successfully for both students.
+Both "Nguyen Van A" and "Tran Thi B" display Educators feedback.</t>
+        </is>
+      </c>
+      <c r="L22" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr"/>
@@ -15273,150 +18013,164 @@
       </c>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: General Rules, User Roles</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="135" customHeight="1">
+          <t>Related Requirement: M05-F08, Rule 6.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="180" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>TC-M04-022</t>
+          <t>TC-M05-022</t>
         </is>
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>M04-F04</t>
+          <t>M05-F09</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
         <is>
-          <t>Auto Draft Saving</t>
+          <t>Feedback Editing</t>
         </is>
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>Verify Draft Storage Device Specificity</t>
+          <t>Edit Saved Internship Feedback Content</t>
         </is>
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>Verify that local drafts are device-specific and not synchronized to other computers.</t>
+          <t>Verify functionality for editing and saving existing feedback content.</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
         <is>
-          <t>Staff user logged in on Computer X and Computer Y.</t>
+          <t>User is logged in as Staff.
+Student "Nguyen Van A" has feedback: Team = "Training", content = "Good progress", date = "2026-08-15".</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
         <is>
-          <t>Computer X: input IT Comment 'Draft text on Computer X' for ST003.</t>
+          <t>StudentName="Nguyen Van A"; NewFeedbackNotes="Outstanding progress and excellent teamwork."</t>
         </is>
       </c>
       <c r="I23" s="28" t="inlineStr">
         <is>
-          <t>1. On Computer X, open ST003 council form and type IT comment 'Draft text on Computer X' (wait for auto-save, do NOT click Save);
-2. On Computer Y, log in to same account and open ST003 Semester 1 council form;
-3. Verify if draft warning appears</t>
+          <t>1. Locate student "Nguyen Van A" and expand feedback list;
+2. Select feedback entry "Good progress" and click Edit button;
+3. Update feedback notes to "Outstanding progress and excellent teamwork.";
+4. Click Save button.</t>
         </is>
       </c>
       <c r="J23" s="28" t="inlineStr">
         <is>
-          <t>No 'Unsaved Draft' warning appears on Computer Y, and the IT comment field is empty (or displays the saved Sheets value). Draft is device-specific.</t>
-        </is>
-      </c>
-      <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Feedback updated successfully.
+New content overwrites previous notes and displays correctly on UI: "Outstanding progress and excellent teamwork.".</t>
+        </is>
+      </c>
+      <c r="K23" s="28" t="inlineStr">
+        <is>
+          <t>Feedback updated successfully.
+New content overwrites previous notes and displays correctly on UI: "Outstanding progress and excellent teamwork.".</t>
+        </is>
+      </c>
+      <c r="L23" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M23" s="26" t="inlineStr"/>
-      <c r="N23" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="N23" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="O23" s="28" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F04, Automatic Draft Saving 6.5, Out of Scope 12</t>
+          <t>Related Requirement: M05-F09, Rule 6.10</t>
         </is>
       </c>
     </row>
     <row r="24" ht="105" customHeight="1">
       <c r="A24" s="21" t="inlineStr">
         <is>
-          <t>TC-M04-023</t>
+          <t>TC-M05-023</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Module 04</t>
+          <t>Module 05 - Internship Management</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>M04-F06</t>
+          <t>M05-F09</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>Batch Feedback Entry</t>
+          <t>Feedback Editing</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>Batch Feedback Entry with Empty Student List</t>
+          <t>Edit Saved Internship Feedback Team and Date</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Verify that batch feedback entry behaves gracefully when the selected batch has no active students.</t>
+          <t>Verify functionality for editing and saving existing feedback team and date.</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>Batch PNV26B is active but has no active students.</t>
+          <t>User is logged in as Staff.
+Student "Nguyen Van A" has feedback: Team = "Training", content = "Good progress", date = "2026-08-15".</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>Batch=PNV26B; Semester=Semester 1; FeedbackType=IT Comment</t>
+          <t>StudentName="Nguyen Van A"; NewFeedbackTeam="ERO";</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>1. Open Batch Feedback page;
-2. Select Batch PNV26B, Semester 'Semester 1', and Feedback Type 'IT Comment';
-3. Verify student list;
-4. Click Save All</t>
+          <t>1. Locate student "Nguyen Van A" and expand feedback list;
+2. Change Feedback Team to "ERO";
+3. Click Save button.</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>The student grid is empty or shows 'No students in this batch'. Clicking Save All shows 'Saved 0 students' successfully with no crashes or errors.</t>
-        </is>
-      </c>
-      <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+          <t>Feedback updated successfully.
+Feedback details update on UI to display new Team "ERO".</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>Feedback updated successfully.
+Feedback details update on UI to display new Team "ERO".</t>
+        </is>
+      </c>
+      <c r="L24" s="24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr"/>
-      <c r="N24" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="N24" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>Related Requirement: M04-F06</t>
+          <t>Related Requirement: M05-F09, Rule 6.10</t>
         </is>
       </c>
     </row>
@@ -15427,2140 +18181,6 @@
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
-      <formula1>"High,Medium,Low"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="20" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C1" s="20" t="inlineStr">
-        <is>
-          <t>Feature ID</t>
-        </is>
-      </c>
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t>Feature Name</t>
-        </is>
-      </c>
-      <c r="E1" s="20" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="F1" s="20" t="inlineStr">
-        <is>
-          <t>Objective</t>
-        </is>
-      </c>
-      <c r="G1" s="20" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="H1" s="20" t="inlineStr">
-        <is>
-          <t>TestData</t>
-        </is>
-      </c>
-      <c r="I1" s="20" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="J1" s="20" t="inlineStr">
-        <is>
-          <t>ExpectedResult</t>
-        </is>
-      </c>
-      <c r="K1" s="20" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="L1" s="20" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="M1" s="20" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="N1" s="20" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="O1" s="20" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="165" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-001</t>
-        </is>
-      </c>
-      <c r="B2" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C2" s="22" t="inlineStr">
-        <is>
-          <t>M05-F01</t>
-        </is>
-      </c>
-      <c r="D2" s="23" t="inlineStr">
-        <is>
-          <t>Internship Group Creation</t>
-        </is>
-      </c>
-      <c r="E2" s="23" t="inlineStr">
-        <is>
-          <t>Create New Internship Group with Valid Information</t>
-        </is>
-      </c>
-      <c r="F2" s="23" t="inlineStr">
-        <is>
-          <t>Verify functionality for creating a new internship group when entering all required and valid information.</t>
-        </is>
-      </c>
-      <c r="G2" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Internship Management interface.
-Classes "PNV26A" and "PNV26B" exist in system and are not assigned to any internship group in the same academic year.</t>
-        </is>
-      </c>
-      <c r="H2" s="23" t="inlineStr">
-        <is>
-          <t>GroupName="Internship Group 2026"; AcademicYear="2026"; Classes="PNV26A, PNV26B"; StartDate="2026-06-01"</t>
-        </is>
-      </c>
-      <c r="I2" s="23" t="inlineStr">
-        <is>
-          <t>1. Click Create New Internship Group button;
-2. Enter Group Name as "Internship Group 2026";
-3. Select Academic Year as "2026";
-4. Select classes "PNV26A" and "PNV26B";
-5. Select Start Date as "2026-06-01";
-6. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J2" s="23" t="inlineStr">
-        <is>
-          <t>Internship group is created successfully.
-Success notification appears and "Internship Group 2026" is displayed in the active internship group list with 2 assigned classes.</t>
-        </is>
-      </c>
-      <c r="K2" s="23" t="inlineStr"/>
-      <c r="L2" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M2" s="21" t="inlineStr"/>
-      <c r="N2" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O2" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F01, Rule 6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="120" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-002</t>
-        </is>
-      </c>
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>M05-F01</t>
-        </is>
-      </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t>Internship Group Creation</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="inlineStr">
-        <is>
-          <t>Internship Group Creation Fails Due to Empty Group Name</t>
-        </is>
-      </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>Verify system displays error and prevents creating internship group when group name is blank.</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Create New Internship Group interface.
-Class "PNV26A" is not assigned to any internship group in the academic year.</t>
-        </is>
-      </c>
-      <c r="H3" s="28" t="inlineStr">
-        <is>
-          <t>GroupName=""; AcademicYear="2026"; Classes="PNV26A"; StartDate="2026-06-01"</t>
-        </is>
-      </c>
-      <c r="I3" s="28" t="inlineStr">
-        <is>
-          <t>1. Leave Group Name blank;
-2. Select Academic Year as "2026";
-3. Select class "PNV26A";
-4. Select Start Date as "2026-06-01";
-5. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J3" s="28" t="inlineStr">
-        <is>
-          <t>System blocks creation.
-Validation error message appears: "Group Name is required."
-Form remains open and no new record is created.</t>
-        </is>
-      </c>
-      <c r="K3" s="28" t="inlineStr"/>
-      <c r="L3" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M3" s="26" t="inlineStr"/>
-      <c r="N3" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O3" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F01, Rule 6.1, Validation Rules (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="135" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-003</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>M05-F01</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t>Internship Group Creation</t>
-        </is>
-      </c>
-      <c r="E4" s="23" t="inlineStr">
-        <is>
-          <t>Internship Group Creation Fails Due to Unselected Classes</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>Verify system displays error and prevents creating internship group when no classes are selected.</t>
-        </is>
-      </c>
-      <c r="G4" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Create New Internship Group interface.</t>
-        </is>
-      </c>
-      <c r="H4" s="23" t="inlineStr">
-        <is>
-          <t>GroupName="Internship Group 2026"; AcademicYear="2026"; Classes=None; StartDate="2026-06-01"</t>
-        </is>
-      </c>
-      <c r="I4" s="23" t="inlineStr">
-        <is>
-          <t>1. Enter Group Name as "Internship Group 2026";
-2. Select Academic Year as "2026";
-3. Do not select any class checkbox;
-4. Select Start Date as "2026-06-01";
-5. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t>System blocks creation.
-Validation error message appears: "At least one class must be selected."
-Group is not created.</t>
-        </is>
-      </c>
-      <c r="K4" s="23" t="inlineStr"/>
-      <c r="L4" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M4" s="21" t="inlineStr"/>
-      <c r="N4" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O4" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F01, Rule 6.1, Validation Rules (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-004</t>
-        </is>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>M05-F01</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="inlineStr">
-        <is>
-          <t>Internship Group Creation</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>Internship Group Creation Fails Due to Missing Start Date</t>
-        </is>
-      </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>Verify system displays error and prevents creating internship group when Start Date is empty.</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Create New Internship Group interface.</t>
-        </is>
-      </c>
-      <c r="H5" s="28" t="inlineStr">
-        <is>
-          <t>GroupName="Internship Group 2026"; AcademicYear="2026"; Classes="PNV26A"; StartDate=""</t>
-        </is>
-      </c>
-      <c r="I5" s="28" t="inlineStr">
-        <is>
-          <t>1. Enter Group Name as "Internship Group 2026";
-2. Select Academic Year as "2026";
-3. Select class "PNV26A";
-4. Leave Start Date blank;
-5. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J5" s="28" t="inlineStr">
-        <is>
-          <t>System blocks creation.
-Validation error message appears: "Start Date is required."
-Group is not created.</t>
-        </is>
-      </c>
-      <c r="K5" s="28" t="inlineStr"/>
-      <c r="L5" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M5" s="26" t="inlineStr"/>
-      <c r="N5" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O5" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F01, Rule 6.1, Validation Rules (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="135" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-005</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>M05-F01</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>Internship Group Creation</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>Internship Group Creation Fails Due to Missing Academic Year</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>Verify system displays error and prevents creating internship group when Academic Year is empty.</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Create New Internship Group interface.</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>GroupName="Internship Group 2026"; AcademicYear=""; Classes="PNV26A"; StartDate="2026-06-01"</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t>1. Enter Group Name as "Internship Group 2026";
-2. Leave Academic Year dropdown unselected/empty;
-3. Select class "PNV26A";
-4. Select Start Date as "2026-06-01";
-5. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
-        <is>
-          <t>System blocks creation.
-Validation error message appears: "Academic Year is required."
-Group is not created.</t>
-        </is>
-      </c>
-      <c r="K6" s="23" t="inlineStr"/>
-      <c r="L6" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M6" s="21" t="inlineStr"/>
-      <c r="N6" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O6" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F01, Rule 6.1, Validation Rules (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="105" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-006</t>
-        </is>
-      </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>M05-F01</t>
-        </is>
-      </c>
-      <c r="D7" s="28" t="inlineStr">
-        <is>
-          <t>Internship Group Creation</t>
-        </is>
-      </c>
-      <c r="E7" s="28" t="inlineStr">
-        <is>
-          <t>Internship Group Creation Fails Due to Class Already Assigned in Same Year</t>
-        </is>
-      </c>
-      <c r="F7" s="28" t="inlineStr">
-        <is>
-          <t>Verify system prevents selecting or saving a class that is already assigned to another active internship group in the same academic year.</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Class "PNV26A" has been assigned to group "Group 1" in academic year 2026.
-Currently on Create New Internship Group interface.</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="inlineStr">
-        <is>
-          <t>GroupName="Group 2"; AcademicYear="2026"; Classes="PNV26A"; StartDate="2026-06-01"</t>
-        </is>
-      </c>
-      <c r="I7" s="28" t="inlineStr">
-        <is>
-          <t>1. Enter Group Name as "Group 2";
-2. Select Academic Year as "2026";
-3. Attempt to select class "PNV26A";
-4. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J7" s="28" t="inlineStr">
-        <is>
-          <t>Class "PNV26A" is either disabled in the dropdown/list or system displays error upon saving: "Class PNV26A is already assigned to another internship group in academic year 2026."
-Creation fails.</t>
-        </is>
-      </c>
-      <c r="K7" s="28" t="inlineStr"/>
-      <c r="L7" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M7" s="26" t="inlineStr"/>
-      <c r="N7" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O7" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F01, Rule 6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-007</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>M05-F01</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>Internship Group Creation</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>Create Internship Group Successfully When Assigning Same Class across Different Academic Years</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>Verify system allows assigning the same class to another internship group if the academic years are different.</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Class "PNV26A" was assigned to an internship group in academic year 2025.</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>GroupName="Internship Group 2026"; AcademicYear="2026"; Classes="PNV26A"; StartDate="2026-06-01"</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>1. Create new group with Academic Year "2026";
-2. Select class "PNV26A";
-3. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>System allows creation successfully without duplicate class error because academic years differ (2025 vs 2026).</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M8" s="21" t="inlineStr"/>
-      <c r="N8" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="O8" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F01, Rule 6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-008</t>
-        </is>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>M05-F02</t>
-        </is>
-      </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>Internship Group Archiving &amp; Reactivation</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>Archive Active Internship Group</t>
-        </is>
-      </c>
-      <c r="F9" s="28" t="inlineStr">
-        <is>
-          <t>Verify functionality for archiving an active internship group.</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Internship group "Internship Group 2025" is in Active status.</t>
-        </is>
-      </c>
-      <c r="H9" s="28" t="inlineStr">
-        <is>
-          <t>GroupName="Internship Group 2025"</t>
-        </is>
-      </c>
-      <c r="I9" s="28" t="inlineStr">
-        <is>
-          <t>1. Navigate to Internship Group list;
-2. Locate group "Internship Group 2025";
-3. Click Action menu and select Archive;
-4. Confirm archiving in confirmation dialog.</t>
-        </is>
-      </c>
-      <c r="J9" s="28" t="inlineStr">
-        <is>
-          <t>Status of "Internship Group 2025" changes from Active to Archived.
-Group is moved to Archived tab or hidden from Active list.</t>
-        </is>
-      </c>
-      <c r="K9" s="28" t="inlineStr"/>
-      <c r="L9" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M9" s="26" t="inlineStr"/>
-      <c r="N9" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O9" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F02, Rule 6.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-009</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>M05-F02</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Internship Group Archiving &amp; Reactivation</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>Reactivate Archived Internship Group</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>Verify functionality for reactivating a previously archived internship group.</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Internship group "Internship Group 2025" is in Archived status.</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>GroupName="Internship Group 2025"</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>1. Navigate to Archived Internship Groups tab;
-2. Locate group "Internship Group 2025";
-3. Click Action menu and select Reactivate;
-4. Confirm reactivation in confirmation dialog.</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>Status of "Internship Group 2025" changes back to Active.
-Group reappears in the Active internship group list.</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="inlineStr"/>
-      <c r="L10" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M10" s="21" t="inlineStr"/>
-      <c r="N10" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F02, Rule 6.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-010</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>M05-F03</t>
-        </is>
-      </c>
-      <c r="D11" s="28" t="inlineStr">
-        <is>
-          <t>Partner Company Management</t>
-        </is>
-      </c>
-      <c r="E11" s="28" t="inlineStr">
-        <is>
-          <t>Add New Partner Company with Valid Name</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>Verify functionality for adding a new partner company with a valid name.</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Company Management interface.
-Company "ABC Technology" does not exist in system.</t>
-        </is>
-      </c>
-      <c r="H11" s="28" t="inlineStr">
-        <is>
-          <t>CompanyName="ABC Technology"</t>
-        </is>
-      </c>
-      <c r="I11" s="28" t="inlineStr">
-        <is>
-          <t>1. Click Add Company button;
-2. Enter Company Name as "ABC Technology";
-3. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J11" s="28" t="inlineStr">
-        <is>
-          <t>Company is added successfully.
-Success notification appears and "ABC Technology" is displayed in company list with status Active.</t>
-        </is>
-      </c>
-      <c r="K11" s="28" t="inlineStr"/>
-      <c r="L11" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M11" s="26" t="inlineStr"/>
-      <c r="N11" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O11" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F03, Rule 6.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="75" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-011</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>M05-F03</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>Partner Company Management</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>Add Company Fails Due to Empty Company Name</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>Verify system displays error and prevents adding company when company name is empty.</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Add Company dialog.</t>
-        </is>
-      </c>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t>CompanyName=""</t>
-        </is>
-      </c>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t>1. Leave Company Name field empty;
-2. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="inlineStr">
-        <is>
-          <t>System blocks action.
-Validation error message appears: "Company Name is required."
-No new company is saved.</t>
-        </is>
-      </c>
-      <c r="K12" s="23" t="inlineStr"/>
-      <c r="L12" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="inlineStr"/>
-      <c r="N12" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O12" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F03, Rule 6.3, Validation Rules (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-012</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>M05-F03</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>Partner Company Management</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>Add Company Fails Due to Duplicate Name (Case Insensitive)</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>Verify system detects duplicate company names regardless of uppercase/lowercase letters.</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Company "ABC Technology" already exists in system.</t>
-        </is>
-      </c>
-      <c r="H13" s="28" t="inlineStr">
-        <is>
-          <t>CompanyName="abc technology"</t>
-        </is>
-      </c>
-      <c r="I13" s="28" t="inlineStr">
-        <is>
-          <t>1. Click Add Company button;
-2. Enter Company Name as "abc technology";
-3. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J13" s="28" t="inlineStr">
-        <is>
-          <t>System blocks action.
-Error message appears: "Company name already exists."
-Duplicate company is not created.</t>
-        </is>
-      </c>
-      <c r="K13" s="28" t="inlineStr"/>
-      <c r="L13" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M13" s="26" t="inlineStr"/>
-      <c r="N13" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O13" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F03, Rule 6.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="75" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-013</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>M05-F03</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>Partner Company Management</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>Add Company Fails Due to Duplicate Name with Leading/Trailing Whitespace</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>Verify system trims leading and trailing spaces before checking for duplicate company names.</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Company "ABC Technology" already exists in system.</t>
-        </is>
-      </c>
-      <c r="H14" s="23" t="inlineStr">
-        <is>
-          <t>CompanyName="  ABC Technology  "</t>
-        </is>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>1. Click Add Company button;
-2. Enter Company Name as "  ABC Technology  ";
-3. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J14" s="23" t="inlineStr">
-        <is>
-          <t>System trims spaces, detects duplicate "ABC Technology", and displays error: "Company name already exists."
-Save is rejected.</t>
-        </is>
-      </c>
-      <c r="K14" s="23" t="inlineStr"/>
-      <c r="L14" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M14" s="21" t="inlineStr"/>
-      <c r="N14" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="O14" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F03, Rule 6.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-014</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>M05-F04</t>
-        </is>
-      </c>
-      <c r="D15" s="28" t="inlineStr">
-        <is>
-          <t>Single Student Internship Assignment</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="inlineStr">
-        <is>
-          <t>Assign Internship to Individual Student</t>
-        </is>
-      </c>
-      <c r="F15" s="28" t="inlineStr">
-        <is>
-          <t>Verify functionality for assigning an internship company to a single student.</t>
-        </is>
-      </c>
-      <c r="G15" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Student List in Internship Group.
-Student "Nguyen Van A" has no assigned company.
-Company "ABC Technology" exists in system.</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="inlineStr">
-        <is>
-          <t>StudentName="Nguyen Van A"; AssignedCompany="ABC Technology"</t>
-        </is>
-      </c>
-      <c r="I15" s="28" t="inlineStr">
-        <is>
-          <t>1. Find student "Nguyen Van A" in list;
-2. Click Company assignment dropdown for this student;
-3. Select company "ABC Technology";
-4. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J15" s="28" t="inlineStr">
-        <is>
-          <t>Assignment saved successfully.
-Student "Nguyen Van A" displays company "ABC Technology" in the table list.</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="inlineStr"/>
-      <c r="L15" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M15" s="26" t="inlineStr"/>
-      <c r="N15" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O15" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F04, Rule 6.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-015</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>M05-F05</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>Batch Student Internship Assignment</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>Batch Assign Internship to Multiple Students</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>Verify functionality for assigning an internship company to multiple selected students simultaneously.</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Student List in Internship Group.
-Students "Nguyen Van A" and "Tran Thi B" have no assigned company.</t>
-        </is>
-      </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>SelectedStudents=["Nguyen Van A", "Tran Thi B"]; AssignedCompany="ABC Technology"</t>
-        </is>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>1. Check selection boxes for "Nguyen Van A" and "Tran Thi B";
-2. Click Batch Assign Company button;
-3. Select company "ABC Technology" in modal dialog;
-4. Click Apply and Save.</t>
-        </is>
-      </c>
-      <c r="J16" s="23" t="inlineStr">
-        <is>
-          <t>Batch assignment saved successfully.
-Both students "Nguyen Van A" and "Tran Thi B" display company "ABC Technology" in the list.</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="inlineStr"/>
-      <c r="L16" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M16" s="21" t="inlineStr"/>
-      <c r="N16" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O16" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F05, Rule 6.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-016</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="inlineStr">
-        <is>
-          <t>M05-F04</t>
-        </is>
-      </c>
-      <c r="D17" s="28" t="inlineStr">
-        <is>
-          <t>Single Student Internship Assignment</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
-        <is>
-          <t>Change Student Assigned Company</t>
-        </is>
-      </c>
-      <c r="F17" s="28" t="inlineStr">
-        <is>
-          <t>Verify functionality for updating the assigned internship company for a student.</t>
-        </is>
-      </c>
-      <c r="G17" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Student "Nguyen Van A" is currently assigned to "ABC Technology".</t>
-        </is>
-      </c>
-      <c r="H17" s="28" t="inlineStr">
-        <is>
-          <t>StudentName="Nguyen Van A"; NewCompany="XYZ Global"</t>
-        </is>
-      </c>
-      <c r="I17" s="28" t="inlineStr">
-        <is>
-          <t>1. Locate student "Nguyen Van A";
-2. Change company dropdown selection from "ABC Technology" to "XYZ Global";
-3. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J17" s="28" t="inlineStr">
-        <is>
-          <t>Assignment updated successfully.
-Student "Nguyen Van A" displays new company "XYZ Global".</t>
-        </is>
-      </c>
-      <c r="K17" s="28" t="inlineStr"/>
-      <c r="L17" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M17" s="26" t="inlineStr"/>
-      <c r="N17" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O17" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F04, Rule 6.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="75" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-017</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>M05-F04</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>Single Student Internship Assignment</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>Unassign Company from Student by Selecting No Company</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>Verify functionality for removing an assigned company from a student by selecting "No Company".</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Student "Nguyen Van A" is currently assigned to "ABC Technology".</t>
-        </is>
-      </c>
-      <c r="H18" s="23" t="inlineStr">
-        <is>
-          <t>StudentName="Nguyen Van A"; AssignedCompany="No Company"</t>
-        </is>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>1. Locate student "Nguyen Van A";
-2. Select "No Company" (or empty option) in company dropdown;
-3. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J18" s="23" t="inlineStr">
-        <is>
-          <t>Company assignment cleared successfully.
-Student "Nguyen Van A" displays "Unassigned" or "No Company" in student list.</t>
-        </is>
-      </c>
-      <c r="K18" s="23" t="inlineStr"/>
-      <c r="L18" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M18" s="21" t="inlineStr"/>
-      <c r="N18" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="O18" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F04, Rule 6.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-018</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>M05-F06</t>
-        </is>
-      </c>
-      <c r="D19" s="28" t="inlineStr">
-        <is>
-          <t>Company Hiding &amp; Deletion Safety</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="inlineStr">
-        <is>
-          <t>Hide Company and Verify Exclusion from New Assignment Options</t>
-        </is>
-      </c>
-      <c r="F19" s="28" t="inlineStr">
-        <is>
-          <t>Verify system hides company from assignment dropdowns when company status is set to Hidden/Inactive.</t>
-        </is>
-      </c>
-      <c r="G19" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Company "Defunct Corp" exists in system.</t>
-        </is>
-      </c>
-      <c r="H19" s="28" t="inlineStr">
-        <is>
-          <t>CompanyName="Defunct Corp"</t>
-        </is>
-      </c>
-      <c r="I19" s="28" t="inlineStr">
-        <is>
-          <t>1. Go to Company Management;
-2. Change status of "Defunct Corp" to Hidden/Inactive;
-3. Go to Student List assignment dropdown.</t>
-        </is>
-      </c>
-      <c r="J19" s="28" t="inlineStr">
-        <is>
-          <t>Company "Defunct Corp" no longer appears in dropdown list for new student assignments.</t>
-        </is>
-      </c>
-      <c r="K19" s="28" t="inlineStr"/>
-      <c r="L19" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M19" s="26" t="inlineStr"/>
-      <c r="N19" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O19" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F06, Rule 6.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-019</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>M05-F06</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>Company Hiding &amp; Deletion Safety</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>Ensure Existing Student Assignment Remains Unaffected When Company Is Hidden</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>Verify hiding a company does not remove or distort historical/existing student assignments associated with that company.</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Student "Tran Thi B" is assigned to company "ABC Technology".</t>
-        </is>
-      </c>
-      <c r="H20" s="23" t="inlineStr">
-        <is>
-          <t>CompanyName="ABC Technology"; StudentName="Tran Thi B"</t>
-        </is>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>1. Change status of company "ABC Technology" to Hidden in Company Management;
-2. View Student List in Internship Group.</t>
-        </is>
-      </c>
-      <c r="J20" s="23" t="inlineStr">
-        <is>
-          <t>Assignment of student "Tran Thi B" still displays "ABC Technology" normally in student list.
-No error notification appears and existing assignment is preserved.</t>
-        </is>
-      </c>
-      <c r="K20" s="23" t="inlineStr"/>
-      <c r="L20" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="inlineStr"/>
-      <c r="N20" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O20" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F06, Rule 6.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="180" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-020</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>M05-F07</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>Feedback Recording by Team</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>Record Internship Feedback Successfully for Student by Training Team</t>
-        </is>
-      </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>Verify functionality for recording internship feedback for a student by Training team.</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Student List in Internship Group.
-Student "Nguyen Van A" has assigned internship.</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="inlineStr">
-        <is>
-          <t>StudentName="Nguyen Van A"; FeedbackTeam="Training"; FeedbackDate="2026-08-15"; FeedbackNotes="Good progress, proactive in assigned tasks."</t>
-        </is>
-      </c>
-      <c r="I21" s="28" t="inlineStr">
-        <is>
-          <t>1. Locate student "Nguyen Van A" in list;
-2. Click Add Feedback button for this student;
-3. Select Feedback Team as "Training";
-4. Enter Feedback Date as "2026-08-15";
-5. Enter Feedback Notes as "Good progress, proactive in assigned tasks.";
-6. Click Save Feedback button.</t>
-        </is>
-      </c>
-      <c r="J21" s="28" t="inlineStr">
-        <is>
-          <t>Feedback saved successfully.
-New feedback entry appears under student name with Team "Training", date, and entered notes.</t>
-        </is>
-      </c>
-      <c r="K21" s="28" t="inlineStr"/>
-      <c r="L21" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M21" s="26" t="inlineStr"/>
-      <c r="N21" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O21" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F07, Rule 6.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="180" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-021</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>M05-F07</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>Feedback Recording by Team</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>Record Internship Feedback Successfully for Student by ERO Team</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>Verify functionality for recording internship feedback for a student by ERO team.</t>
-        </is>
-      </c>
-      <c r="G22" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Student List in Internship Group.
-Student "Nguyen Van A" has assigned internship.</t>
-        </is>
-      </c>
-      <c r="H22" s="23" t="inlineStr">
-        <is>
-          <t>StudentName="Nguyen Van A"; FeedbackTeam="ERO"; FeedbackDate="2026-08-15"; FeedbackNotes="Strong technical skills and professional attitude."</t>
-        </is>
-      </c>
-      <c r="I22" s="23" t="inlineStr">
-        <is>
-          <t>1. Locate student "Nguyen Van A" in list;
-2. Click Add Feedback button for this student;
-3. Select Feedback Team as "ERO";
-4. Enter Feedback Date as "2026-08-15";
-5. Enter Feedback Notes as "Strong technical skills and professional attitude.";
-6. Click Save Feedback button.</t>
-        </is>
-      </c>
-      <c r="J22" s="23" t="inlineStr">
-        <is>
-          <t>Feedback saved successfully.
-New feedback entry appears under student name with Team "ERO", date, and entered notes.</t>
-        </is>
-      </c>
-      <c r="K22" s="23" t="inlineStr"/>
-      <c r="L22" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr"/>
-      <c r="N22" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O22" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F07, Rule 6.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="180" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-022</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>M05-F07</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="inlineStr">
-        <is>
-          <t>Feedback Recording by Team</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="inlineStr">
-        <is>
-          <t>Record Internship Feedback Successfully for Student by Educators Team</t>
-        </is>
-      </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>Verify functionality for recording internship feedback for a student by Educators team.</t>
-        </is>
-      </c>
-      <c r="G23" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Student List in Internship Group.
-Student "Nguyen Van A" has assigned internship.</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="inlineStr">
-        <is>
-          <t>StudentName="Nguyen Van A"; FeedbackTeam="Educators"; FeedbackDate="2026-08-15"; FeedbackNotes="Actively contributes constructive ideas to group."</t>
-        </is>
-      </c>
-      <c r="I23" s="28" t="inlineStr">
-        <is>
-          <t>1. Locate student "Nguyen Van A" in list;
-2. Click Add Feedback button for this student;
-3. Select Feedback Team as "Educators";
-4. Enter Feedback Date as "2026-08-15";
-5. Enter Feedback Notes as "Actively contributes constructive ideas to group.";
-6. Click Save Feedback button.</t>
-        </is>
-      </c>
-      <c r="J23" s="28" t="inlineStr">
-        <is>
-          <t>Feedback saved successfully.
-New feedback entry appears under student name with Team "Educators", date, and entered notes.</t>
-        </is>
-      </c>
-      <c r="K23" s="28" t="inlineStr"/>
-      <c r="L23" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M23" s="26" t="inlineStr"/>
-      <c r="N23" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O23" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F07, Rule 6.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="105" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-023</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>M05-F07</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr">
-        <is>
-          <t>Feedback Recording by Team</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
-        <is>
-          <t>Ignore Blank Feedback Entries Without Saving</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>Verify system ignores and does not save feedback entries when feedback notes field is empty.</t>
-        </is>
-      </c>
-      <c r="G24" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Add Feedback dialog for student.</t>
-        </is>
-      </c>
-      <c r="H24" s="23" t="inlineStr">
-        <is>
-          <t>FeedbackTeam="ERO"; FeedbackDate="2026-08-15"; FeedbackNotes=""</t>
-        </is>
-      </c>
-      <c r="I24" s="23" t="inlineStr">
-        <is>
-          <t>1. Open Add Feedback dialog;
-2. Select Team as "ERO" and select date;
-3. Leave Feedback Notes empty;
-4. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J24" s="23" t="inlineStr">
-        <is>
-          <t>System ignores blank feedback entry without saving new database record.
-No error appears and no empty feedback row is displayed on UI.</t>
-        </is>
-      </c>
-      <c r="K24" s="23" t="inlineStr"/>
-      <c r="L24" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="inlineStr"/>
-      <c r="N24" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="O24" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: Rule 6.8, Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-024</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>M05-F08</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="inlineStr">
-        <is>
-          <t>Same for All Feedback</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>Record Batch Feedback for Multiple Students Simultaneously (Same for All)</t>
-        </is>
-      </c>
-      <c r="F25" s="28" t="inlineStr">
-        <is>
-          <t>Verify batch feedback feature applies identical feedback content to multiple selected students.</t>
-        </is>
-      </c>
-      <c r="G25" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Student List in Internship Group.
-At least 2 students selected (e.g., Nguyen Van A, Tran Thi B).</t>
-        </is>
-      </c>
-      <c r="H25" s="28" t="inlineStr">
-        <is>
-          <t>SelectedStudents=["Nguyen Van A", "Tran Thi B"]; FeedbackTeam="Educators"; FeedbackDate="2026-08-15"; FeedbackNotes="Excellent communication skills."</t>
-        </is>
-      </c>
-      <c r="I25" s="28" t="inlineStr">
-        <is>
-          <t>1. Select checkboxes for students "Nguyen Van A" and "Tran Thi B";
-2. Click Batch Feedback (Same for All) button;
-3. Select Team as "Educators", Feedback Date as "2026-08-15", enter Notes as "Excellent communication skills.";
-4. Click Apply and Save button.</t>
-        </is>
-      </c>
-      <c r="J25" s="28" t="inlineStr">
-        <is>
-          <t>Feedback saved successfully for both students.
-Both "Nguyen Van A" and "Tran Thi B" display Educators feedback entry with content "Excellent communication skills." dated 2026-08-15.</t>
-        </is>
-      </c>
-      <c r="K25" s="28" t="inlineStr"/>
-      <c r="L25" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M25" s="26" t="inlineStr"/>
-      <c r="N25" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O25" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F08, Rule 6.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="135" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-025</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>M05-F09</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
-        <is>
-          <t>Feedback Editing</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>Edit Saved Internship Feedback Content</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>Verify functionality for editing and saving existing feedback content.</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Student "Nguyen Van A" has feedback: Team = "Training", content = "Good progress", date = "2026-08-15".</t>
-        </is>
-      </c>
-      <c r="H26" s="23" t="inlineStr">
-        <is>
-          <t>StudentName="Nguyen Van A"; NewFeedbackNotes="Outstanding progress and excellent teamwork."</t>
-        </is>
-      </c>
-      <c r="I26" s="23" t="inlineStr">
-        <is>
-          <t>1. Locate student "Nguyen Van A" and expand feedback list;
-2. Select feedback entry "Good progress" and click Edit button;
-3. Update feedback notes to "Outstanding progress and excellent teamwork.";
-4. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t>Feedback updated successfully.
-New content overwrites previous notes and displays correctly on UI: "Outstanding progress and excellent teamwork.".</t>
-        </is>
-      </c>
-      <c r="K26" s="23" t="inlineStr"/>
-      <c r="L26" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr"/>
-      <c r="N26" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O26" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F09, Rule 6.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>TC-M05-026</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>M05-F09</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="inlineStr">
-        <is>
-          <t>Feedback Editing</t>
-        </is>
-      </c>
-      <c r="E27" s="28" t="inlineStr">
-        <is>
-          <t>Edit Saved Internship Feedback Team and Date</t>
-        </is>
-      </c>
-      <c r="F27" s="28" t="inlineStr">
-        <is>
-          <t>Verify functionality for editing and saving existing feedback team and date.</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Student "Nguyen Van A" has feedback: Team = "Training", content = "Good progress", date = "2026-08-15".</t>
-        </is>
-      </c>
-      <c r="H27" s="28" t="inlineStr">
-        <is>
-          <t>StudentName="Nguyen Van A"; NewFeedbackTeam="ERO"; NewFeedbackDate="2026-08-20"</t>
-        </is>
-      </c>
-      <c r="I27" s="28" t="inlineStr">
-        <is>
-          <t>1. Locate student "Nguyen Van A" and expand feedback list;
-2. Select feedback entry "Good progress" and click Edit button;
-3. Change Feedback Team to "ERO";
-4. Change Feedback Date to "2026-08-20";
-5. Click Save button.</t>
-        </is>
-      </c>
-      <c r="J27" s="28" t="inlineStr">
-        <is>
-          <t>Feedback updated successfully.
-Feedback details update on UI to display new Team "ERO" and new date "2026-08-20".</t>
-        </is>
-      </c>
-      <c r="K27" s="28" t="inlineStr"/>
-      <c r="L27" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M27" s="26" t="inlineStr"/>
-      <c r="N27" s="25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O27" s="28" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F09, Rule 6.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="135" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>TC-M05-027</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>Module 05 - Internship Management</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>M05-F10</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>Group List Display</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>Expand/Collapse Student List and Display Warning Badges in Internship Group List</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>Verify functionality for expanding/collapsing each internship group and correctly displaying warning badges for unassigned students.</t>
-        </is>
-      </c>
-      <c r="G28" s="23" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Currently on Internship Group List page.
-Group "Internship Group 2026" contains 2 students without assigned company.</t>
-        </is>
-      </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>GroupName="Internship Group 2026"</t>
-        </is>
-      </c>
-      <c r="I28" s="23" t="inlineStr">
-        <is>
-          <t>1. Observe group row for "Internship Group 2026";
-2. Verify warning badge for unassigned students (e.g., "2 Unassigned");
-3. Click Expand arrow icon on group row;
-4. Click Collapse arrow icon on group row.</t>
-        </is>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>Warning badge "2 Unassigned" displays accurately on group row.
-Clicking Expand expands student list cleanly.
-Clicking Collapse hides student list cleanly.</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr"/>
-      <c r="L28" s="30" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M28" s="21" t="inlineStr"/>
-      <c r="N28" s="29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="O28" s="23" t="inlineStr">
-        <is>
-          <t>Related Requirement: M05-F10, UI Standards</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:O28"/>
-  <dataValidations count="2">
-    <dataValidation sqref="L2:L128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
-      <formula1>"Passed,Failed,Not Run"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
